--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="310">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -993,14 +993,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1250,7 +1249,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1415,39 +1414,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1559,9 +1546,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>407160</xdr:colOff>
+      <xdr:colOff>406800</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>263520</xdr:rowOff>
+      <xdr:rowOff>263160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1575,7 +1562,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2194920" cy="2341080"/>
+          <a:ext cx="2194560" cy="2340720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7153,12 +7140,12 @@
   <dimension ref="A1:AE77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="28" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="28" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7362,6538 +7349,6354 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F6</f>
         <v>16.71</v>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G6</f>
         <v>18.381</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H6="","",'RSEA vs Quoted Comparison'!H6)</f>
         <v>16.93275</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I6="","",'RSEA vs Quoted Comparison'!I6)</f>
         <v>18.626025</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D6</f>
         <v>42.99</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E6</f>
         <v>39.0818181818182</v>
       </c>
-      <c r="J6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N6" s="43" t="n">
+      <c r="J6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N6" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O6" s="43" t="n">
+      <c r="O6" s="11" t="n">
         <f aca="false">N6/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P6" s="43" t="n">
+      <c r="P6" s="11" t="n">
         <v>22.05</v>
       </c>
-      <c r="Q6" s="43" t="n">
+      <c r="Q6" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="R6" s="43" t="n">
+      <c r="R6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="S6" s="43" t="n">
+      <c r="S6" s="11" t="n">
         <f aca="false">R6/1.1</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="T6" s="43" t="n">
+      <c r="T6" s="11" t="n">
         <v>31.19</v>
       </c>
-      <c r="U6" s="43" t="n">
+      <c r="U6" s="11" t="n">
         <f aca="false">T6/1.1</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="V6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W6" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X6" s="43" t="n">
+      <c r="V6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X6" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y6" s="43" t="n">
+      <c r="Y6" s="11" t="n">
         <f aca="false">X6/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z6" s="43" t="n">
+      <c r="Z6" s="11" t="n">
         <v>65.63</v>
       </c>
-      <c r="AA6" s="43" t="n">
+      <c r="AA6" s="11" t="n">
         <f aca="false">Z6/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB6" s="43" t="n">
+      <c r="AB6" s="11" t="n">
         <f aca="false">IF(COUNT(I6,K6,M6,O6,Q6,S6,U6,W6,Y6,AA6)=0,"N/A",MIN(I6,K6,M6,O6,Q6,S6,U6,W6,Y6,AA6))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC6" s="45" t="n">
+      <c r="AC6" s="43" t="n">
         <f aca="false">IF(OR(D6="",AB6="",AB6="N/A"),"N/A",D6/AB6-1)</f>
         <v>0.786297376093295</v>
       </c>
-      <c r="AD6" s="45" t="n">
+      <c r="AD6" s="43" t="n">
         <f aca="false">IF(OR(F6="",AB6="",AB6="N/A"),"N/A",F6/AB6-1)</f>
         <v>0.810109329446064</v>
       </c>
-      <c r="AE6" s="42" t="s">
+      <c r="AE6" s="41" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F7</f>
         <v>66.83</v>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G7</f>
         <v>73.513</v>
       </c>
-      <c r="F7" s="43" t="str">
+      <c r="F7" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H7="","",'RSEA vs Quoted Comparison'!H7)</f>
         <v/>
       </c>
-      <c r="G7" s="43" t="str">
+      <c r="G7" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I7="","",'RSEA vs Quoted Comparison'!I7)</f>
         <v/>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D7</f>
         <v>134.99</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E7</f>
         <v>122.718181818182</v>
       </c>
-      <c r="J7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA7" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB7" s="43" t="n">
+      <c r="J7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y7" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="42"/>
+      <c r="AB7" s="11" t="n">
         <f aca="false">IF(COUNT(I7,K7,M7,O7,Q7,S7,U7,W7,Y7,AA7)=0,"N/A",MIN(I7,K7,M7,O7,Q7,S7,U7,W7,Y7,AA7))</f>
         <v>122.718181818182</v>
       </c>
-      <c r="AC7" s="45" t="n">
+      <c r="AC7" s="43" t="n">
         <f aca="false">IF(OR(D7="",AB7="",AB7="N/A"),"N/A",D7/AB7-1)</f>
         <v>-0.455418919919994</v>
       </c>
-      <c r="AD7" s="45" t="str">
+      <c r="AD7" s="43" t="str">
         <f aca="false">IF(OR(F7="",AB7="",AB7="N/A"),"N/A",F7/AB7-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE7" s="42" t="s">
+      <c r="AE7" s="41" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F8</f>
         <v>44.55</v>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G8</f>
         <v>49.005</v>
       </c>
-      <c r="F8" s="43" t="str">
+      <c r="F8" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H8="","",'RSEA vs Quoted Comparison'!H8)</f>
         <v/>
       </c>
-      <c r="G8" s="43" t="str">
+      <c r="G8" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I8="","",'RSEA vs Quoted Comparison'!I8)</f>
         <v/>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D8</f>
         <v>167.99</v>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E8</f>
         <v>152.718181818182</v>
       </c>
-      <c r="J8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA8" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB8" s="43" t="n">
+      <c r="J8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y8" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="42"/>
+      <c r="AB8" s="11" t="n">
         <f aca="false">IF(COUNT(I8,K8,M8,O8,Q8,S8,U8,W8,Y8,AA8)=0,"N/A",MIN(I8,K8,M8,O8,Q8,S8,U8,W8,Y8,AA8))</f>
         <v>152.718181818182</v>
       </c>
-      <c r="AC8" s="45" t="n">
+      <c r="AC8" s="43" t="n">
         <f aca="false">IF(OR(D8="",AB8="",AB8="N/A"),"N/A",D8/AB8-1)</f>
         <v>-0.708286207512352</v>
       </c>
-      <c r="AD8" s="45" t="str">
+      <c r="AD8" s="43" t="str">
         <f aca="false">IF(OR(F8="",AB8="",AB8="N/A"),"N/A",F8/AB8-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE8" s="42" t="s">
+      <c r="AE8" s="41" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F9</f>
         <v>44.55</v>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G9</f>
         <v>49.005</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H9="","",'RSEA vs Quoted Comparison'!H9)</f>
         <v>45.144</v>
       </c>
-      <c r="G9" s="43" t="n">
+      <c r="G9" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I9="","",'RSEA vs Quoted Comparison'!I9)</f>
         <v>49.6584</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D9</f>
         <v>147.99</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E9</f>
         <v>134.536363636364</v>
       </c>
-      <c r="J9" s="43" t="n">
+      <c r="J9" s="11" t="n">
         <f aca="false">K9*1.1</f>
         <v>71.038</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="11" t="n">
         <v>64.58</v>
       </c>
-      <c r="L9" s="43" t="n">
+      <c r="L9" s="11" t="n">
         <v>93.25</v>
       </c>
-      <c r="M9" s="43" t="n">
+      <c r="M9" s="11" t="n">
         <v>84.77</v>
       </c>
-      <c r="N9" s="43" t="n">
+      <c r="N9" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="O9" s="43" t="n">
+      <c r="O9" s="11" t="n">
         <f aca="false">N9/1.1</f>
         <v>90</v>
       </c>
-      <c r="P9" s="43" t="n">
+      <c r="P9" s="11" t="n">
         <v>77.4</v>
       </c>
-      <c r="Q9" s="43" t="n">
+      <c r="Q9" s="11" t="n">
         <v>70.36</v>
       </c>
-      <c r="R9" s="43" t="n">
+      <c r="R9" s="11" t="n">
         <v>92.4</v>
       </c>
-      <c r="S9" s="43" t="n">
+      <c r="S9" s="11" t="n">
         <f aca="false">R9/1.1</f>
         <v>84</v>
       </c>
-      <c r="T9" s="43" t="n">
+      <c r="T9" s="11" t="n">
         <v>106.09</v>
       </c>
-      <c r="U9" s="43" t="n">
+      <c r="U9" s="11" t="n">
         <f aca="false">T9/1.1</f>
         <v>96.4454545454545</v>
       </c>
-      <c r="V9" s="43" t="n">
+      <c r="V9" s="11" t="n">
         <f aca="false">W9*1.1</f>
         <v>69.245</v>
       </c>
-      <c r="W9" s="43" t="n">
+      <c r="W9" s="11" t="n">
         <v>62.95</v>
       </c>
-      <c r="X9" s="43" t="n">
+      <c r="X9" s="11" t="n">
         <v>117.4</v>
       </c>
-      <c r="Y9" s="43" t="n">
+      <c r="Y9" s="11" t="n">
         <f aca="false">X9/1.1</f>
         <v>106.727272727273</v>
       </c>
-      <c r="Z9" s="43" t="n">
+      <c r="Z9" s="11" t="n">
         <v>128.81</v>
       </c>
-      <c r="AA9" s="43" t="n">
+      <c r="AA9" s="11" t="n">
         <f aca="false">Z9/1.1</f>
         <v>117.1</v>
       </c>
-      <c r="AB9" s="43" t="n">
+      <c r="AB9" s="11" t="n">
         <f aca="false">IF(COUNT(I9,K9,M9,O9,Q9,S9,U9,W9,Y9,AA9)=0,"N/A",MIN(I9,K9,M9,O9,Q9,S9,U9,W9,Y9,AA9))</f>
         <v>62.95</v>
       </c>
-      <c r="AC9" s="45" t="n">
+      <c r="AC9" s="43" t="n">
         <f aca="false">IF(OR(D9="",AB9="",AB9="N/A"),"N/A",D9/AB9-1)</f>
         <v>-0.2922954725973</v>
       </c>
-      <c r="AD9" s="45" t="n">
+      <c r="AD9" s="43" t="n">
         <f aca="false">IF(OR(F9="",AB9="",AB9="N/A"),"N/A",F9/AB9-1)</f>
         <v>-0.28285941223193</v>
       </c>
-      <c r="AE9" s="42" t="s">
+      <c r="AE9" s="41" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F10</f>
         <v>69.61</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G10</f>
         <v>76.571</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H10="","",'RSEA vs Quoted Comparison'!H10)</f>
         <v>70.538125</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I10="","",'RSEA vs Quoted Comparison'!I10)</f>
         <v>77.5919375</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H10" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D10</f>
         <v>167.99</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E10</f>
         <v>152.718181818182</v>
       </c>
-      <c r="J10" s="43" t="n">
+      <c r="J10" s="11" t="n">
         <f aca="false">K10*1.1</f>
         <v>84.15</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="11" t="n">
         <v>76.5</v>
       </c>
-      <c r="L10" s="43" t="n">
+      <c r="L10" s="11" t="n">
         <v>117.3</v>
       </c>
-      <c r="M10" s="43" t="n">
+      <c r="M10" s="11" t="n">
         <v>106.64</v>
       </c>
-      <c r="N10" s="43" t="n">
+      <c r="N10" s="11" t="n">
         <v>124.95</v>
       </c>
-      <c r="O10" s="43" t="n">
+      <c r="O10" s="11" t="n">
         <f aca="false">N10/1.1</f>
         <v>113.590909090909</v>
       </c>
-      <c r="P10" s="43" t="n">
+      <c r="P10" s="11" t="n">
         <v>95.4</v>
       </c>
-      <c r="Q10" s="43" t="n">
+      <c r="Q10" s="11" t="n">
         <v>86.73</v>
       </c>
-      <c r="R10" s="43" t="n">
+      <c r="R10" s="11" t="n">
         <v>118.8</v>
       </c>
-      <c r="S10" s="43" t="n">
+      <c r="S10" s="11" t="n">
         <f aca="false">R10/1.1</f>
         <v>108</v>
       </c>
-      <c r="T10" s="43" t="n">
+      <c r="T10" s="11" t="n">
         <v>98.18</v>
       </c>
-      <c r="U10" s="43" t="n">
+      <c r="U10" s="11" t="n">
         <f aca="false">T10/1.1</f>
         <v>89.2545454545455</v>
       </c>
-      <c r="V10" s="43" t="n">
+      <c r="V10" s="11" t="n">
         <f aca="false">W10*1.1</f>
         <v>81.4</v>
       </c>
-      <c r="W10" s="43" t="n">
+      <c r="W10" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="X10" s="43" t="n">
+      <c r="X10" s="11" t="n">
         <v>128.32</v>
       </c>
-      <c r="Y10" s="43" t="n">
+      <c r="Y10" s="11" t="n">
         <f aca="false">X10/1.1</f>
         <v>116.654545454545</v>
       </c>
-      <c r="Z10" s="43" t="n">
+      <c r="Z10" s="11" t="n">
         <v>220.92</v>
       </c>
-      <c r="AA10" s="43" t="n">
+      <c r="AA10" s="11" t="n">
         <f aca="false">Z10/1.1</f>
         <v>200.836363636364</v>
       </c>
-      <c r="AB10" s="43" t="n">
+      <c r="AB10" s="11" t="n">
         <f aca="false">IF(COUNT(I10,K10,M10,O10,Q10,S10,U10,W10,Y10,AA10)=0,"N/A",MIN(I10,K10,M10,O10,Q10,S10,U10,W10,Y10,AA10))</f>
         <v>74</v>
       </c>
-      <c r="AC10" s="45" t="n">
+      <c r="AC10" s="43" t="n">
         <f aca="false">IF(OR(D10="",AB10="",AB10="N/A"),"N/A",D10/AB10-1)</f>
         <v>-0.0593243243243243</v>
       </c>
-      <c r="AD10" s="45" t="n">
+      <c r="AD10" s="43" t="n">
         <f aca="false">IF(OR(F10="",AB10="",AB10="N/A"),"N/A",F10/AB10-1)</f>
         <v>-0.0467820945945947</v>
       </c>
-      <c r="AE10" s="42" t="s">
+      <c r="AE10" s="41" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F11</f>
         <v>33.41</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G11</f>
         <v>36.751</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H11="","",'RSEA vs Quoted Comparison'!H11)</f>
         <v>33.8555</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I11="","",'RSEA vs Quoted Comparison'!I11)</f>
         <v>37.24105</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D11</f>
         <v>142.99</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E11</f>
         <v>129.990909090909</v>
       </c>
-      <c r="J11" s="43" t="n">
+      <c r="J11" s="11" t="n">
         <f aca="false">K11*1.1</f>
         <v>44.209</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="11" t="n">
         <v>40.19</v>
       </c>
-      <c r="L11" s="43" t="n">
+      <c r="L11" s="11" t="n">
         <v>63.11</v>
       </c>
-      <c r="M11" s="43" t="n">
+      <c r="M11" s="11" t="n">
         <v>57.37</v>
       </c>
-      <c r="N11" s="43" t="n">
+      <c r="N11" s="11" t="n">
         <v>90.3</v>
       </c>
-      <c r="O11" s="43" t="n">
+      <c r="O11" s="11" t="n">
         <f aca="false">N11/1.1</f>
         <v>82.0909090909091</v>
       </c>
-      <c r="P11" s="43" t="n">
+      <c r="P11" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q11" s="43" t="n">
+      <c r="Q11" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R11" s="43" t="n">
+      <c r="R11" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S11" s="43" t="n">
+      <c r="S11" s="11" t="n">
         <f aca="false">R11/1.1</f>
         <v>68</v>
       </c>
-      <c r="T11" s="43" t="n">
+      <c r="T11" s="11" t="n">
         <v>78.64</v>
       </c>
-      <c r="U11" s="43" t="n">
+      <c r="U11" s="11" t="n">
         <f aca="false">T11/1.1</f>
         <v>71.4909090909091</v>
       </c>
-      <c r="V11" s="43" t="n">
+      <c r="V11" s="11" t="n">
         <f aca="false">W11*1.1</f>
         <v>63.8</v>
       </c>
-      <c r="W11" s="43" t="n">
+      <c r="W11" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="X11" s="43" t="n">
+      <c r="X11" s="11" t="n">
         <v>80.22</v>
       </c>
-      <c r="Y11" s="43" t="n">
+      <c r="Y11" s="11" t="n">
         <f aca="false">X11/1.1</f>
         <v>72.9272727272727</v>
       </c>
-      <c r="Z11" s="43" t="n">
+      <c r="Z11" s="11" t="n">
         <v>173.98</v>
       </c>
-      <c r="AA11" s="43" t="n">
+      <c r="AA11" s="11" t="n">
         <f aca="false">Z11/1.1</f>
         <v>158.163636363636</v>
       </c>
-      <c r="AB11" s="43" t="n">
+      <c r="AB11" s="11" t="n">
         <f aca="false">IF(COUNT(I11,K11,M11,O11,Q11,S11,U11,W11,Y11,AA11)=0,"N/A",MIN(I11,K11,M11,O11,Q11,S11,U11,W11,Y11,AA11))</f>
         <v>40.19</v>
       </c>
-      <c r="AC11" s="45" t="n">
+      <c r="AC11" s="43" t="n">
         <f aca="false">IF(OR(D11="",AB11="",AB11="N/A"),"N/A",D11/AB11-1)</f>
         <v>-0.168698681263996</v>
       </c>
-      <c r="AD11" s="45" t="n">
+      <c r="AD11" s="43" t="n">
         <f aca="false">IF(OR(F11="",AB11="",AB11="N/A"),"N/A",F11/AB11-1)</f>
         <v>-0.157613834287136</v>
       </c>
-      <c r="AE11" s="42" t="s">
+      <c r="AE11" s="41" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F12</f>
         <v>44.55</v>
       </c>
-      <c r="E12" s="43" t="n">
+      <c r="E12" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G12</f>
         <v>49.005</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H12="","",'RSEA vs Quoted Comparison'!H12)</f>
         <v>45.144</v>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I12="","",'RSEA vs Quoted Comparison'!I12)</f>
         <v>49.6584</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D12</f>
         <v>157.99</v>
       </c>
-      <c r="I12" s="43" t="n">
+      <c r="I12" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E12</f>
         <v>143.627272727273</v>
       </c>
-      <c r="J12" s="43" t="n">
+      <c r="J12" s="11" t="n">
         <f aca="false">K12*1.1</f>
         <v>88.781</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="11" t="n">
         <v>80.71</v>
       </c>
-      <c r="L12" s="43" t="n">
+      <c r="L12" s="11" t="n">
         <v>95.35</v>
       </c>
-      <c r="M12" s="43" t="n">
+      <c r="M12" s="11" t="n">
         <v>86.68</v>
       </c>
-      <c r="N12" s="43" t="n">
+      <c r="N12" s="11" t="n">
         <v>105.6</v>
       </c>
-      <c r="O12" s="43" t="n">
+      <c r="O12" s="11" t="n">
         <f aca="false">N12/1.1</f>
         <v>96</v>
       </c>
-      <c r="P12" s="43" t="n">
+      <c r="P12" s="11" t="n">
         <v>77.4</v>
       </c>
-      <c r="Q12" s="43" t="n">
+      <c r="Q12" s="11" t="n">
         <v>70.36</v>
       </c>
-      <c r="R12" s="43" t="n">
+      <c r="R12" s="11" t="n">
         <v>107.8</v>
       </c>
-      <c r="S12" s="43" t="n">
+      <c r="S12" s="11" t="n">
         <f aca="false">R12/1.1</f>
         <v>98</v>
       </c>
-      <c r="T12" s="43" t="n">
+      <c r="T12" s="11" t="n">
         <v>94.5</v>
       </c>
-      <c r="U12" s="43" t="n">
+      <c r="U12" s="11" t="n">
         <f aca="false">T12/1.1</f>
         <v>85.9090909090909</v>
       </c>
-      <c r="V12" s="43" t="n">
+      <c r="V12" s="11" t="n">
         <f aca="false">W12*1.1</f>
         <v>97.35</v>
       </c>
-      <c r="W12" s="43" t="n">
+      <c r="W12" s="11" t="n">
         <v>88.5</v>
       </c>
-      <c r="X12" s="43" t="n">
+      <c r="X12" s="11" t="n">
         <v>127.75</v>
       </c>
-      <c r="Y12" s="43" t="n">
+      <c r="Y12" s="11" t="n">
         <f aca="false">X12/1.1</f>
         <v>116.136363636364</v>
       </c>
-      <c r="Z12" s="43" t="n">
+      <c r="Z12" s="11" t="n">
         <v>179.74</v>
       </c>
-      <c r="AA12" s="43" t="n">
+      <c r="AA12" s="11" t="n">
         <f aca="false">Z12/1.1</f>
         <v>163.4</v>
       </c>
-      <c r="AB12" s="43" t="n">
+      <c r="AB12" s="11" t="n">
         <f aca="false">IF(COUNT(I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12)=0,"N/A",MIN(I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12))</f>
         <v>70.36</v>
       </c>
-      <c r="AC12" s="45" t="n">
+      <c r="AC12" s="43" t="n">
         <f aca="false">IF(OR(D12="",AB12="",AB12="N/A"),"N/A",D12/AB12-1)</f>
         <v>-0.366827743035816</v>
       </c>
-      <c r="AD12" s="45" t="n">
+      <c r="AD12" s="43" t="n">
         <f aca="false">IF(OR(F12="",AB12="",AB12="N/A"),"N/A",F12/AB12-1)</f>
         <v>-0.358385446276293</v>
       </c>
-      <c r="AE12" s="42" t="s">
+      <c r="AE12" s="41" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F13</f>
         <v>33.41</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E13" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G13</f>
         <v>36.751</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H13="","",'RSEA vs Quoted Comparison'!H13)</f>
         <v>33.8555</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I13="","",'RSEA vs Quoted Comparison'!I13)</f>
         <v>37.24105</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D13</f>
         <v>142.99</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E13</f>
         <v>129.990909090909</v>
       </c>
-      <c r="J13" s="43" t="n">
+      <c r="J13" s="11" t="n">
         <f aca="false">K13*1.1</f>
         <v>109.153</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L13" s="43" t="n">
+      <c r="L13" s="11" t="n">
         <v>61.59</v>
       </c>
-      <c r="M13" s="43" t="n">
+      <c r="M13" s="11" t="n">
         <v>55.99</v>
       </c>
-      <c r="N13" s="43" t="n">
+      <c r="N13" s="11" t="n">
         <v>36.5</v>
       </c>
-      <c r="O13" s="43" t="n">
+      <c r="O13" s="11" t="n">
         <f aca="false">N13/1.1</f>
         <v>33.1818181818182</v>
       </c>
-      <c r="P13" s="43" t="n">
+      <c r="P13" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q13" s="43" t="n">
+      <c r="Q13" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R13" s="43" t="n">
+      <c r="R13" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S13" s="43" t="n">
+      <c r="S13" s="11" t="n">
         <f aca="false">R13/1.1</f>
         <v>68</v>
       </c>
-      <c r="T13" s="43" t="n">
+      <c r="T13" s="11" t="n">
         <v>31.19</v>
       </c>
-      <c r="U13" s="43" t="n">
+      <c r="U13" s="11" t="n">
         <f aca="false">T13/1.1</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="V13" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W13" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X13" s="43" t="n">
+      <c r="V13" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W13" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X13" s="11" t="n">
         <v>110.1</v>
       </c>
-      <c r="Y13" s="43" t="n">
+      <c r="Y13" s="11" t="n">
         <f aca="false">X13/1.1</f>
         <v>100.090909090909</v>
       </c>
-      <c r="Z13" s="43" t="n">
+      <c r="Z13" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="AA13" s="43" t="n">
+      <c r="AA13" s="11" t="n">
         <f aca="false">Z13/1.1</f>
         <v>40</v>
       </c>
-      <c r="AB13" s="43" t="n">
+      <c r="AB13" s="11" t="n">
         <f aca="false">IF(COUNT(I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13)=0,"N/A",MIN(I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13))</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="AC13" s="45" t="n">
+      <c r="AC13" s="43" t="n">
         <f aca="false">IF(OR(D13="",AB13="",AB13="N/A"),"N/A",D13/AB13-1)</f>
         <v>0.1782943251042</v>
       </c>
-      <c r="AD13" s="45" t="n">
+      <c r="AD13" s="43" t="n">
         <f aca="false">IF(OR(F13="",AB13="",AB13="N/A"),"N/A",F13/AB13-1)</f>
         <v>0.194006091696056</v>
       </c>
-      <c r="AE13" s="42" t="s">
+      <c r="AE13" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F14</f>
         <v>25.06</v>
       </c>
-      <c r="E14" s="43" t="n">
+      <c r="E14" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G14</f>
         <v>27.566</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H14="","",'RSEA vs Quoted Comparison'!H14)</f>
         <v>25.394125</v>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I14="","",'RSEA vs Quoted Comparison'!I14)</f>
         <v>27.9335375</v>
       </c>
-      <c r="H14" s="43" t="n">
+      <c r="H14" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D14</f>
         <v>112.99</v>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E14</f>
         <v>102.718181818182</v>
       </c>
-      <c r="J14" s="43" t="n">
+      <c r="J14" s="11" t="n">
         <f aca="false">K14*1.1</f>
         <v>77.968</v>
       </c>
-      <c r="K14" s="43" t="n">
+      <c r="K14" s="11" t="n">
         <v>70.88</v>
       </c>
-      <c r="L14" s="43" t="n">
+      <c r="L14" s="11" t="n">
         <v>61.29</v>
       </c>
-      <c r="M14" s="43" t="n">
+      <c r="M14" s="11" t="n">
         <v>55.72</v>
       </c>
-      <c r="N14" s="43" t="n">
+      <c r="N14" s="11" t="n">
         <v>49.5</v>
       </c>
-      <c r="O14" s="43" t="n">
+      <c r="O14" s="11" t="n">
         <f aca="false">N14/1.1</f>
         <v>45</v>
       </c>
-      <c r="P14" s="43" t="n">
+      <c r="P14" s="11" t="n">
         <v>47.4</v>
       </c>
-      <c r="Q14" s="43" t="n">
+      <c r="Q14" s="11" t="n">
         <v>43.09</v>
       </c>
-      <c r="R14" s="43" t="n">
+      <c r="R14" s="11" t="n">
         <v>61.6</v>
       </c>
-      <c r="S14" s="43" t="n">
+      <c r="S14" s="11" t="n">
         <f aca="false">R14/1.1</f>
         <v>56</v>
       </c>
-      <c r="T14" s="43" t="n">
+      <c r="T14" s="11" t="n">
         <v>76.56</v>
       </c>
-      <c r="U14" s="43" t="n">
+      <c r="U14" s="11" t="n">
         <f aca="false">T14/1.1</f>
         <v>69.6</v>
       </c>
-      <c r="V14" s="43" t="n">
+      <c r="V14" s="11" t="n">
         <f aca="false">W14*1.1</f>
         <v>69.245</v>
       </c>
-      <c r="W14" s="43" t="n">
+      <c r="W14" s="11" t="n">
         <v>62.95</v>
       </c>
-      <c r="X14" s="43" t="n">
+      <c r="X14" s="11" t="n">
         <v>100.71</v>
       </c>
-      <c r="Y14" s="43" t="n">
+      <c r="Y14" s="11" t="n">
         <f aca="false">X14/1.1</f>
         <v>91.5545454545455</v>
       </c>
-      <c r="Z14" s="43" t="n">
+      <c r="Z14" s="11" t="n">
         <v>159.24</v>
       </c>
-      <c r="AA14" s="43" t="n">
+      <c r="AA14" s="11" t="n">
         <f aca="false">Z14/1.1</f>
         <v>144.763636363636</v>
       </c>
-      <c r="AB14" s="43" t="n">
+      <c r="AB14" s="11" t="n">
         <f aca="false">IF(COUNT(I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14)=0,"N/A",MIN(I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14))</f>
         <v>43.09</v>
       </c>
-      <c r="AC14" s="45" t="n">
+      <c r="AC14" s="43" t="n">
         <f aca="false">IF(OR(D14="",AB14="",AB14="N/A"),"N/A",D14/AB14-1)</f>
         <v>-0.418426549083314</v>
       </c>
-      <c r="AD14" s="45" t="n">
+      <c r="AD14" s="43" t="n">
         <f aca="false">IF(OR(F14="",AB14="",AB14="N/A"),"N/A",F14/AB14-1)</f>
         <v>-0.410672429798097</v>
       </c>
-      <c r="AE14" s="42" t="s">
+      <c r="AE14" s="41" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F15</f>
         <v>8.35</v>
       </c>
-      <c r="E15" s="43" t="n">
+      <c r="E15" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G15</f>
         <v>9.185</v>
       </c>
-      <c r="F15" s="43" t="n">
+      <c r="F15" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H15="","",'RSEA vs Quoted Comparison'!H15)</f>
         <v>8.461375</v>
       </c>
-      <c r="G15" s="43" t="n">
+      <c r="G15" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I15="","",'RSEA vs Quoted Comparison'!I15)</f>
         <v>9.3075125</v>
       </c>
-      <c r="H15" s="43" t="n">
+      <c r="H15" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D15</f>
         <v>32.99</v>
       </c>
-      <c r="I15" s="43" t="n">
+      <c r="I15" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E15</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA15" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB15" s="43" t="n">
+      <c r="J15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y15" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="11" t="n">
         <f aca="false">IF(COUNT(I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15)=0,"N/A",MIN(I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC15" s="45" t="n">
+      <c r="AC15" s="43" t="n">
         <f aca="false">IF(OR(D15="",AB15="",AB15="N/A"),"N/A",D15/AB15-1)</f>
         <v>-0.721582297665959</v>
       </c>
-      <c r="AD15" s="45" t="n">
+      <c r="AD15" s="43" t="n">
         <f aca="false">IF(OR(F15="",AB15="",AB15="N/A"),"N/A",F15/AB15-1)</f>
         <v>-0.717868672324947</v>
       </c>
-      <c r="AE15" s="42" t="s">
+      <c r="AE15" s="41" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F16</f>
         <v>15.59</v>
       </c>
-      <c r="E16" s="43" t="n">
+      <c r="E16" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G16</f>
         <v>17.149</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F16" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H16="","",'RSEA vs Quoted Comparison'!H16)</f>
         <v>15.81275</v>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G16" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I16="","",'RSEA vs Quoted Comparison'!I16)</f>
         <v>17.394025</v>
       </c>
-      <c r="H16" s="43" t="n">
+      <c r="H16" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D16</f>
         <v>44.99</v>
       </c>
-      <c r="I16" s="43" t="n">
+      <c r="I16" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E16</f>
         <v>40.9</v>
       </c>
-      <c r="J16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA16" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB16" s="43" t="n">
+      <c r="J16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y16" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z16" s="42"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="11" t="n">
         <f aca="false">IF(COUNT(I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16)=0,"N/A",MIN(I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16))</f>
         <v>40.9</v>
       </c>
-      <c r="AC16" s="45" t="n">
+      <c r="AC16" s="43" t="n">
         <f aca="false">IF(OR(D16="",AB16="",AB16="N/A"),"N/A",D16/AB16-1)</f>
         <v>-0.618826405867971</v>
       </c>
-      <c r="AD16" s="45" t="n">
+      <c r="AD16" s="43" t="n">
         <f aca="false">IF(OR(F16="",AB16="",AB16="N/A"),"N/A",F16/AB16-1)</f>
         <v>-0.613380195599022</v>
       </c>
-      <c r="AE16" s="42" t="s">
+      <c r="AE16" s="41" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F17</f>
         <v>8.35</v>
       </c>
-      <c r="E17" s="43" t="n">
+      <c r="E17" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G17</f>
         <v>9.185</v>
       </c>
-      <c r="F17" s="43" t="n">
+      <c r="F17" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H17="","",'RSEA vs Quoted Comparison'!H17)</f>
         <v>8.461375</v>
       </c>
-      <c r="G17" s="43" t="n">
+      <c r="G17" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I17="","",'RSEA vs Quoted Comparison'!I17)</f>
         <v>9.3075125</v>
       </c>
-      <c r="H17" s="43" t="n">
+      <c r="H17" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D17</f>
         <v>32.99</v>
       </c>
-      <c r="I17" s="43" t="n">
+      <c r="I17" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E17</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA17" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB17" s="43" t="n">
+      <c r="J17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="11" t="n">
         <f aca="false">IF(COUNT(I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17)=0,"N/A",MIN(I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC17" s="45" t="n">
+      <c r="AC17" s="43" t="n">
         <f aca="false">IF(OR(D17="",AB17="",AB17="N/A"),"N/A",D17/AB17-1)</f>
         <v>-0.721582297665959</v>
       </c>
-      <c r="AD17" s="45" t="n">
+      <c r="AD17" s="43" t="n">
         <f aca="false">IF(OR(F17="",AB17="",AB17="N/A"),"N/A",F17/AB17-1)</f>
         <v>-0.717868672324947</v>
       </c>
-      <c r="AE17" s="42" t="s">
+      <c r="AE17" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F18</f>
         <v>29.7</v>
       </c>
-      <c r="E18" s="43" t="n">
+      <c r="E18" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G18</f>
         <v>32.67</v>
       </c>
-      <c r="F18" s="43" t="n">
+      <c r="F18" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H18="","",'RSEA vs Quoted Comparison'!H18)</f>
         <v>30.1455</v>
       </c>
-      <c r="G18" s="43" t="n">
+      <c r="G18" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I18="","",'RSEA vs Quoted Comparison'!I18)</f>
         <v>33.16005</v>
       </c>
-      <c r="H18" s="43" t="n">
+      <c r="H18" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D18</f>
         <v>69.99</v>
       </c>
-      <c r="I18" s="43" t="n">
+      <c r="I18" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E18</f>
         <v>63.6272727272727</v>
       </c>
-      <c r="J18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P18" s="43" t="n">
+      <c r="J18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P18" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q18" s="43" t="n">
+      <c r="Q18" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R18" s="43" t="n">
+      <c r="R18" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S18" s="43" t="n">
+      <c r="S18" s="11" t="n">
         <f aca="false">R18/1.1</f>
         <v>68</v>
       </c>
-      <c r="T18" s="43" t="n">
+      <c r="T18" s="11" t="n">
         <v>41.13</v>
       </c>
-      <c r="U18" s="43" t="n">
+      <c r="U18" s="11" t="n">
         <f aca="false">T18/1.1</f>
         <v>37.3909090909091</v>
       </c>
-      <c r="V18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X18" s="43" t="n">
+      <c r="V18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W18" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X18" s="11" t="n">
         <v>110.1</v>
       </c>
-      <c r="Y18" s="43" t="n">
+      <c r="Y18" s="11" t="n">
         <f aca="false">X18/1.1</f>
         <v>100.090909090909</v>
       </c>
-      <c r="Z18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB18" s="43" t="n">
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="11" t="n">
         <f aca="false">IF(COUNT(I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18)=0,"N/A",MIN(I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18))</f>
         <v>37.3909090909091</v>
       </c>
-      <c r="AC18" s="45" t="n">
+      <c r="AC18" s="43" t="n">
         <f aca="false">IF(OR(D18="",AB18="",AB18="N/A"),"N/A",D18/AB18-1)</f>
         <v>-0.205689277899344</v>
       </c>
-      <c r="AD18" s="45" t="n">
+      <c r="AD18" s="43" t="n">
         <f aca="false">IF(OR(F18="",AB18="",AB18="N/A"),"N/A",F18/AB18-1)</f>
         <v>-0.193774617067834</v>
       </c>
-      <c r="AE18" s="42" t="s">
+      <c r="AE18" s="41" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F19</f>
         <v>29.7</v>
       </c>
-      <c r="E19" s="43" t="n">
+      <c r="E19" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G19</f>
         <v>32.67</v>
       </c>
-      <c r="F19" s="43" t="n">
+      <c r="F19" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H19="","",'RSEA vs Quoted Comparison'!H19)</f>
         <v>30.1455</v>
       </c>
-      <c r="G19" s="43" t="n">
+      <c r="G19" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I19="","",'RSEA vs Quoted Comparison'!I19)</f>
         <v>33.16005</v>
       </c>
-      <c r="H19" s="43" t="n">
+      <c r="H19" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D19</f>
         <v>84.99</v>
       </c>
-      <c r="I19" s="43" t="n">
+      <c r="I19" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E19</f>
         <v>77.2636363636364</v>
       </c>
-      <c r="J19" s="43" t="n">
+      <c r="J19" s="11" t="n">
         <f aca="false">K19*1.1</f>
         <v>109.153</v>
       </c>
-      <c r="K19" s="43" t="n">
+      <c r="K19" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N19" s="43" t="n">
+      <c r="L19" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M19" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N19" s="11" t="n">
         <v>36.5</v>
       </c>
-      <c r="O19" s="43" t="n">
+      <c r="O19" s="11" t="n">
         <f aca="false">N19/1.1</f>
         <v>33.1818181818182</v>
       </c>
-      <c r="P19" s="43" t="n">
+      <c r="P19" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q19" s="43" t="n">
+      <c r="Q19" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R19" s="43" t="n">
+      <c r="R19" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S19" s="43" t="n">
+      <c r="S19" s="11" t="n">
         <f aca="false">R19/1.1</f>
         <v>68</v>
       </c>
-      <c r="T19" s="43" t="n">
+      <c r="T19" s="11" t="n">
         <v>31.19</v>
       </c>
-      <c r="U19" s="43" t="n">
+      <c r="U19" s="11" t="n">
         <f aca="false">T19/1.1</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="V19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X19" s="43" t="n">
+      <c r="V19" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W19" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X19" s="11" t="n">
         <v>110.1</v>
       </c>
-      <c r="Y19" s="43" t="n">
+      <c r="Y19" s="11" t="n">
         <f aca="false">X19/1.1</f>
         <v>100.090909090909</v>
       </c>
-      <c r="Z19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA19" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB19" s="43" t="n">
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="11" t="n">
         <f aca="false">IF(COUNT(I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19)=0,"N/A",MIN(I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19))</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="AC19" s="45" t="n">
+      <c r="AC19" s="43" t="n">
         <f aca="false">IF(OR(D19="",AB19="",AB19="N/A"),"N/A",D19/AB19-1)</f>
         <v>0.0474511061237577</v>
       </c>
-      <c r="AD19" s="45" t="n">
+      <c r="AD19" s="43" t="n">
         <f aca="false">IF(OR(F19="",AB19="",AB19="N/A"),"N/A",F19/AB19-1)</f>
         <v>0.0631628727156139</v>
       </c>
-      <c r="AE19" s="42" t="s">
+      <c r="AE19" s="41" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F20</f>
         <v>16.71</v>
       </c>
-      <c r="E20" s="43" t="n">
+      <c r="E20" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G20</f>
         <v>18.381</v>
       </c>
-      <c r="F20" s="43" t="n">
+      <c r="F20" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H20="","",'RSEA vs Quoted Comparison'!H20)</f>
         <v>16.93275</v>
       </c>
-      <c r="G20" s="43" t="n">
+      <c r="G20" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I20="","",'RSEA vs Quoted Comparison'!I20)</f>
         <v>18.626025</v>
       </c>
-      <c r="H20" s="43" t="n">
+      <c r="H20" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D20</f>
         <v>44.99</v>
       </c>
-      <c r="I20" s="43" t="n">
+      <c r="I20" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E20</f>
         <v>40.9</v>
       </c>
-      <c r="J20" s="43" t="n">
+      <c r="J20" s="11" t="n">
         <f aca="false">K20*1.1</f>
         <v>26.653</v>
       </c>
-      <c r="K20" s="43" t="n">
+      <c r="K20" s="11" t="n">
         <v>24.23</v>
       </c>
-      <c r="L20" s="43" t="n">
+      <c r="L20" s="11" t="n">
         <v>29.61</v>
       </c>
-      <c r="M20" s="43" t="n">
+      <c r="M20" s="11" t="n">
         <v>26.92</v>
       </c>
-      <c r="N20" s="43" t="n">
+      <c r="N20" s="11" t="n">
         <v>35.7</v>
       </c>
-      <c r="O20" s="43" t="n">
+      <c r="O20" s="11" t="n">
         <f aca="false">N20/1.1</f>
         <v>32.4545454545455</v>
       </c>
-      <c r="P20" s="43" t="n">
+      <c r="P20" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="Q20" s="43" t="n">
+      <c r="Q20" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="R20" s="43" t="n">
+      <c r="R20" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="S20" s="43" t="n">
+      <c r="S20" s="11" t="n">
         <f aca="false">R20/1.1</f>
         <v>25</v>
       </c>
-      <c r="T20" s="43" t="n">
+      <c r="T20" s="11" t="n">
         <v>25.64</v>
       </c>
-      <c r="U20" s="43" t="n">
+      <c r="U20" s="11" t="n">
         <f aca="false">T20/1.1</f>
         <v>23.3090909090909</v>
       </c>
-      <c r="V20" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W20" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X20" s="43" t="n">
+      <c r="V20" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W20" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X20" s="11" t="n">
         <v>26.77</v>
       </c>
-      <c r="Y20" s="43" t="n">
+      <c r="Y20" s="11" t="n">
         <f aca="false">X20/1.1</f>
         <v>24.3363636363636</v>
       </c>
-      <c r="Z20" s="43" t="n">
+      <c r="Z20" s="11" t="n">
         <v>49.78</v>
       </c>
-      <c r="AA20" s="43" t="n">
+      <c r="AA20" s="11" t="n">
         <f aca="false">Z20/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB20" s="43" t="n">
+      <c r="AB20" s="11" t="n">
         <f aca="false">IF(COUNT(I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20)=0,"N/A",MIN(I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20))</f>
         <v>23.3090909090909</v>
       </c>
-      <c r="AC20" s="45" t="n">
+      <c r="AC20" s="43" t="n">
         <f aca="false">IF(OR(D20="",AB20="",AB20="N/A"),"N/A",D20/AB20-1)</f>
         <v>-0.28311232449298</v>
       </c>
-      <c r="AD20" s="45" t="n">
+      <c r="AD20" s="43" t="n">
         <f aca="false">IF(OR(F20="",AB20="",AB20="N/A"),"N/A",F20/AB20-1)</f>
         <v>-0.27355596723869</v>
       </c>
-      <c r="AE20" s="42" t="s">
+      <c r="AE20" s="41" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F21</f>
         <v>33.41</v>
       </c>
-      <c r="E21" s="43" t="n">
+      <c r="E21" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G21</f>
         <v>36.751</v>
       </c>
-      <c r="F21" s="43" t="n">
+      <c r="F21" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H21="","",'RSEA vs Quoted Comparison'!H21)</f>
         <v>33.8555</v>
       </c>
-      <c r="G21" s="43" t="n">
+      <c r="G21" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I21="","",'RSEA vs Quoted Comparison'!I21)</f>
         <v>37.24105</v>
       </c>
-      <c r="H21" s="43" t="n">
+      <c r="H21" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D21</f>
         <v>64.99</v>
       </c>
-      <c r="I21" s="43" t="n">
+      <c r="I21" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E21</f>
         <v>59.0818181818182</v>
       </c>
-      <c r="J21" s="43" t="n">
+      <c r="J21" s="11" t="n">
         <f aca="false">K21*1.1</f>
         <v>26.653</v>
       </c>
-      <c r="K21" s="43" t="n">
+      <c r="K21" s="11" t="n">
         <v>24.23</v>
       </c>
-      <c r="L21" s="43" t="n">
+      <c r="L21" s="11" t="n">
         <v>31.89</v>
       </c>
-      <c r="M21" s="43" t="n">
+      <c r="M21" s="11" t="n">
         <v>28.99</v>
       </c>
-      <c r="N21" s="43" t="n">
+      <c r="N21" s="11" t="n">
         <v>53.4</v>
       </c>
-      <c r="O21" s="43" t="n">
+      <c r="O21" s="11" t="n">
         <f aca="false">N21/1.1</f>
         <v>48.5454545454545</v>
       </c>
-      <c r="P21" s="43" t="n">
+      <c r="P21" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Q21" s="43" t="n">
+      <c r="Q21" s="11" t="n">
         <v>40.91</v>
       </c>
-      <c r="R21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T21" s="43" t="n">
+      <c r="R21" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S21" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T21" s="11" t="n">
         <v>82.82</v>
       </c>
-      <c r="U21" s="43" t="n">
+      <c r="U21" s="11" t="n">
         <f aca="false">T21/1.1</f>
         <v>75.2909090909091</v>
       </c>
-      <c r="V21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X21" s="43" t="n">
+      <c r="V21" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W21" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X21" s="11" t="n">
         <v>23.32</v>
       </c>
-      <c r="Y21" s="43" t="n">
+      <c r="Y21" s="11" t="n">
         <f aca="false">X21/1.1</f>
         <v>21.2</v>
       </c>
-      <c r="Z21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA21" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB21" s="43" t="n">
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="11" t="n">
         <f aca="false">IF(COUNT(I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21)=0,"N/A",MIN(I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21))</f>
         <v>21.2</v>
       </c>
-      <c r="AC21" s="45" t="n">
+      <c r="AC21" s="43" t="n">
         <f aca="false">IF(OR(D21="",AB21="",AB21="N/A"),"N/A",D21/AB21-1)</f>
         <v>0.575943396226415</v>
       </c>
-      <c r="AD21" s="45" t="n">
+      <c r="AD21" s="43" t="n">
         <f aca="false">IF(OR(F21="",AB21="",AB21="N/A"),"N/A",F21/AB21-1)</f>
         <v>0.596957547169811</v>
       </c>
-      <c r="AE21" s="42" t="s">
+      <c r="AE21" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F22</f>
         <v>11.81</v>
       </c>
-      <c r="E22" s="43" t="n">
+      <c r="E22" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G22</f>
         <v>12.991</v>
       </c>
-      <c r="F22" s="43" t="n">
+      <c r="F22" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H22="","",'RSEA vs Quoted Comparison'!H22)</f>
         <v>12.03275</v>
       </c>
-      <c r="G22" s="43" t="n">
+      <c r="G22" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I22="","",'RSEA vs Quoted Comparison'!I22)</f>
         <v>13.236025</v>
       </c>
-      <c r="H22" s="43" t="n">
+      <c r="H22" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D22</f>
         <v>44.99</v>
       </c>
-      <c r="I22" s="43" t="n">
+      <c r="I22" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E22</f>
         <v>40.9</v>
       </c>
-      <c r="J22" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K22" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L22" s="43" t="n">
+      <c r="J22" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L22" s="11" t="n">
         <v>29.61</v>
       </c>
-      <c r="M22" s="43" t="n">
+      <c r="M22" s="11" t="n">
         <v>26.92</v>
       </c>
-      <c r="N22" s="43" t="n">
+      <c r="N22" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O22" s="43" t="n">
+      <c r="O22" s="11" t="n">
         <f aca="false">N22/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P22" s="43" t="n">
+      <c r="P22" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q22" s="43" t="n">
+      <c r="Q22" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R22" s="43" t="n">
+      <c r="R22" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="S22" s="43" t="n">
+      <c r="S22" s="11" t="n">
         <f aca="false">R22/1.1</f>
         <v>25</v>
       </c>
-      <c r="T22" s="43" t="n">
+      <c r="T22" s="11" t="n">
         <v>33.12</v>
       </c>
-      <c r="U22" s="43" t="n">
+      <c r="U22" s="11" t="n">
         <f aca="false">T22/1.1</f>
         <v>30.1090909090909</v>
       </c>
-      <c r="V22" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W22" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X22" s="43" t="n">
+      <c r="V22" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W22" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X22" s="11" t="n">
         <v>23.32</v>
       </c>
-      <c r="Y22" s="43" t="n">
+      <c r="Y22" s="11" t="n">
         <f aca="false">X22/1.1</f>
         <v>21.2</v>
       </c>
-      <c r="Z22" s="43" t="n">
+      <c r="Z22" s="11" t="n">
         <v>48.85</v>
       </c>
-      <c r="AA22" s="43" t="n">
+      <c r="AA22" s="11" t="n">
         <f aca="false">Z22/1.1</f>
         <v>44.4090909090909</v>
       </c>
-      <c r="AB22" s="43" t="n">
+      <c r="AB22" s="11" t="n">
         <f aca="false">IF(COUNT(I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22)=0,"N/A",MIN(I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22))</f>
         <v>21.2</v>
       </c>
-      <c r="AC22" s="45" t="n">
+      <c r="AC22" s="43" t="n">
         <f aca="false">IF(OR(D22="",AB22="",AB22="N/A"),"N/A",D22/AB22-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD22" s="45" t="n">
+      <c r="AD22" s="43" t="n">
         <f aca="false">IF(OR(F22="",AB22="",AB22="N/A"),"N/A",F22/AB22-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE22" s="42" t="s">
+      <c r="AE22" s="41" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F23</f>
         <v>11.81</v>
       </c>
-      <c r="E23" s="43" t="n">
+      <c r="E23" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G23</f>
         <v>12.991</v>
       </c>
-      <c r="F23" s="43" t="n">
+      <c r="F23" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H23="","",'RSEA vs Quoted Comparison'!H23)</f>
         <v>12.03275</v>
       </c>
-      <c r="G23" s="43" t="n">
+      <c r="G23" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I23="","",'RSEA vs Quoted Comparison'!I23)</f>
         <v>13.236025</v>
       </c>
-      <c r="H23" s="43" t="n">
+      <c r="H23" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D23</f>
         <v>49.99</v>
       </c>
-      <c r="I23" s="43" t="n">
+      <c r="I23" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E23</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J23" s="43" t="n">
+      <c r="J23" s="11" t="n">
         <f aca="false">K23*1.1</f>
         <v>26.653</v>
       </c>
-      <c r="K23" s="43" t="n">
+      <c r="K23" s="11" t="n">
         <v>24.23</v>
       </c>
-      <c r="L23" s="43" t="n">
+      <c r="L23" s="11" t="n">
         <v>31.21</v>
       </c>
-      <c r="M23" s="43" t="n">
+      <c r="M23" s="11" t="n">
         <v>28.37</v>
       </c>
-      <c r="N23" s="43" t="n">
+      <c r="N23" s="11" t="n">
         <v>53.4</v>
       </c>
-      <c r="O23" s="43" t="n">
+      <c r="O23" s="11" t="n">
         <f aca="false">N23/1.1</f>
         <v>48.5454545454545</v>
       </c>
-      <c r="P23" s="43" t="n">
+      <c r="P23" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q23" s="43" t="n">
+      <c r="Q23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R23" s="43" t="n">
+      <c r="R23" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="S23" s="43" t="n">
+      <c r="S23" s="11" t="n">
         <f aca="false">R23/1.1</f>
         <v>25</v>
       </c>
-      <c r="T23" s="43" t="n">
+      <c r="T23" s="11" t="n">
         <v>33.33</v>
       </c>
-      <c r="U23" s="43" t="n">
+      <c r="U23" s="11" t="n">
         <f aca="false">T23/1.1</f>
         <v>30.3</v>
       </c>
-      <c r="V23" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W23" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X23" s="43" t="n">
+      <c r="V23" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W23" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X23" s="11" t="n">
         <v>23.32</v>
       </c>
-      <c r="Y23" s="43" t="n">
+      <c r="Y23" s="11" t="n">
         <f aca="false">X23/1.1</f>
         <v>21.2</v>
       </c>
-      <c r="Z23" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA23" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB23" s="43" t="n">
+      <c r="Z23" s="42"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="11" t="n">
         <f aca="false">IF(COUNT(I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23)=0,"N/A",MIN(I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23))</f>
         <v>21.2</v>
       </c>
-      <c r="AC23" s="45" t="n">
+      <c r="AC23" s="43" t="n">
         <f aca="false">IF(OR(D23="",AB23="",AB23="N/A"),"N/A",D23/AB23-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD23" s="45" t="n">
+      <c r="AD23" s="43" t="n">
         <f aca="false">IF(OR(F23="",AB23="",AB23="N/A"),"N/A",F23/AB23-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE23" s="42" t="s">
+      <c r="AE23" s="41" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F24</f>
         <v>5.9</v>
       </c>
-      <c r="E24" s="43" t="n">
+      <c r="E24" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G24</f>
         <v>6.49</v>
       </c>
-      <c r="F24" s="43" t="n">
+      <c r="F24" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H24="","",'RSEA vs Quoted Comparison'!H24)</f>
         <v>6.011375</v>
       </c>
-      <c r="G24" s="43" t="n">
+      <c r="G24" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I24="","",'RSEA vs Quoted Comparison'!I24)</f>
         <v>6.6125125</v>
       </c>
-      <c r="H24" s="43" t="n">
+      <c r="H24" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D24</f>
         <v>37.99</v>
       </c>
-      <c r="I24" s="43" t="n">
+      <c r="I24" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E24</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="J24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA24" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB24" s="43" t="n">
+      <c r="J24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z24" s="42"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="11" t="n">
         <f aca="false">IF(COUNT(I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24)=0,"N/A",MIN(I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC24" s="45" t="n">
+      <c r="AC24" s="43" t="n">
         <f aca="false">IF(OR(D24="",AB24="",AB24="N/A"),"N/A",D24/AB24-1)</f>
         <v>-0.829165569886812</v>
       </c>
-      <c r="AD24" s="45" t="n">
+      <c r="AD24" s="43" t="n">
         <f aca="false">IF(OR(F24="",AB24="",AB24="N/A"),"N/A",F24/AB24-1)</f>
         <v>-0.825940708081074</v>
       </c>
-      <c r="AE24" s="42" t="s">
+      <c r="AE24" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F25</f>
         <v>11.81</v>
       </c>
-      <c r="E25" s="43" t="n">
+      <c r="E25" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G25</f>
         <v>12.991</v>
       </c>
-      <c r="F25" s="43" t="n">
+      <c r="F25" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H25="","",'RSEA vs Quoted Comparison'!H25)</f>
         <v>12.03275</v>
       </c>
-      <c r="G25" s="43" t="n">
+      <c r="G25" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I25="","",'RSEA vs Quoted Comparison'!I25)</f>
         <v>13.236025</v>
       </c>
-      <c r="H25" s="43" t="n">
+      <c r="H25" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D25</f>
         <v>49.99</v>
       </c>
-      <c r="I25" s="43" t="n">
+      <c r="I25" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E25</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N25" s="43" t="n">
+      <c r="J25" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L25" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M25" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N25" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O25" s="43" t="n">
+      <c r="O25" s="11" t="n">
         <f aca="false">N25/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P25" s="43" t="n">
+      <c r="P25" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q25" s="43" t="n">
+      <c r="Q25" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R25" s="43" t="n">
+      <c r="R25" s="11" t="n">
         <v>33.5</v>
       </c>
-      <c r="S25" s="43" t="n">
+      <c r="S25" s="11" t="n">
         <f aca="false">R25/1.1</f>
         <v>30.4545454545455</v>
       </c>
-      <c r="T25" s="43" t="n">
+      <c r="T25" s="11" t="n">
         <v>34.46</v>
       </c>
-      <c r="U25" s="43" t="n">
+      <c r="U25" s="11" t="n">
         <f aca="false">T25/1.1</f>
         <v>31.3272727272727</v>
       </c>
-      <c r="V25" s="43" t="n">
+      <c r="V25" s="11" t="n">
         <f aca="false">W25*1.1</f>
         <v>24.75</v>
       </c>
-      <c r="W25" s="43" t="n">
+      <c r="W25" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="X25" s="43" t="n">
+      <c r="X25" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y25" s="43" t="n">
+      <c r="Y25" s="11" t="n">
         <f aca="false">X25/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB25" s="43" t="n">
+      <c r="Z25" s="42"/>
+      <c r="AA25" s="42"/>
+      <c r="AB25" s="11" t="n">
         <f aca="false">IF(COUNT(I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25)=0,"N/A",MIN(I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC25" s="45" t="n">
+      <c r="AC25" s="43" t="n">
         <f aca="false">IF(OR(D25="",AB25="",AB25="N/A"),"N/A",D25/AB25-1)</f>
         <v>0.262487852283771</v>
       </c>
-      <c r="AD25" s="45" t="n">
+      <c r="AD25" s="43" t="n">
         <f aca="false">IF(OR(F25="",AB25="",AB25="N/A"),"N/A",F25/AB25-1)</f>
         <v>0.28629980563654</v>
       </c>
-      <c r="AE25" s="42" t="s">
+      <c r="AE25" s="41" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F26</f>
         <v>11.81</v>
       </c>
-      <c r="E26" s="43" t="n">
+      <c r="E26" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G26</f>
         <v>12.991</v>
       </c>
-      <c r="F26" s="43" t="n">
+      <c r="F26" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H26="","",'RSEA vs Quoted Comparison'!H26)</f>
         <v>12.03275</v>
       </c>
-      <c r="G26" s="43" t="n">
+      <c r="G26" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I26="","",'RSEA vs Quoted Comparison'!I26)</f>
         <v>13.236025</v>
       </c>
-      <c r="H26" s="43" t="n">
+      <c r="H26" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D26</f>
         <v>44.99</v>
       </c>
-      <c r="I26" s="43" t="n">
+      <c r="I26" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E26</f>
         <v>40.9</v>
       </c>
-      <c r="J26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N26" s="43" t="n">
+      <c r="J26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N26" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O26" s="43" t="n">
+      <c r="O26" s="11" t="n">
         <f aca="false">N26/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P26" s="43" t="n">
+      <c r="P26" s="11" t="n">
         <v>22.05</v>
       </c>
-      <c r="Q26" s="43" t="n">
+      <c r="Q26" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="R26" s="43" t="n">
+      <c r="R26" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="S26" s="43" t="n">
+      <c r="S26" s="11" t="n">
         <f aca="false">R26/1.1</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="T26" s="43" t="n">
+      <c r="T26" s="11" t="n">
         <v>31.19</v>
       </c>
-      <c r="U26" s="43" t="n">
+      <c r="U26" s="11" t="n">
         <f aca="false">T26/1.1</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="V26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W26" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X26" s="43" t="n">
+      <c r="V26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W26" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X26" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y26" s="43" t="n">
+      <c r="Y26" s="11" t="n">
         <f aca="false">X26/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z26" s="43" t="n">
+      <c r="Z26" s="11" t="n">
         <v>65.63</v>
       </c>
-      <c r="AA26" s="43" t="n">
+      <c r="AA26" s="11" t="n">
         <f aca="false">Z26/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB26" s="43" t="n">
+      <c r="AB26" s="11" t="n">
         <f aca="false">IF(COUNT(I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26)=0,"N/A",MIN(I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC26" s="45" t="n">
+      <c r="AC26" s="43" t="n">
         <f aca="false">IF(OR(D26="",AB26="",AB26="N/A"),"N/A",D26/AB26-1)</f>
         <v>0.262487852283771</v>
       </c>
-      <c r="AD26" s="45" t="n">
+      <c r="AD26" s="43" t="n">
         <f aca="false">IF(OR(F26="",AB26="",AB26="N/A"),"N/A",F26/AB26-1)</f>
         <v>0.28629980563654</v>
       </c>
-      <c r="AE26" s="42" t="s">
+      <c r="AE26" s="41" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="43" t="n">
+      <c r="D27" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F27</f>
         <v>11.81</v>
       </c>
-      <c r="E27" s="43" t="n">
+      <c r="E27" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G27</f>
         <v>12.991</v>
       </c>
-      <c r="F27" s="43" t="n">
+      <c r="F27" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H27="","",'RSEA vs Quoted Comparison'!H27)</f>
         <v>12.03275</v>
       </c>
-      <c r="G27" s="43" t="n">
+      <c r="G27" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I27="","",'RSEA vs Quoted Comparison'!I27)</f>
         <v>13.236025</v>
       </c>
-      <c r="H27" s="43" t="n">
+      <c r="H27" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D27</f>
         <v>44.99</v>
       </c>
-      <c r="I27" s="43" t="n">
+      <c r="I27" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E27</f>
         <v>40.9</v>
       </c>
-      <c r="J27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N27" s="43" t="n">
+      <c r="J27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N27" s="11" t="n">
         <v>35.75</v>
       </c>
-      <c r="O27" s="43" t="n">
+      <c r="O27" s="11" t="n">
         <f aca="false">N27/1.1</f>
         <v>32.5</v>
       </c>
-      <c r="P27" s="43" t="n">
+      <c r="P27" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="Q27" s="43" t="n">
+      <c r="Q27" s="11" t="n">
         <v>38.64</v>
       </c>
-      <c r="R27" s="43" t="n">
+      <c r="R27" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="S27" s="43" t="n">
+      <c r="S27" s="11" t="n">
         <f aca="false">R27/1.1</f>
         <v>25</v>
       </c>
-      <c r="T27" s="43" t="n">
+      <c r="T27" s="11" t="n">
         <v>30.11</v>
       </c>
-      <c r="U27" s="43" t="n">
+      <c r="U27" s="11" t="n">
         <f aca="false">T27/1.1</f>
         <v>27.3727272727273</v>
       </c>
-      <c r="V27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X27" s="43" t="n">
+      <c r="V27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X27" s="11" t="n">
         <v>23.32</v>
       </c>
-      <c r="Y27" s="43" t="n">
+      <c r="Y27" s="11" t="n">
         <f aca="false">X27/1.1</f>
         <v>21.2</v>
       </c>
-      <c r="Z27" s="43" t="n">
+      <c r="Z27" s="11" t="n">
         <v>49.78</v>
       </c>
-      <c r="AA27" s="43" t="n">
+      <c r="AA27" s="11" t="n">
         <f aca="false">Z27/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB27" s="43" t="n">
+      <c r="AB27" s="11" t="n">
         <f aca="false">IF(COUNT(I27,K27,M27,O27,Q27,S27,U27,W27,Y27,AA27)=0,"N/A",MIN(I27,K27,M27,O27,Q27,S27,U27,W27,Y27,AA27))</f>
         <v>21.2</v>
       </c>
-      <c r="AC27" s="45" t="n">
+      <c r="AC27" s="43" t="n">
         <f aca="false">IF(OR(D27="",AB27="",AB27="N/A"),"N/A",D27/AB27-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD27" s="45" t="n">
+      <c r="AD27" s="43" t="n">
         <f aca="false">IF(OR(F27="",AB27="",AB27="N/A"),"N/A",F27/AB27-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE27" s="42" t="s">
+      <c r="AE27" s="41" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F28</f>
         <v>33.41</v>
       </c>
-      <c r="E28" s="43" t="n">
+      <c r="E28" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G28</f>
         <v>36.751</v>
       </c>
-      <c r="F28" s="43" t="n">
+      <c r="F28" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H28="","",'RSEA vs Quoted Comparison'!H28)</f>
         <v>33.8555</v>
       </c>
-      <c r="G28" s="43" t="n">
+      <c r="G28" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I28="","",'RSEA vs Quoted Comparison'!I28)</f>
         <v>37.24105</v>
       </c>
-      <c r="H28" s="43" t="n">
+      <c r="H28" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D28</f>
         <v>142.99</v>
       </c>
-      <c r="I28" s="43" t="n">
+      <c r="I28" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E28</f>
         <v>129.990909090909</v>
       </c>
-      <c r="J28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N28" s="43" t="n">
+      <c r="J28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N28" s="11" t="n">
         <v>35.75</v>
       </c>
-      <c r="O28" s="43" t="n">
+      <c r="O28" s="11" t="n">
         <f aca="false">N28/1.1</f>
         <v>32.5</v>
       </c>
-      <c r="P28" s="43" t="n">
+      <c r="P28" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q28" s="43" t="n">
+      <c r="Q28" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R28" s="43" t="n">
+      <c r="R28" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S28" s="43" t="n">
+      <c r="S28" s="11" t="n">
         <f aca="false">R28/1.1</f>
         <v>68</v>
       </c>
-      <c r="T28" s="43" t="n">
+      <c r="T28" s="11" t="n">
         <v>98.07</v>
       </c>
-      <c r="U28" s="43" t="n">
+      <c r="U28" s="11" t="n">
         <f aca="false">T28/1.1</f>
         <v>89.1545454545454</v>
       </c>
-      <c r="V28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X28" s="43" t="n">
+      <c r="V28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W28" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X28" s="11" t="n">
         <v>110.1</v>
       </c>
-      <c r="Y28" s="43" t="n">
+      <c r="Y28" s="11" t="n">
         <f aca="false">X28/1.1</f>
         <v>100.090909090909</v>
       </c>
-      <c r="Z28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA28" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB28" s="43" t="n">
+      <c r="Z28" s="42"/>
+      <c r="AA28" s="42"/>
+      <c r="AB28" s="11" t="n">
         <f aca="false">IF(COUNT(I28,K28,M28,O28,Q28,S28,U28,W28,Y28,AA28)=0,"N/A",MIN(I28,K28,M28,O28,Q28,S28,U28,W28,Y28,AA28))</f>
         <v>32.5</v>
       </c>
-      <c r="AC28" s="45" t="n">
+      <c r="AC28" s="43" t="n">
         <f aca="false">IF(OR(D28="",AB28="",AB28="N/A"),"N/A",D28/AB28-1)</f>
         <v>0.0279999999999998</v>
       </c>
-      <c r="AD28" s="45" t="n">
+      <c r="AD28" s="43" t="n">
         <f aca="false">IF(OR(F28="",AB28="",AB28="N/A"),"N/A",F28/AB28-1)</f>
         <v>0.0417076923076922</v>
       </c>
-      <c r="AE28" s="42" t="s">
+      <c r="AE28" s="41" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F29</f>
         <v>33.41</v>
       </c>
-      <c r="E29" s="43" t="n">
+      <c r="E29" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G29</f>
         <v>36.751</v>
       </c>
-      <c r="F29" s="43" t="n">
+      <c r="F29" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H29="","",'RSEA vs Quoted Comparison'!H29)</f>
         <v>33.8555</v>
       </c>
-      <c r="G29" s="43" t="n">
+      <c r="G29" s="11" t="n">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I29="","",'RSEA vs Quoted Comparison'!I29)</f>
         <v>37.24105</v>
       </c>
-      <c r="H29" s="43" t="n">
+      <c r="H29" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D29</f>
         <v>142.99</v>
       </c>
-      <c r="I29" s="43" t="n">
+      <c r="I29" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E29</f>
         <v>129.990909090909</v>
       </c>
-      <c r="J29" s="43" t="n">
+      <c r="J29" s="11" t="n">
         <f aca="false">K29*1.1</f>
         <v>109.153</v>
       </c>
-      <c r="K29" s="43" t="n">
+      <c r="K29" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L29" s="43" t="n">
+      <c r="L29" s="11" t="n">
         <v>61.59</v>
       </c>
-      <c r="M29" s="43" t="n">
+      <c r="M29" s="11" t="n">
         <v>55.99</v>
       </c>
-      <c r="N29" s="43" t="n">
+      <c r="N29" s="11" t="n">
         <v>49.5</v>
       </c>
-      <c r="O29" s="43" t="n">
+      <c r="O29" s="11" t="n">
         <f aca="false">N29/1.1</f>
         <v>45</v>
       </c>
-      <c r="P29" s="43" t="n">
+      <c r="P29" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="Q29" s="43" t="n">
+      <c r="Q29" s="11" t="n">
         <v>51.82</v>
       </c>
-      <c r="R29" s="43" t="n">
+      <c r="R29" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="S29" s="43" t="n">
+      <c r="S29" s="11" t="n">
         <f aca="false">R29/1.1</f>
         <v>68</v>
       </c>
-      <c r="T29" s="43" t="n">
+      <c r="T29" s="11" t="n">
         <v>114.08</v>
       </c>
-      <c r="U29" s="43" t="n">
+      <c r="U29" s="11" t="n">
         <f aca="false">T29/1.1</f>
         <v>103.709090909091</v>
       </c>
-      <c r="V29" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W29" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X29" s="43" t="n">
+      <c r="V29" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W29" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X29" s="11" t="n">
         <v>110.1</v>
       </c>
-      <c r="Y29" s="43" t="n">
+      <c r="Y29" s="11" t="n">
         <f aca="false">X29/1.1</f>
         <v>100.090909090909</v>
       </c>
-      <c r="Z29" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA29" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB29" s="43" t="n">
+      <c r="Z29" s="42"/>
+      <c r="AA29" s="42"/>
+      <c r="AB29" s="11" t="n">
         <f aca="false">IF(COUNT(I29,K29,M29,O29,Q29,S29,U29,W29,Y29,AA29)=0,"N/A",MIN(I29,K29,M29,O29,Q29,S29,U29,W29,Y29,AA29))</f>
         <v>45</v>
       </c>
-      <c r="AC29" s="45" t="n">
+      <c r="AC29" s="43" t="n">
         <f aca="false">IF(OR(D29="",AB29="",AB29="N/A"),"N/A",D29/AB29-1)</f>
         <v>-0.257555555555556</v>
       </c>
-      <c r="AD29" s="45" t="n">
+      <c r="AD29" s="43" t="n">
         <f aca="false">IF(OR(F29="",AB29="",AB29="N/A"),"N/A",F29/AB29-1)</f>
         <v>-0.247655555555555</v>
       </c>
-      <c r="AE29" s="42" t="s">
+      <c r="AE29" s="41" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F30</f>
         <v>13.07</v>
       </c>
-      <c r="E30" s="43" t="n">
+      <c r="E30" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G30</f>
         <v>14.377</v>
       </c>
-      <c r="F30" s="43" t="str">
+      <c r="F30" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H30="","",'RSEA vs Quoted Comparison'!H30)</f>
         <v/>
       </c>
-      <c r="G30" s="43" t="str">
+      <c r="G30" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I30="","",'RSEA vs Quoted Comparison'!I30)</f>
         <v/>
       </c>
-      <c r="H30" s="43" t="n">
+      <c r="H30" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D30</f>
         <v>57.99</v>
       </c>
-      <c r="I30" s="43" t="n">
+      <c r="I30" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E30</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J30" s="43" t="n">
+      <c r="J30" s="11" t="n">
         <f aca="false">K30*1.1</f>
         <v>164.098</v>
       </c>
-      <c r="K30" s="43" t="n">
+      <c r="K30" s="11" t="n">
         <v>149.18</v>
       </c>
-      <c r="L30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R30" s="43" t="n">
+      <c r="L30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R30" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S30" s="43" t="n">
+      <c r="S30" s="11" t="n">
         <f aca="false">R30/1.1</f>
         <v>31</v>
       </c>
-      <c r="T30" s="43" t="n">
+      <c r="T30" s="11" t="n">
         <v>61.04</v>
       </c>
-      <c r="U30" s="43" t="n">
+      <c r="U30" s="11" t="n">
         <f aca="false">T30/1.1</f>
         <v>55.4909090909091</v>
       </c>
-      <c r="V30" s="43" t="n">
+      <c r="V30" s="11" t="n">
         <f aca="false">W30*1.1</f>
         <v>30.8</v>
       </c>
-      <c r="W30" s="43" t="n">
+      <c r="W30" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="X30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA30" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB30" s="43" t="n">
+      <c r="X30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z30" s="42"/>
+      <c r="AA30" s="42"/>
+      <c r="AB30" s="11" t="n">
         <f aca="false">IF(COUNT(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30)=0,"N/A",MIN(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30))</f>
         <v>28</v>
       </c>
-      <c r="AC30" s="45" t="n">
+      <c r="AC30" s="43" t="n">
         <f aca="false">IF(OR(D30="",AB30="",AB30="N/A"),"N/A",D30/AB30-1)</f>
         <v>-0.533214285714286</v>
       </c>
-      <c r="AD30" s="45" t="str">
+      <c r="AD30" s="43" t="str">
         <f aca="false">IF(OR(F30="",AB30="",AB30="N/A"),"N/A",F30/AB30-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE30" s="42" t="s">
+      <c r="AE30" s="41" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F31</f>
         <v>13.07</v>
       </c>
-      <c r="E31" s="43" t="n">
+      <c r="E31" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G31</f>
         <v>14.377</v>
       </c>
-      <c r="F31" s="43" t="str">
+      <c r="F31" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H31="","",'RSEA vs Quoted Comparison'!H31)</f>
         <v/>
       </c>
-      <c r="G31" s="43" t="str">
+      <c r="G31" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I31="","",'RSEA vs Quoted Comparison'!I31)</f>
         <v/>
       </c>
-      <c r="H31" s="43" t="n">
+      <c r="H31" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D31</f>
         <v>44.99</v>
       </c>
-      <c r="I31" s="43" t="n">
+      <c r="I31" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E31</f>
         <v>40.9</v>
       </c>
-      <c r="J31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R31" s="43" t="n">
+      <c r="J31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R31" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S31" s="43" t="n">
+      <c r="S31" s="11" t="n">
         <f aca="false">R31/1.1</f>
         <v>31</v>
       </c>
-      <c r="T31" s="43" t="n">
+      <c r="T31" s="11" t="n">
         <v>47.14</v>
       </c>
-      <c r="U31" s="43" t="n">
+      <c r="U31" s="11" t="n">
         <f aca="false">T31/1.1</f>
         <v>42.8545454545455</v>
       </c>
-      <c r="V31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X31" s="43" t="n">
+      <c r="V31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X31" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y31" s="43" t="n">
+      <c r="Y31" s="11" t="n">
         <f aca="false">X31/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA31" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB31" s="43" t="n">
+      <c r="Z31" s="42"/>
+      <c r="AA31" s="42"/>
+      <c r="AB31" s="11" t="n">
         <f aca="false">IF(COUNT(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31)=0,"N/A",MIN(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31))</f>
         <v>31</v>
       </c>
-      <c r="AC31" s="45" t="n">
+      <c r="AC31" s="43" t="n">
         <f aca="false">IF(OR(D31="",AB31="",AB31="N/A"),"N/A",D31/AB31-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD31" s="45" t="str">
+      <c r="AD31" s="43" t="str">
         <f aca="false">IF(OR(F31="",AB31="",AB31="N/A"),"N/A",F31/AB31-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE31" s="42" t="s">
+      <c r="AE31" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="43" t="n">
+      <c r="D32" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F32</f>
         <v>16.04</v>
       </c>
-      <c r="E32" s="43" t="n">
+      <c r="E32" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G32</f>
         <v>17.644</v>
       </c>
-      <c r="F32" s="43" t="str">
+      <c r="F32" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H32="","",'RSEA vs Quoted Comparison'!H32)</f>
         <v/>
       </c>
-      <c r="G32" s="43" t="str">
+      <c r="G32" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I32="","",'RSEA vs Quoted Comparison'!I32)</f>
         <v/>
       </c>
-      <c r="H32" s="43" t="n">
+      <c r="H32" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D32</f>
         <v>52.99</v>
       </c>
-      <c r="I32" s="43" t="n">
+      <c r="I32" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E32</f>
         <v>48.1727272727273</v>
       </c>
-      <c r="J32" s="43" t="n">
+      <c r="J32" s="11" t="n">
         <f aca="false">K32*1.1</f>
         <v>159.885</v>
       </c>
-      <c r="K32" s="43" t="n">
+      <c r="K32" s="11" t="n">
         <v>145.35</v>
       </c>
-      <c r="L32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R32" s="43" t="n">
+      <c r="L32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R32" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S32" s="43" t="n">
+      <c r="S32" s="11" t="n">
         <f aca="false">R32/1.1</f>
         <v>31</v>
       </c>
-      <c r="T32" s="43" t="n">
+      <c r="T32" s="11" t="n">
         <v>86.85</v>
       </c>
-      <c r="U32" s="43" t="n">
+      <c r="U32" s="11" t="n">
         <f aca="false">T32/1.1</f>
         <v>78.9545454545454</v>
       </c>
-      <c r="V32" s="43" t="n">
+      <c r="V32" s="11" t="n">
         <f aca="false">W32*1.1</f>
         <v>56.65</v>
       </c>
-      <c r="W32" s="43" t="n">
+      <c r="W32" s="11" t="n">
         <v>51.5</v>
       </c>
-      <c r="X32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA32" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB32" s="43" t="n">
+      <c r="X32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z32" s="42"/>
+      <c r="AA32" s="42"/>
+      <c r="AB32" s="11" t="n">
         <f aca="false">IF(COUNT(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32)=0,"N/A",MIN(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32))</f>
         <v>31</v>
       </c>
-      <c r="AC32" s="45" t="n">
+      <c r="AC32" s="43" t="n">
         <f aca="false">IF(OR(D32="",AB32="",AB32="N/A"),"N/A",D32/AB32-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD32" s="45" t="str">
+      <c r="AD32" s="43" t="str">
         <f aca="false">IF(OR(F32="",AB32="",AB32="N/A"),"N/A",F32/AB32-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE32" s="42" t="s">
+      <c r="AE32" s="41" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="43" t="n">
+      <c r="D33" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F33</f>
         <v>16.04</v>
       </c>
-      <c r="E33" s="43" t="n">
+      <c r="E33" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G33</f>
         <v>17.644</v>
       </c>
-      <c r="F33" s="43" t="str">
+      <c r="F33" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H33="","",'RSEA vs Quoted Comparison'!H33)</f>
         <v/>
       </c>
-      <c r="G33" s="43" t="str">
+      <c r="G33" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I33="","",'RSEA vs Quoted Comparison'!I33)</f>
         <v/>
       </c>
-      <c r="H33" s="43" t="n">
+      <c r="H33" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D33</f>
         <v>57.99</v>
       </c>
-      <c r="I33" s="43" t="n">
+      <c r="I33" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E33</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J33" s="43" t="n">
+      <c r="J33" s="11" t="n">
         <f aca="false">K33*1.1</f>
         <v>200.354</v>
       </c>
-      <c r="K33" s="43" t="n">
+      <c r="K33" s="11" t="n">
         <v>182.14</v>
       </c>
-      <c r="L33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R33" s="43" t="n">
+      <c r="L33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R33" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S33" s="43" t="n">
+      <c r="S33" s="11" t="n">
         <f aca="false">R33/1.1</f>
         <v>31</v>
       </c>
-      <c r="T33" s="43" t="n">
+      <c r="T33" s="11" t="n">
         <v>58.84</v>
       </c>
-      <c r="U33" s="43" t="n">
+      <c r="U33" s="11" t="n">
         <f aca="false">T33/1.1</f>
         <v>53.4909090909091</v>
       </c>
-      <c r="V33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X33" s="43" t="n">
+      <c r="V33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X33" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y33" s="43" t="n">
+      <c r="Y33" s="11" t="n">
         <f aca="false">X33/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB33" s="43" t="n">
+      <c r="Z33" s="42"/>
+      <c r="AA33" s="42"/>
+      <c r="AB33" s="11" t="n">
         <f aca="false">IF(COUNT(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33)=0,"N/A",MIN(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33))</f>
         <v>31</v>
       </c>
-      <c r="AC33" s="45" t="n">
+      <c r="AC33" s="43" t="n">
         <f aca="false">IF(OR(D33="",AB33="",AB33="N/A"),"N/A",D33/AB33-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD33" s="45" t="str">
+      <c r="AD33" s="43" t="str">
         <f aca="false">IF(OR(F33="",AB33="",AB33="N/A"),"N/A",F33/AB33-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE33" s="42" t="s">
+      <c r="AE33" s="41" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F34</f>
         <v>16.04</v>
       </c>
-      <c r="E34" s="43" t="n">
+      <c r="E34" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G34</f>
         <v>17.644</v>
       </c>
-      <c r="F34" s="43" t="str">
+      <c r="F34" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H34="","",'RSEA vs Quoted Comparison'!H34)</f>
         <v/>
       </c>
-      <c r="G34" s="43" t="str">
+      <c r="G34" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I34="","",'RSEA vs Quoted Comparison'!I34)</f>
         <v/>
       </c>
-      <c r="H34" s="43" t="n">
+      <c r="H34" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D34</f>
         <v>57.99</v>
       </c>
-      <c r="I34" s="43" t="n">
+      <c r="I34" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E34</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J34" s="43" t="n">
+      <c r="J34" s="11" t="n">
         <f aca="false">K34*1.1</f>
         <v>200.354</v>
       </c>
-      <c r="K34" s="43" t="n">
+      <c r="K34" s="11" t="n">
         <v>182.14</v>
       </c>
-      <c r="L34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R34" s="43" t="n">
+      <c r="L34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R34" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S34" s="43" t="n">
+      <c r="S34" s="11" t="n">
         <f aca="false">R34/1.1</f>
         <v>31</v>
       </c>
-      <c r="T34" s="43" t="n">
+      <c r="T34" s="11" t="n">
         <v>60.6</v>
       </c>
-      <c r="U34" s="43" t="n">
+      <c r="U34" s="11" t="n">
         <f aca="false">T34/1.1</f>
         <v>55.0909090909091</v>
       </c>
-      <c r="V34" s="43" t="n">
+      <c r="V34" s="11" t="n">
         <f aca="false">W34*1.1</f>
         <v>56.65</v>
       </c>
-      <c r="W34" s="43" t="n">
+      <c r="W34" s="11" t="n">
         <v>51.5</v>
       </c>
-      <c r="X34" s="43" t="n">
+      <c r="X34" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y34" s="43" t="n">
+      <c r="Y34" s="11" t="n">
         <f aca="false">X34/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA34" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB34" s="43" t="n">
+      <c r="Z34" s="42"/>
+      <c r="AA34" s="42"/>
+      <c r="AB34" s="11" t="n">
         <f aca="false">IF(COUNT(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34)=0,"N/A",MIN(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34))</f>
         <v>31</v>
       </c>
-      <c r="AC34" s="45" t="n">
+      <c r="AC34" s="43" t="n">
         <f aca="false">IF(OR(D34="",AB34="",AB34="N/A"),"N/A",D34/AB34-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD34" s="45" t="str">
+      <c r="AD34" s="43" t="str">
         <f aca="false">IF(OR(F34="",AB34="",AB34="N/A"),"N/A",F34/AB34-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE34" s="42" t="s">
+      <c r="AE34" s="41" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="43" t="n">
+      <c r="D35" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F35</f>
         <v>16.04</v>
       </c>
-      <c r="E35" s="43" t="n">
+      <c r="E35" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G35</f>
         <v>17.644</v>
       </c>
-      <c r="F35" s="43" t="str">
+      <c r="F35" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H35="","",'RSEA vs Quoted Comparison'!H35)</f>
         <v/>
       </c>
-      <c r="G35" s="43" t="str">
+      <c r="G35" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I35="","",'RSEA vs Quoted Comparison'!I35)</f>
         <v/>
       </c>
-      <c r="H35" s="43" t="n">
+      <c r="H35" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D35</f>
         <v>57.99</v>
       </c>
-      <c r="I35" s="43" t="n">
+      <c r="I35" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E35</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J35" s="43" t="n">
+      <c r="J35" s="11" t="n">
         <f aca="false">K35*1.1</f>
         <v>130.24</v>
       </c>
-      <c r="K35" s="43" t="n">
+      <c r="K35" s="11" t="n">
         <v>118.4</v>
       </c>
-      <c r="L35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R35" s="43" t="n">
+      <c r="L35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R35" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S35" s="43" t="n">
+      <c r="S35" s="11" t="n">
         <f aca="false">R35/1.1</f>
         <v>31</v>
       </c>
-      <c r="T35" s="43" t="n">
+      <c r="T35" s="11" t="n">
         <v>59.05</v>
       </c>
-      <c r="U35" s="43" t="n">
+      <c r="U35" s="11" t="n">
         <f aca="false">T35/1.1</f>
         <v>53.6818181818182</v>
       </c>
-      <c r="V35" s="43" t="n">
+      <c r="V35" s="11" t="n">
         <f aca="false">W35*1.1</f>
         <v>56.65</v>
       </c>
-      <c r="W35" s="43" t="n">
+      <c r="W35" s="11" t="n">
         <v>51.5</v>
       </c>
-      <c r="X35" s="43" t="n">
+      <c r="X35" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y35" s="43" t="n">
+      <c r="Y35" s="11" t="n">
         <f aca="false">X35/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA35" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB35" s="43" t="n">
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="42"/>
+      <c r="AB35" s="11" t="n">
         <f aca="false">IF(COUNT(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35)=0,"N/A",MIN(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35))</f>
         <v>31</v>
       </c>
-      <c r="AC35" s="45" t="n">
+      <c r="AC35" s="43" t="n">
         <f aca="false">IF(OR(D35="",AB35="",AB35="N/A"),"N/A",D35/AB35-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD35" s="45" t="str">
+      <c r="AD35" s="43" t="str">
         <f aca="false">IF(OR(F35="",AB35="",AB35="N/A"),"N/A",F35/AB35-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE35" s="42" t="s">
+      <c r="AE35" s="41" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C36" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="43" t="n">
+      <c r="D36" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F36</f>
         <v>13.07</v>
       </c>
-      <c r="E36" s="43" t="n">
+      <c r="E36" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G36</f>
         <v>14.377</v>
       </c>
-      <c r="F36" s="43" t="str">
+      <c r="F36" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H36="","",'RSEA vs Quoted Comparison'!H36)</f>
         <v/>
       </c>
-      <c r="G36" s="43" t="str">
+      <c r="G36" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I36="","",'RSEA vs Quoted Comparison'!I36)</f>
         <v/>
       </c>
-      <c r="H36" s="43" t="n">
+      <c r="H36" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D36</f>
         <v>57.99</v>
       </c>
-      <c r="I36" s="43" t="n">
+      <c r="I36" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E36</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J36" s="43" t="n">
+      <c r="J36" s="11" t="n">
         <f aca="false">K36*1.1</f>
         <v>164.098</v>
       </c>
-      <c r="K36" s="43" t="n">
+      <c r="K36" s="11" t="n">
         <v>149.18</v>
       </c>
-      <c r="L36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N36" s="43" t="n">
+      <c r="L36" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M36" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N36" s="11" t="n">
         <v>46.6</v>
       </c>
-      <c r="O36" s="43" t="n">
+      <c r="O36" s="11" t="n">
         <f aca="false">N36/1.1</f>
         <v>42.3636363636364</v>
       </c>
-      <c r="P36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R36" s="43" t="n">
+      <c r="P36" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q36" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R36" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S36" s="43" t="n">
+      <c r="S36" s="11" t="n">
         <f aca="false">R36/1.1</f>
         <v>31</v>
       </c>
-      <c r="T36" s="43" t="n">
+      <c r="T36" s="11" t="n">
         <v>73.96</v>
       </c>
-      <c r="U36" s="43" t="n">
+      <c r="U36" s="11" t="n">
         <f aca="false">T36/1.1</f>
         <v>67.2363636363636</v>
       </c>
-      <c r="V36" s="43" t="n">
+      <c r="V36" s="11" t="n">
         <f aca="false">W36*1.1</f>
         <v>52.25</v>
       </c>
-      <c r="W36" s="43" t="n">
+      <c r="W36" s="11" t="n">
         <v>47.5</v>
       </c>
-      <c r="X36" s="43" t="n">
+      <c r="X36" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y36" s="43" t="n">
+      <c r="Y36" s="11" t="n">
         <f aca="false">X36/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA36" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB36" s="43" t="n">
+      <c r="Z36" s="42"/>
+      <c r="AA36" s="42"/>
+      <c r="AB36" s="11" t="n">
         <f aca="false">IF(COUNT(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36)=0,"N/A",MIN(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36))</f>
         <v>31</v>
       </c>
-      <c r="AC36" s="45" t="n">
+      <c r="AC36" s="43" t="n">
         <f aca="false">IF(OR(D36="",AB36="",AB36="N/A"),"N/A",D36/AB36-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD36" s="45" t="str">
+      <c r="AD36" s="43" t="str">
         <f aca="false">IF(OR(F36="",AB36="",AB36="N/A"),"N/A",F36/AB36-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE36" s="42" t="s">
+      <c r="AE36" s="41" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="s">
+      <c r="A37" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="43" t="n">
+      <c r="D37" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F37</f>
         <v>16.04</v>
       </c>
-      <c r="E37" s="43" t="n">
+      <c r="E37" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G37</f>
         <v>17.644</v>
       </c>
-      <c r="F37" s="43" t="str">
+      <c r="F37" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H37="","",'RSEA vs Quoted Comparison'!H37)</f>
         <v/>
       </c>
-      <c r="G37" s="43" t="str">
+      <c r="G37" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I37="","",'RSEA vs Quoted Comparison'!I37)</f>
         <v/>
       </c>
-      <c r="H37" s="43" t="n">
+      <c r="H37" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D37</f>
         <v>59.99</v>
       </c>
-      <c r="I37" s="43" t="n">
+      <c r="I37" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E37</f>
         <v>54.5363636363636</v>
       </c>
-      <c r="J37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R37" s="43" t="n">
+      <c r="J37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R37" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S37" s="43" t="n">
+      <c r="S37" s="11" t="n">
         <f aca="false">R37/1.1</f>
         <v>31</v>
       </c>
-      <c r="T37" s="43" t="n">
+      <c r="T37" s="11" t="n">
         <v>61.03</v>
       </c>
-      <c r="U37" s="43" t="n">
+      <c r="U37" s="11" t="n">
         <f aca="false">T37/1.1</f>
         <v>55.4818181818182</v>
       </c>
-      <c r="V37" s="43" t="n">
+      <c r="V37" s="11" t="n">
         <f aca="false">W37*1.1</f>
         <v>52.25</v>
       </c>
-      <c r="W37" s="43" t="n">
+      <c r="W37" s="11" t="n">
         <v>47.5</v>
       </c>
-      <c r="X37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA37" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB37" s="43" t="n">
+      <c r="X37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z37" s="42"/>
+      <c r="AA37" s="42"/>
+      <c r="AB37" s="11" t="n">
         <f aca="false">IF(COUNT(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37)=0,"N/A",MIN(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37))</f>
         <v>31</v>
       </c>
-      <c r="AC37" s="45" t="n">
+      <c r="AC37" s="43" t="n">
         <f aca="false">IF(OR(D37="",AB37="",AB37="N/A"),"N/A",D37/AB37-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD37" s="45" t="str">
+      <c r="AD37" s="43" t="str">
         <f aca="false">IF(OR(F37="",AB37="",AB37="N/A"),"N/A",F37/AB37-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE37" s="42" t="s">
+      <c r="AE37" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="43" t="n">
+      <c r="D38" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F38</f>
         <v>13.07</v>
       </c>
-      <c r="E38" s="43" t="n">
+      <c r="E38" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G38</f>
         <v>14.377</v>
       </c>
-      <c r="F38" s="43" t="str">
+      <c r="F38" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H38="","",'RSEA vs Quoted Comparison'!H38)</f>
         <v/>
       </c>
-      <c r="G38" s="43" t="str">
+      <c r="G38" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I38="","",'RSEA vs Quoted Comparison'!I38)</f>
         <v/>
       </c>
-      <c r="H38" s="43" t="n">
+      <c r="H38" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D38</f>
         <v>57.99</v>
       </c>
-      <c r="I38" s="43" t="n">
+      <c r="I38" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E38</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J38" s="43" t="n">
+      <c r="J38" s="11" t="n">
         <f aca="false">K38*1.1</f>
         <v>102.047</v>
       </c>
-      <c r="K38" s="43" t="n">
+      <c r="K38" s="11" t="n">
         <v>92.77</v>
       </c>
-      <c r="L38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R38" s="43" t="n">
+      <c r="L38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R38" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S38" s="43" t="n">
+      <c r="S38" s="11" t="n">
         <f aca="false">R38/1.1</f>
         <v>31</v>
       </c>
-      <c r="T38" s="43" t="n">
+      <c r="T38" s="11" t="n">
         <v>59.05</v>
       </c>
-      <c r="U38" s="43" t="n">
+      <c r="U38" s="11" t="n">
         <f aca="false">T38/1.1</f>
         <v>53.6818181818182</v>
       </c>
-      <c r="V38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X38" s="43" t="n">
+      <c r="V38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X38" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y38" s="43" t="n">
+      <c r="Y38" s="11" t="n">
         <f aca="false">X38/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA38" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB38" s="43" t="n">
+      <c r="Z38" s="42"/>
+      <c r="AA38" s="42"/>
+      <c r="AB38" s="11" t="n">
         <f aca="false">IF(COUNT(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38)=0,"N/A",MIN(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38))</f>
         <v>31</v>
       </c>
-      <c r="AC38" s="45" t="n">
+      <c r="AC38" s="43" t="n">
         <f aca="false">IF(OR(D38="",AB38="",AB38="N/A"),"N/A",D38/AB38-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD38" s="45" t="str">
+      <c r="AD38" s="43" t="str">
         <f aca="false">IF(OR(F38="",AB38="",AB38="N/A"),"N/A",F38/AB38-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE38" s="42" t="s">
+      <c r="AE38" s="41" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="41" t="s">
+      <c r="A39" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="43" t="n">
+      <c r="D39" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F39</f>
         <v>13.07</v>
       </c>
-      <c r="E39" s="43" t="n">
+      <c r="E39" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G39</f>
         <v>14.377</v>
       </c>
-      <c r="F39" s="43" t="str">
+      <c r="F39" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H39="","",'RSEA vs Quoted Comparison'!H39)</f>
         <v/>
       </c>
-      <c r="G39" s="43" t="str">
+      <c r="G39" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I39="","",'RSEA vs Quoted Comparison'!I39)</f>
         <v/>
       </c>
-      <c r="H39" s="43" t="n">
+      <c r="H39" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D39</f>
         <v>57.99</v>
       </c>
-      <c r="I39" s="43" t="n">
+      <c r="I39" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E39</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J39" s="43" t="n">
+      <c r="J39" s="11" t="n">
         <f aca="false">K39*1.1</f>
         <v>72.391</v>
       </c>
-      <c r="K39" s="43" t="n">
+      <c r="K39" s="11" t="n">
         <v>65.81</v>
       </c>
-      <c r="L39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N39" s="43" t="n">
+      <c r="L39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N39" s="11" t="n">
         <v>115.9</v>
       </c>
-      <c r="O39" s="43" t="n">
+      <c r="O39" s="11" t="n">
         <f aca="false">N39/1.1</f>
         <v>105.363636363636</v>
       </c>
-      <c r="P39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R39" s="43" t="n">
+      <c r="P39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R39" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S39" s="43" t="n">
+      <c r="S39" s="11" t="n">
         <f aca="false">R39/1.1</f>
         <v>31</v>
       </c>
-      <c r="T39" s="43" t="n">
+      <c r="T39" s="11" t="n">
         <v>61.04</v>
       </c>
-      <c r="U39" s="43" t="n">
+      <c r="U39" s="11" t="n">
         <f aca="false">T39/1.1</f>
         <v>55.4909090909091</v>
       </c>
-      <c r="V39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X39" s="43" t="n">
+      <c r="V39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X39" s="11" t="n">
         <v>124.21</v>
       </c>
-      <c r="Y39" s="43" t="n">
+      <c r="Y39" s="11" t="n">
         <f aca="false">X39/1.1</f>
         <v>112.918181818182</v>
       </c>
-      <c r="Z39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA39" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB39" s="43" t="n">
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="11" t="n">
         <f aca="false">IF(COUNT(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39)=0,"N/A",MIN(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39))</f>
         <v>31</v>
       </c>
-      <c r="AC39" s="45" t="n">
+      <c r="AC39" s="43" t="n">
         <f aca="false">IF(OR(D39="",AB39="",AB39="N/A"),"N/A",D39/AB39-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD39" s="45" t="str">
+      <c r="AD39" s="43" t="str">
         <f aca="false">IF(OR(F39="",AB39="",AB39="N/A"),"N/A",F39/AB39-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE39" s="42" t="s">
+      <c r="AE39" s="41" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="42" t="s">
+      <c r="C40" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="43" t="n">
+      <c r="D40" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F40</f>
         <v>13.07</v>
       </c>
-      <c r="E40" s="43" t="n">
+      <c r="E40" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G40</f>
         <v>14.377</v>
       </c>
-      <c r="F40" s="43" t="str">
+      <c r="F40" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H40="","",'RSEA vs Quoted Comparison'!H40)</f>
         <v/>
       </c>
-      <c r="G40" s="43" t="str">
+      <c r="G40" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I40="","",'RSEA vs Quoted Comparison'!I40)</f>
         <v/>
       </c>
-      <c r="H40" s="43" t="n">
+      <c r="H40" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D40</f>
         <v>57.99</v>
       </c>
-      <c r="I40" s="43" t="n">
+      <c r="I40" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E40</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J40" s="43" t="n">
+      <c r="J40" s="11" t="n">
         <f aca="false">K40*1.1</f>
         <v>72.391</v>
       </c>
-      <c r="K40" s="43" t="n">
+      <c r="K40" s="11" t="n">
         <v>65.81</v>
       </c>
-      <c r="L40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N40" s="43" t="n">
+      <c r="L40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N40" s="11" t="n">
         <v>115.9</v>
       </c>
-      <c r="O40" s="43" t="n">
+      <c r="O40" s="11" t="n">
         <f aca="false">N40/1.1</f>
         <v>105.363636363636</v>
       </c>
-      <c r="P40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R40" s="43" t="n">
+      <c r="P40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R40" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S40" s="43" t="n">
+      <c r="S40" s="11" t="n">
         <f aca="false">R40/1.1</f>
         <v>31</v>
       </c>
-      <c r="T40" s="43" t="n">
+      <c r="T40" s="11" t="n">
         <v>61.04</v>
       </c>
-      <c r="U40" s="43" t="n">
+      <c r="U40" s="11" t="n">
         <f aca="false">T40/1.1</f>
         <v>55.4909090909091</v>
       </c>
-      <c r="V40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X40" s="43" t="n">
+      <c r="V40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X40" s="11" t="n">
         <v>124.21</v>
       </c>
-      <c r="Y40" s="43" t="n">
+      <c r="Y40" s="11" t="n">
         <f aca="false">X40/1.1</f>
         <v>112.918181818182</v>
       </c>
-      <c r="Z40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA40" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB40" s="43" t="n">
+      <c r="Z40" s="42"/>
+      <c r="AA40" s="42"/>
+      <c r="AB40" s="11" t="n">
         <f aca="false">IF(COUNT(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40)=0,"N/A",MIN(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40))</f>
         <v>31</v>
       </c>
-      <c r="AC40" s="45" t="n">
+      <c r="AC40" s="43" t="n">
         <f aca="false">IF(OR(D40="",AB40="",AB40="N/A"),"N/A",D40/AB40-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD40" s="45" t="str">
+      <c r="AD40" s="43" t="str">
         <f aca="false">IF(OR(F40="",AB40="",AB40="N/A"),"N/A",F40/AB40-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE40" s="42" t="s">
+      <c r="AE40" s="41" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="41" t="s">
+      <c r="A41" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="43" t="n">
+      <c r="D41" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F41</f>
         <v>13.07</v>
       </c>
-      <c r="E41" s="43" t="n">
+      <c r="E41" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G41</f>
         <v>14.377</v>
       </c>
-      <c r="F41" s="43" t="str">
+      <c r="F41" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H41="","",'RSEA vs Quoted Comparison'!H41)</f>
         <v/>
       </c>
-      <c r="G41" s="43" t="str">
+      <c r="G41" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I41="","",'RSEA vs Quoted Comparison'!I41)</f>
         <v/>
       </c>
-      <c r="H41" s="43" t="n">
+      <c r="H41" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D41</f>
         <v>57.99</v>
       </c>
-      <c r="I41" s="43" t="n">
+      <c r="I41" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E41</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J41" s="43" t="n">
+      <c r="J41" s="11" t="n">
         <f aca="false">K41*1.1</f>
         <v>108.163</v>
       </c>
-      <c r="K41" s="43" t="n">
+      <c r="K41" s="11" t="n">
         <v>98.33</v>
       </c>
-      <c r="L41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P41" s="43" t="n">
+      <c r="L41" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M41" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O41" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P41" s="11" t="n">
         <v>96.1</v>
       </c>
-      <c r="Q41" s="43" t="n">
+      <c r="Q41" s="11" t="n">
         <v>87.36</v>
       </c>
-      <c r="R41" s="43" t="n">
+      <c r="R41" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S41" s="43" t="n">
+      <c r="S41" s="11" t="n">
         <f aca="false">R41/1.1</f>
         <v>31</v>
       </c>
-      <c r="T41" s="43" t="n">
+      <c r="T41" s="11" t="n">
         <v>59.26</v>
       </c>
-      <c r="U41" s="43" t="n">
+      <c r="U41" s="11" t="n">
         <f aca="false">T41/1.1</f>
         <v>53.8727272727273</v>
       </c>
-      <c r="V41" s="43" t="n">
+      <c r="V41" s="11" t="n">
         <f aca="false">W41*1.1</f>
         <v>85.745</v>
       </c>
-      <c r="W41" s="43" t="n">
+      <c r="W41" s="11" t="n">
         <v>77.95</v>
       </c>
-      <c r="X41" s="43" t="n">
+      <c r="X41" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y41" s="43" t="n">
+      <c r="Y41" s="11" t="n">
         <f aca="false">X41/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA41" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB41" s="43" t="n">
+      <c r="Z41" s="42"/>
+      <c r="AA41" s="42"/>
+      <c r="AB41" s="11" t="n">
         <f aca="false">IF(COUNT(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41)=0,"N/A",MIN(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41))</f>
         <v>31</v>
       </c>
-      <c r="AC41" s="45" t="n">
+      <c r="AC41" s="43" t="n">
         <f aca="false">IF(OR(D41="",AB41="",AB41="N/A"),"N/A",D41/AB41-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD41" s="45" t="str">
+      <c r="AD41" s="43" t="str">
         <f aca="false">IF(OR(F41="",AB41="",AB41="N/A"),"N/A",F41/AB41-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE41" s="42" t="s">
+      <c r="AE41" s="41" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D42" s="43" t="n">
+      <c r="D42" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F42</f>
         <v>13.07</v>
       </c>
-      <c r="E42" s="43" t="n">
+      <c r="E42" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G42</f>
         <v>14.377</v>
       </c>
-      <c r="F42" s="43" t="str">
+      <c r="F42" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H42="","",'RSEA vs Quoted Comparison'!H42)</f>
         <v/>
       </c>
-      <c r="G42" s="43" t="str">
+      <c r="G42" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I42="","",'RSEA vs Quoted Comparison'!I42)</f>
         <v/>
       </c>
-      <c r="H42" s="43" t="n">
+      <c r="H42" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D42</f>
         <v>57.99</v>
       </c>
-      <c r="I42" s="43" t="n">
+      <c r="I42" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E42</f>
         <v>52.7181818181818</v>
       </c>
-      <c r="J42" s="43" t="n">
+      <c r="J42" s="11" t="n">
         <f aca="false">K42*1.1</f>
         <v>108.163</v>
       </c>
-      <c r="K42" s="43" t="n">
+      <c r="K42" s="11" t="n">
         <v>98.33</v>
       </c>
-      <c r="L42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P42" s="43" t="n">
+      <c r="L42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P42" s="11" t="n">
         <v>96.1</v>
       </c>
-      <c r="Q42" s="43" t="n">
+      <c r="Q42" s="11" t="n">
         <v>87.36</v>
       </c>
-      <c r="R42" s="43" t="n">
+      <c r="R42" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="S42" s="43" t="n">
+      <c r="S42" s="11" t="n">
         <f aca="false">R42/1.1</f>
         <v>31</v>
       </c>
-      <c r="T42" s="43" t="n">
+      <c r="T42" s="11" t="n">
         <v>59.26</v>
       </c>
-      <c r="U42" s="43" t="n">
+      <c r="U42" s="11" t="n">
         <f aca="false">T42/1.1</f>
         <v>53.8727272727273</v>
       </c>
-      <c r="V42" s="43" t="n">
+      <c r="V42" s="11" t="n">
         <f aca="false">W42*1.1</f>
         <v>52.8</v>
       </c>
-      <c r="W42" s="43" t="n">
+      <c r="W42" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="X42" s="43" t="n">
+      <c r="X42" s="11" t="n">
         <v>53.22</v>
       </c>
-      <c r="Y42" s="43" t="n">
+      <c r="Y42" s="11" t="n">
         <f aca="false">X42/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA42" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB42" s="43" t="n">
+      <c r="Z42" s="42"/>
+      <c r="AA42" s="42"/>
+      <c r="AB42" s="11" t="n">
         <f aca="false">IF(COUNT(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42)=0,"N/A",MIN(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42))</f>
         <v>31</v>
       </c>
-      <c r="AC42" s="45" t="n">
+      <c r="AC42" s="43" t="n">
         <f aca="false">IF(OR(D42="",AB42="",AB42="N/A"),"N/A",D42/AB42-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD42" s="45" t="str">
+      <c r="AD42" s="43" t="str">
         <f aca="false">IF(OR(F42="",AB42="",AB42="N/A"),"N/A",F42/AB42-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE42" s="42" t="s">
+      <c r="AE42" s="41" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F43</f>
         <v>5.35</v>
       </c>
-      <c r="E43" s="43" t="n">
+      <c r="E43" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G43</f>
         <v>5.885</v>
       </c>
-      <c r="F43" s="43" t="str">
+      <c r="F43" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H43="","",'RSEA vs Quoted Comparison'!H43)</f>
         <v/>
       </c>
-      <c r="G43" s="43" t="str">
+      <c r="G43" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I43="","",'RSEA vs Quoted Comparison'!I43)</f>
         <v/>
       </c>
-      <c r="H43" s="43" t="n">
+      <c r="H43" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D43</f>
         <v>37.99</v>
       </c>
-      <c r="I43" s="43" t="n">
+      <c r="I43" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E43</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="J43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA43" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB43" s="43" t="n">
+      <c r="J43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y43" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z43" s="42"/>
+      <c r="AA43" s="42"/>
+      <c r="AB43" s="11" t="n">
         <f aca="false">IF(COUNT(I43,K43,M43,O43,Q43,S43,U43,W43,Y43,AA43)=0,"N/A",MIN(I43,K43,M43,O43,Q43,S43,U43,W43,Y43,AA43))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC43" s="45" t="n">
+      <c r="AC43" s="43" t="n">
         <f aca="false">IF(OR(D43="",AB43="",AB43="N/A"),"N/A",D43/AB43-1)</f>
         <v>-0.84509081337194</v>
       </c>
-      <c r="AD43" s="45" t="str">
+      <c r="AD43" s="43" t="str">
         <f aca="false">IF(OR(F43="",AB43="",AB43="N/A"),"N/A",F43/AB43-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE43" s="42" t="s">
+      <c r="AE43" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="43" t="n">
+      <c r="D44" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F44</f>
         <v>2.67</v>
       </c>
-      <c r="E44" s="43" t="n">
+      <c r="E44" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G44</f>
         <v>2.937</v>
       </c>
-      <c r="F44" s="43" t="str">
+      <c r="F44" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H44="","",'RSEA vs Quoted Comparison'!H44)</f>
         <v/>
       </c>
-      <c r="G44" s="43" t="str">
+      <c r="G44" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I44="","",'RSEA vs Quoted Comparison'!I44)</f>
         <v/>
       </c>
-      <c r="H44" s="43" t="n">
+      <c r="H44" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D44</f>
         <v>24.99</v>
       </c>
-      <c r="I44" s="43" t="n">
+      <c r="I44" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E44</f>
         <v>22.7181818181818</v>
       </c>
-      <c r="J44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L44" s="43" t="n">
+      <c r="J44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L44" s="11" t="n">
         <v>34.67</v>
       </c>
-      <c r="M44" s="43" t="n">
+      <c r="M44" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N44" s="43" t="n">
+      <c r="N44" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O44" s="43" t="n">
+      <c r="O44" s="11" t="n">
         <f aca="false">N44/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P44" s="43" t="n">
+      <c r="P44" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q44" s="43" t="n">
+      <c r="Q44" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T44" s="43" t="n">
+      <c r="R44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T44" s="11" t="n">
         <v>21.12</v>
       </c>
-      <c r="U44" s="43" t="n">
+      <c r="U44" s="11" t="n">
         <f aca="false">T44/1.1</f>
         <v>19.2</v>
       </c>
-      <c r="V44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W44" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X44" s="43" t="n">
+      <c r="V44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W44" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X44" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y44" s="43" t="n">
+      <c r="Y44" s="11" t="n">
         <f aca="false">X44/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z44" s="43" t="n">
+      <c r="Z44" s="11" t="n">
         <v>32.72</v>
       </c>
-      <c r="AA44" s="43" t="n">
+      <c r="AA44" s="11" t="n">
         <f aca="false">Z44/1.1</f>
         <v>29.7454545454545</v>
       </c>
-      <c r="AB44" s="43" t="n">
+      <c r="AB44" s="11" t="n">
         <f aca="false">IF(COUNT(I44,K44,M44,O44,Q44,S44,U44,W44,Y44,AA44)=0,"N/A",MIN(I44,K44,M44,O44,Q44,S44,U44,W44,Y44,AA44))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC44" s="45" t="n">
+      <c r="AC44" s="43" t="n">
         <f aca="false">IF(OR(D44="",AB44="",AB44="N/A"),"N/A",D44/AB44-1)</f>
         <v>-0.714577259475219</v>
       </c>
-      <c r="AD44" s="45" t="str">
+      <c r="AD44" s="43" t="str">
         <f aca="false">IF(OR(F44="",AB44="",AB44="N/A"),"N/A",F44/AB44-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE44" s="42" t="s">
+      <c r="AE44" s="41" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="43" t="n">
+      <c r="D45" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F45</f>
         <v>10.69</v>
       </c>
-      <c r="E45" s="43" t="n">
+      <c r="E45" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G45</f>
         <v>11.759</v>
       </c>
-      <c r="F45" s="43" t="str">
+      <c r="F45" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H45="","",'RSEA vs Quoted Comparison'!H45)</f>
         <v/>
       </c>
-      <c r="G45" s="43" t="str">
+      <c r="G45" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I45="","",'RSEA vs Quoted Comparison'!I45)</f>
         <v/>
       </c>
-      <c r="H45" s="43" t="n">
+      <c r="H45" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D45</f>
         <v>44.99</v>
       </c>
-      <c r="I45" s="43" t="n">
+      <c r="I45" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E45</f>
         <v>40.9</v>
       </c>
-      <c r="J45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L45" s="43" t="n">
+      <c r="J45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L45" s="11" t="n">
         <v>39.58</v>
       </c>
-      <c r="M45" s="43" t="n">
+      <c r="M45" s="11" t="n">
         <v>35.98</v>
       </c>
-      <c r="N45" s="43" t="n">
+      <c r="N45" s="11" t="n">
         <v>42.5</v>
       </c>
-      <c r="O45" s="43" t="n">
+      <c r="O45" s="11" t="n">
         <f aca="false">N45/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P45" s="43" t="n">
+      <c r="P45" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="Q45" s="43" t="n">
+      <c r="Q45" s="11" t="n">
         <v>46.36</v>
       </c>
-      <c r="R45" s="43" t="n">
+      <c r="R45" s="11" t="n">
         <v>25.75</v>
       </c>
-      <c r="S45" s="43" t="n">
+      <c r="S45" s="11" t="n">
         <f aca="false">R45/1.1</f>
         <v>23.4090909090909</v>
       </c>
-      <c r="T45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V45" s="43" t="n">
+      <c r="T45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V45" s="11" t="n">
         <f aca="false">W45*1.1</f>
         <v>29.15</v>
       </c>
-      <c r="W45" s="43" t="n">
+      <c r="W45" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="X45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA45" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB45" s="43" t="n">
+      <c r="X45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y45" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z45" s="42"/>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="11" t="n">
         <f aca="false">IF(COUNT(I45,K45,M45,O45,Q45,S45,U45,W45,Y45,AA45)=0,"N/A",MIN(I45,K45,M45,O45,Q45,S45,U45,W45,Y45,AA45))</f>
         <v>23.4090909090909</v>
       </c>
-      <c r="AC45" s="45" t="n">
+      <c r="AC45" s="43" t="n">
         <f aca="false">IF(OR(D45="",AB45="",AB45="N/A"),"N/A",D45/AB45-1)</f>
         <v>-0.543339805825243</v>
       </c>
-      <c r="AD45" s="45" t="str">
+      <c r="AD45" s="43" t="str">
         <f aca="false">IF(OR(F45="",AB45="",AB45="N/A"),"N/A",F45/AB45-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE45" s="42" t="s">
+      <c r="AE45" s="41" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="43" t="n">
+      <c r="D46" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F46</f>
         <v>2.67</v>
       </c>
-      <c r="E46" s="43" t="n">
+      <c r="E46" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G46</f>
         <v>2.937</v>
       </c>
-      <c r="F46" s="43" t="str">
+      <c r="F46" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H46="","",'RSEA vs Quoted Comparison'!H46)</f>
         <v/>
       </c>
-      <c r="G46" s="43" t="str">
+      <c r="G46" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I46="","",'RSEA vs Quoted Comparison'!I46)</f>
         <v/>
       </c>
-      <c r="H46" s="43" t="n">
+      <c r="H46" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D46</f>
         <v>24.99</v>
       </c>
-      <c r="I46" s="43" t="n">
+      <c r="I46" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E46</f>
         <v>22.7181818181818</v>
       </c>
-      <c r="J46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA46" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB46" s="43" t="n">
+      <c r="J46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y46" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z46" s="42"/>
+      <c r="AA46" s="42"/>
+      <c r="AB46" s="11" t="n">
         <f aca="false">IF(COUNT(I46,K46,M46,O46,Q46,S46,U46,W46,Y46,AA46)=0,"N/A",MIN(I46,K46,M46,O46,Q46,S46,U46,W46,Y46,AA46))</f>
         <v>22.7181818181818</v>
       </c>
-      <c r="AC46" s="45" t="n">
+      <c r="AC46" s="43" t="n">
         <f aca="false">IF(OR(D46="",AB46="",AB46="N/A"),"N/A",D46/AB46-1)</f>
         <v>-0.882472989195678</v>
       </c>
-      <c r="AD46" s="45" t="str">
+      <c r="AD46" s="43" t="str">
         <f aca="false">IF(OR(F46="",AB46="",AB46="N/A"),"N/A",F46/AB46-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE46" s="42" t="s">
+      <c r="AE46" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="43" t="n">
+      <c r="D47" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F47</f>
         <v>9.5</v>
       </c>
-      <c r="E47" s="43" t="n">
+      <c r="E47" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G47</f>
         <v>10.45</v>
       </c>
-      <c r="F47" s="43" t="str">
+      <c r="F47" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H47="","",'RSEA vs Quoted Comparison'!H47)</f>
         <v/>
       </c>
-      <c r="G47" s="43" t="str">
+      <c r="G47" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I47="","",'RSEA vs Quoted Comparison'!I47)</f>
         <v/>
       </c>
-      <c r="H47" s="43" t="n">
+      <c r="H47" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D47</f>
         <v>44.99</v>
       </c>
-      <c r="I47" s="43" t="n">
+      <c r="I47" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E47</f>
         <v>40.9</v>
       </c>
-      <c r="J47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA47" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB47" s="43" t="n">
+      <c r="J47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y47" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z47" s="42"/>
+      <c r="AA47" s="42"/>
+      <c r="AB47" s="11" t="n">
         <f aca="false">IF(COUNT(I47,K47,M47,O47,Q47,S47,U47,W47,Y47,AA47)=0,"N/A",MIN(I47,K47,M47,O47,Q47,S47,U47,W47,Y47,AA47))</f>
         <v>40.9</v>
       </c>
-      <c r="AC47" s="45" t="n">
+      <c r="AC47" s="43" t="n">
         <f aca="false">IF(OR(D47="",AB47="",AB47="N/A"),"N/A",D47/AB47-1)</f>
         <v>-0.767726161369193</v>
       </c>
-      <c r="AD47" s="45" t="str">
+      <c r="AD47" s="43" t="str">
         <f aca="false">IF(OR(F47="",AB47="",AB47="N/A"),"N/A",F47/AB47-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE47" s="42" t="s">
+      <c r="AE47" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B48" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="43" t="n">
+      <c r="D48" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F48</f>
         <v>10.69</v>
       </c>
-      <c r="E48" s="43" t="n">
+      <c r="E48" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G48</f>
         <v>11.759</v>
       </c>
-      <c r="F48" s="43" t="str">
+      <c r="F48" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H48="","",'RSEA vs Quoted Comparison'!H48)</f>
         <v/>
       </c>
-      <c r="G48" s="43" t="str">
+      <c r="G48" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I48="","",'RSEA vs Quoted Comparison'!I48)</f>
         <v/>
       </c>
-      <c r="H48" s="43" t="n">
+      <c r="H48" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D48</f>
         <v>44.99</v>
       </c>
-      <c r="I48" s="43" t="n">
+      <c r="I48" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E48</f>
         <v>40.9</v>
       </c>
-      <c r="J48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA48" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB48" s="43" t="n">
+      <c r="J48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="11" t="n">
         <f aca="false">IF(COUNT(I48,K48,M48,O48,Q48,S48,U48,W48,Y48,AA48)=0,"N/A",MIN(I48,K48,M48,O48,Q48,S48,U48,W48,Y48,AA48))</f>
         <v>40.9</v>
       </c>
-      <c r="AC48" s="45" t="n">
+      <c r="AC48" s="43" t="n">
         <f aca="false">IF(OR(D48="",AB48="",AB48="N/A"),"N/A",D48/AB48-1)</f>
         <v>-0.738630806845966</v>
       </c>
-      <c r="AD48" s="45" t="str">
+      <c r="AD48" s="43" t="str">
         <f aca="false">IF(OR(F48="",AB48="",AB48="N/A"),"N/A",F48/AB48-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE48" s="42" t="s">
+      <c r="AE48" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B49" s="41" t="s">
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D49" s="43" t="n">
+      <c r="D49" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F49</f>
         <v>5.35</v>
       </c>
-      <c r="E49" s="43" t="n">
+      <c r="E49" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G49</f>
         <v>5.885</v>
       </c>
-      <c r="F49" s="43" t="str">
+      <c r="F49" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H49="","",'RSEA vs Quoted Comparison'!H49)</f>
         <v/>
       </c>
-      <c r="G49" s="43" t="str">
+      <c r="G49" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I49="","",'RSEA vs Quoted Comparison'!I49)</f>
         <v/>
       </c>
-      <c r="H49" s="43" t="n">
+      <c r="H49" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D49</f>
         <v>32.99</v>
       </c>
-      <c r="I49" s="43" t="n">
+      <c r="I49" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E49</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L49" s="43" t="n">
+      <c r="J49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L49" s="11" t="n">
         <v>34.67</v>
       </c>
-      <c r="M49" s="43" t="n">
+      <c r="M49" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R49" s="43" t="n">
+      <c r="N49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R49" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="S49" s="43" t="n">
+      <c r="S49" s="11" t="n">
         <f aca="false">R49/1.1</f>
         <v>20.9090909090909</v>
       </c>
-      <c r="T49" s="43" t="n">
+      <c r="T49" s="11" t="n">
         <v>35.73</v>
       </c>
-      <c r="U49" s="43" t="n">
+      <c r="U49" s="11" t="n">
         <f aca="false">T49/1.1</f>
         <v>32.4818181818182</v>
       </c>
-      <c r="V49" s="43" t="n">
+      <c r="V49" s="11" t="n">
         <f aca="false">W49*1.1</f>
         <v>24.09</v>
       </c>
-      <c r="W49" s="43" t="n">
+      <c r="W49" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA49" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB49" s="43" t="n">
+      <c r="X49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y49" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z49" s="42"/>
+      <c r="AA49" s="42"/>
+      <c r="AB49" s="11" t="n">
         <f aca="false">IF(COUNT(I49,K49,M49,O49,Q49,S49,U49,W49,Y49,AA49)=0,"N/A",MIN(I49,K49,M49,O49,Q49,S49,U49,W49,Y49,AA49))</f>
         <v>20.9090909090909</v>
       </c>
-      <c r="AC49" s="45" t="n">
+      <c r="AC49" s="43" t="n">
         <f aca="false">IF(OR(D49="",AB49="",AB49="N/A"),"N/A",D49/AB49-1)</f>
         <v>-0.744130434782609</v>
       </c>
-      <c r="AD49" s="45" t="str">
+      <c r="AD49" s="43" t="str">
         <f aca="false">IF(OR(F49="",AB49="",AB49="N/A"),"N/A",F49/AB49-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE49" s="42" t="s">
+      <c r="AE49" s="41" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B50" s="41" t="s">
+      <c r="B50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="42" t="s">
+      <c r="C50" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="43" t="n">
+      <c r="D50" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F50</f>
         <v>5.35</v>
       </c>
-      <c r="E50" s="43" t="n">
+      <c r="E50" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G50</f>
         <v>5.885</v>
       </c>
-      <c r="F50" s="43" t="str">
+      <c r="F50" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H50="","",'RSEA vs Quoted Comparison'!H50)</f>
         <v/>
       </c>
-      <c r="G50" s="43" t="str">
+      <c r="G50" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I50="","",'RSEA vs Quoted Comparison'!I50)</f>
         <v/>
       </c>
-      <c r="H50" s="43" t="n">
+      <c r="H50" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D50</f>
         <v>49.99</v>
       </c>
-      <c r="I50" s="43" t="n">
+      <c r="I50" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E50</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J50" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K50" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L50" s="43" t="n">
+      <c r="J50" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K50" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L50" s="11" t="n">
         <v>34.67</v>
       </c>
-      <c r="M50" s="43" t="n">
+      <c r="M50" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N50" s="43" t="n">
+      <c r="N50" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="O50" s="43" t="n">
+      <c r="O50" s="11" t="n">
         <f aca="false">N50/1.1</f>
         <v>25.7272727272727</v>
       </c>
-      <c r="P50" s="43" t="n">
+      <c r="P50" s="11" t="n">
         <v>11.55</v>
       </c>
-      <c r="Q50" s="43" t="n">
+      <c r="Q50" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="R50" s="43" t="n">
+      <c r="R50" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="S50" s="43" t="n">
+      <c r="S50" s="11" t="n">
         <f aca="false">R50/1.1</f>
         <v>20.9090909090909</v>
       </c>
-      <c r="T50" s="43" t="n">
+      <c r="T50" s="11" t="n">
         <v>35.01</v>
       </c>
-      <c r="U50" s="43" t="n">
+      <c r="U50" s="11" t="n">
         <f aca="false">T50/1.1</f>
         <v>31.8272727272727</v>
       </c>
-      <c r="V50" s="43" t="n">
+      <c r="V50" s="11" t="n">
         <f aca="false">W50*1.1</f>
         <v>25.3</v>
       </c>
-      <c r="W50" s="43" t="n">
+      <c r="W50" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="X50" s="43" t="n">
+      <c r="X50" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y50" s="43" t="n">
+      <c r="Y50" s="11" t="n">
         <f aca="false">X50/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z50" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA50" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB50" s="43" t="n">
+      <c r="Z50" s="42"/>
+      <c r="AA50" s="42"/>
+      <c r="AB50" s="11" t="n">
         <f aca="false">IF(COUNT(I50,K50,M50,O50,Q50,S50,U50,W50,Y50,AA50)=0,"N/A",MIN(I50,K50,M50,O50,Q50,S50,U50,W50,Y50,AA50))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC50" s="45" t="n">
+      <c r="AC50" s="43" t="n">
         <f aca="false">IF(OR(D50="",AB50="",AB50="N/A"),"N/A",D50/AB50-1)</f>
         <v>-0.428085519922255</v>
       </c>
-      <c r="AD50" s="45" t="str">
+      <c r="AD50" s="43" t="str">
         <f aca="false">IF(OR(F50="",AB50="",AB50="N/A"),"N/A",F50/AB50-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE50" s="42" t="s">
+      <c r="AE50" s="41" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C51" s="42" t="s">
+      <c r="C51" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D51" s="43" t="n">
+      <c r="D51" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F51</f>
         <v>2.67</v>
       </c>
-      <c r="E51" s="43" t="n">
+      <c r="E51" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G51</f>
         <v>2.937</v>
       </c>
-      <c r="F51" s="43" t="str">
+      <c r="F51" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H51="","",'RSEA vs Quoted Comparison'!H51)</f>
         <v/>
       </c>
-      <c r="G51" s="43" t="str">
+      <c r="G51" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I51="","",'RSEA vs Quoted Comparison'!I51)</f>
         <v/>
       </c>
-      <c r="H51" s="43" t="n">
+      <c r="H51" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D51</f>
         <v>27.99</v>
       </c>
-      <c r="I51" s="43" t="n">
+      <c r="I51" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E51</f>
         <v>25.4454545454545</v>
       </c>
-      <c r="J51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA51" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB51" s="43" t="n">
+      <c r="J51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y51" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z51" s="42"/>
+      <c r="AA51" s="42"/>
+      <c r="AB51" s="11" t="n">
         <f aca="false">IF(COUNT(I51,K51,M51,O51,Q51,S51,U51,W51,Y51,AA51)=0,"N/A",MIN(I51,K51,M51,O51,Q51,S51,U51,W51,Y51,AA51))</f>
         <v>25.4454545454545</v>
       </c>
-      <c r="AC51" s="45" t="n">
+      <c r="AC51" s="43" t="n">
         <f aca="false">IF(OR(D51="",AB51="",AB51="N/A"),"N/A",D51/AB51-1)</f>
         <v>-0.895069667738478</v>
       </c>
-      <c r="AD51" s="45" t="str">
+      <c r="AD51" s="43" t="str">
         <f aca="false">IF(OR(F51="",AB51="",AB51="N/A"),"N/A",F51/AB51-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE51" s="42" t="s">
+      <c r="AE51" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="41" t="s">
+      <c r="A52" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B52" s="41" t="s">
+      <c r="B52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="42" t="s">
+      <c r="C52" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="43" t="n">
+      <c r="D52" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F52</f>
         <v>9.5</v>
       </c>
-      <c r="E52" s="43" t="n">
+      <c r="E52" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G52</f>
         <v>10.45</v>
       </c>
-      <c r="F52" s="43" t="str">
+      <c r="F52" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H52="","",'RSEA vs Quoted Comparison'!H52)</f>
         <v/>
       </c>
-      <c r="G52" s="43" t="str">
+      <c r="G52" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I52="","",'RSEA vs Quoted Comparison'!I52)</f>
         <v/>
       </c>
-      <c r="H52" s="43" t="n">
+      <c r="H52" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D52</f>
         <v>44.99</v>
       </c>
-      <c r="I52" s="43" t="n">
+      <c r="I52" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E52</f>
         <v>40.9</v>
       </c>
-      <c r="J52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA52" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB52" s="43" t="n">
+      <c r="J52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y52" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z52" s="42"/>
+      <c r="AA52" s="42"/>
+      <c r="AB52" s="11" t="n">
         <f aca="false">IF(COUNT(I52,K52,M52,O52,Q52,S52,U52,W52,Y52,AA52)=0,"N/A",MIN(I52,K52,M52,O52,Q52,S52,U52,W52,Y52,AA52))</f>
         <v>40.9</v>
       </c>
-      <c r="AC52" s="45" t="n">
+      <c r="AC52" s="43" t="n">
         <f aca="false">IF(OR(D52="",AB52="",AB52="N/A"),"N/A",D52/AB52-1)</f>
         <v>-0.767726161369193</v>
       </c>
-      <c r="AD52" s="45" t="str">
+      <c r="AD52" s="43" t="str">
         <f aca="false">IF(OR(F52="",AB52="",AB52="N/A"),"N/A",F52/AB52-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE52" s="42" t="s">
+      <c r="AE52" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="41" t="s">
+      <c r="A53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B53" s="41" t="s">
+      <c r="B53" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="42" t="s">
+      <c r="C53" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="43" t="n">
+      <c r="D53" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F53</f>
         <v>2</v>
       </c>
-      <c r="E53" s="43" t="n">
+      <c r="E53" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G53</f>
         <v>2.2</v>
       </c>
-      <c r="F53" s="43" t="str">
+      <c r="F53" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H53="","",'RSEA vs Quoted Comparison'!H53)</f>
         <v/>
       </c>
-      <c r="G53" s="43" t="str">
+      <c r="G53" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I53="","",'RSEA vs Quoted Comparison'!I53)</f>
         <v/>
       </c>
-      <c r="H53" s="43" t="n">
+      <c r="H53" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D53</f>
         <v>49.99</v>
       </c>
-      <c r="I53" s="43" t="n">
+      <c r="I53" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E53</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J53" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K53" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L53" s="43" t="n">
+      <c r="J53" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K53" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L53" s="11" t="n">
         <v>21.51</v>
       </c>
-      <c r="M53" s="43" t="n">
+      <c r="M53" s="11" t="n">
         <v>19.55</v>
       </c>
-      <c r="N53" s="43" t="n">
+      <c r="N53" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="O53" s="43" t="n">
+      <c r="O53" s="11" t="n">
         <f aca="false">N53/1.1</f>
         <v>7.81818181818182</v>
       </c>
-      <c r="P53" s="43" t="n">
+      <c r="P53" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="Q53" s="43" t="n">
+      <c r="Q53" s="11" t="n">
         <v>20.55</v>
       </c>
-      <c r="R53" s="43" t="n">
+      <c r="R53" s="11" t="n">
         <v>28.5</v>
       </c>
-      <c r="S53" s="43" t="n">
+      <c r="S53" s="11" t="n">
         <f aca="false">R53/1.1</f>
         <v>25.9090909090909</v>
       </c>
-      <c r="T53" s="43" t="n">
+      <c r="T53" s="11" t="n">
         <v>22.12</v>
       </c>
-      <c r="U53" s="43" t="n">
+      <c r="U53" s="11" t="n">
         <f aca="false">T53/1.1</f>
         <v>20.1090909090909</v>
       </c>
-      <c r="V53" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W53" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X53" s="43" t="n">
+      <c r="V53" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W53" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X53" s="11" t="n">
         <v>10.29</v>
       </c>
-      <c r="Y53" s="43" t="n">
+      <c r="Y53" s="11" t="n">
         <f aca="false">X53/1.1</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="Z53" s="43" t="n">
+      <c r="Z53" s="11" t="n">
         <v>61.33</v>
       </c>
-      <c r="AA53" s="43" t="n">
+      <c r="AA53" s="11" t="n">
         <f aca="false">Z53/1.1</f>
         <v>55.7545454545455</v>
       </c>
-      <c r="AB53" s="43" t="n">
+      <c r="AB53" s="11" t="n">
         <f aca="false">IF(COUNT(I53,K53,M53,O53,Q53,S53,U53,W53,Y53,AA53)=0,"N/A",MIN(I53,K53,M53,O53,Q53,S53,U53,W53,Y53,AA53))</f>
         <v>7.81818181818182</v>
       </c>
-      <c r="AC53" s="45" t="n">
+      <c r="AC53" s="43" t="n">
         <f aca="false">IF(OR(D53="",AB53="",AB53="N/A"),"N/A",D53/AB53-1)</f>
         <v>-0.744186046511628</v>
       </c>
-      <c r="AD53" s="45" t="str">
+      <c r="AD53" s="43" t="str">
         <f aca="false">IF(OR(F53="",AB53="",AB53="N/A"),"N/A",F53/AB53-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE53" s="42" t="s">
+      <c r="AE53" s="41" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="C54" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="43" t="n">
+      <c r="D54" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F54</f>
         <v>2.67</v>
       </c>
-      <c r="E54" s="43" t="n">
+      <c r="E54" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G54</f>
         <v>2.937</v>
       </c>
-      <c r="F54" s="43" t="str">
+      <c r="F54" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H54="","",'RSEA vs Quoted Comparison'!H54)</f>
         <v/>
       </c>
-      <c r="G54" s="43" t="str">
+      <c r="G54" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I54="","",'RSEA vs Quoted Comparison'!I54)</f>
         <v/>
       </c>
-      <c r="H54" s="43" t="n">
+      <c r="H54" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D54</f>
         <v>32.99</v>
       </c>
-      <c r="I54" s="43" t="n">
+      <c r="I54" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E54</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA54" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB54" s="43" t="n">
+      <c r="J54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y54" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z54" s="42"/>
+      <c r="AA54" s="42"/>
+      <c r="AB54" s="11" t="n">
         <f aca="false">IF(COUNT(I54,K54,M54,O54,Q54,S54,U54,W54,Y54,AA54)=0,"N/A",MIN(I54,K54,M54,O54,Q54,S54,U54,W54,Y54,AA54))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC54" s="45" t="n">
+      <c r="AC54" s="43" t="n">
         <f aca="false">IF(OR(D54="",AB54="",AB54="N/A"),"N/A",D54/AB54-1)</f>
         <v>-0.910973022127918</v>
       </c>
-      <c r="AD54" s="45" t="str">
+      <c r="AD54" s="43" t="str">
         <f aca="false">IF(OR(F54="",AB54="",AB54="N/A"),"N/A",F54/AB54-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE54" s="42" t="s">
+      <c r="AE54" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="41" t="s">
+      <c r="A55" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B55" s="41" t="s">
+      <c r="B55" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="42" t="s">
+      <c r="C55" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="43" t="n">
+      <c r="D55" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F55</f>
         <v>4.01</v>
       </c>
-      <c r="E55" s="43" t="n">
+      <c r="E55" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G55</f>
         <v>4.411</v>
       </c>
-      <c r="F55" s="43" t="str">
+      <c r="F55" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H55="","",'RSEA vs Quoted Comparison'!H55)</f>
         <v/>
       </c>
-      <c r="G55" s="43" t="str">
+      <c r="G55" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I55="","",'RSEA vs Quoted Comparison'!I55)</f>
         <v/>
       </c>
-      <c r="H55" s="43" t="n">
+      <c r="H55" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D55</f>
         <v>37.99</v>
       </c>
-      <c r="I55" s="43" t="n">
+      <c r="I55" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E55</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="J55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA55" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB55" s="43" t="n">
+      <c r="J55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y55" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z55" s="42"/>
+      <c r="AA55" s="42"/>
+      <c r="AB55" s="11" t="n">
         <f aca="false">IF(COUNT(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55)=0,"N/A",MIN(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC55" s="45" t="n">
+      <c r="AC55" s="43" t="n">
         <f aca="false">IF(OR(D55="",AB55="",AB55="N/A"),"N/A",D55/AB55-1)</f>
         <v>-0.883890497499342</v>
       </c>
-      <c r="AD55" s="45" t="str">
+      <c r="AD55" s="43" t="str">
         <f aca="false">IF(OR(F55="",AB55="",AB55="N/A"),"N/A",F55/AB55-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE55" s="42" t="s">
+      <c r="AE55" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C56" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D56" s="43" t="n">
+      <c r="D56" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F56</f>
         <v>10.69</v>
       </c>
-      <c r="E56" s="43" t="n">
+      <c r="E56" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G56</f>
         <v>11.759</v>
       </c>
-      <c r="F56" s="43" t="str">
+      <c r="F56" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H56="","",'RSEA vs Quoted Comparison'!H56)</f>
         <v/>
       </c>
-      <c r="G56" s="43" t="str">
+      <c r="G56" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I56="","",'RSEA vs Quoted Comparison'!I56)</f>
         <v/>
       </c>
-      <c r="H56" s="43" t="n">
+      <c r="H56" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D56</f>
         <v>37.99</v>
       </c>
-      <c r="I56" s="43" t="n">
+      <c r="I56" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E56</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="J56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA56" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB56" s="43" t="n">
+      <c r="J56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y56" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z56" s="42"/>
+      <c r="AA56" s="42"/>
+      <c r="AB56" s="11" t="n">
         <f aca="false">IF(COUNT(I56,K56,M56,O56,Q56,S56,U56,W56,Y56,AA56)=0,"N/A",MIN(I56,K56,M56,O56,Q56,S56,U56,W56,Y56,AA56))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC56" s="45" t="n">
+      <c r="AC56" s="43" t="n">
         <f aca="false">IF(OR(D56="",AB56="",AB56="N/A"),"N/A",D56/AB56-1)</f>
         <v>-0.690471176625428</v>
       </c>
-      <c r="AD56" s="45" t="str">
+      <c r="AD56" s="43" t="str">
         <f aca="false">IF(OR(F56="",AB56="",AB56="N/A"),"N/A",F56/AB56-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE56" s="42" t="s">
+      <c r="AE56" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C57" s="42" t="s">
+      <c r="C57" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D57" s="43" t="n">
+      <c r="D57" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F57</f>
         <v>10.69</v>
       </c>
-      <c r="E57" s="43" t="n">
+      <c r="E57" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G57</f>
         <v>11.759</v>
       </c>
-      <c r="F57" s="43" t="str">
+      <c r="F57" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H57="","",'RSEA vs Quoted Comparison'!H57)</f>
         <v/>
       </c>
-      <c r="G57" s="43" t="str">
+      <c r="G57" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I57="","",'RSEA vs Quoted Comparison'!I57)</f>
         <v/>
       </c>
-      <c r="H57" s="43" t="n">
+      <c r="H57" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D57</f>
         <v>37.99</v>
       </c>
-      <c r="I57" s="43" t="n">
+      <c r="I57" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E57</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="J57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA57" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB57" s="43" t="n">
+      <c r="J57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y57" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z57" s="42"/>
+      <c r="AA57" s="42"/>
+      <c r="AB57" s="11" t="n">
         <f aca="false">IF(COUNT(I57,K57,M57,O57,Q57,S57,U57,W57,Y57,AA57)=0,"N/A",MIN(I57,K57,M57,O57,Q57,S57,U57,W57,Y57,AA57))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC57" s="45" t="n">
+      <c r="AC57" s="43" t="n">
         <f aca="false">IF(OR(D57="",AB57="",AB57="N/A"),"N/A",D57/AB57-1)</f>
         <v>-0.690471176625428</v>
       </c>
-      <c r="AD57" s="45" t="str">
+      <c r="AD57" s="43" t="str">
         <f aca="false">IF(OR(F57="",AB57="",AB57="N/A"),"N/A",F57/AB57-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE57" s="42" t="s">
+      <c r="AE57" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B58" s="41" t="s">
+      <c r="B58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="42" t="s">
+      <c r="C58" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="43" t="n">
+      <c r="D58" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F58</f>
         <v>10.69</v>
       </c>
-      <c r="E58" s="43" t="n">
+      <c r="E58" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G58</f>
         <v>11.759</v>
       </c>
-      <c r="F58" s="43" t="str">
+      <c r="F58" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H58="","",'RSEA vs Quoted Comparison'!H58)</f>
         <v/>
       </c>
-      <c r="G58" s="43" t="str">
+      <c r="G58" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I58="","",'RSEA vs Quoted Comparison'!I58)</f>
         <v/>
       </c>
-      <c r="H58" s="43" t="n">
+      <c r="H58" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D58</f>
         <v>44.99</v>
       </c>
-      <c r="I58" s="43" t="n">
+      <c r="I58" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E58</f>
         <v>40.9</v>
       </c>
-      <c r="J58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA58" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB58" s="43" t="n">
+      <c r="J58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y58" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z58" s="42"/>
+      <c r="AA58" s="42"/>
+      <c r="AB58" s="11" t="n">
         <f aca="false">IF(COUNT(I58,K58,M58,O58,Q58,S58,U58,W58,Y58,AA58)=0,"N/A",MIN(I58,K58,M58,O58,Q58,S58,U58,W58,Y58,AA58))</f>
         <v>40.9</v>
       </c>
-      <c r="AC58" s="45" t="n">
+      <c r="AC58" s="43" t="n">
         <f aca="false">IF(OR(D58="",AB58="",AB58="N/A"),"N/A",D58/AB58-1)</f>
         <v>-0.738630806845966</v>
       </c>
-      <c r="AD58" s="45" t="str">
+      <c r="AD58" s="43" t="str">
         <f aca="false">IF(OR(F58="",AB58="",AB58="N/A"),"N/A",F58/AB58-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE58" s="42" t="s">
+      <c r="AE58" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B59" s="41" t="s">
+      <c r="B59" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="42" t="s">
+      <c r="C59" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="43" t="n">
+      <c r="D59" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F59</f>
         <v>2.89</v>
       </c>
-      <c r="E59" s="43" t="n">
+      <c r="E59" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G59</f>
         <v>3.179</v>
       </c>
-      <c r="F59" s="43" t="str">
+      <c r="F59" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H59="","",'RSEA vs Quoted Comparison'!H59)</f>
         <v/>
       </c>
-      <c r="G59" s="43" t="str">
+      <c r="G59" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I59="","",'RSEA vs Quoted Comparison'!I59)</f>
         <v/>
       </c>
-      <c r="H59" s="43" t="n">
+      <c r="H59" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D59</f>
         <v>32.99</v>
       </c>
-      <c r="I59" s="43" t="n">
+      <c r="I59" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E59</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA59" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB59" s="43" t="n">
+      <c r="J59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y59" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z59" s="42"/>
+      <c r="AA59" s="42"/>
+      <c r="AB59" s="11" t="n">
         <f aca="false">IF(COUNT(I59,K59,M59,O59,Q59,S59,U59,W59,Y59,AA59)=0,"N/A",MIN(I59,K59,M59,O59,Q59,S59,U59,W59,Y59,AA59))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC59" s="45" t="n">
+      <c r="AC59" s="43" t="n">
         <f aca="false">IF(OR(D59="",AB59="",AB59="N/A"),"N/A",D59/AB59-1)</f>
         <v>-0.903637465898757</v>
       </c>
-      <c r="AD59" s="45" t="str">
+      <c r="AD59" s="43" t="str">
         <f aca="false">IF(OR(F59="",AB59="",AB59="N/A"),"N/A",F59/AB59-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE59" s="42" t="s">
+      <c r="AE59" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B60" s="41" t="s">
+      <c r="B60" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="42" t="s">
+      <c r="C60" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="D60" s="43" t="n">
+      <c r="D60" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F60</f>
         <v>1.94</v>
       </c>
-      <c r="E60" s="43" t="n">
+      <c r="E60" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G60</f>
         <v>2.134</v>
       </c>
-      <c r="F60" s="43" t="str">
+      <c r="F60" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H60="","",'RSEA vs Quoted Comparison'!H60)</f>
         <v/>
       </c>
-      <c r="G60" s="43" t="str">
+      <c r="G60" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I60="","",'RSEA vs Quoted Comparison'!I60)</f>
         <v/>
       </c>
-      <c r="H60" s="43" t="n">
+      <c r="H60" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D60</f>
         <v>49.99</v>
       </c>
-      <c r="I60" s="43" t="n">
+      <c r="I60" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E60</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA60" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB60" s="43" t="n">
+      <c r="J60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y60" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z60" s="42"/>
+      <c r="AA60" s="42"/>
+      <c r="AB60" s="11" t="n">
         <f aca="false">IF(COUNT(I60,K60,M60,O60,Q60,S60,U60,W60,Y60,AA60)=0,"N/A",MIN(I60,K60,M60,O60,Q60,S60,U60,W60,Y60,AA60))</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="AC60" s="45" t="n">
+      <c r="AC60" s="43" t="n">
         <f aca="false">IF(OR(D60="",AB60="",AB60="N/A"),"N/A",D60/AB60-1)</f>
         <v>-0.957311462292458</v>
       </c>
-      <c r="AD60" s="45" t="str">
+      <c r="AD60" s="43" t="str">
         <f aca="false">IF(OR(F60="",AB60="",AB60="N/A"),"N/A",F60/AB60-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE60" s="42" t="s">
+      <c r="AE60" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="41" t="s">
+      <c r="A61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B61" s="41" t="s">
+      <c r="B61" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C61" s="42" t="s">
+      <c r="C61" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D61" s="43" t="n">
+      <c r="D61" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F61</f>
         <v>10.69</v>
       </c>
-      <c r="E61" s="43" t="n">
+      <c r="E61" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G61</f>
         <v>11.759</v>
       </c>
-      <c r="F61" s="43" t="str">
+      <c r="F61" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H61="","",'RSEA vs Quoted Comparison'!H61)</f>
         <v/>
       </c>
-      <c r="G61" s="43" t="str">
+      <c r="G61" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I61="","",'RSEA vs Quoted Comparison'!I61)</f>
         <v/>
       </c>
-      <c r="H61" s="43" t="n">
+      <c r="H61" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D61</f>
         <v>49.99</v>
       </c>
-      <c r="I61" s="43" t="n">
+      <c r="I61" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E61</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="J61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA61" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB61" s="43" t="n">
+      <c r="J61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y61" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z61" s="42"/>
+      <c r="AA61" s="42"/>
+      <c r="AB61" s="11" t="n">
         <f aca="false">IF(COUNT(I61,K61,M61,O61,Q61,S61,U61,W61,Y61,AA61)=0,"N/A",MIN(I61,K61,M61,O61,Q61,S61,U61,W61,Y61,AA61))</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="AC61" s="45" t="n">
+      <c r="AC61" s="43" t="n">
         <f aca="false">IF(OR(D61="",AB61="",AB61="N/A"),"N/A",D61/AB61-1)</f>
         <v>-0.764772954590918</v>
       </c>
-      <c r="AD61" s="45" t="str">
+      <c r="AD61" s="43" t="str">
         <f aca="false">IF(OR(F61="",AB61="",AB61="N/A"),"N/A",F61/AB61-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE61" s="42" t="s">
+      <c r="AE61" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B62" s="41" t="s">
+      <c r="B62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="42" t="s">
+      <c r="C62" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D62" s="43" t="n">
+      <c r="D62" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F62</f>
         <v>3.201</v>
       </c>
-      <c r="E62" s="43" t="n">
+      <c r="E62" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G62</f>
         <v>3.5211</v>
       </c>
-      <c r="F62" s="43" t="str">
+      <c r="F62" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H62="","",'RSEA vs Quoted Comparison'!H62)</f>
         <v/>
       </c>
-      <c r="G62" s="43" t="str">
+      <c r="G62" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I62="","",'RSEA vs Quoted Comparison'!I62)</f>
         <v/>
       </c>
-      <c r="H62" s="43" t="n">
+      <c r="H62" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D62</f>
         <v>32.99</v>
       </c>
-      <c r="I62" s="43" t="n">
+      <c r="I62" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E62</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA62" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB62" s="43" t="n">
+      <c r="J62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y62" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z62" s="42"/>
+      <c r="AA62" s="42"/>
+      <c r="AB62" s="11" t="n">
         <f aca="false">IF(COUNT(I62,K62,M62,O62,Q62,S62,U62,W62,Y62,AA62)=0,"N/A",MIN(I62,K62,M62,O62,Q62,S62,U62,W62,Y62,AA62))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC62" s="45" t="n">
+      <c r="AC62" s="43" t="n">
         <f aca="false">IF(OR(D62="",AB62="",AB62="N/A"),"N/A",D62/AB62-1)</f>
         <v>-0.893267656865717</v>
       </c>
-      <c r="AD62" s="45" t="str">
+      <c r="AD62" s="43" t="str">
         <f aca="false">IF(OR(F62="",AB62="",AB62="N/A"),"N/A",F62/AB62-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE62" s="42" t="s">
+      <c r="AE62" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="41" t="s">
+      <c r="A63" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="41" t="s">
+      <c r="B63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C63" s="42" t="s">
+      <c r="C63" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D63" s="43" t="n">
+      <c r="D63" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F63</f>
         <v>5.35</v>
       </c>
-      <c r="E63" s="43" t="n">
+      <c r="E63" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G63</f>
         <v>5.885</v>
       </c>
-      <c r="F63" s="43" t="str">
+      <c r="F63" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H63="","",'RSEA vs Quoted Comparison'!H63)</f>
         <v/>
       </c>
-      <c r="G63" s="43" t="str">
+      <c r="G63" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I63="","",'RSEA vs Quoted Comparison'!I63)</f>
         <v/>
       </c>
-      <c r="H63" s="43" t="n">
+      <c r="H63" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D63</f>
         <v>32.99</v>
       </c>
-      <c r="I63" s="43" t="n">
+      <c r="I63" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E63</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA63" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB63" s="43" t="n">
+      <c r="J63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y63" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z63" s="42"/>
+      <c r="AA63" s="42"/>
+      <c r="AB63" s="11" t="n">
         <f aca="false">IF(COUNT(I63,K63,M63,O63,Q63,S63,U63,W63,Y63,AA63)=0,"N/A",MIN(I63,K63,M63,O63,Q63,S63,U63,W63,Y63,AA63))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC63" s="45" t="n">
+      <c r="AC63" s="43" t="n">
         <f aca="false">IF(OR(D63="",AB63="",AB63="N/A"),"N/A",D63/AB63-1)</f>
         <v>-0.821612609881782</v>
       </c>
-      <c r="AD63" s="45" t="str">
+      <c r="AD63" s="43" t="str">
         <f aca="false">IF(OR(F63="",AB63="",AB63="N/A"),"N/A",F63/AB63-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE63" s="42" t="s">
+      <c r="AE63" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="41" t="s">
+      <c r="A64" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B64" s="41" t="s">
+      <c r="B64" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C64" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D64" s="43" t="n">
+      <c r="D64" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F64</f>
         <v>2.67</v>
       </c>
-      <c r="E64" s="43" t="n">
+      <c r="E64" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G64</f>
         <v>2.937</v>
       </c>
-      <c r="F64" s="43" t="str">
+      <c r="F64" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H64="","",'RSEA vs Quoted Comparison'!H64)</f>
         <v/>
       </c>
-      <c r="G64" s="43" t="str">
+      <c r="G64" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I64="","",'RSEA vs Quoted Comparison'!I64)</f>
         <v/>
       </c>
-      <c r="H64" s="43" t="n">
+      <c r="H64" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D64</f>
         <v>32.99</v>
       </c>
-      <c r="I64" s="43" t="n">
+      <c r="I64" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E64</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="O64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="P64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="S64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="T64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="V64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="W64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="X64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA64" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB64" s="43" t="n">
+      <c r="J64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="P64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="S64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="T64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="U64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="V64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="W64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="X64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y64" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z64" s="42"/>
+      <c r="AA64" s="42"/>
+      <c r="AB64" s="11" t="n">
         <f aca="false">IF(COUNT(I64,K64,M64,O64,Q64,S64,U64,W64,Y64,AA64)=0,"N/A",MIN(I64,K64,M64,O64,Q64,S64,U64,W64,Y64,AA64))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC64" s="45" t="n">
+      <c r="AC64" s="43" t="n">
         <f aca="false">IF(OR(D64="",AB64="",AB64="N/A"),"N/A",D64/AB64-1)</f>
         <v>-0.910973022127918</v>
       </c>
-      <c r="AD64" s="45" t="str">
+      <c r="AD64" s="43" t="str">
         <f aca="false">IF(OR(F64="",AB64="",AB64="N/A"),"N/A",F64/AB64-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE64" s="42" t="s">
+      <c r="AE64" s="41" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B65" s="41" t="s">
+      <c r="B65" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="42" t="s">
+      <c r="C65" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="43" t="n">
+      <c r="D65" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!F65</f>
         <v>10.69</v>
       </c>
-      <c r="E65" s="43" t="n">
+      <c r="E65" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!G65</f>
         <v>11.759</v>
       </c>
-      <c r="F65" s="43" t="str">
+      <c r="F65" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!H65="","",'RSEA vs Quoted Comparison'!H65)</f>
         <v/>
       </c>
-      <c r="G65" s="43" t="str">
+      <c r="G65" s="11" t="str">
         <f aca="false">IF('RSEA vs Quoted Comparison'!I65="","",'RSEA vs Quoted Comparison'!I65)</f>
         <v/>
       </c>
-      <c r="H65" s="43" t="n">
+      <c r="H65" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!D65</f>
         <v>32.99</v>
       </c>
-      <c r="I65" s="43" t="n">
+      <c r="I65" s="11" t="n">
         <f aca="false">'RSEA vs Quoted Comparison'!E65</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="J65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="L65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="M65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="N65" s="43" t="n">
+      <c r="J65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="N65" s="11" t="n">
         <v>108.6</v>
       </c>
-      <c r="O65" s="43" t="n">
+      <c r="O65" s="11" t="n">
         <f aca="false">N65/1.1</f>
         <v>98.7272727272727</v>
       </c>
-      <c r="P65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q65" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="R65" s="43" t="n">
+      <c r="P65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q65" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="R65" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="S65" s="43" t="n">
+      <c r="S65" s="11" t="n">
         <f aca="false">R65/1.1</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="T65" s="43" t="n">
+      <c r="T65" s="11" t="n">
         <v>33.19</v>
       </c>
-      <c r="U65" s="43" t="n">
+      <c r="U65" s="11" t="n">
         <f aca="false">T65/1.1</f>
         <v>30.1727272727273</v>
       </c>
-      <c r="V65" s="43" t="n">
+      <c r="V65" s="11" t="n">
         <f aca="false">W65*1.1</f>
         <v>40.15</v>
       </c>
-      <c r="W65" s="43" t="n">
+      <c r="W65" s="11" t="n">
         <v>36.5</v>
       </c>
-      <c r="X65" s="43" t="n">
+      <c r="X65" s="11" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="43" t="n">
+      <c r="Y65" s="11" t="n">
         <f aca="false">X65/1.1</f>
         <v>36.9</v>
       </c>
-      <c r="Z65" s="43" t="n">
+      <c r="Z65" s="11" t="n">
         <v>35.06</v>
       </c>
-      <c r="AA65" s="43" t="n">
+      <c r="AA65" s="11" t="n">
         <f aca="false">Z65/1.1</f>
         <v>31.8727272727273</v>
       </c>
-      <c r="AB65" s="43" t="n">
+      <c r="AB65" s="11" t="n">
         <f aca="false">IF(COUNT(I65,K65,M65,O65,Q65,S65,U65,W65,Y65,AA65)=0,"N/A",MIN(I65,K65,M65,O65,Q65,S65,U65,W65,Y65,AA65))</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="AC65" s="45" t="n">
+      <c r="AC65" s="43" t="n">
         <f aca="false">IF(OR(D65="",AB65="",AB65="N/A"),"N/A",D65/AB65-1)</f>
         <v>-0.608033333333333</v>
       </c>
-      <c r="AD65" s="45" t="str">
+      <c r="AD65" s="43" t="str">
         <f aca="false">IF(OR(F65="",AB65="",AB65="N/A"),"N/A",F65/AB65-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE65" s="42" t="s">
+      <c r="AE65" s="41" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="46" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="44" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="47"/>
-      <c r="D68" s="48" t="n">
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="45" t="n">
         <f aca="false">COUNTA(B6:B65)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="47" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="48" t="n">
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="45" t="n">
         <f aca="false">COUNTIF(K6:K65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(W6:W65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")</f>
         <v>222</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="47" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="48" t="n">
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="45" t="n">
         <f aca="false">COUNTIF(AC6:AC65,"&lt;0")</f>
         <v>53</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="47" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="48" t="n">
+      <c r="B71" s="35"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="45" t="n">
         <f aca="false">COUNTIF(AC6:AC65,"&gt;0")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="47" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="B72" s="47"/>
-      <c r="C72" s="47"/>
-      <c r="D72" s="49" t="n">
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="46" t="n">
         <f aca="false">AVERAGE(AC6:AC65)</f>
         <v>-0.502241855727076</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="47" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="B73" s="47"/>
-      <c r="C73" s="47"/>
-      <c r="D73" s="49" t="n">
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="46" t="n">
         <f aca="false">MEDIAN(AC6:AC65)</f>
         <v>-0.578387096774194</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="47" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="48" t="n">
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="45" t="n">
         <f aca="false">COUNTIF(AD6:AD65,"&lt;0")</f>
         <v>15</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="48" t="n">
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="45" t="n">
         <f aca="false">COUNTIF(AD6:AD65,"&gt;0")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="49" t="n">
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="46" t="n">
         <f aca="false">AVERAGE(AD6:AD65)</f>
         <v>-0.175684855421017</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="47" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
-      <c r="D77" s="49" t="n">
+      <c r="B77" s="35"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="46" t="n">
         <f aca="false">MEDIAN(AD6:AD65)</f>
         <v>-0.260605761397123</v>
       </c>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="310">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -1546,9 +1546,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>406800</xdr:colOff>
+      <xdr:colOff>406440</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>263160</xdr:rowOff>
+      <xdr:rowOff>262800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1562,7 +1562,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2194560" cy="2340720"/>
+          <a:ext cx="2194200" cy="2340360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9976,8 +9976,12 @@
       <c r="Y30" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="42"/>
+      <c r="Z30" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA30" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB30" s="11" t="n">
         <f aca="false">IF(COUNT(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30)=0,"N/A",MIN(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30))</f>
         <v>28</v>
@@ -10079,8 +10083,12 @@
         <f aca="false">X31/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z31" s="42"/>
-      <c r="AA31" s="42"/>
+      <c r="Z31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA31" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB31" s="11" t="n">
         <f aca="false">IF(COUNT(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31)=0,"N/A",MIN(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31))</f>
         <v>31</v>
@@ -10183,8 +10191,12 @@
       <c r="Y32" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="Z32" s="42"/>
-      <c r="AA32" s="42"/>
+      <c r="Z32" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA32" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB32" s="11" t="n">
         <f aca="false">IF(COUNT(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32)=0,"N/A",MIN(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32))</f>
         <v>31</v>
@@ -10287,8 +10299,12 @@
         <f aca="false">X33/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z33" s="42"/>
-      <c r="AA33" s="42"/>
+      <c r="Z33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA33" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB33" s="11" t="n">
         <f aca="false">IF(COUNT(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33)=0,"N/A",MIN(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33))</f>
         <v>31</v>
@@ -10392,8 +10408,12 @@
         <f aca="false">X34/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z34" s="42"/>
-      <c r="AA34" s="42"/>
+      <c r="Z34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA34" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB34" s="11" t="n">
         <f aca="false">IF(COUNT(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34)=0,"N/A",MIN(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34))</f>
         <v>31</v>
@@ -10497,8 +10517,12 @@
         <f aca="false">X35/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z35" s="42"/>
-      <c r="AA35" s="42"/>
+      <c r="Z35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA35" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB35" s="11" t="n">
         <f aca="false">IF(COUNT(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35)=0,"N/A",MIN(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35))</f>
         <v>31</v>
@@ -10603,8 +10627,12 @@
         <f aca="false">X36/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z36" s="42"/>
-      <c r="AA36" s="42"/>
+      <c r="Z36" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA36" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB36" s="11" t="n">
         <f aca="false">IF(COUNT(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36)=0,"N/A",MIN(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36))</f>
         <v>31</v>
@@ -10706,8 +10734,12 @@
       <c r="Y37" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="Z37" s="42"/>
-      <c r="AA37" s="42"/>
+      <c r="Z37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA37" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB37" s="11" t="n">
         <f aca="false">IF(COUNT(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37)=0,"N/A",MIN(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37))</f>
         <v>31</v>
@@ -10810,8 +10842,12 @@
         <f aca="false">X38/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z38" s="42"/>
-      <c r="AA38" s="42"/>
+      <c r="Z38" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA38" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB38" s="11" t="n">
         <f aca="false">IF(COUNT(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38)=0,"N/A",MIN(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38))</f>
         <v>31</v>
@@ -10915,8 +10951,12 @@
         <f aca="false">X39/1.1</f>
         <v>112.918181818182</v>
       </c>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
+      <c r="Z39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA39" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB39" s="11" t="n">
         <f aca="false">IF(COUNT(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39)=0,"N/A",MIN(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39))</f>
         <v>31</v>
@@ -11020,8 +11060,12 @@
         <f aca="false">X40/1.1</f>
         <v>112.918181818182</v>
       </c>
-      <c r="Z40" s="42"/>
-      <c r="AA40" s="42"/>
+      <c r="Z40" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA40" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB40" s="11" t="n">
         <f aca="false">IF(COUNT(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40)=0,"N/A",MIN(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40))</f>
         <v>31</v>
@@ -11125,8 +11169,12 @@
         <f aca="false">X41/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z41" s="42"/>
-      <c r="AA41" s="42"/>
+      <c r="Z41" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA41" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB41" s="11" t="n">
         <f aca="false">IF(COUNT(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41)=0,"N/A",MIN(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41))</f>
         <v>31</v>
@@ -11230,8 +11278,12 @@
         <f aca="false">X42/1.1</f>
         <v>48.3818181818182</v>
       </c>
-      <c r="Z42" s="42"/>
-      <c r="AA42" s="42"/>
+      <c r="Z42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA42" s="42" t="s">
+        <v>257</v>
+      </c>
       <c r="AB42" s="11" t="n">
         <f aca="false">IF(COUNT(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42)=0,"N/A",MIN(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42))</f>
         <v>31</v>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -15,6 +15,7 @@
     <sheet name="POLY ON WEBSITE" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="RSEA vs Quoted Comparison" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Market Comparison" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="337">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -806,11 +807,11 @@
   </si>
   <si>
     <t xml:space="preserve">Seton
-(inc GST, as shown)</t>
+(inc GST)</t>
   </si>
   <si>
     <t xml:space="preserve">Seton
-(ex GST, calc.)</t>
+(ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">Cheapest of RSEA +
@@ -956,6 +957,9 @@
     <t xml:space="preserve">Jaybro: 150x150, size differs from 225x225 | All Trades Group: 150x225, size differs | eSafety Supplies: 300x450, closest, '600x450 also stocked' | Safety Signs Australia: 225x225 poly EXACT, double-sided | SafetyXpress: range 21.11-23.12, 225x300 size differs slightly | Traffic Control Products: Only physical extinguisher unit stocked, not a wall sign | National Safety Signs: From, F1411, 225x225 not confirmed | Seton: MEDIUM conf, 225x225 poly EXACT, inc GST (55.75 ex)</t>
   </si>
   <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
     <t xml:space="preserve">All Trades Group: 900x600 corflute, size differs (larger) | Safety Signs Australia: 450x600 poly EXACT | SafetyXpress: 450x600 metal EXACT size, material differs | Traffic Control Products: 600x450, 'Danger Crane Working Overhead' - different wording, poly | National Safety Signs: From, D10279 | Seton: LOW conf, bulk tier range 33.21-36.91, 600x450 Flute</t>
   </si>
   <si>
@@ -987,13 +991,97 @@
   </si>
   <si>
     <t xml:space="preserve">Median of (our 1220-Stock quote ÷ cheapest − 1), ex GST — negative means our quote is cheaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary — Closest-Priced Competitor &amp; Where We're More Expensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each of our 60 line items: the competitor (or RSEA) whose ex-GST price is CLOSEST to our current quoted price (1200-stock, ex GST) — this can be either above or below ours — and the $ / % gap to that closest price. This is a different question from "cheapest": closest tells you who's most directly comparable to us in the market; cheapest (separately reported, see 'Items we're MORE EXPENSIVE on' below) tells you who undercuts us the most. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Quoted Price
+(ex GST, 1200 Stock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closest-Priced
+Competitor (or RSEA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their Price
+(ex GST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ Difference
+(Them − Us)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Difference
+(vs Our Price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are We More
+Expensive?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eSafety Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traffic Control Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Trades Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SafetyXpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Safety Signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety Signs Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Items We're MORE EXPENSIVE On (our 1200-Stock quote vs the single cheapest alternative — 7 of 60 items)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest Alternative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their Price (ex GST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Price (ex GST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ We're More Expensive By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% We're More Expensive By</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
@@ -1001,8 +1089,9 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
+    <numFmt numFmtId="171" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1111,6 +1200,52 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B7A4D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1225,7 +1360,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1414,6 +1549,50 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1452,7 +1631,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1463,7 +1642,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1B7A4D"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -12690,7 +12869,7 @@
         <v>257</v>
       </c>
       <c r="AA55" s="41" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="AB55" s="10" t="n">
         <f aca="false">IF(COUNT(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55)=0,"N/A",MIN(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55))</f>
@@ -13759,7 +13938,7 @@
         <v>N/A</v>
       </c>
       <c r="AE65" s="40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13769,7 +13948,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
@@ -13780,7 +13959,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
@@ -13791,7 +13970,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B70" s="34"/>
       <c r="C70" s="34"/>
@@ -13802,7 +13981,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -13813,7 +13992,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B72" s="34"/>
       <c r="C72" s="34"/>
@@ -13824,7 +14003,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B73" s="34"/>
       <c r="C73" s="34"/>
@@ -13835,7 +14014,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B74" s="34"/>
       <c r="C74" s="34"/>
@@ -13846,7 +14025,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B75" s="34"/>
       <c r="C75" s="34"/>
@@ -13857,7 +14036,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="34" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B76" s="34"/>
       <c r="C76" s="34"/>
@@ -13868,7 +14047,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B77" s="34"/>
       <c r="C77" s="34"/>
@@ -13901,4 +14080,2157 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J74"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="47" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+    </row>
+    <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+    </row>
+    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="51" t="n">
+        <f aca="false">'Market Comparison'!D6</f>
+        <v>16.71</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="F5" s="51" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="G5" s="52" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H5" s="53" t="n">
+        <v>0.199880311190904</v>
+      </c>
+      <c r="I5" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J5" s="40"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="51" t="n">
+        <f aca="false">'Market Comparison'!D7</f>
+        <v>66.83</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F6" s="51" t="n">
+        <v>122.718181818182</v>
+      </c>
+      <c r="G6" s="52" t="n">
+        <v>55.8881818181818</v>
+      </c>
+      <c r="H6" s="53" t="n">
+        <v>0.836273856324732</v>
+      </c>
+      <c r="I6" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="51" t="n">
+        <f aca="false">'Market Comparison'!D8</f>
+        <v>44.55</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="G7" s="52" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H7" s="53" t="n">
+        <v>1.89001122334456</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J7" s="40"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="51" t="n">
+        <f aca="false">'Market Comparison'!D9</f>
+        <v>44.55</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="F8" s="51" t="n">
+        <v>69.245</v>
+      </c>
+      <c r="G8" s="52" t="n">
+        <v>24.695</v>
+      </c>
+      <c r="H8" s="53" t="n">
+        <v>0.554320987654321</v>
+      </c>
+      <c r="I8" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J8" s="40"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="51" t="n">
+        <f aca="false">'Market Comparison'!D10</f>
+        <v>69.61</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" s="51" t="n">
+        <v>81.4</v>
+      </c>
+      <c r="G9" s="52" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H9" s="53" t="n">
+        <v>0.169372216635541</v>
+      </c>
+      <c r="I9" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J9" s="40"/>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="51" t="n">
+        <f aca="false">'Market Comparison'!D11</f>
+        <v>33.41</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <v>44.209</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>10.799</v>
+      </c>
+      <c r="H10" s="53" t="n">
+        <v>0.323226578868603</v>
+      </c>
+      <c r="I10" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J10" s="40"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="51" t="n">
+        <f aca="false">'Market Comparison'!D12</f>
+        <v>44.55</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="H11" s="53" t="n">
+        <v>0.579349046015713</v>
+      </c>
+      <c r="I11" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J11" s="40"/>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="51" t="n">
+        <f aca="false">'Market Comparison'!D13</f>
+        <v>33.41</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" s="51" t="n">
+        <v>33.1818181818182</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>-0.228181818181817</v>
+      </c>
+      <c r="H12" s="55" t="n">
+        <v>-0.00682974612935698</v>
+      </c>
+      <c r="I12" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J12" s="40"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="51" t="n">
+        <f aca="false">'Market Comparison'!D14</f>
+        <v>25.06</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="F13" s="51" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="H13" s="53" t="n">
+        <v>0.719473264166002</v>
+      </c>
+      <c r="I13" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J13" s="40"/>
+    </row>
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="51" t="n">
+        <f aca="false">'Market Comparison'!D15</f>
+        <v>8.35</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>21.6409090909091</v>
+      </c>
+      <c r="H14" s="53" t="n">
+        <v>2.59172563962983</v>
+      </c>
+      <c r="I14" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J14" s="40"/>
+    </row>
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="51" t="n">
+        <f aca="false">'Market Comparison'!D16</f>
+        <v>15.59</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15" s="51" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G15" s="52" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="H15" s="53" t="n">
+        <v>1.62347658755613</v>
+      </c>
+      <c r="I15" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J15" s="40"/>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="51" t="n">
+        <f aca="false">'Market Comparison'!D17</f>
+        <v>8.35</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>21.6409090909091</v>
+      </c>
+      <c r="H16" s="53" t="n">
+        <v>2.59172563962983</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="51" t="n">
+        <f aca="false">'Market Comparison'!D18</f>
+        <v>29.7</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <v>37.3909090909091</v>
+      </c>
+      <c r="G17" s="52" t="n">
+        <v>7.69090909090909</v>
+      </c>
+      <c r="H17" s="53" t="n">
+        <v>0.258953168044077</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J17" s="40"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="51" t="n">
+        <f aca="false">'Market Comparison'!D19</f>
+        <v>29.7</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>28.3545454545455</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>-1.34545454545455</v>
+      </c>
+      <c r="H18" s="55" t="n">
+        <v>-0.0453014998469545</v>
+      </c>
+      <c r="I18" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J18" s="40"/>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="51" t="n">
+        <f aca="false">'Market Comparison'!D20</f>
+        <v>16.71</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>23.3090909090909</v>
+      </c>
+      <c r="G19" s="52" t="n">
+        <v>6.59909090909091</v>
+      </c>
+      <c r="H19" s="53" t="n">
+        <v>0.394918666013819</v>
+      </c>
+      <c r="I19" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J19" s="40"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="51" t="n">
+        <f aca="false">'Market Comparison'!D21</f>
+        <v>33.41</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="H20" s="55" t="n">
+        <v>-0.132295719844358</v>
+      </c>
+      <c r="I20" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J20" s="40"/>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="51" t="n">
+        <f aca="false">'Market Comparison'!D22</f>
+        <v>11.81</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" s="51" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G21" s="52" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="H21" s="53" t="n">
+        <v>0.795088907705334</v>
+      </c>
+      <c r="I21" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="51" t="n">
+        <f aca="false">'Market Comparison'!D23</f>
+        <v>11.81</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F22" s="51" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="H22" s="53" t="n">
+        <v>0.795088907705334</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J22" s="40"/>
+    </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="51" t="n">
+        <f aca="false">'Market Comparison'!D24</f>
+        <v>5.9</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F23" s="51" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="G23" s="52" t="n">
+        <v>28.6363636363636</v>
+      </c>
+      <c r="H23" s="53" t="n">
+        <v>4.85362095531587</v>
+      </c>
+      <c r="I23" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="51" t="n">
+        <f aca="false">'Market Comparison'!D25</f>
+        <v>11.81</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>-2.45545454545455</v>
+      </c>
+      <c r="H24" s="55" t="n">
+        <v>-0.207913170656609</v>
+      </c>
+      <c r="I24" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="51" t="n">
+        <f aca="false">'Market Comparison'!D26</f>
+        <v>11.81</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F25" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>-2.45545454545455</v>
+      </c>
+      <c r="H25" s="55" t="n">
+        <v>-0.207913170656609</v>
+      </c>
+      <c r="I25" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J25" s="40"/>
+    </row>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="51" t="n">
+        <f aca="false">'Market Comparison'!D27</f>
+        <v>11.81</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F26" s="51" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G26" s="52" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="H26" s="53" t="n">
+        <v>0.795088907705334</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J26" s="40"/>
+    </row>
+    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="51" t="n">
+        <f aca="false">'Market Comparison'!D28</f>
+        <v>33.41</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="F27" s="51" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>-0.909999999999997</v>
+      </c>
+      <c r="H27" s="55" t="n">
+        <v>-0.027237354085603</v>
+      </c>
+      <c r="I27" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="J27" s="40"/>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="51" t="n">
+        <f aca="false">'Market Comparison'!D29</f>
+        <v>33.41</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>45</v>
+      </c>
+      <c r="G28" s="52" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="H28" s="53" t="n">
+        <v>0.346902125112242</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J28" s="40"/>
+    </row>
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="51" t="n">
+        <f aca="false">'Market Comparison'!D30</f>
+        <v>13.07</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="F29" s="51" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="H29" s="53" t="n">
+        <v>1.35654169854629</v>
+      </c>
+      <c r="I29" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J29" s="40"/>
+    </row>
+    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="51" t="n">
+        <f aca="false">'Market Comparison'!D31</f>
+        <v>13.07</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F30" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G30" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H30" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J30" s="40"/>
+    </row>
+    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="51" t="n">
+        <f aca="false">'Market Comparison'!D32</f>
+        <v>16.04</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F31" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G31" s="52" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H31" s="53" t="n">
+        <v>0.932668329177057</v>
+      </c>
+      <c r="I31" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J31" s="40"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="51" t="n">
+        <f aca="false">'Market Comparison'!D33</f>
+        <v>16.04</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F32" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G32" s="52" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H32" s="53" t="n">
+        <v>0.932668329177057</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J32" s="40"/>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="51" t="n">
+        <f aca="false">'Market Comparison'!D34</f>
+        <v>16.04</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F33" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G33" s="52" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H33" s="53" t="n">
+        <v>0.932668329177057</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J33" s="40"/>
+    </row>
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="51" t="n">
+        <f aca="false">'Market Comparison'!D35</f>
+        <v>16.04</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F34" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G34" s="52" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H34" s="53" t="n">
+        <v>0.932668329177057</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J34" s="40"/>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="51" t="n">
+        <f aca="false">'Market Comparison'!D36</f>
+        <v>13.07</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F35" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G35" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H35" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J35" s="40"/>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="51" t="n">
+        <f aca="false">'Market Comparison'!D37</f>
+        <v>16.04</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F36" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G36" s="52" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H36" s="53" t="n">
+        <v>0.932668329177057</v>
+      </c>
+      <c r="I36" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J36" s="40"/>
+    </row>
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="51" t="n">
+        <f aca="false">'Market Comparison'!D38</f>
+        <v>13.07</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F37" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G37" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H37" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J37" s="40"/>
+    </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="n">
+        <f aca="false">'Market Comparison'!D39</f>
+        <v>13.07</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F38" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G38" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H38" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J38" s="40"/>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="51" t="n">
+        <f aca="false">'Market Comparison'!D40</f>
+        <v>13.07</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F39" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G39" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H39" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J39" s="40"/>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="51" t="n">
+        <f aca="false">'Market Comparison'!D41</f>
+        <v>13.07</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F40" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G40" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H40" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I40" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J40" s="40"/>
+    </row>
+    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="51" t="n">
+        <f aca="false">'Market Comparison'!D42</f>
+        <v>13.07</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F41" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="G41" s="52" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H41" s="53" t="n">
+        <v>1.37184391736802</v>
+      </c>
+      <c r="I41" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J41" s="40"/>
+    </row>
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="51" t="n">
+        <f aca="false">'Market Comparison'!D43</f>
+        <v>5.35</v>
+      </c>
+      <c r="E42" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F42" s="51" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="G42" s="52" t="n">
+        <v>29.1863636363636</v>
+      </c>
+      <c r="H42" s="53" t="n">
+        <v>5.4553950722175</v>
+      </c>
+      <c r="I42" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J42" s="40"/>
+    </row>
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" s="51" t="n">
+        <f aca="false">'Market Comparison'!D44</f>
+        <v>2.67</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F43" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="G43" s="52" t="n">
+        <v>6.68454545454545</v>
+      </c>
+      <c r="H43" s="53" t="n">
+        <v>2.50357507660878</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J43" s="40"/>
+    </row>
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="51" t="n">
+        <f aca="false">'Market Comparison'!D45</f>
+        <v>10.69</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F44" s="51" t="n">
+        <v>23.4090909090909</v>
+      </c>
+      <c r="G44" s="52" t="n">
+        <v>12.7190909090909</v>
+      </c>
+      <c r="H44" s="53" t="n">
+        <v>1.18981205884854</v>
+      </c>
+      <c r="I44" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J44" s="40"/>
+    </row>
+    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="51" t="n">
+        <f aca="false">'Market Comparison'!D46</f>
+        <v>2.67</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F45" s="51" t="n">
+        <v>22.7181818181818</v>
+      </c>
+      <c r="G45" s="52" t="n">
+        <v>20.0481818181818</v>
+      </c>
+      <c r="H45" s="53" t="n">
+        <v>7.50868232890705</v>
+      </c>
+      <c r="I45" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J45" s="40"/>
+    </row>
+    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="51" t="n">
+        <f aca="false">'Market Comparison'!D47</f>
+        <v>9.5</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F46" s="51" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G46" s="52" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H46" s="53" t="n">
+        <v>3.30526315789474</v>
+      </c>
+      <c r="I46" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J46" s="40"/>
+    </row>
+    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="51" t="n">
+        <f aca="false">'Market Comparison'!D48</f>
+        <v>10.69</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F47" s="51" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G47" s="52" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="H47" s="53" t="n">
+        <v>2.82600561272217</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J47" s="40"/>
+    </row>
+    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="51" t="n">
+        <f aca="false">'Market Comparison'!D49</f>
+        <v>5.35</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F48" s="51" t="n">
+        <v>20.9090909090909</v>
+      </c>
+      <c r="G48" s="52" t="n">
+        <v>15.5590909090909</v>
+      </c>
+      <c r="H48" s="53" t="n">
+        <v>2.90824129141886</v>
+      </c>
+      <c r="I48" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J48" s="40"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B49" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="51" t="n">
+        <f aca="false">'Market Comparison'!D50</f>
+        <v>5.35</v>
+      </c>
+      <c r="E49" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F49" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="G49" s="52" t="n">
+        <v>4.00454545454545</v>
+      </c>
+      <c r="H49" s="53" t="n">
+        <v>0.748513169073917</v>
+      </c>
+      <c r="I49" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J49" s="40"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="51" t="n">
+        <f aca="false">'Market Comparison'!D51</f>
+        <v>2.67</v>
+      </c>
+      <c r="E50" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F50" s="51" t="n">
+        <v>25.4454545454545</v>
+      </c>
+      <c r="G50" s="52" t="n">
+        <v>22.7754545454545</v>
+      </c>
+      <c r="H50" s="53" t="n">
+        <v>8.53013278855975</v>
+      </c>
+      <c r="I50" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J50" s="40"/>
+    </row>
+    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="51" t="n">
+        <f aca="false">'Market Comparison'!D52</f>
+        <v>9.5</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F51" s="51" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G51" s="52" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H51" s="53" t="n">
+        <v>3.30526315789474</v>
+      </c>
+      <c r="I51" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J51" s="40"/>
+    </row>
+    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" s="51" t="n">
+        <f aca="false">'Market Comparison'!D53</f>
+        <v>2</v>
+      </c>
+      <c r="E52" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="F52" s="51" t="n">
+        <v>7.81818181818182</v>
+      </c>
+      <c r="G52" s="52" t="n">
+        <v>5.81818181818182</v>
+      </c>
+      <c r="H52" s="53" t="n">
+        <v>2.90909090909091</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J52" s="40"/>
+    </row>
+    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="51" t="n">
+        <f aca="false">'Market Comparison'!D54</f>
+        <v>2.67</v>
+      </c>
+      <c r="E53" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F53" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G53" s="52" t="n">
+        <v>27.3209090909091</v>
+      </c>
+      <c r="H53" s="53" t="n">
+        <v>10.2325502213143</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J53" s="40"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="51" t="n">
+        <f aca="false">'Market Comparison'!D55</f>
+        <v>4.01</v>
+      </c>
+      <c r="E54" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F54" s="51" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="G54" s="52" t="n">
+        <v>30.5263636363636</v>
+      </c>
+      <c r="H54" s="53" t="n">
+        <v>7.61255951031512</v>
+      </c>
+      <c r="I54" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J54" s="40"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" s="51" t="n">
+        <f aca="false">'Market Comparison'!D56</f>
+        <v>10.69</v>
+      </c>
+      <c r="E55" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F55" s="51" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="G55" s="52" t="n">
+        <v>23.8463636363636</v>
+      </c>
+      <c r="H55" s="53" t="n">
+        <v>2.23071689769538</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J55" s="40"/>
+    </row>
+    <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B56" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" s="51" t="n">
+        <f aca="false">'Market Comparison'!D57</f>
+        <v>10.69</v>
+      </c>
+      <c r="E56" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F56" s="51" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="G56" s="52" t="n">
+        <v>23.8463636363636</v>
+      </c>
+      <c r="H56" s="53" t="n">
+        <v>2.23071689769538</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J56" s="40"/>
+    </row>
+    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="51" t="n">
+        <f aca="false">'Market Comparison'!D58</f>
+        <v>10.69</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F57" s="51" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G57" s="52" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="H57" s="53" t="n">
+        <v>2.82600561272217</v>
+      </c>
+      <c r="I57" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J57" s="40"/>
+    </row>
+    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="51" t="n">
+        <f aca="false">'Market Comparison'!D59</f>
+        <v>2.89</v>
+      </c>
+      <c r="E58" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F58" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G58" s="52" t="n">
+        <v>27.1009090909091</v>
+      </c>
+      <c r="H58" s="53" t="n">
+        <v>9.37747719408619</v>
+      </c>
+      <c r="I58" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J58" s="40"/>
+    </row>
+    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B59" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" s="51" t="n">
+        <f aca="false">'Market Comparison'!D60</f>
+        <v>1.94</v>
+      </c>
+      <c r="E59" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F59" s="51" t="n">
+        <v>45.4454545454546</v>
+      </c>
+      <c r="G59" s="52" t="n">
+        <v>43.5054545454546</v>
+      </c>
+      <c r="H59" s="53" t="n">
+        <v>22.4254920337395</v>
+      </c>
+      <c r="I59" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J59" s="40"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B60" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" s="51" t="n">
+        <f aca="false">'Market Comparison'!D61</f>
+        <v>10.69</v>
+      </c>
+      <c r="E60" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="F60" s="51" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="G60" s="52" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="H60" s="53" t="n">
+        <v>3.07390084190833</v>
+      </c>
+      <c r="I60" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J60" s="40"/>
+    </row>
+    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D61" s="51" t="n">
+        <f aca="false">'Market Comparison'!D62</f>
+        <v>3.201</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F61" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G61" s="52" t="n">
+        <v>26.7899090909091</v>
+      </c>
+      <c r="H61" s="53" t="n">
+        <v>8.36923120615717</v>
+      </c>
+      <c r="I61" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J61" s="40"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B62" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="D62" s="51" t="n">
+        <f aca="false">'Market Comparison'!D63</f>
+        <v>5.35</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F62" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G62" s="52" t="n">
+        <v>24.6409090909091</v>
+      </c>
+      <c r="H62" s="53" t="n">
+        <v>4.60577740016992</v>
+      </c>
+      <c r="I62" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J62" s="40"/>
+    </row>
+    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B63" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" s="51" t="n">
+        <f aca="false">'Market Comparison'!D64</f>
+        <v>2.67</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F63" s="51" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="G63" s="52" t="n">
+        <v>27.3209090909091</v>
+      </c>
+      <c r="H63" s="53" t="n">
+        <v>10.2325502213143</v>
+      </c>
+      <c r="I63" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J63" s="40"/>
+    </row>
+    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" s="51" t="n">
+        <f aca="false">'Market Comparison'!D65</f>
+        <v>10.69</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F64" s="51" t="n">
+        <v>27.2727272727273</v>
+      </c>
+      <c r="G64" s="52" t="n">
+        <v>16.5827272727273</v>
+      </c>
+      <c r="H64" s="53" t="n">
+        <v>1.55123735011481</v>
+      </c>
+      <c r="I64" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J64" s="40"/>
+    </row>
+    <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+    </row>
+    <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="D68" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="E68" s="51" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="F68" s="52" t="n">
+        <v>7.35545454545455</v>
+      </c>
+      <c r="G68" s="53" t="n">
+        <v>0.440182797453893</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B69" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="D69" s="51" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E69" s="51" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="F69" s="52" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="G69" s="53" t="n">
+        <v>0.365459443280455</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="D70" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="E70" s="51" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="F70" s="52" t="n">
+        <v>2.45545454545455</v>
+      </c>
+      <c r="G70" s="53" t="n">
+        <v>0.207913170656609</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C71" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="D71" s="51" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="E71" s="51" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="F71" s="52" t="n">
+        <v>2.45545454545455</v>
+      </c>
+      <c r="G71" s="53" t="n">
+        <v>0.207913170656609</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72" s="51" t="n">
+        <v>28.3545454545455</v>
+      </c>
+      <c r="E72" s="51" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="F72" s="52" t="n">
+        <v>5.05545454545455</v>
+      </c>
+      <c r="G72" s="53" t="n">
+        <v>0.151315610459579</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C73" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="D73" s="51" t="n">
+        <v>28.3545454545455</v>
+      </c>
+      <c r="E73" s="51" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F73" s="52" t="n">
+        <v>1.34545454545455</v>
+      </c>
+      <c r="G73" s="53" t="n">
+        <v>0.0453014998469545</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="C74" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="D74" s="51" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E74" s="51" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="F74" s="52" t="n">
+        <v>0.909999999999997</v>
+      </c>
+      <c r="G74" s="53" t="n">
+        <v>0.027237354085603</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A66:J66"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="337">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -993,18 +993,18 @@
     <t xml:space="preserve">Median of (our 1220-Stock quote ÷ cheapest − 1), ex GST — negative means our quote is cheaper</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary — Closest-Priced Competitor &amp; Where We're More Expensive (1200 &amp; 1220 Stock)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each of our 60 line items: the competitor (or RSEA) whose ex-GST price is CLOSEST to our quoted price — this can be either above or below ours — shown separately for the 1200-stock and 1220-stock quoted prices, with the $ and % gap to that closest price. This is a different question from "cheapest": closest tells you who's most directly comparable to us in the market; cheapest (separately reported, see the two call-out sections below) tells you who undercuts us the most. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
+    <t xml:space="preserve">Summary — Closest-Priced Competitor &amp; Where We're More Expensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Our Quoted Price
-(ex GST, 1200 Stock)</t>
+(ex GST, higher of 1200/1220)</t>
   </si>
   <si>
     <t xml:space="preserve">Closest-Priced
-Competitor (1200)</t>
+Competitor (or RSEA)</t>
   </si>
   <si>
     <t xml:space="preserve">Their Price
@@ -1020,15 +1020,7 @@
   </si>
   <si>
     <t xml:space="preserve">Are We More
-Expensive? (1200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closest-Priced
-Competitor (1220)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Are We More
-Expensive? (1220)</t>
+Expensive?</t>
   </si>
   <si>
     <t xml:space="preserve">eSafety Supplies</t>
@@ -1040,9 +1032,6 @@
     <t xml:space="preserve">RSEA</t>
   </si>
   <si>
-    <t xml:space="preserve">N/A — no 1220 price</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seton</t>
   </si>
   <si>
@@ -1070,7 +1059,7 @@
     <t xml:space="preserve">Safety Signs Australia</t>
   </si>
   <si>
-    <t xml:space="preserve">Items We're MORE EXPENSIVE On — 1200 Stock (7 of 60 items)</t>
+    <t xml:space="preserve">Items We're MORE EXPENSIVE On (our higher-of-1200/1220 quote vs the single cheapest alternative — 7 of 60 items)</t>
   </si>
   <si>
     <t xml:space="preserve">Cheapest Alternative</t>
@@ -1086,9 +1075,6 @@
   </si>
   <si>
     <t xml:space="preserve">% We're More Expensive By</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Items We're MORE EXPENSIVE On — 1220 Stock (7 of 60 items)</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1090,7 @@
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1241,7 +1227,22 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF1F6FEB"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1262,7 +1263,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1290,13 +1291,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1373,7 +1380,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1582,15 +1589,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1602,12 +1605,48 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1664,7 +1703,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1686,7 +1725,7 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF1F6FEB"/>
       <rgbColor rgb="FF45B1E1"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
@@ -1718,9 +1757,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>405720</xdr:colOff>
+      <xdr:colOff>405360</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>262080</xdr:rowOff>
+      <xdr:rowOff>261720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1734,7 +1773,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2193480" cy="2339640"/>
+          <a:ext cx="2193120" cy="2339280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14104,23 +14143,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14136,12 +14170,6 @@
       <c r="H1" s="48"/>
       <c r="I1" s="48"/>
       <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="s">
@@ -14156,14 +14184,8 @@
       <c r="H2" s="49"/>
       <c r="I2" s="49"/>
       <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-    </row>
-    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
         <v>212</v>
       </c>
@@ -14192,24 +14214,6 @@
         <v>318</v>
       </c>
       <c r="J4" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="K4" s="50" t="s">
-        <v>319</v>
-      </c>
-      <c r="L4" s="50" t="s">
-        <v>315</v>
-      </c>
-      <c r="M4" s="50" t="s">
-        <v>316</v>
-      </c>
-      <c r="N4" s="50" t="s">
-        <v>317</v>
-      </c>
-      <c r="O4" s="50" t="s">
-        <v>320</v>
-      </c>
-      <c r="P4" s="50" t="s">
         <v>221</v>
       </c>
     </row>
@@ -14224,44 +14228,24 @@
         <v>8</v>
       </c>
       <c r="D5" s="52" t="n">
-        <f aca="false">'Market Comparison'!D6</f>
-        <v>16.71</v>
+        <v>16.93275</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F5" s="52" t="n">
+        <v>319</v>
+      </c>
+      <c r="F5" s="53" t="n">
         <v>20.05</v>
       </c>
-      <c r="G5" s="53" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>0.199880311190904</v>
+      <c r="G5" s="54" t="n">
+        <v>3.11725</v>
+      </c>
+      <c r="H5" s="55" t="n">
+        <v>0.184095908815757</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J5" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F6="","",'Market Comparison'!F6)</f>
-        <v>16.93275</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="L5" s="52" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="M5" s="53" t="n">
-        <v>3.11725</v>
-      </c>
-      <c r="N5" s="54" t="n">
-        <v>0.184095908815757</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P5" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
@@ -14273,45 +14257,25 @@
       <c r="C6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="52" t="n">
-        <f aca="false">'Market Comparison'!D7</f>
+      <c r="D6" s="56" t="n">
         <v>66.83</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F6" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F6" s="53" t="n">
         <v>122.718181818182</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="54" t="n">
         <v>55.888181818182</v>
       </c>
-      <c r="H6" s="54" t="n">
+      <c r="H6" s="55" t="n">
         <v>0.836273856324735</v>
       </c>
       <c r="I6" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J6" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F7="","",'Market Comparison'!F7)</f>
-        <v/>
-      </c>
-      <c r="K6" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O6" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P6" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J6" s="51"/>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
@@ -14323,45 +14287,25 @@
       <c r="C7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="52" t="n">
-        <f aca="false">'Market Comparison'!D8</f>
+      <c r="D7" s="56" t="n">
         <v>44.55</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" s="52" t="n">
+        <v>322</v>
+      </c>
+      <c r="F7" s="53" t="n">
         <v>128.75</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="54" t="n">
         <v>84.2</v>
       </c>
-      <c r="H7" s="54" t="n">
+      <c r="H7" s="55" t="n">
         <v>1.89001122334456</v>
       </c>
       <c r="I7" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J7" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F8="","",'Market Comparison'!F8)</f>
-        <v/>
-      </c>
-      <c r="K7" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L7" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P7" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J7" s="51"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
@@ -14374,44 +14318,24 @@
         <v>14</v>
       </c>
       <c r="D8" s="52" t="n">
-        <f aca="false">'Market Comparison'!D9</f>
-        <v>44.55</v>
+        <v>45.144</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" s="52" t="n">
+        <v>323</v>
+      </c>
+      <c r="F8" s="53" t="n">
         <v>69.245</v>
       </c>
-      <c r="G8" s="53" t="n">
-        <v>24.695</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>0.554320987654321</v>
+      <c r="G8" s="54" t="n">
+        <v>24.101</v>
+      </c>
+      <c r="H8" s="55" t="n">
+        <v>0.533869395711501</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J8" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F9="","",'Market Comparison'!F9)</f>
-        <v>45.144</v>
-      </c>
-      <c r="K8" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L8" s="52" t="n">
-        <v>69.245</v>
-      </c>
-      <c r="M8" s="53" t="n">
-        <v>24.101</v>
-      </c>
-      <c r="N8" s="54" t="n">
-        <v>0.533869395711501</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P8" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J8" s="51"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
@@ -14424,44 +14348,24 @@
         <v>16</v>
       </c>
       <c r="D9" s="52" t="n">
-        <f aca="false">'Market Comparison'!D10</f>
-        <v>69.61</v>
+        <v>70.538125</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="F9" s="52" t="n">
+        <v>323</v>
+      </c>
+      <c r="F9" s="53" t="n">
         <v>81.4</v>
       </c>
-      <c r="G9" s="53" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>0.169372216635541</v>
+      <c r="G9" s="54" t="n">
+        <v>10.861875</v>
+      </c>
+      <c r="H9" s="55" t="n">
+        <v>0.153985876432072</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J9" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F10="","",'Market Comparison'!F10)</f>
-        <v>70.538125</v>
-      </c>
-      <c r="K9" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L9" s="52" t="n">
-        <v>81.4</v>
-      </c>
-      <c r="M9" s="53" t="n">
-        <v>10.861875</v>
-      </c>
-      <c r="N9" s="54" t="n">
-        <v>0.153985876432072</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P9" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J9" s="51"/>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
@@ -14474,44 +14378,24 @@
         <v>18</v>
       </c>
       <c r="D10" s="52" t="n">
-        <f aca="false">'Market Comparison'!D11</f>
-        <v>33.41</v>
+        <v>33.8555</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="F10" s="52" t="n">
+        <v>324</v>
+      </c>
+      <c r="F10" s="53" t="n">
         <v>44.209</v>
       </c>
-      <c r="G10" s="53" t="n">
-        <v>10.799</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>0.323226578868603</v>
+      <c r="G10" s="54" t="n">
+        <v>10.3535</v>
+      </c>
+      <c r="H10" s="55" t="n">
+        <v>0.305814417155263</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J10" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F11="","",'Market Comparison'!F11)</f>
-        <v>33.8555</v>
-      </c>
-      <c r="K10" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="L10" s="52" t="n">
-        <v>44.209</v>
-      </c>
-      <c r="M10" s="53" t="n">
-        <v>10.3535</v>
-      </c>
-      <c r="N10" s="54" t="n">
-        <v>0.305814417155263</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P10" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
@@ -14524,94 +14408,54 @@
         <v>20</v>
       </c>
       <c r="D11" s="52" t="n">
-        <f aca="false">'Market Comparison'!D12</f>
-        <v>44.55</v>
+        <v>45.144</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F11" s="52" t="n">
+        <v>319</v>
+      </c>
+      <c r="F11" s="53" t="n">
         <v>70.36</v>
       </c>
-      <c r="G11" s="53" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="H11" s="54" t="n">
-        <v>0.579349046015713</v>
+      <c r="G11" s="54" t="n">
+        <v>25.216</v>
+      </c>
+      <c r="H11" s="55" t="n">
+        <v>0.558568137515506</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J11" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F12="","",'Market Comparison'!F12)</f>
-        <v>45.144</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="L11" s="52" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="M11" s="53" t="n">
-        <v>25.216</v>
-      </c>
-      <c r="N11" s="54" t="n">
-        <v>0.558568137515506</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P11" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J11" s="51"/>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="52" t="n">
-        <f aca="false">'Market Comparison'!D13</f>
-        <v>33.41</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="F12" s="52" t="n">
+      <c r="D12" s="59" t="n">
+        <v>33.8555</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" s="60" t="n">
         <v>33.1818181818182</v>
       </c>
-      <c r="G12" s="55" t="n">
-        <v>-0.228181818181795</v>
-      </c>
-      <c r="H12" s="56" t="n">
-        <v>-0.00682974612935634</v>
-      </c>
-      <c r="I12" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="J12" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F13="","",'Market Comparison'!F13)</f>
-        <v>33.8555</v>
-      </c>
-      <c r="K12" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="L12" s="52" t="n">
-        <v>33.1818181818182</v>
-      </c>
-      <c r="M12" s="55" t="n">
+      <c r="G12" s="61" t="n">
         <v>-0.673681818181798</v>
       </c>
-      <c r="N12" s="56" t="n">
+      <c r="H12" s="62" t="n">
         <v>-0.019898740771272</v>
       </c>
-      <c r="O12" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P12" s="41"/>
+      <c r="I12" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
@@ -14624,44 +14468,24 @@
         <v>82</v>
       </c>
       <c r="D13" s="52" t="n">
-        <f aca="false">'Market Comparison'!D14</f>
-        <v>25.06</v>
+        <v>25.394125</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F13" s="52" t="n">
+        <v>319</v>
+      </c>
+      <c r="F13" s="53" t="n">
         <v>43.09</v>
       </c>
-      <c r="G13" s="53" t="n">
-        <v>18.03</v>
-      </c>
-      <c r="H13" s="54" t="n">
-        <v>0.719473264166002</v>
+      <c r="G13" s="54" t="n">
+        <v>17.695875</v>
+      </c>
+      <c r="H13" s="55" t="n">
+        <v>0.696849172790951</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J13" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F14="","",'Market Comparison'!F14)</f>
-        <v>25.394125</v>
-      </c>
-      <c r="K13" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="L13" s="52" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="M13" s="53" t="n">
-        <v>17.695875</v>
-      </c>
-      <c r="N13" s="54" t="n">
-        <v>0.696849172790951</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P13" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
@@ -14674,44 +14498,24 @@
         <v>102</v>
       </c>
       <c r="D14" s="52" t="n">
-        <f aca="false">'Market Comparison'!D15</f>
-        <v>8.35</v>
+        <v>8.461375</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F14" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F14" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G14" s="53" t="n">
-        <v>21.6409090909091</v>
-      </c>
-      <c r="H14" s="54" t="n">
-        <v>2.59172563962983</v>
+      <c r="G14" s="54" t="n">
+        <v>21.5295340909091</v>
+      </c>
+      <c r="H14" s="55" t="n">
+        <v>2.54444863759248</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J14" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F15="","",'Market Comparison'!F15)</f>
-        <v>8.461375</v>
-      </c>
-      <c r="K14" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="L14" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="M14" s="53" t="n">
-        <v>21.5295340909091</v>
-      </c>
-      <c r="N14" s="54" t="n">
-        <v>2.54444863759248</v>
-      </c>
-      <c r="O14" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P14" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J14" s="51"/>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="51" t="s">
@@ -14724,44 +14528,24 @@
         <v>108</v>
       </c>
       <c r="D15" s="52" t="n">
-        <f aca="false">'Market Comparison'!D16</f>
-        <v>15.59</v>
+        <v>15.81275</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F15" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F15" s="53" t="n">
         <v>40.9</v>
       </c>
-      <c r="G15" s="53" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="H15" s="54" t="n">
-        <v>1.62347658755613</v>
+      <c r="G15" s="54" t="n">
+        <v>25.08725</v>
+      </c>
+      <c r="H15" s="55" t="n">
+        <v>1.58652037121943</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J15" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F16="","",'Market Comparison'!F16)</f>
-        <v>15.81275</v>
-      </c>
-      <c r="K15" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="L15" s="52" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="M15" s="53" t="n">
-        <v>25.08725</v>
-      </c>
-      <c r="N15" s="54" t="n">
-        <v>1.58652037121943</v>
-      </c>
-      <c r="O15" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P15" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J15" s="51"/>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
@@ -14774,44 +14558,24 @@
         <v>118</v>
       </c>
       <c r="D16" s="52" t="n">
-        <f aca="false">'Market Comparison'!D17</f>
-        <v>8.35</v>
+        <v>8.461375</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F16" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F16" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G16" s="53" t="n">
-        <v>21.6409090909091</v>
-      </c>
-      <c r="H16" s="54" t="n">
-        <v>2.59172563962983</v>
+      <c r="G16" s="54" t="n">
+        <v>21.5295340909091</v>
+      </c>
+      <c r="H16" s="55" t="n">
+        <v>2.54444863759248</v>
       </c>
       <c r="I16" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J16" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F17="","",'Market Comparison'!F17)</f>
-        <v>8.461375</v>
-      </c>
-      <c r="K16" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="L16" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="M16" s="53" t="n">
-        <v>21.5295340909091</v>
-      </c>
-      <c r="N16" s="54" t="n">
-        <v>2.54444863759248</v>
-      </c>
-      <c r="O16" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P16" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
@@ -14824,94 +14588,54 @@
         <v>128</v>
       </c>
       <c r="D17" s="52" t="n">
-        <f aca="false">'Market Comparison'!D18</f>
-        <v>29.7</v>
+        <v>30.1455</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F17" s="52" t="n">
+        <v>327</v>
+      </c>
+      <c r="F17" s="53" t="n">
         <v>37.3909090909091</v>
       </c>
-      <c r="G17" s="53" t="n">
-        <v>7.6909090909091</v>
-      </c>
-      <c r="H17" s="54" t="n">
-        <v>0.258953168044077</v>
+      <c r="G17" s="54" t="n">
+        <v>7.2454090909091</v>
+      </c>
+      <c r="H17" s="55" t="n">
+        <v>0.240347948811899</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J17" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F18="","",'Market Comparison'!F18)</f>
+        <v>320</v>
+      </c>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="59" t="n">
         <v>30.1455</v>
       </c>
-      <c r="K17" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="L17" s="52" t="n">
-        <v>37.3909090909091</v>
-      </c>
-      <c r="M17" s="53" t="n">
-        <v>7.2454090909091</v>
-      </c>
-      <c r="N17" s="54" t="n">
-        <v>0.240347948811899</v>
-      </c>
-      <c r="O17" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P17" s="41"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="52" t="n">
-        <f aca="false">'Market Comparison'!D19</f>
-        <v>29.7</v>
-      </c>
-      <c r="E18" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="52" t="n">
+      <c r="E18" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="G18" s="55" t="n">
-        <v>-1.3454545454545</v>
-      </c>
-      <c r="H18" s="56" t="n">
-        <v>-0.0453014998469528</v>
-      </c>
-      <c r="I18" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="J18" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F19="","",'Market Comparison'!F19)</f>
-        <v>30.1455</v>
-      </c>
-      <c r="K18" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="L18" s="52" t="n">
-        <v>28.3545454545455</v>
-      </c>
-      <c r="M18" s="55" t="n">
+      <c r="G18" s="61" t="n">
         <v>-1.7909545454545</v>
       </c>
-      <c r="N18" s="56" t="n">
+      <c r="H18" s="62" t="n">
         <v>-0.0594103446768007</v>
       </c>
-      <c r="O18" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P18" s="41"/>
+      <c r="I18" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="51" t="s">
@@ -14924,94 +14648,54 @@
         <v>138</v>
       </c>
       <c r="D19" s="52" t="n">
-        <f aca="false">'Market Comparison'!D20</f>
-        <v>16.71</v>
+        <v>16.93275</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F19" s="52" t="n">
+        <v>327</v>
+      </c>
+      <c r="F19" s="53" t="n">
         <v>23.3090909090909</v>
       </c>
-      <c r="G19" s="53" t="n">
-        <v>6.5990909090909</v>
-      </c>
-      <c r="H19" s="54" t="n">
-        <v>0.394918666013818</v>
+      <c r="G19" s="54" t="n">
+        <v>6.3763409090909</v>
+      </c>
+      <c r="H19" s="55" t="n">
+        <v>0.376568537838857</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J19" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F20="","",'Market Comparison'!F20)</f>
-        <v>16.93275</v>
-      </c>
-      <c r="K19" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="L19" s="52" t="n">
-        <v>23.3090909090909</v>
-      </c>
-      <c r="M19" s="53" t="n">
-        <v>6.3763409090909</v>
-      </c>
-      <c r="N19" s="54" t="n">
-        <v>0.376568537838857</v>
-      </c>
-      <c r="O19" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P19" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="52" t="n">
-        <f aca="false">'Market Comparison'!D21</f>
-        <v>33.41</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="F20" s="52" t="n">
+      <c r="D20" s="59" t="n">
+        <v>33.8555</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="F20" s="60" t="n">
         <v>28.99</v>
       </c>
-      <c r="G20" s="55" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="H20" s="56" t="n">
-        <v>-0.132295719844358</v>
-      </c>
-      <c r="I20" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="J20" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F21="","",'Market Comparison'!F21)</f>
-        <v>33.8555</v>
-      </c>
-      <c r="K20" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="L20" s="52" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="M20" s="55" t="n">
+      <c r="G20" s="61" t="n">
         <v>-4.8655</v>
       </c>
-      <c r="N20" s="56" t="n">
+      <c r="H20" s="62" t="n">
         <v>-0.14371372450562</v>
       </c>
-      <c r="O20" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P20" s="41"/>
+      <c r="I20" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="51" t="s">
@@ -15024,44 +14708,24 @@
         <v>148</v>
       </c>
       <c r="D21" s="52" t="n">
-        <f aca="false">'Market Comparison'!D22</f>
-        <v>11.81</v>
+        <v>12.03275</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F21" s="52" t="n">
+        <v>329</v>
+      </c>
+      <c r="F21" s="53" t="n">
         <v>21.2</v>
       </c>
-      <c r="G21" s="53" t="n">
-        <v>9.39</v>
-      </c>
-      <c r="H21" s="54" t="n">
-        <v>0.795088907705334</v>
+      <c r="G21" s="54" t="n">
+        <v>9.16725</v>
+      </c>
+      <c r="H21" s="55" t="n">
+        <v>0.761858261827097</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J21" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F22="","",'Market Comparison'!F22)</f>
-        <v>12.03275</v>
-      </c>
-      <c r="K21" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="L21" s="52" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M21" s="53" t="n">
-        <v>9.16725</v>
-      </c>
-      <c r="N21" s="54" t="n">
-        <v>0.761858261827097</v>
-      </c>
-      <c r="O21" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P21" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="51" t="s">
@@ -15074,44 +14738,24 @@
         <v>152</v>
       </c>
       <c r="D22" s="52" t="n">
-        <f aca="false">'Market Comparison'!D23</f>
-        <v>11.81</v>
+        <v>12.03275</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F22" s="52" t="n">
+        <v>329</v>
+      </c>
+      <c r="F22" s="53" t="n">
         <v>21.2</v>
       </c>
-      <c r="G22" s="53" t="n">
-        <v>9.39</v>
-      </c>
-      <c r="H22" s="54" t="n">
-        <v>0.795088907705334</v>
+      <c r="G22" s="54" t="n">
+        <v>9.16725</v>
+      </c>
+      <c r="H22" s="55" t="n">
+        <v>0.761858261827097</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J22" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F23="","",'Market Comparison'!F23)</f>
-        <v>12.03275</v>
-      </c>
-      <c r="K22" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="L22" s="52" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M22" s="53" t="n">
-        <v>9.16725</v>
-      </c>
-      <c r="N22" s="54" t="n">
-        <v>0.761858261827097</v>
-      </c>
-      <c r="O22" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P22" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="51" t="s">
@@ -15124,144 +14768,84 @@
         <v>154</v>
       </c>
       <c r="D23" s="52" t="n">
-        <f aca="false">'Market Comparison'!D24</f>
-        <v>5.9</v>
+        <v>6.011375</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F23" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F23" s="53" t="n">
         <v>34.5363636363636</v>
       </c>
-      <c r="G23" s="53" t="n">
-        <v>28.6363636363636</v>
-      </c>
-      <c r="H23" s="54" t="n">
-        <v>4.85362095531587</v>
+      <c r="G23" s="54" t="n">
+        <v>28.5249886363636</v>
+      </c>
+      <c r="H23" s="55" t="n">
+        <v>4.74516872368861</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J23" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F24="","",'Market Comparison'!F24)</f>
-        <v>6.011375</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="L23" s="52" t="n">
-        <v>34.5363636363636</v>
-      </c>
-      <c r="M23" s="53" t="n">
-        <v>28.5249886363636</v>
-      </c>
-      <c r="N23" s="54" t="n">
-        <v>4.74516872368861</v>
-      </c>
-      <c r="O23" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P23" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J23" s="51"/>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="52" t="n">
-        <f aca="false">'Market Comparison'!D25</f>
-        <v>11.81</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F24" s="52" t="n">
+      <c r="D24" s="59" t="n">
+        <v>12.03275</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="F24" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="G24" s="55" t="n">
-        <v>-2.45545454545455</v>
-      </c>
-      <c r="H24" s="56" t="n">
-        <v>-0.207913170656609</v>
-      </c>
-      <c r="I24" s="57" t="s">
+      <c r="G24" s="61" t="n">
+        <v>-2.67820454545455</v>
+      </c>
+      <c r="H24" s="62" t="n">
+        <v>-0.222576264399622</v>
+      </c>
+      <c r="I24" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J24" s="57"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="59" t="n">
+        <v>12.03275</v>
+      </c>
+      <c r="E25" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="J24" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F25="","",'Market Comparison'!F25)</f>
-        <v>12.03275</v>
-      </c>
-      <c r="K24" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="L24" s="52" t="n">
+      <c r="F25" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="M24" s="55" t="n">
+      <c r="G25" s="61" t="n">
         <v>-2.67820454545455</v>
       </c>
-      <c r="N24" s="56" t="n">
+      <c r="H25" s="62" t="n">
         <v>-0.222576264399622</v>
       </c>
-      <c r="O24" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P24" s="41"/>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="52" t="n">
-        <f aca="false">'Market Comparison'!D26</f>
-        <v>11.81</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F25" s="52" t="n">
-        <v>9.35454545454545</v>
-      </c>
-      <c r="G25" s="55" t="n">
-        <v>-2.45545454545455</v>
-      </c>
-      <c r="H25" s="56" t="n">
-        <v>-0.207913170656609</v>
-      </c>
-      <c r="I25" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="J25" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F26="","",'Market Comparison'!F26)</f>
-        <v>12.03275</v>
-      </c>
-      <c r="K25" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="L25" s="52" t="n">
-        <v>9.35454545454545</v>
-      </c>
-      <c r="M25" s="55" t="n">
-        <v>-2.67820454545455</v>
-      </c>
-      <c r="N25" s="56" t="n">
-        <v>-0.222576264399622</v>
-      </c>
-      <c r="O25" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P25" s="41"/>
+      <c r="I25" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J25" s="57"/>
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
@@ -15274,94 +14858,54 @@
         <v>173</v>
       </c>
       <c r="D26" s="52" t="n">
-        <f aca="false">'Market Comparison'!D27</f>
-        <v>11.81</v>
+        <v>12.03275</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F26" s="52" t="n">
+        <v>329</v>
+      </c>
+      <c r="F26" s="53" t="n">
         <v>21.2</v>
       </c>
-      <c r="G26" s="53" t="n">
-        <v>9.39</v>
-      </c>
-      <c r="H26" s="54" t="n">
-        <v>0.795088907705334</v>
+      <c r="G26" s="54" t="n">
+        <v>9.16725</v>
+      </c>
+      <c r="H26" s="55" t="n">
+        <v>0.761858261827097</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J26" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F27="","",'Market Comparison'!F27)</f>
-        <v>12.03275</v>
-      </c>
-      <c r="K26" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="L26" s="52" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M26" s="53" t="n">
-        <v>9.16725</v>
-      </c>
-      <c r="N26" s="54" t="n">
-        <v>0.761858261827097</v>
-      </c>
-      <c r="O26" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P26" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J26" s="51"/>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="52" t="n">
-        <f aca="false">'Market Comparison'!D28</f>
-        <v>33.41</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="F27" s="52" t="n">
+      <c r="D27" s="59" t="n">
+        <v>33.8555</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="F27" s="60" t="n">
         <v>32.5</v>
       </c>
-      <c r="G27" s="55" t="n">
-        <v>-0.909999999999997</v>
-      </c>
-      <c r="H27" s="56" t="n">
-        <v>-0.027237354085603</v>
-      </c>
-      <c r="I27" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="J27" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F28="","",'Market Comparison'!F28)</f>
-        <v>33.8555</v>
-      </c>
-      <c r="K27" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="L27" s="52" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M27" s="55" t="n">
+      <c r="G27" s="61" t="n">
         <v>-1.3555</v>
       </c>
-      <c r="N27" s="56" t="n">
+      <c r="H27" s="62" t="n">
         <v>-0.0400378077417258</v>
       </c>
-      <c r="O27" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="P27" s="41"/>
+      <c r="I27" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="51" t="s">
@@ -15374,44 +14918,24 @@
         <v>175</v>
       </c>
       <c r="D28" s="52" t="n">
-        <f aca="false">'Market Comparison'!D29</f>
-        <v>33.41</v>
+        <v>33.8555</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="F28" s="52" t="n">
+        <v>325</v>
+      </c>
+      <c r="F28" s="53" t="n">
         <v>45</v>
       </c>
-      <c r="G28" s="53" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="H28" s="54" t="n">
-        <v>0.346902125112242</v>
+      <c r="G28" s="54" t="n">
+        <v>11.1445</v>
+      </c>
+      <c r="H28" s="55" t="n">
+        <v>0.329178420049918</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J28" s="52" t="n">
-        <f aca="false">IF('Market Comparison'!F29="","",'Market Comparison'!F29)</f>
-        <v>33.8555</v>
-      </c>
-      <c r="K28" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="L28" s="52" t="n">
-        <v>45</v>
-      </c>
-      <c r="M28" s="53" t="n">
-        <v>11.1445</v>
-      </c>
-      <c r="N28" s="54" t="n">
-        <v>0.329178420049918</v>
-      </c>
-      <c r="O28" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="P28" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J28" s="51"/>
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="51" t="s">
@@ -15423,45 +14947,25 @@
       <c r="C29" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="52" t="n">
-        <f aca="false">'Market Comparison'!D30</f>
+      <c r="D29" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="F29" s="52" t="n">
+        <v>323</v>
+      </c>
+      <c r="F29" s="53" t="n">
         <v>30.8</v>
       </c>
-      <c r="G29" s="53" t="n">
+      <c r="G29" s="54" t="n">
         <v>17.73</v>
       </c>
-      <c r="H29" s="54" t="n">
+      <c r="H29" s="55" t="n">
         <v>1.35654169854629</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J29" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F30="","",'Market Comparison'!F30)</f>
-        <v/>
-      </c>
-      <c r="K29" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L29" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M29" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N29" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O29" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P29" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J29" s="51"/>
     </row>
     <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="51" t="s">
@@ -15473,45 +14977,25 @@
       <c r="C30" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="52" t="n">
-        <f aca="false">'Market Comparison'!D31</f>
+      <c r="D30" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F30" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F30" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G30" s="53" t="n">
+      <c r="G30" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H30" s="54" t="n">
+      <c r="H30" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J30" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F31="","",'Market Comparison'!F31)</f>
-        <v/>
-      </c>
-      <c r="K30" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L30" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M30" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N30" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O30" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P30" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J30" s="51"/>
     </row>
     <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="51" t="s">
@@ -15523,45 +15007,25 @@
       <c r="C31" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="52" t="n">
-        <f aca="false">'Market Comparison'!D32</f>
+      <c r="D31" s="56" t="n">
         <v>16.04</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F31" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F31" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G31" s="53" t="n">
+      <c r="G31" s="54" t="n">
         <v>14.96</v>
       </c>
-      <c r="H31" s="54" t="n">
+      <c r="H31" s="55" t="n">
         <v>0.932668329177057</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J31" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F32="","",'Market Comparison'!F32)</f>
-        <v/>
-      </c>
-      <c r="K31" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L31" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M31" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N31" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O31" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P31" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J31" s="51"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="51" t="s">
@@ -15573,45 +15037,25 @@
       <c r="C32" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="52" t="n">
-        <f aca="false">'Market Comparison'!D33</f>
+      <c r="D32" s="56" t="n">
         <v>16.04</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F32" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F32" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G32" s="53" t="n">
+      <c r="G32" s="54" t="n">
         <v>14.96</v>
       </c>
-      <c r="H32" s="54" t="n">
+      <c r="H32" s="55" t="n">
         <v>0.932668329177057</v>
       </c>
       <c r="I32" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J32" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F33="","",'Market Comparison'!F33)</f>
-        <v/>
-      </c>
-      <c r="K32" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L32" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M32" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N32" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O32" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P32" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J32" s="51"/>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="51" t="s">
@@ -15623,45 +15067,25 @@
       <c r="C33" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="52" t="n">
-        <f aca="false">'Market Comparison'!D34</f>
+      <c r="D33" s="56" t="n">
         <v>16.04</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F33" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F33" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G33" s="53" t="n">
+      <c r="G33" s="54" t="n">
         <v>14.96</v>
       </c>
-      <c r="H33" s="54" t="n">
+      <c r="H33" s="55" t="n">
         <v>0.932668329177057</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J33" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F34="","",'Market Comparison'!F34)</f>
-        <v/>
-      </c>
-      <c r="K33" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L33" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M33" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N33" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O33" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P33" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J33" s="51"/>
     </row>
     <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="51" t="s">
@@ -15673,45 +15097,25 @@
       <c r="C34" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="52" t="n">
-        <f aca="false">'Market Comparison'!D35</f>
+      <c r="D34" s="56" t="n">
         <v>16.04</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F34" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F34" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G34" s="53" t="n">
+      <c r="G34" s="54" t="n">
         <v>14.96</v>
       </c>
-      <c r="H34" s="54" t="n">
+      <c r="H34" s="55" t="n">
         <v>0.932668329177057</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J34" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F35="","",'Market Comparison'!F35)</f>
-        <v/>
-      </c>
-      <c r="K34" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L34" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M34" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N34" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O34" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P34" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J34" s="51"/>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
@@ -15723,45 +15127,25 @@
       <c r="C35" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="52" t="n">
-        <f aca="false">'Market Comparison'!D36</f>
+      <c r="D35" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F35" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F35" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G35" s="53" t="n">
+      <c r="G35" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H35" s="54" t="n">
+      <c r="H35" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J35" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F36="","",'Market Comparison'!F36)</f>
-        <v/>
-      </c>
-      <c r="K35" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L35" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M35" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N35" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O35" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P35" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J35" s="51"/>
     </row>
     <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="51" t="s">
@@ -15773,45 +15157,25 @@
       <c r="C36" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="52" t="n">
-        <f aca="false">'Market Comparison'!D37</f>
+      <c r="D36" s="56" t="n">
         <v>16.04</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F36" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F36" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G36" s="53" t="n">
+      <c r="G36" s="54" t="n">
         <v>14.96</v>
       </c>
-      <c r="H36" s="54" t="n">
+      <c r="H36" s="55" t="n">
         <v>0.932668329177057</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J36" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F37="","",'Market Comparison'!F37)</f>
-        <v/>
-      </c>
-      <c r="K36" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L36" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M36" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N36" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O36" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P36" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J36" s="51"/>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="51" t="s">
@@ -15823,45 +15187,25 @@
       <c r="C37" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="52" t="n">
-        <f aca="false">'Market Comparison'!D38</f>
+      <c r="D37" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F37" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F37" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G37" s="53" t="n">
+      <c r="G37" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H37" s="54" t="n">
+      <c r="H37" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J37" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F38="","",'Market Comparison'!F38)</f>
-        <v/>
-      </c>
-      <c r="K37" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L37" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M37" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N37" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O37" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P37" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J37" s="51"/>
     </row>
     <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="51" t="s">
@@ -15873,45 +15217,25 @@
       <c r="C38" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="52" t="n">
-        <f aca="false">'Market Comparison'!D39</f>
+      <c r="D38" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F38" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F38" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G38" s="53" t="n">
+      <c r="G38" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H38" s="54" t="n">
+      <c r="H38" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I38" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J38" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F39="","",'Market Comparison'!F39)</f>
-        <v/>
-      </c>
-      <c r="K38" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L38" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M38" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N38" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O38" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P38" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J38" s="51"/>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="51" t="s">
@@ -15923,45 +15247,25 @@
       <c r="C39" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="52" t="n">
-        <f aca="false">'Market Comparison'!D40</f>
+      <c r="D39" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F39" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F39" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G39" s="53" t="n">
+      <c r="G39" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H39" s="54" t="n">
+      <c r="H39" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J39" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F40="","",'Market Comparison'!F40)</f>
-        <v/>
-      </c>
-      <c r="K39" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L39" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M39" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N39" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O39" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P39" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J39" s="51"/>
     </row>
     <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="51" t="s">
@@ -15973,45 +15277,25 @@
       <c r="C40" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="52" t="n">
-        <f aca="false">'Market Comparison'!D41</f>
+      <c r="D40" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F40" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F40" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G40" s="53" t="n">
+      <c r="G40" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H40" s="54" t="n">
+      <c r="H40" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I40" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J40" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F41="","",'Market Comparison'!F41)</f>
-        <v/>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L40" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M40" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N40" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O40" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P40" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J40" s="51"/>
     </row>
     <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="51" t="s">
@@ -16023,45 +15307,25 @@
       <c r="C41" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="52" t="n">
-        <f aca="false">'Market Comparison'!D42</f>
+      <c r="D41" s="56" t="n">
         <v>13.07</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F41" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F41" s="53" t="n">
         <v>31</v>
       </c>
-      <c r="G41" s="53" t="n">
+      <c r="G41" s="54" t="n">
         <v>17.93</v>
       </c>
-      <c r="H41" s="54" t="n">
+      <c r="H41" s="55" t="n">
         <v>1.37184391736802</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J41" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F42="","",'Market Comparison'!F42)</f>
-        <v/>
-      </c>
-      <c r="K41" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L41" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M41" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N41" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O41" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P41" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J41" s="51"/>
     </row>
     <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="51" t="s">
@@ -16073,45 +15337,25 @@
       <c r="C42" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="52" t="n">
-        <f aca="false">'Market Comparison'!D43</f>
+      <c r="D42" s="56" t="n">
         <v>5.35</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F42" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F42" s="53" t="n">
         <v>34.5363636363636</v>
       </c>
-      <c r="G42" s="53" t="n">
+      <c r="G42" s="54" t="n">
         <v>29.1863636363636</v>
       </c>
-      <c r="H42" s="54" t="n">
+      <c r="H42" s="55" t="n">
         <v>5.4553950722175</v>
       </c>
       <c r="I42" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J42" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F43="","",'Market Comparison'!F43)</f>
-        <v/>
-      </c>
-      <c r="K42" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L42" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M42" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N42" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O42" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P42" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J42" s="51"/>
     </row>
     <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="51" t="s">
@@ -16123,45 +15367,25 @@
       <c r="C43" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="52" t="n">
-        <f aca="false">'Market Comparison'!D44</f>
+      <c r="D43" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F43" s="52" t="n">
+        <v>329</v>
+      </c>
+      <c r="F43" s="53" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="G43" s="53" t="n">
+      <c r="G43" s="54" t="n">
         <v>6.68454545454545</v>
       </c>
-      <c r="H43" s="54" t="n">
+      <c r="H43" s="55" t="n">
         <v>2.50357507660878</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J43" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F44="","",'Market Comparison'!F44)</f>
-        <v/>
-      </c>
-      <c r="K43" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L43" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M43" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N43" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O43" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P43" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J43" s="51"/>
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="51" t="s">
@@ -16173,45 +15397,25 @@
       <c r="C44" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="52" t="n">
-        <f aca="false">'Market Comparison'!D45</f>
+      <c r="D44" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F44" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F44" s="53" t="n">
         <v>23.4090909090909</v>
       </c>
-      <c r="G44" s="53" t="n">
+      <c r="G44" s="54" t="n">
         <v>12.7190909090909</v>
       </c>
-      <c r="H44" s="54" t="n">
+      <c r="H44" s="55" t="n">
         <v>1.18981205884854</v>
       </c>
       <c r="I44" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J44" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F45="","",'Market Comparison'!F45)</f>
-        <v/>
-      </c>
-      <c r="K44" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L44" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M44" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N44" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O44" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P44" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J44" s="51"/>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="51" t="s">
@@ -16223,45 +15427,25 @@
       <c r="C45" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="52" t="n">
-        <f aca="false">'Market Comparison'!D46</f>
+      <c r="D45" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F45" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F45" s="53" t="n">
         <v>22.7181818181818</v>
       </c>
-      <c r="G45" s="53" t="n">
+      <c r="G45" s="54" t="n">
         <v>20.0481818181818</v>
       </c>
-      <c r="H45" s="54" t="n">
+      <c r="H45" s="55" t="n">
         <v>7.50868232890704</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J45" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F46="","",'Market Comparison'!F46)</f>
-        <v/>
-      </c>
-      <c r="K45" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L45" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M45" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N45" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O45" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P45" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J45" s="51"/>
     </row>
     <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="51" t="s">
@@ -16273,45 +15457,25 @@
       <c r="C46" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="52" t="n">
-        <f aca="false">'Market Comparison'!D47</f>
+      <c r="D46" s="56" t="n">
         <v>9.5</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F46" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F46" s="53" t="n">
         <v>40.9</v>
       </c>
-      <c r="G46" s="53" t="n">
+      <c r="G46" s="54" t="n">
         <v>31.4</v>
       </c>
-      <c r="H46" s="54" t="n">
+      <c r="H46" s="55" t="n">
         <v>3.30526315789474</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J46" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F47="","",'Market Comparison'!F47)</f>
-        <v/>
-      </c>
-      <c r="K46" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L46" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M46" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N46" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O46" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P46" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J46" s="51"/>
     </row>
     <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="51" t="s">
@@ -16323,45 +15487,25 @@
       <c r="C47" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="52" t="n">
-        <f aca="false">'Market Comparison'!D48</f>
+      <c r="D47" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F47" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F47" s="53" t="n">
         <v>40.9</v>
       </c>
-      <c r="G47" s="53" t="n">
+      <c r="G47" s="54" t="n">
         <v>30.21</v>
       </c>
-      <c r="H47" s="54" t="n">
+      <c r="H47" s="55" t="n">
         <v>2.82600561272217</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J47" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F48="","",'Market Comparison'!F48)</f>
-        <v/>
-      </c>
-      <c r="K47" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L47" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M47" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N47" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O47" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P47" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J47" s="51"/>
     </row>
     <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="51" t="s">
@@ -16373,45 +15517,25 @@
       <c r="C48" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="52" t="n">
-        <f aca="false">'Market Comparison'!D49</f>
+      <c r="D48" s="56" t="n">
         <v>5.35</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F48" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F48" s="53" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="G48" s="53" t="n">
+      <c r="G48" s="54" t="n">
         <v>15.5590909090909</v>
       </c>
-      <c r="H48" s="54" t="n">
+      <c r="H48" s="55" t="n">
         <v>2.90824129141886</v>
       </c>
       <c r="I48" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J48" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F49="","",'Market Comparison'!F49)</f>
-        <v/>
-      </c>
-      <c r="K48" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L48" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M48" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N48" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O48" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P48" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J48" s="51"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="51" t="s">
@@ -16423,45 +15547,25 @@
       <c r="C49" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="52" t="n">
-        <f aca="false">'Market Comparison'!D50</f>
+      <c r="D49" s="56" t="n">
         <v>5.35</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="F49" s="52" t="n">
+        <v>329</v>
+      </c>
+      <c r="F49" s="53" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="G49" s="53" t="n">
+      <c r="G49" s="54" t="n">
         <v>4.00454545454545</v>
       </c>
-      <c r="H49" s="54" t="n">
+      <c r="H49" s="55" t="n">
         <v>0.748513169073916</v>
       </c>
       <c r="I49" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J49" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F50="","",'Market Comparison'!F50)</f>
-        <v/>
-      </c>
-      <c r="K49" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L49" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M49" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N49" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O49" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P49" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J49" s="51"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="51" t="s">
@@ -16473,45 +15577,25 @@
       <c r="C50" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="52" t="n">
-        <f aca="false">'Market Comparison'!D51</f>
+      <c r="D50" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="E50" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F50" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F50" s="53" t="n">
         <v>25.4454545454545</v>
       </c>
-      <c r="G50" s="53" t="n">
+      <c r="G50" s="54" t="n">
         <v>22.7754545454545</v>
       </c>
-      <c r="H50" s="54" t="n">
+      <c r="H50" s="55" t="n">
         <v>8.53013278855974</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J50" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F51="","",'Market Comparison'!F51)</f>
-        <v/>
-      </c>
-      <c r="K50" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L50" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M50" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N50" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O50" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P50" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J50" s="51"/>
     </row>
     <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="51" t="s">
@@ -16523,45 +15607,25 @@
       <c r="C51" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="52" t="n">
-        <f aca="false">'Market Comparison'!D52</f>
+      <c r="D51" s="56" t="n">
         <v>9.5</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F51" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F51" s="53" t="n">
         <v>40.9</v>
       </c>
-      <c r="G51" s="53" t="n">
+      <c r="G51" s="54" t="n">
         <v>31.4</v>
       </c>
-      <c r="H51" s="54" t="n">
+      <c r="H51" s="55" t="n">
         <v>3.30526315789474</v>
       </c>
       <c r="I51" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J51" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F52="","",'Market Comparison'!F52)</f>
-        <v/>
-      </c>
-      <c r="K51" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L51" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M51" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N51" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O51" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P51" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J51" s="51"/>
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="51" t="s">
@@ -16573,45 +15637,25 @@
       <c r="C52" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="52" t="n">
-        <f aca="false">'Market Comparison'!D53</f>
+      <c r="D52" s="56" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="F52" s="52" t="n">
+        <v>325</v>
+      </c>
+      <c r="F52" s="53" t="n">
         <v>7.81818181818182</v>
       </c>
-      <c r="G52" s="53" t="n">
+      <c r="G52" s="54" t="n">
         <v>5.81818181818182</v>
       </c>
-      <c r="H52" s="54" t="n">
+      <c r="H52" s="55" t="n">
         <v>2.90909090909091</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J52" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F53="","",'Market Comparison'!F53)</f>
-        <v/>
-      </c>
-      <c r="K52" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L52" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M52" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N52" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O52" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P52" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J52" s="51"/>
     </row>
     <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="51" t="s">
@@ -16623,45 +15667,25 @@
       <c r="C53" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D53" s="52" t="n">
-        <f aca="false">'Market Comparison'!D54</f>
+      <c r="D53" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F53" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F53" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G53" s="53" t="n">
+      <c r="G53" s="54" t="n">
         <v>27.3209090909091</v>
       </c>
-      <c r="H53" s="54" t="n">
+      <c r="H53" s="55" t="n">
         <v>10.2325502213143</v>
       </c>
       <c r="I53" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J53" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F54="","",'Market Comparison'!F54)</f>
-        <v/>
-      </c>
-      <c r="K53" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L53" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M53" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N53" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O53" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P53" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J53" s="51"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="51" t="s">
@@ -16673,45 +15697,25 @@
       <c r="C54" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="52" t="n">
-        <f aca="false">'Market Comparison'!D55</f>
+      <c r="D54" s="56" t="n">
         <v>4.01</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F54" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F54" s="53" t="n">
         <v>34.5363636363636</v>
       </c>
-      <c r="G54" s="53" t="n">
+      <c r="G54" s="54" t="n">
         <v>30.5263636363636</v>
       </c>
-      <c r="H54" s="54" t="n">
+      <c r="H54" s="55" t="n">
         <v>7.61255951031511</v>
       </c>
       <c r="I54" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J54" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F55="","",'Market Comparison'!F55)</f>
-        <v/>
-      </c>
-      <c r="K54" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L54" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M54" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N54" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O54" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P54" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J54" s="51"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="51" t="s">
@@ -16723,45 +15727,25 @@
       <c r="C55" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D55" s="52" t="n">
-        <f aca="false">'Market Comparison'!D56</f>
+      <c r="D55" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F55" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F55" s="53" t="n">
         <v>34.5363636363636</v>
       </c>
-      <c r="G55" s="53" t="n">
+      <c r="G55" s="54" t="n">
         <v>23.8463636363636</v>
       </c>
-      <c r="H55" s="54" t="n">
+      <c r="H55" s="55" t="n">
         <v>2.23071689769538</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J55" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F56="","",'Market Comparison'!F56)</f>
-        <v/>
-      </c>
-      <c r="K55" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L55" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M55" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N55" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O55" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P55" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J55" s="51"/>
     </row>
     <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="51" t="s">
@@ -16773,45 +15757,25 @@
       <c r="C56" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="52" t="n">
-        <f aca="false">'Market Comparison'!D57</f>
+      <c r="D56" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F56" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F56" s="53" t="n">
         <v>34.5363636363636</v>
       </c>
-      <c r="G56" s="53" t="n">
+      <c r="G56" s="54" t="n">
         <v>23.8463636363636</v>
       </c>
-      <c r="H56" s="54" t="n">
+      <c r="H56" s="55" t="n">
         <v>2.23071689769538</v>
       </c>
       <c r="I56" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J56" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F57="","",'Market Comparison'!F57)</f>
-        <v/>
-      </c>
-      <c r="K56" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L56" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M56" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N56" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O56" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P56" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J56" s="51"/>
     </row>
     <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="51" t="s">
@@ -16823,45 +15787,25 @@
       <c r="C57" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="52" t="n">
-        <f aca="false">'Market Comparison'!D58</f>
+      <c r="D57" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F57" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F57" s="53" t="n">
         <v>40.9</v>
       </c>
-      <c r="G57" s="53" t="n">
+      <c r="G57" s="54" t="n">
         <v>30.21</v>
       </c>
-      <c r="H57" s="54" t="n">
+      <c r="H57" s="55" t="n">
         <v>2.82600561272217</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J57" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F58="","",'Market Comparison'!F58)</f>
-        <v/>
-      </c>
-      <c r="K57" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L57" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M57" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N57" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O57" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P57" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J57" s="51"/>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="51" t="s">
@@ -16873,45 +15817,25 @@
       <c r="C58" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="52" t="n">
-        <f aca="false">'Market Comparison'!D59</f>
+      <c r="D58" s="56" t="n">
         <v>2.89</v>
       </c>
       <c r="E58" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F58" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F58" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G58" s="53" t="n">
+      <c r="G58" s="54" t="n">
         <v>27.1009090909091</v>
       </c>
-      <c r="H58" s="54" t="n">
+      <c r="H58" s="55" t="n">
         <v>9.37747719408619</v>
       </c>
       <c r="I58" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J58" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F59="","",'Market Comparison'!F59)</f>
-        <v/>
-      </c>
-      <c r="K58" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L58" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M58" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N58" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O58" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P58" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J58" s="51"/>
     </row>
     <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="51" t="s">
@@ -16923,45 +15847,25 @@
       <c r="C59" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="52" t="n">
-        <f aca="false">'Market Comparison'!D60</f>
+      <c r="D59" s="56" t="n">
         <v>1.94</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F59" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F59" s="53" t="n">
         <v>45.4454545454545</v>
       </c>
-      <c r="G59" s="53" t="n">
+      <c r="G59" s="54" t="n">
         <v>43.5054545454545</v>
       </c>
-      <c r="H59" s="54" t="n">
+      <c r="H59" s="55" t="n">
         <v>22.4254920337394</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J59" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F60="","",'Market Comparison'!F60)</f>
-        <v/>
-      </c>
-      <c r="K59" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L59" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M59" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N59" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O59" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P59" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J59" s="51"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="51" t="s">
@@ -16973,45 +15877,25 @@
       <c r="C60" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D60" s="52" t="n">
-        <f aca="false">'Market Comparison'!D61</f>
+      <c r="D60" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E60" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F60" s="52" t="n">
+        <v>322</v>
+      </c>
+      <c r="F60" s="53" t="n">
         <v>43.55</v>
       </c>
-      <c r="G60" s="53" t="n">
+      <c r="G60" s="54" t="n">
         <v>32.86</v>
       </c>
-      <c r="H60" s="54" t="n">
+      <c r="H60" s="55" t="n">
         <v>3.07390084190833</v>
       </c>
       <c r="I60" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J60" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F61="","",'Market Comparison'!F61)</f>
-        <v/>
-      </c>
-      <c r="K60" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L60" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M60" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N60" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O60" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P60" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J60" s="51"/>
     </row>
     <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="51" t="s">
@@ -17023,45 +15907,25 @@
       <c r="C61" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="52" t="n">
-        <f aca="false">'Market Comparison'!D62</f>
+      <c r="D61" s="56" t="n">
         <v>3.201</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F61" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F61" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G61" s="53" t="n">
+      <c r="G61" s="54" t="n">
         <v>26.7899090909091</v>
       </c>
-      <c r="H61" s="54" t="n">
+      <c r="H61" s="55" t="n">
         <v>8.36923120615717</v>
       </c>
       <c r="I61" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J61" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F62="","",'Market Comparison'!F62)</f>
-        <v/>
-      </c>
-      <c r="K61" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L61" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M61" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N61" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O61" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P61" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J61" s="51"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="51" t="s">
@@ -17073,45 +15937,25 @@
       <c r="C62" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D62" s="52" t="n">
-        <f aca="false">'Market Comparison'!D63</f>
+      <c r="D62" s="56" t="n">
         <v>5.35</v>
       </c>
       <c r="E62" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F62" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F62" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G62" s="53" t="n">
+      <c r="G62" s="54" t="n">
         <v>24.6409090909091</v>
       </c>
-      <c r="H62" s="54" t="n">
+      <c r="H62" s="55" t="n">
         <v>4.60577740016993</v>
       </c>
       <c r="I62" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J62" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F63="","",'Market Comparison'!F63)</f>
-        <v/>
-      </c>
-      <c r="K62" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L62" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M62" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N62" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O62" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P62" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J62" s="51"/>
     </row>
     <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="51" t="s">
@@ -17123,45 +15967,25 @@
       <c r="C63" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="52" t="n">
-        <f aca="false">'Market Comparison'!D64</f>
+      <c r="D63" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F63" s="52" t="n">
+        <v>321</v>
+      </c>
+      <c r="F63" s="53" t="n">
         <v>29.9909090909091</v>
       </c>
-      <c r="G63" s="53" t="n">
+      <c r="G63" s="54" t="n">
         <v>27.3209090909091</v>
       </c>
-      <c r="H63" s="54" t="n">
+      <c r="H63" s="55" t="n">
         <v>10.2325502213143</v>
       </c>
       <c r="I63" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J63" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F64="","",'Market Comparison'!F64)</f>
-        <v/>
-      </c>
-      <c r="K63" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L63" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M63" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N63" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O63" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P63" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J63" s="51"/>
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="51" t="s">
@@ -17173,65 +15997,39 @@
       <c r="C64" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D64" s="52" t="n">
-        <f aca="false">'Market Comparison'!D65</f>
+      <c r="D64" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F64" s="52" t="n">
+        <v>330</v>
+      </c>
+      <c r="F64" s="53" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="G64" s="53" t="n">
+      <c r="G64" s="54" t="n">
         <v>16.5827272727273</v>
       </c>
-      <c r="H64" s="54" t="n">
+      <c r="H64" s="55" t="n">
         <v>1.55123735011481</v>
       </c>
       <c r="I64" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J64" s="52" t="str">
-        <f aca="false">IF('Market Comparison'!F65="","",'Market Comparison'!F65)</f>
-        <v/>
-      </c>
-      <c r="K64" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="L64" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="M64" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="N64" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="O64" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="P64" s="41"/>
+        <v>320</v>
+      </c>
+      <c r="J64" s="51"/>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
-      <c r="J66" s="58"/>
-      <c r="K66" s="58"/>
-      <c r="L66" s="58"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="58"/>
-      <c r="O66" s="58"/>
-      <c r="P66" s="58"/>
+      <c r="A66" s="64" t="s">
+        <v>331</v>
+      </c>
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="50" t="s">
@@ -17241,392 +16039,187 @@
         <v>1</v>
       </c>
       <c r="C67" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="F67" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="D67" s="50" t="s">
+      <c r="G67" s="50" t="s">
         <v>336</v>
       </c>
-      <c r="E67" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="F67" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="G67" s="50" t="s">
-        <v>339</v>
-      </c>
     </row>
     <row r="68" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="51" t="s">
+      <c r="A68" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="41" t="s">
+      <c r="B68" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D68" s="52" t="n">
+      <c r="C68" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="D68" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E68" s="52" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="F68" s="53" t="n">
-        <v>7.35545454545455</v>
-      </c>
-      <c r="G68" s="54" t="n">
-        <v>0.440182797453893</v>
+      <c r="E68" s="60" t="n">
+        <v>16.93275</v>
+      </c>
+      <c r="F68" s="65" t="n">
+        <v>7.57820454545455</v>
+      </c>
+      <c r="G68" s="66" t="n">
+        <v>0.447547181967167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="51" t="s">
+      <c r="A69" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="41" t="s">
+      <c r="B69" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D69" s="52" t="n">
+      <c r="C69" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="D69" s="60" t="n">
         <v>21.2</v>
       </c>
-      <c r="E69" s="52" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="F69" s="53" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="G69" s="54" t="n">
-        <v>0.365459443280455</v>
+      <c r="E69" s="60" t="n">
+        <v>33.8555</v>
+      </c>
+      <c r="F69" s="65" t="n">
+        <v>12.6555</v>
+      </c>
+      <c r="G69" s="66" t="n">
+        <v>0.373809277665372</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="51" t="s">
+      <c r="A70" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="41" t="s">
+      <c r="B70" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="C70" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D70" s="52" t="n">
+      <c r="C70" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="D70" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E70" s="52" t="n">
-        <v>11.81</v>
-      </c>
-      <c r="F70" s="53" t="n">
-        <v>2.45545454545455</v>
-      </c>
-      <c r="G70" s="54" t="n">
-        <v>0.207913170656609</v>
+      <c r="E70" s="60" t="n">
+        <v>12.03275</v>
+      </c>
+      <c r="F70" s="65" t="n">
+        <v>2.67820454545455</v>
+      </c>
+      <c r="G70" s="66" t="n">
+        <v>0.222576264399622</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="51" t="s">
+      <c r="A71" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="41" t="s">
+      <c r="B71" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D71" s="52" t="n">
+      <c r="C71" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="D71" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E71" s="52" t="n">
-        <v>11.81</v>
-      </c>
-      <c r="F71" s="53" t="n">
-        <v>2.45545454545455</v>
-      </c>
-      <c r="G71" s="54" t="n">
-        <v>0.207913170656609</v>
+      <c r="E71" s="60" t="n">
+        <v>12.03275</v>
+      </c>
+      <c r="F71" s="65" t="n">
+        <v>2.67820454545455</v>
+      </c>
+      <c r="G71" s="66" t="n">
+        <v>0.222576264399622</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="51" t="s">
+      <c r="A72" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="41" t="s">
+      <c r="B72" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D72" s="52" t="n">
+      <c r="C72" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E72" s="52" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="F72" s="53" t="n">
-        <v>5.0554545454545</v>
-      </c>
-      <c r="G72" s="54" t="n">
-        <v>0.151315610459578</v>
+      <c r="E72" s="60" t="n">
+        <v>33.8555</v>
+      </c>
+      <c r="F72" s="65" t="n">
+        <v>5.5009545454545</v>
+      </c>
+      <c r="G72" s="66" t="n">
+        <v>0.162483334922081</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="51" t="s">
+      <c r="A73" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="41" t="s">
+      <c r="B73" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="C73" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D73" s="52" t="n">
+      <c r="C73" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="D73" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E73" s="52" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F73" s="53" t="n">
-        <v>1.3454545454545</v>
-      </c>
-      <c r="G73" s="54" t="n">
-        <v>0.0453014998469528</v>
+      <c r="E73" s="60" t="n">
+        <v>30.1455</v>
+      </c>
+      <c r="F73" s="65" t="n">
+        <v>1.7909545454545</v>
+      </c>
+      <c r="G73" s="66" t="n">
+        <v>0.0594103446768007</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="51" t="s">
+      <c r="A74" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="41" t="s">
+      <c r="B74" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="D74" s="52" t="n">
+      <c r="C74" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="D74" s="60" t="n">
         <v>32.5</v>
       </c>
-      <c r="E74" s="52" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="F74" s="53" t="n">
-        <v>0.909999999999997</v>
-      </c>
-      <c r="G74" s="54" t="n">
-        <v>0.027237354085603</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="58" t="s">
-        <v>340</v>
-      </c>
-      <c r="B76" s="58"/>
-      <c r="C76" s="58"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
-      <c r="J76" s="58"/>
-      <c r="K76" s="58"/>
-      <c r="L76" s="58"/>
-      <c r="M76" s="58"/>
-      <c r="N76" s="58"/>
-      <c r="O76" s="58"/>
-      <c r="P76" s="58"/>
-    </row>
-    <row r="77" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="D77" s="50" t="s">
-        <v>336</v>
-      </c>
-      <c r="E77" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="F77" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="G77" s="50" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D78" s="52" t="n">
-        <v>9.35454545454545</v>
-      </c>
-      <c r="E78" s="52" t="n">
-        <v>16.93275</v>
-      </c>
-      <c r="F78" s="53" t="n">
-        <v>7.57820454545455</v>
-      </c>
-      <c r="G78" s="54" t="n">
-        <v>0.447547181967167</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="B79" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D79" s="52" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E79" s="52" t="n">
+      <c r="E74" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F79" s="53" t="n">
-        <v>12.6555</v>
-      </c>
-      <c r="G79" s="54" t="n">
-        <v>0.373809277665372</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="B80" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="C80" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D80" s="52" t="n">
-        <v>9.35454545454545</v>
-      </c>
-      <c r="E80" s="52" t="n">
-        <v>12.03275</v>
-      </c>
-      <c r="F80" s="53" t="n">
-        <v>2.67820454545455</v>
-      </c>
-      <c r="G80" s="54" t="n">
-        <v>0.222576264399622</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="B81" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="C81" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D81" s="52" t="n">
-        <v>9.35454545454545</v>
-      </c>
-      <c r="E81" s="52" t="n">
-        <v>12.03275</v>
-      </c>
-      <c r="F81" s="53" t="n">
-        <v>2.67820454545455</v>
-      </c>
-      <c r="G81" s="54" t="n">
-        <v>0.222576264399622</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B82" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D82" s="52" t="n">
-        <v>28.3545454545455</v>
-      </c>
-      <c r="E82" s="52" t="n">
-        <v>33.8555</v>
-      </c>
-      <c r="F82" s="53" t="n">
-        <v>5.5009545454545</v>
-      </c>
-      <c r="G82" s="54" t="n">
-        <v>0.162483334922081</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="B83" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="C83" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D83" s="52" t="n">
-        <v>28.3545454545455</v>
-      </c>
-      <c r="E83" s="52" t="n">
-        <v>30.1455</v>
-      </c>
-      <c r="F83" s="53" t="n">
-        <v>1.7909545454545</v>
-      </c>
-      <c r="G83" s="54" t="n">
-        <v>0.0594103446768007</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="B84" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="C84" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="D84" s="52" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E84" s="52" t="n">
-        <v>33.8555</v>
-      </c>
-      <c r="F84" s="53" t="n">
+      <c r="F74" s="65" t="n">
         <v>1.3555</v>
       </c>
-      <c r="G84" s="54" t="n">
+      <c r="G74" s="66" t="n">
         <v>0.0400378077417258</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A66:P66"/>
-    <mergeCell ref="A76:P76"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A66:J66"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -996,27 +996,27 @@
     <t xml:space="preserve">Summary — Closest-Priced Competitor &amp; Where We're More Expensive</t>
   </si>
   <si>
-    <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our Quoted Price
-(ex GST, higher of 1200/1220)</t>
+    <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. "$ Difference" and "% Difference" are now expressed as Us − Them: a positive (red) figure means we are MORE expensive than that competitor; a negative (green) figure means we are cheaper. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Us
+(Our Quoted Price, ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">Closest-Priced
 Competitor (or RSEA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Their Price
-(ex GST)</t>
+    <t xml:space="preserve">Them
+(Their Price, ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">$ Difference
-(Them − Us)</t>
+(Us − Them)</t>
   </si>
   <si>
     <t xml:space="preserve">% Difference
-(vs Our Price)</t>
+(Us vs Them)</t>
   </si>
   <si>
     <t xml:space="preserve">Are We More
@@ -1233,9 +1233,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF1B7A4D"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1248,8 +1247,9 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF1B7A4D"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1380,7 +1380,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1633,20 +1633,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1757,9 +1749,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>405360</xdr:colOff>
+      <xdr:colOff>405000</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>261720</xdr:rowOff>
+      <xdr:rowOff>261360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1773,7 +1765,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2193120" cy="2339280"/>
+          <a:ext cx="2192760" cy="2338920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14237,10 +14229,10 @@
         <v>20.05</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>3.11725</v>
+        <v>-3.11725</v>
       </c>
       <c r="H5" s="55" t="n">
-        <v>0.184095908815757</v>
+        <v>-0.184095908815757</v>
       </c>
       <c r="I5" s="51" t="s">
         <v>320</v>
@@ -14267,10 +14259,10 @@
         <v>122.718181818182</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>55.888181818182</v>
+        <v>-55.888181818182</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>0.836273856324735</v>
+        <v>-0.836273856324735</v>
       </c>
       <c r="I6" s="51" t="s">
         <v>320</v>
@@ -14297,10 +14289,10 @@
         <v>128.75</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>84.2</v>
+        <v>-84.2</v>
       </c>
       <c r="H7" s="55" t="n">
-        <v>1.89001122334456</v>
+        <v>-1.89001122334456</v>
       </c>
       <c r="I7" s="51" t="s">
         <v>320</v>
@@ -14327,10 +14319,10 @@
         <v>69.245</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>24.101</v>
+        <v>-24.101</v>
       </c>
       <c r="H8" s="55" t="n">
-        <v>0.533869395711501</v>
+        <v>-0.533869395711501</v>
       </c>
       <c r="I8" s="51" t="s">
         <v>320</v>
@@ -14357,10 +14349,10 @@
         <v>81.4</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>10.861875</v>
+        <v>-10.861875</v>
       </c>
       <c r="H9" s="55" t="n">
-        <v>0.153985876432072</v>
+        <v>-0.153985876432072</v>
       </c>
       <c r="I9" s="51" t="s">
         <v>320</v>
@@ -14387,10 +14379,10 @@
         <v>44.209</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>10.3535</v>
+        <v>-10.3535</v>
       </c>
       <c r="H10" s="55" t="n">
-        <v>0.305814417155263</v>
+        <v>-0.305814417155263</v>
       </c>
       <c r="I10" s="51" t="s">
         <v>320</v>
@@ -14417,10 +14409,10 @@
         <v>70.36</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>25.216</v>
+        <v>-25.216</v>
       </c>
       <c r="H11" s="55" t="n">
-        <v>0.558568137515506</v>
+        <v>-0.558568137515506</v>
       </c>
       <c r="I11" s="51" t="s">
         <v>320</v>
@@ -14447,10 +14439,10 @@
         <v>33.1818181818182</v>
       </c>
       <c r="G12" s="61" t="n">
-        <v>-0.673681818181798</v>
+        <v>0.673681818181798</v>
       </c>
       <c r="H12" s="62" t="n">
-        <v>-0.019898740771272</v>
+        <v>0.019898740771272</v>
       </c>
       <c r="I12" s="63" t="s">
         <v>326</v>
@@ -14477,10 +14469,10 @@
         <v>43.09</v>
       </c>
       <c r="G13" s="54" t="n">
-        <v>17.695875</v>
+        <v>-17.695875</v>
       </c>
       <c r="H13" s="55" t="n">
-        <v>0.696849172790951</v>
+        <v>-0.696849172790951</v>
       </c>
       <c r="I13" s="51" t="s">
         <v>320</v>
@@ -14507,10 +14499,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G14" s="54" t="n">
-        <v>21.5295340909091</v>
+        <v>-21.5295340909091</v>
       </c>
       <c r="H14" s="55" t="n">
-        <v>2.54444863759248</v>
+        <v>-2.54444863759248</v>
       </c>
       <c r="I14" s="51" t="s">
         <v>320</v>
@@ -14537,10 +14529,10 @@
         <v>40.9</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>25.08725</v>
+        <v>-25.08725</v>
       </c>
       <c r="H15" s="55" t="n">
-        <v>1.58652037121943</v>
+        <v>-1.58652037121943</v>
       </c>
       <c r="I15" s="51" t="s">
         <v>320</v>
@@ -14567,10 +14559,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>21.5295340909091</v>
+        <v>-21.5295340909091</v>
       </c>
       <c r="H16" s="55" t="n">
-        <v>2.54444863759248</v>
+        <v>-2.54444863759248</v>
       </c>
       <c r="I16" s="51" t="s">
         <v>320</v>
@@ -14597,10 +14589,10 @@
         <v>37.3909090909091</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>7.2454090909091</v>
+        <v>-7.2454090909091</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.240347948811899</v>
+        <v>-0.240347948811899</v>
       </c>
       <c r="I17" s="51" t="s">
         <v>320</v>
@@ -14627,10 +14619,10 @@
         <v>28.3545454545455</v>
       </c>
       <c r="G18" s="61" t="n">
-        <v>-1.7909545454545</v>
+        <v>1.7909545454545</v>
       </c>
       <c r="H18" s="62" t="n">
-        <v>-0.0594103446768007</v>
+        <v>0.0594103446768007</v>
       </c>
       <c r="I18" s="63" t="s">
         <v>326</v>
@@ -14657,10 +14649,10 @@
         <v>23.3090909090909</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>6.3763409090909</v>
+        <v>-6.3763409090909</v>
       </c>
       <c r="H19" s="55" t="n">
-        <v>0.376568537838857</v>
+        <v>-0.376568537838857</v>
       </c>
       <c r="I19" s="51" t="s">
         <v>320</v>
@@ -14687,10 +14679,10 @@
         <v>28.99</v>
       </c>
       <c r="G20" s="61" t="n">
-        <v>-4.8655</v>
+        <v>4.8655</v>
       </c>
       <c r="H20" s="62" t="n">
-        <v>-0.14371372450562</v>
+        <v>0.14371372450562</v>
       </c>
       <c r="I20" s="63" t="s">
         <v>326</v>
@@ -14717,10 +14709,10 @@
         <v>21.2</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>9.16725</v>
+        <v>-9.16725</v>
       </c>
       <c r="H21" s="55" t="n">
-        <v>0.761858261827097</v>
+        <v>-0.761858261827097</v>
       </c>
       <c r="I21" s="51" t="s">
         <v>320</v>
@@ -14747,10 +14739,10 @@
         <v>21.2</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>9.16725</v>
+        <v>-9.16725</v>
       </c>
       <c r="H22" s="55" t="n">
-        <v>0.761858261827097</v>
+        <v>-0.761858261827097</v>
       </c>
       <c r="I22" s="51" t="s">
         <v>320</v>
@@ -14777,10 +14769,10 @@
         <v>34.5363636363636</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>28.5249886363636</v>
+        <v>-28.5249886363636</v>
       </c>
       <c r="H23" s="55" t="n">
-        <v>4.74516872368861</v>
+        <v>-4.74516872368861</v>
       </c>
       <c r="I23" s="51" t="s">
         <v>320</v>
@@ -14807,10 +14799,10 @@
         <v>9.35454545454545</v>
       </c>
       <c r="G24" s="61" t="n">
-        <v>-2.67820454545455</v>
+        <v>2.67820454545455</v>
       </c>
       <c r="H24" s="62" t="n">
-        <v>-0.222576264399622</v>
+        <v>0.222576264399622</v>
       </c>
       <c r="I24" s="63" t="s">
         <v>326</v>
@@ -14837,10 +14829,10 @@
         <v>9.35454545454545</v>
       </c>
       <c r="G25" s="61" t="n">
-        <v>-2.67820454545455</v>
+        <v>2.67820454545455</v>
       </c>
       <c r="H25" s="62" t="n">
-        <v>-0.222576264399622</v>
+        <v>0.222576264399622</v>
       </c>
       <c r="I25" s="63" t="s">
         <v>326</v>
@@ -14867,10 +14859,10 @@
         <v>21.2</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>9.16725</v>
+        <v>-9.16725</v>
       </c>
       <c r="H26" s="55" t="n">
-        <v>0.761858261827097</v>
+        <v>-0.761858261827097</v>
       </c>
       <c r="I26" s="51" t="s">
         <v>320</v>
@@ -14897,10 +14889,10 @@
         <v>32.5</v>
       </c>
       <c r="G27" s="61" t="n">
-        <v>-1.3555</v>
+        <v>1.3555</v>
       </c>
       <c r="H27" s="62" t="n">
-        <v>-0.0400378077417258</v>
+        <v>0.0400378077417258</v>
       </c>
       <c r="I27" s="63" t="s">
         <v>326</v>
@@ -14927,10 +14919,10 @@
         <v>45</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>11.1445</v>
+        <v>-11.1445</v>
       </c>
       <c r="H28" s="55" t="n">
-        <v>0.329178420049918</v>
+        <v>-0.329178420049918</v>
       </c>
       <c r="I28" s="51" t="s">
         <v>320</v>
@@ -14957,10 +14949,10 @@
         <v>30.8</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>17.73</v>
+        <v>-17.73</v>
       </c>
       <c r="H29" s="55" t="n">
-        <v>1.35654169854629</v>
+        <v>-1.35654169854629</v>
       </c>
       <c r="I29" s="51" t="s">
         <v>320</v>
@@ -14987,10 +14979,10 @@
         <v>31</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H30" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I30" s="51" t="s">
         <v>320</v>
@@ -15017,10 +15009,10 @@
         <v>31</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>14.96</v>
+        <v>-14.96</v>
       </c>
       <c r="H31" s="55" t="n">
-        <v>0.932668329177057</v>
+        <v>-0.932668329177057</v>
       </c>
       <c r="I31" s="51" t="s">
         <v>320</v>
@@ -15047,10 +15039,10 @@
         <v>31</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>14.96</v>
+        <v>-14.96</v>
       </c>
       <c r="H32" s="55" t="n">
-        <v>0.932668329177057</v>
+        <v>-0.932668329177057</v>
       </c>
       <c r="I32" s="51" t="s">
         <v>320</v>
@@ -15077,10 +15069,10 @@
         <v>31</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>14.96</v>
+        <v>-14.96</v>
       </c>
       <c r="H33" s="55" t="n">
-        <v>0.932668329177057</v>
+        <v>-0.932668329177057</v>
       </c>
       <c r="I33" s="51" t="s">
         <v>320</v>
@@ -15107,10 +15099,10 @@
         <v>31</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>14.96</v>
+        <v>-14.96</v>
       </c>
       <c r="H34" s="55" t="n">
-        <v>0.932668329177057</v>
+        <v>-0.932668329177057</v>
       </c>
       <c r="I34" s="51" t="s">
         <v>320</v>
@@ -15137,10 +15129,10 @@
         <v>31</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H35" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I35" s="51" t="s">
         <v>320</v>
@@ -15167,10 +15159,10 @@
         <v>31</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>14.96</v>
+        <v>-14.96</v>
       </c>
       <c r="H36" s="55" t="n">
-        <v>0.932668329177057</v>
+        <v>-0.932668329177057</v>
       </c>
       <c r="I36" s="51" t="s">
         <v>320</v>
@@ -15197,10 +15189,10 @@
         <v>31</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H37" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I37" s="51" t="s">
         <v>320</v>
@@ -15227,10 +15219,10 @@
         <v>31</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H38" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I38" s="51" t="s">
         <v>320</v>
@@ -15257,10 +15249,10 @@
         <v>31</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H39" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I39" s="51" t="s">
         <v>320</v>
@@ -15287,10 +15279,10 @@
         <v>31</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H40" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I40" s="51" t="s">
         <v>320</v>
@@ -15317,10 +15309,10 @@
         <v>31</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>17.93</v>
+        <v>-17.93</v>
       </c>
       <c r="H41" s="55" t="n">
-        <v>1.37184391736802</v>
+        <v>-1.37184391736802</v>
       </c>
       <c r="I41" s="51" t="s">
         <v>320</v>
@@ -15347,10 +15339,10 @@
         <v>34.5363636363636</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>29.1863636363636</v>
+        <v>-29.1863636363636</v>
       </c>
       <c r="H42" s="55" t="n">
-        <v>5.4553950722175</v>
+        <v>-5.4553950722175</v>
       </c>
       <c r="I42" s="51" t="s">
         <v>320</v>
@@ -15377,10 +15369,10 @@
         <v>9.35454545454545</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>6.68454545454545</v>
+        <v>-6.68454545454545</v>
       </c>
       <c r="H43" s="55" t="n">
-        <v>2.50357507660878</v>
+        <v>-2.50357507660878</v>
       </c>
       <c r="I43" s="51" t="s">
         <v>320</v>
@@ -15407,10 +15399,10 @@
         <v>23.4090909090909</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>12.7190909090909</v>
+        <v>-12.7190909090909</v>
       </c>
       <c r="H44" s="55" t="n">
-        <v>1.18981205884854</v>
+        <v>-1.18981205884854</v>
       </c>
       <c r="I44" s="51" t="s">
         <v>320</v>
@@ -15437,10 +15429,10 @@
         <v>22.7181818181818</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>20.0481818181818</v>
+        <v>-20.0481818181818</v>
       </c>
       <c r="H45" s="55" t="n">
-        <v>7.50868232890704</v>
+        <v>-7.50868232890704</v>
       </c>
       <c r="I45" s="51" t="s">
         <v>320</v>
@@ -15467,10 +15459,10 @@
         <v>40.9</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>31.4</v>
+        <v>-31.4</v>
       </c>
       <c r="H46" s="55" t="n">
-        <v>3.30526315789474</v>
+        <v>-3.30526315789474</v>
       </c>
       <c r="I46" s="51" t="s">
         <v>320</v>
@@ -15497,10 +15489,10 @@
         <v>40.9</v>
       </c>
       <c r="G47" s="54" t="n">
-        <v>30.21</v>
+        <v>-30.21</v>
       </c>
       <c r="H47" s="55" t="n">
-        <v>2.82600561272217</v>
+        <v>-2.82600561272217</v>
       </c>
       <c r="I47" s="51" t="s">
         <v>320</v>
@@ -15527,10 +15519,10 @@
         <v>20.9090909090909</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>15.5590909090909</v>
+        <v>-15.5590909090909</v>
       </c>
       <c r="H48" s="55" t="n">
-        <v>2.90824129141886</v>
+        <v>-2.90824129141886</v>
       </c>
       <c r="I48" s="51" t="s">
         <v>320</v>
@@ -15557,10 +15549,10 @@
         <v>9.35454545454545</v>
       </c>
       <c r="G49" s="54" t="n">
-        <v>4.00454545454545</v>
+        <v>-4.00454545454545</v>
       </c>
       <c r="H49" s="55" t="n">
-        <v>0.748513169073916</v>
+        <v>-0.748513169073916</v>
       </c>
       <c r="I49" s="51" t="s">
         <v>320</v>
@@ -15587,10 +15579,10 @@
         <v>25.4454545454545</v>
       </c>
       <c r="G50" s="54" t="n">
-        <v>22.7754545454545</v>
+        <v>-22.7754545454545</v>
       </c>
       <c r="H50" s="55" t="n">
-        <v>8.53013278855974</v>
+        <v>-8.53013278855974</v>
       </c>
       <c r="I50" s="51" t="s">
         <v>320</v>
@@ -15617,10 +15609,10 @@
         <v>40.9</v>
       </c>
       <c r="G51" s="54" t="n">
-        <v>31.4</v>
+        <v>-31.4</v>
       </c>
       <c r="H51" s="55" t="n">
-        <v>3.30526315789474</v>
+        <v>-3.30526315789474</v>
       </c>
       <c r="I51" s="51" t="s">
         <v>320</v>
@@ -15647,10 +15639,10 @@
         <v>7.81818181818182</v>
       </c>
       <c r="G52" s="54" t="n">
-        <v>5.81818181818182</v>
+        <v>-5.81818181818182</v>
       </c>
       <c r="H52" s="55" t="n">
-        <v>2.90909090909091</v>
+        <v>-2.90909090909091</v>
       </c>
       <c r="I52" s="51" t="s">
         <v>320</v>
@@ -15677,10 +15669,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G53" s="54" t="n">
-        <v>27.3209090909091</v>
+        <v>-27.3209090909091</v>
       </c>
       <c r="H53" s="55" t="n">
-        <v>10.2325502213143</v>
+        <v>-10.2325502213143</v>
       </c>
       <c r="I53" s="51" t="s">
         <v>320</v>
@@ -15707,10 +15699,10 @@
         <v>34.5363636363636</v>
       </c>
       <c r="G54" s="54" t="n">
-        <v>30.5263636363636</v>
+        <v>-30.5263636363636</v>
       </c>
       <c r="H54" s="55" t="n">
-        <v>7.61255951031511</v>
+        <v>-7.61255951031511</v>
       </c>
       <c r="I54" s="51" t="s">
         <v>320</v>
@@ -15737,10 +15729,10 @@
         <v>34.5363636363636</v>
       </c>
       <c r="G55" s="54" t="n">
-        <v>23.8463636363636</v>
+        <v>-23.8463636363636</v>
       </c>
       <c r="H55" s="55" t="n">
-        <v>2.23071689769538</v>
+        <v>-2.23071689769538</v>
       </c>
       <c r="I55" s="51" t="s">
         <v>320</v>
@@ -15767,10 +15759,10 @@
         <v>34.5363636363636</v>
       </c>
       <c r="G56" s="54" t="n">
-        <v>23.8463636363636</v>
+        <v>-23.8463636363636</v>
       </c>
       <c r="H56" s="55" t="n">
-        <v>2.23071689769538</v>
+        <v>-2.23071689769538</v>
       </c>
       <c r="I56" s="51" t="s">
         <v>320</v>
@@ -15797,10 +15789,10 @@
         <v>40.9</v>
       </c>
       <c r="G57" s="54" t="n">
-        <v>30.21</v>
+        <v>-30.21</v>
       </c>
       <c r="H57" s="55" t="n">
-        <v>2.82600561272217</v>
+        <v>-2.82600561272217</v>
       </c>
       <c r="I57" s="51" t="s">
         <v>320</v>
@@ -15827,10 +15819,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G58" s="54" t="n">
-        <v>27.1009090909091</v>
+        <v>-27.1009090909091</v>
       </c>
       <c r="H58" s="55" t="n">
-        <v>9.37747719408619</v>
+        <v>-9.37747719408619</v>
       </c>
       <c r="I58" s="51" t="s">
         <v>320</v>
@@ -15857,10 +15849,10 @@
         <v>45.4454545454545</v>
       </c>
       <c r="G59" s="54" t="n">
-        <v>43.5054545454545</v>
+        <v>-43.5054545454545</v>
       </c>
       <c r="H59" s="55" t="n">
-        <v>22.4254920337394</v>
+        <v>-22.4254920337394</v>
       </c>
       <c r="I59" s="51" t="s">
         <v>320</v>
@@ -15887,10 +15879,10 @@
         <v>43.55</v>
       </c>
       <c r="G60" s="54" t="n">
-        <v>32.86</v>
+        <v>-32.86</v>
       </c>
       <c r="H60" s="55" t="n">
-        <v>3.07390084190833</v>
+        <v>-3.07390084190833</v>
       </c>
       <c r="I60" s="51" t="s">
         <v>320</v>
@@ -15917,10 +15909,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G61" s="54" t="n">
-        <v>26.7899090909091</v>
+        <v>-26.7899090909091</v>
       </c>
       <c r="H61" s="55" t="n">
-        <v>8.36923120615717</v>
+        <v>-8.36923120615717</v>
       </c>
       <c r="I61" s="51" t="s">
         <v>320</v>
@@ -15947,10 +15939,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G62" s="54" t="n">
-        <v>24.6409090909091</v>
+        <v>-24.6409090909091</v>
       </c>
       <c r="H62" s="55" t="n">
-        <v>4.60577740016993</v>
+        <v>-4.60577740016993</v>
       </c>
       <c r="I62" s="51" t="s">
         <v>320</v>
@@ -15977,10 +15969,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="G63" s="54" t="n">
-        <v>27.3209090909091</v>
+        <v>-27.3209090909091</v>
       </c>
       <c r="H63" s="55" t="n">
-        <v>10.2325502213143</v>
+        <v>-10.2325502213143</v>
       </c>
       <c r="I63" s="51" t="s">
         <v>320</v>
@@ -16007,10 +15999,10 @@
         <v>27.2727272727273</v>
       </c>
       <c r="G64" s="54" t="n">
-        <v>16.5827272727273</v>
+        <v>-16.5827272727273</v>
       </c>
       <c r="H64" s="55" t="n">
-        <v>1.55123735011481</v>
+        <v>-1.55123735011481</v>
       </c>
       <c r="I64" s="51" t="s">
         <v>320</v>
@@ -16070,10 +16062,10 @@
       <c r="E68" s="60" t="n">
         <v>16.93275</v>
       </c>
-      <c r="F68" s="65" t="n">
+      <c r="F68" s="61" t="n">
         <v>7.57820454545455</v>
       </c>
-      <c r="G68" s="66" t="n">
+      <c r="G68" s="62" t="n">
         <v>0.447547181967167</v>
       </c>
     </row>
@@ -16093,10 +16085,10 @@
       <c r="E69" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F69" s="65" t="n">
+      <c r="F69" s="61" t="n">
         <v>12.6555</v>
       </c>
-      <c r="G69" s="66" t="n">
+      <c r="G69" s="62" t="n">
         <v>0.373809277665372</v>
       </c>
     </row>
@@ -16116,10 +16108,10 @@
       <c r="E70" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F70" s="65" t="n">
+      <c r="F70" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G70" s="66" t="n">
+      <c r="G70" s="62" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
@@ -16139,10 +16131,10 @@
       <c r="E71" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F71" s="65" t="n">
+      <c r="F71" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G71" s="66" t="n">
+      <c r="G71" s="62" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
@@ -16162,10 +16154,10 @@
       <c r="E72" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F72" s="65" t="n">
+      <c r="F72" s="61" t="n">
         <v>5.5009545454545</v>
       </c>
-      <c r="G72" s="66" t="n">
+      <c r="G72" s="62" t="n">
         <v>0.162483334922081</v>
       </c>
     </row>
@@ -16185,10 +16177,10 @@
       <c r="E73" s="60" t="n">
         <v>30.1455</v>
       </c>
-      <c r="F73" s="65" t="n">
+      <c r="F73" s="61" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="G73" s="66" t="n">
+      <c r="G73" s="62" t="n">
         <v>0.0594103446768007</v>
       </c>
     </row>
@@ -16208,10 +16200,10 @@
       <c r="E74" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F74" s="65" t="n">
+      <c r="F74" s="61" t="n">
         <v>1.3555</v>
       </c>
-      <c r="G74" s="66" t="n">
+      <c r="G74" s="62" t="n">
         <v>0.0400378077417258</v>
       </c>
     </row>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -999,16 +999,16 @@
     <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. "$ Difference" and "% Difference" are now expressed as Us − Them: a positive (red) figure means we are MORE expensive than that competitor; a negative (green) figure means we are cheaper. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
   </si>
   <si>
-    <t xml:space="preserve">Us
-(Our Quoted Price, ex GST)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Closest-Priced
 Competitor (or RSEA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Them
-(Their Price, ex GST)</t>
+    <t xml:space="preserve">Their Price
+(ex GST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Price
+(ex GST, higher of 1200/1220)</t>
   </si>
   <si>
     <t xml:space="preserve">$ Difference
@@ -1589,11 +1589,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1617,11 +1617,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1749,9 +1749,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>405000</xdr:colOff>
+      <xdr:colOff>404640</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>261360</xdr:rowOff>
+      <xdr:rowOff>261000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1765,7 +1765,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2192760" cy="2338920"/>
+          <a:ext cx="2192400" cy="2338560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14141,9 +14141,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
@@ -14219,14 +14220,14 @@
       <c r="C5" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" s="52" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="F5" s="53" t="n">
         <v>16.93275</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="F5" s="53" t="n">
-        <v>20.05</v>
       </c>
       <c r="G5" s="54" t="n">
         <v>-3.11725</v>
@@ -14249,14 +14250,14 @@
       <c r="C6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="56" t="n">
+      <c r="D6" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="52" t="n">
+        <v>122.718181818182</v>
+      </c>
+      <c r="F6" s="56" t="n">
         <v>66.83</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F6" s="53" t="n">
-        <v>122.718181818182</v>
       </c>
       <c r="G6" s="54" t="n">
         <v>-55.888181818182</v>
@@ -14279,14 +14280,14 @@
       <c r="C7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="56" t="n">
+      <c r="D7" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="E7" s="52" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="F7" s="56" t="n">
         <v>44.55</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="F7" s="53" t="n">
-        <v>128.75</v>
       </c>
       <c r="G7" s="54" t="n">
         <v>-84.2</v>
@@ -14309,14 +14310,14 @@
       <c r="C8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="52" t="n">
+        <v>69.245</v>
+      </c>
+      <c r="F8" s="53" t="n">
         <v>45.144</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F8" s="53" t="n">
-        <v>69.245</v>
       </c>
       <c r="G8" s="54" t="n">
         <v>-24.101</v>
@@ -14339,14 +14340,14 @@
       <c r="C9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="E9" s="52" t="n">
+        <v>81.4</v>
+      </c>
+      <c r="F9" s="53" t="n">
         <v>70.538125</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F9" s="53" t="n">
-        <v>81.4</v>
       </c>
       <c r="G9" s="54" t="n">
         <v>-10.861875</v>
@@ -14369,14 +14370,14 @@
       <c r="C10" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="52" t="n">
+        <v>44.209</v>
+      </c>
+      <c r="F10" s="53" t="n">
         <v>33.8555</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="F10" s="53" t="n">
-        <v>44.209</v>
       </c>
       <c r="G10" s="54" t="n">
         <v>-10.3535</v>
@@ -14399,14 +14400,14 @@
       <c r="C11" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="52" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="F11" s="53" t="n">
         <v>45.144</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="F11" s="53" t="n">
-        <v>70.36</v>
       </c>
       <c r="G11" s="54" t="n">
         <v>-25.216</v>
@@ -14429,14 +14430,14 @@
       <c r="C12" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="59" t="n">
+      <c r="D12" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>33.1818181818182</v>
+      </c>
+      <c r="F12" s="60" t="n">
         <v>33.8555</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>325</v>
-      </c>
-      <c r="F12" s="60" t="n">
-        <v>33.1818181818182</v>
       </c>
       <c r="G12" s="61" t="n">
         <v>0.673681818181798</v>
@@ -14459,14 +14460,14 @@
       <c r="C13" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="52" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="F13" s="53" t="n">
         <v>25.394125</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="F13" s="53" t="n">
-        <v>43.09</v>
       </c>
       <c r="G13" s="54" t="n">
         <v>-17.695875</v>
@@ -14489,14 +14490,14 @@
       <c r="C14" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F14" s="53" t="n">
         <v>8.461375</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F14" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G14" s="54" t="n">
         <v>-21.5295340909091</v>
@@ -14519,14 +14520,14 @@
       <c r="C15" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E15" s="52" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F15" s="53" t="n">
         <v>15.81275</v>
-      </c>
-      <c r="E15" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F15" s="53" t="n">
-        <v>40.9</v>
       </c>
       <c r="G15" s="54" t="n">
         <v>-25.08725</v>
@@ -14549,14 +14550,14 @@
       <c r="C16" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="52" t="n">
+      <c r="D16" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F16" s="53" t="n">
         <v>8.461375</v>
-      </c>
-      <c r="E16" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F16" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>-21.5295340909091</v>
@@ -14579,14 +14580,14 @@
       <c r="C17" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="52" t="n">
+      <c r="D17" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>37.3909090909091</v>
+      </c>
+      <c r="F17" s="53" t="n">
         <v>30.1455</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="F17" s="53" t="n">
-        <v>37.3909090909091</v>
       </c>
       <c r="G17" s="54" t="n">
         <v>-7.2454090909091</v>
@@ -14609,14 +14610,14 @@
       <c r="C18" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="59" t="n">
+      <c r="D18" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>28.3545454545455</v>
+      </c>
+      <c r="F18" s="60" t="n">
         <v>30.1455</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="60" t="n">
-        <v>28.3545454545455</v>
       </c>
       <c r="G18" s="61" t="n">
         <v>1.7909545454545</v>
@@ -14639,14 +14640,14 @@
       <c r="C19" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <v>23.3090909090909</v>
+      </c>
+      <c r="F19" s="53" t="n">
         <v>16.93275</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="F19" s="53" t="n">
-        <v>23.3090909090909</v>
       </c>
       <c r="G19" s="54" t="n">
         <v>-6.3763409090909</v>
@@ -14669,14 +14670,14 @@
       <c r="C20" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="59" t="n">
+      <c r="D20" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="F20" s="60" t="n">
         <v>33.8555</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>328</v>
-      </c>
-      <c r="F20" s="60" t="n">
-        <v>28.99</v>
       </c>
       <c r="G20" s="61" t="n">
         <v>4.8655</v>
@@ -14699,14 +14700,14 @@
       <c r="C21" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="52" t="n">
+      <c r="D21" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" s="52" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F21" s="53" t="n">
         <v>12.03275</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="F21" s="53" t="n">
-        <v>21.2</v>
       </c>
       <c r="G21" s="54" t="n">
         <v>-9.16725</v>
@@ -14729,14 +14730,14 @@
       <c r="C22" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="52" t="n">
+      <c r="D22" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F22" s="53" t="n">
         <v>12.03275</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="F22" s="53" t="n">
-        <v>21.2</v>
       </c>
       <c r="G22" s="54" t="n">
         <v>-9.16725</v>
@@ -14759,14 +14760,14 @@
       <c r="C23" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="F23" s="53" t="n">
         <v>6.011375</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F23" s="53" t="n">
-        <v>34.5363636363636</v>
       </c>
       <c r="G23" s="54" t="n">
         <v>-28.5249886363636</v>
@@ -14789,14 +14790,14 @@
       <c r="C24" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="59" t="n">
+      <c r="D24" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="E24" s="59" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="F24" s="60" t="n">
         <v>12.03275</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="F24" s="60" t="n">
-        <v>9.35454545454545</v>
       </c>
       <c r="G24" s="61" t="n">
         <v>2.67820454545455</v>
@@ -14819,14 +14820,14 @@
       <c r="C25" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="59" t="n">
+      <c r="D25" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="E25" s="59" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="F25" s="60" t="n">
         <v>12.03275</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="F25" s="60" t="n">
-        <v>9.35454545454545</v>
       </c>
       <c r="G25" s="61" t="n">
         <v>2.67820454545455</v>
@@ -14849,14 +14850,14 @@
       <c r="C26" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D26" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="52" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F26" s="53" t="n">
         <v>12.03275</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="F26" s="53" t="n">
-        <v>21.2</v>
       </c>
       <c r="G26" s="54" t="n">
         <v>-9.16725</v>
@@ -14879,14 +14880,14 @@
       <c r="C27" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="59" t="n">
+      <c r="D27" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="E27" s="59" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F27" s="60" t="n">
         <v>33.8555</v>
-      </c>
-      <c r="E27" s="57" t="s">
-        <v>325</v>
-      </c>
-      <c r="F27" s="60" t="n">
-        <v>32.5</v>
       </c>
       <c r="G27" s="61" t="n">
         <v>1.3555</v>
@@ -14909,14 +14910,14 @@
       <c r="C28" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="52" t="n">
+      <c r="D28" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="E28" s="52" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" s="53" t="n">
         <v>33.8555</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F28" s="53" t="n">
-        <v>45</v>
       </c>
       <c r="G28" s="54" t="n">
         <v>-11.1445</v>
@@ -14939,14 +14940,14 @@
       <c r="C29" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="56" t="n">
+      <c r="D29" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="E29" s="52" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F29" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F29" s="53" t="n">
-        <v>30.8</v>
       </c>
       <c r="G29" s="54" t="n">
         <v>-17.73</v>
@@ -14969,14 +14970,14 @@
       <c r="C30" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="56" t="n">
+      <c r="D30" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E30" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F30" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E30" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F30" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G30" s="54" t="n">
         <v>-17.93</v>
@@ -14999,14 +15000,14 @@
       <c r="C31" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="56" t="n">
+      <c r="D31" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F31" s="56" t="n">
         <v>16.04</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F31" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G31" s="54" t="n">
         <v>-14.96</v>
@@ -15029,14 +15030,14 @@
       <c r="C32" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="56" t="n">
+      <c r="D32" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E32" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" s="56" t="n">
         <v>16.04</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F32" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G32" s="54" t="n">
         <v>-14.96</v>
@@ -15059,14 +15060,14 @@
       <c r="C33" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="56" t="n">
+      <c r="D33" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E33" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F33" s="56" t="n">
         <v>16.04</v>
-      </c>
-      <c r="E33" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F33" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G33" s="54" t="n">
         <v>-14.96</v>
@@ -15089,14 +15090,14 @@
       <c r="C34" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="56" t="n">
+      <c r="D34" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E34" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34" s="56" t="n">
         <v>16.04</v>
-      </c>
-      <c r="E34" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F34" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G34" s="54" t="n">
         <v>-14.96</v>
@@ -15119,14 +15120,14 @@
       <c r="C35" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="56" t="n">
+      <c r="D35" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E35" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F35" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F35" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G35" s="54" t="n">
         <v>-17.93</v>
@@ -15149,14 +15150,14 @@
       <c r="C36" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="56" t="n">
+      <c r="D36" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E36" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F36" s="56" t="n">
         <v>16.04</v>
-      </c>
-      <c r="E36" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F36" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G36" s="54" t="n">
         <v>-14.96</v>
@@ -15179,14 +15180,14 @@
       <c r="C37" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="56" t="n">
+      <c r="D37" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E37" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F37" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F37" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G37" s="54" t="n">
         <v>-17.93</v>
@@ -15209,14 +15210,14 @@
       <c r="C38" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="56" t="n">
+      <c r="D38" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E38" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F38" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E38" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F38" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G38" s="54" t="n">
         <v>-17.93</v>
@@ -15239,14 +15240,14 @@
       <c r="C39" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="56" t="n">
+      <c r="D39" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E39" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F39" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F39" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G39" s="54" t="n">
         <v>-17.93</v>
@@ -15269,14 +15270,14 @@
       <c r="C40" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="56" t="n">
+      <c r="D40" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E40" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F40" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E40" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F40" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G40" s="54" t="n">
         <v>-17.93</v>
@@ -15299,14 +15300,14 @@
       <c r="C41" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="56" t="n">
+      <c r="D41" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E41" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F41" s="56" t="n">
         <v>13.07</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F41" s="53" t="n">
-        <v>31</v>
       </c>
       <c r="G41" s="54" t="n">
         <v>-17.93</v>
@@ -15329,14 +15330,14 @@
       <c r="C42" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="56" t="n">
+      <c r="D42" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E42" s="52" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="F42" s="56" t="n">
         <v>5.35</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F42" s="53" t="n">
-        <v>34.5363636363636</v>
       </c>
       <c r="G42" s="54" t="n">
         <v>-29.1863636363636</v>
@@ -15359,14 +15360,14 @@
       <c r="C43" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="56" t="n">
+      <c r="D43" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E43" s="52" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="F43" s="56" t="n">
         <v>2.67</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="F43" s="53" t="n">
-        <v>9.35454545454545</v>
       </c>
       <c r="G43" s="54" t="n">
         <v>-6.68454545454545</v>
@@ -15389,14 +15390,14 @@
       <c r="C44" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="56" t="n">
+      <c r="D44" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E44" s="52" t="n">
+        <v>23.4090909090909</v>
+      </c>
+      <c r="F44" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F44" s="53" t="n">
-        <v>23.4090909090909</v>
       </c>
       <c r="G44" s="54" t="n">
         <v>-12.7190909090909</v>
@@ -15419,14 +15420,14 @@
       <c r="C45" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="56" t="n">
+      <c r="D45" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E45" s="52" t="n">
+        <v>22.7181818181818</v>
+      </c>
+      <c r="F45" s="56" t="n">
         <v>2.67</v>
-      </c>
-      <c r="E45" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F45" s="53" t="n">
-        <v>22.7181818181818</v>
       </c>
       <c r="G45" s="54" t="n">
         <v>-20.0481818181818</v>
@@ -15449,14 +15450,14 @@
       <c r="C46" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="56" t="n">
+      <c r="D46" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E46" s="52" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F46" s="56" t="n">
         <v>9.5</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F46" s="53" t="n">
-        <v>40.9</v>
       </c>
       <c r="G46" s="54" t="n">
         <v>-31.4</v>
@@ -15479,14 +15480,14 @@
       <c r="C47" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="56" t="n">
+      <c r="D47" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E47" s="52" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F47" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F47" s="53" t="n">
-        <v>40.9</v>
       </c>
       <c r="G47" s="54" t="n">
         <v>-30.21</v>
@@ -15509,14 +15510,14 @@
       <c r="C48" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="56" t="n">
+      <c r="D48" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E48" s="52" t="n">
+        <v>20.9090909090909</v>
+      </c>
+      <c r="F48" s="56" t="n">
         <v>5.35</v>
-      </c>
-      <c r="E48" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F48" s="53" t="n">
-        <v>20.9090909090909</v>
       </c>
       <c r="G48" s="54" t="n">
         <v>-15.5590909090909</v>
@@ -15539,14 +15540,14 @@
       <c r="C49" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="56" t="n">
+      <c r="D49" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E49" s="52" t="n">
+        <v>9.35454545454545</v>
+      </c>
+      <c r="F49" s="56" t="n">
         <v>5.35</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="F49" s="53" t="n">
-        <v>9.35454545454545</v>
       </c>
       <c r="G49" s="54" t="n">
         <v>-4.00454545454545</v>
@@ -15569,14 +15570,14 @@
       <c r="C50" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="56" t="n">
+      <c r="D50" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E50" s="52" t="n">
+        <v>25.4454545454545</v>
+      </c>
+      <c r="F50" s="56" t="n">
         <v>2.67</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F50" s="53" t="n">
-        <v>25.4454545454545</v>
       </c>
       <c r="G50" s="54" t="n">
         <v>-22.7754545454545</v>
@@ -15599,14 +15600,14 @@
       <c r="C51" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="56" t="n">
+      <c r="D51" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51" s="52" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F51" s="56" t="n">
         <v>9.5</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F51" s="53" t="n">
-        <v>40.9</v>
       </c>
       <c r="G51" s="54" t="n">
         <v>-31.4</v>
@@ -15629,14 +15630,14 @@
       <c r="C52" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="56" t="n">
+      <c r="D52" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="E52" s="52" t="n">
+        <v>7.81818181818182</v>
+      </c>
+      <c r="F52" s="56" t="n">
         <v>2</v>
-      </c>
-      <c r="E52" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F52" s="53" t="n">
-        <v>7.81818181818182</v>
       </c>
       <c r="G52" s="54" t="n">
         <v>-5.81818181818182</v>
@@ -15659,14 +15660,14 @@
       <c r="C53" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D53" s="56" t="n">
+      <c r="D53" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E53" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F53" s="56" t="n">
         <v>2.67</v>
-      </c>
-      <c r="E53" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F53" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G53" s="54" t="n">
         <v>-27.3209090909091</v>
@@ -15689,14 +15690,14 @@
       <c r="C54" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="56" t="n">
+      <c r="D54" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E54" s="52" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="F54" s="56" t="n">
         <v>4.01</v>
-      </c>
-      <c r="E54" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F54" s="53" t="n">
-        <v>34.5363636363636</v>
       </c>
       <c r="G54" s="54" t="n">
         <v>-30.5263636363636</v>
@@ -15719,14 +15720,14 @@
       <c r="C55" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D55" s="56" t="n">
+      <c r="D55" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E55" s="52" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="F55" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F55" s="53" t="n">
-        <v>34.5363636363636</v>
       </c>
       <c r="G55" s="54" t="n">
         <v>-23.8463636363636</v>
@@ -15749,14 +15750,14 @@
       <c r="C56" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="56" t="n">
+      <c r="D56" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E56" s="52" t="n">
+        <v>34.5363636363636</v>
+      </c>
+      <c r="F56" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F56" s="53" t="n">
-        <v>34.5363636363636</v>
       </c>
       <c r="G56" s="54" t="n">
         <v>-23.8463636363636</v>
@@ -15779,14 +15780,14 @@
       <c r="C57" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="56" t="n">
+      <c r="D57" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E57" s="52" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F57" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F57" s="53" t="n">
-        <v>40.9</v>
       </c>
       <c r="G57" s="54" t="n">
         <v>-30.21</v>
@@ -15809,14 +15810,14 @@
       <c r="C58" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="56" t="n">
+      <c r="D58" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E58" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F58" s="56" t="n">
         <v>2.89</v>
-      </c>
-      <c r="E58" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F58" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G58" s="54" t="n">
         <v>-27.1009090909091</v>
@@ -15839,14 +15840,14 @@
       <c r="C59" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="56" t="n">
+      <c r="D59" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E59" s="52" t="n">
+        <v>45.4454545454545</v>
+      </c>
+      <c r="F59" s="56" t="n">
         <v>1.94</v>
-      </c>
-      <c r="E59" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F59" s="53" t="n">
-        <v>45.4454545454545</v>
       </c>
       <c r="G59" s="54" t="n">
         <v>-43.5054545454545</v>
@@ -15869,14 +15870,14 @@
       <c r="C60" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D60" s="56" t="n">
+      <c r="D60" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="E60" s="52" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="F60" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E60" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="F60" s="53" t="n">
-        <v>43.55</v>
       </c>
       <c r="G60" s="54" t="n">
         <v>-32.86</v>
@@ -15899,14 +15900,14 @@
       <c r="C61" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="56" t="n">
+      <c r="D61" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E61" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F61" s="56" t="n">
         <v>3.201</v>
-      </c>
-      <c r="E61" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F61" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G61" s="54" t="n">
         <v>-26.7899090909091</v>
@@ -15929,14 +15930,14 @@
       <c r="C62" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D62" s="56" t="n">
+      <c r="D62" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E62" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F62" s="56" t="n">
         <v>5.35</v>
-      </c>
-      <c r="E62" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F62" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G62" s="54" t="n">
         <v>-24.6409090909091</v>
@@ -15959,14 +15960,14 @@
       <c r="C63" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="56" t="n">
+      <c r="D63" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E63" s="52" t="n">
+        <v>29.9909090909091</v>
+      </c>
+      <c r="F63" s="56" t="n">
         <v>2.67</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="F63" s="53" t="n">
-        <v>29.9909090909091</v>
       </c>
       <c r="G63" s="54" t="n">
         <v>-27.3209090909091</v>
@@ -15989,14 +15990,14 @@
       <c r="C64" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D64" s="56" t="n">
+      <c r="D64" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E64" s="52" t="n">
+        <v>27.2727272727273</v>
+      </c>
+      <c r="F64" s="56" t="n">
         <v>10.69</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F64" s="53" t="n">
-        <v>27.2727272727273</v>
       </c>
       <c r="G64" s="54" t="n">
         <v>-16.5827272727273</v>
@@ -16056,10 +16057,10 @@
       <c r="C68" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="D68" s="60" t="n">
+      <c r="D68" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E68" s="60" t="n">
+      <c r="E68" s="59" t="n">
         <v>16.93275</v>
       </c>
       <c r="F68" s="61" t="n">
@@ -16079,10 +16080,10 @@
       <c r="C69" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="D69" s="60" t="n">
+      <c r="D69" s="59" t="n">
         <v>21.2</v>
       </c>
-      <c r="E69" s="60" t="n">
+      <c r="E69" s="59" t="n">
         <v>33.8555</v>
       </c>
       <c r="F69" s="61" t="n">
@@ -16102,10 +16103,10 @@
       <c r="C70" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="D70" s="60" t="n">
+      <c r="D70" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E70" s="60" t="n">
+      <c r="E70" s="59" t="n">
         <v>12.03275</v>
       </c>
       <c r="F70" s="61" t="n">
@@ -16125,10 +16126,10 @@
       <c r="C71" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="D71" s="60" t="n">
+      <c r="D71" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E71" s="60" t="n">
+      <c r="E71" s="59" t="n">
         <v>12.03275</v>
       </c>
       <c r="F71" s="61" t="n">
@@ -16148,10 +16149,10 @@
       <c r="C72" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="D72" s="60" t="n">
+      <c r="D72" s="59" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E72" s="60" t="n">
+      <c r="E72" s="59" t="n">
         <v>33.8555</v>
       </c>
       <c r="F72" s="61" t="n">
@@ -16171,10 +16172,10 @@
       <c r="C73" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="D73" s="60" t="n">
+      <c r="D73" s="59" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E73" s="60" t="n">
+      <c r="E73" s="59" t="n">
         <v>30.1455</v>
       </c>
       <c r="F73" s="61" t="n">
@@ -16194,10 +16195,10 @@
       <c r="C74" s="57" t="s">
         <v>325</v>
       </c>
-      <c r="D74" s="60" t="n">
+      <c r="D74" s="59" t="n">
         <v>32.5</v>
       </c>
-      <c r="E74" s="60" t="n">
+      <c r="E74" s="59" t="n">
         <v>33.8555</v>
       </c>
       <c r="F74" s="61" t="n">

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="RSEA Safety Signs" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="345">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -733,13 +733,13 @@
     <t xml:space="preserve">Median RSEA price vs our quote (ex GST) — less skewed by outliers</t>
   </si>
   <si>
-    <t xml:space="preserve">Market-Wide Price Comparison — Our Pricing, RSEA &amp; 9 Retailers (All GST Bases Confirmed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methodology: all 9 retailers' GST treatment is now confirmed (4 stated it directly on-site; the remaining 5 — Safety Signs Australia, SafetyXpress, Traffic Control Products, National Safety Signs, Seton — were confirmed by direct check). Safety Signs Australia, SafetyXpress, National Safety Signs and Seton display prices INC GST; Traffic Control Products displays EX GST; HiVis displays EX GST; Jaybro and eSafety Supplies display both inc and ex GST directly; All Trades Group marks its prices "Tax included" (INC GST). Every price below is shown both ex and inc GST, with whichever figure is NOT the retailer's own displayed figure calculated (×1.1 or ÷1.1). Our Quoted Price (both 1200- and 1220-stock) and the RSEA Website Price are pulled by formula from the 'RSEA vs Quoted Comparison' tab; competitor figures were captured live from each retailer's own website on 14 October 2026 and are hardcoded (not formulas) since they come from outside this workbook.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where a retailer did not carry the exact size/material of our line item, the closest equivalent sign TYPE was used instead and the mismatch is flagged in the Notes column — treat those rows as directionally indicative, not an exact apples-to-apples match. "N/A" means that retailer does not appear to carry a comparable product (confirmed via the research, not a blank/forgotten cell). Seton additionally blocked direct automated access (403/bot protection) during research, so its prices were recovered from search-engine cache only and are flagged LOW CONFIDENCE in the Notes column — that is a data-reliability flag, separate from its (confirmed) GST treatment. Sources: hivis.com/collections/signage · jaybro.com.au/road-traffic/permanent-signs/regulatory-signs/ · alltradesgroup.net.au/collections/site-safety-signage-roads-traffic-signs · esafetysupplies.com.au/collections/traffic-road-safety-sign · safetysigns.com.au/collections/road-car-park-signs · safetyxpress.com.au/traffic-signs/ · trafficcontrolproducts.com.au/collections/road-signs-traffic · nationalsafetysigns.com.au/product-category/road-and-traffic-signs/road-signs/ · seton.net.au. Captured 14 October 2026.</t>
+    <t xml:space="preserve">Market-Wide Price Comparison — Our Pricing, RSEA &amp; 10 Retailers (All GST Bases Confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methodology: all 9 retailers' GST treatment is now confirmed (4 stated it directly on-site; the remaining 5 — Safety Signs Australia, SafetyXpress, Traffic Control Products, National Safety Signs, Seton — were confirmed by direct check). Safety Signs Australia, SafetyXpress, National Safety Signs and Seton display prices INC GST; Traffic Control Products displays EX GST; HiVis displays EX GST; Jaybro and eSafety Supplies display both inc and ex GST directly; All Trades Group marks its prices "Tax included" (INC GST). Every price below is shown both ex and inc GST, with whichever figure is NOT the retailer's own displayed figure calculated (×1.1 or ÷1.1). Our Quoted Price (both 1200- and 1220-stock) and the RSEA Website Price are pulled by formula from the 'RSEA vs Quoted Comparison' tab; competitor figures were captured live from each retailer's own website on 14 October 2026 and are hardcoded (not formulas) since they come from outside this workbook. Advanced Group (advancedgroup.com.au) was added on 15 October 2026 as a 10th competitor: its per-item prices are individually labelled 'Inc GST' (a generic 'all prices are GST exclusive' banner also appears on some of its category pages but conflicts with every per-item label, so it is treated as boilerplate and the per-item Inc-GST label is used, same convention as the other as-shown-inc retailers above). Its catalogue runs to 200+ paginated categories, so research there was a representative sample, not exhaustive — rows with no Advanced Group price are genuinely unresearched (left blank), not confirmed-absent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where a retailer did not carry the exact size/material of our line item, the closest equivalent sign TYPE was used instead and the mismatch is flagged in the Notes column — treat those rows as directionally indicative, not an exact apples-to-apples match. "N/A" means that retailer does not appear to carry a comparable product (confirmed via the research, not a blank/forgotten cell). Seton additionally blocked direct automated access (403/bot protection) during research, so its prices were recovered from search-engine cache only and are flagged LOW CONFIDENCE in the Notes column — that is a data-reliability flag, separate from its (confirmed) GST treatment. Sources: hivis.com/collections/signage · jaybro.com.au/road-traffic/permanent-signs/regulatory-signs/ · alltradesgroup.net.au/collections/site-safety-signage-roads-traffic-signs · esafetysupplies.com.au/collections/traffic-road-safety-sign · safetysigns.com.au/collections/road-car-park-signs · safetyxpress.com.au/traffic-signs/ · trafficcontrolproducts.com.au/collections/road-signs-traffic · nationalsafetysigns.com.au/product-category/road-and-traffic-signs/road-signs/ · seton.net.au · advancedgroup.com.au (Advanced Group, captured 15 October 2026, representative sample only — see methodology above). Captured 14 October 2026 unless noted.</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis
@@ -814,8 +814,16 @@
 (ex GST)</t>
   </si>
   <si>
+    <t xml:space="preserve">Advanced Group
+(inc GST, as shown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Group
+(ex GST, calc.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cheapest of RSEA +
-9 Competitors (ex GST)</t>
+10 Competitors (ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">Our Quote (1200 Stock)
@@ -840,22 +848,22 @@
     <t xml:space="preserve">Swing-stand temporary traffic-control sign - no comparable product found at any of the 9 researched retailers.</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: 600x600/750x750/900x900 options | Jaybro: 600x600 exact | All Trades Group: 600mm (450/600/750 avail) | eSafety Supplies: 600x600 exact | Safety Signs Australia: 600x600 Class1 refl alu | SafetyXpress: range 84.67-127.50, midpoint used | Traffic Control Products: 600x600 'Hexagonal' CL1X (alt 750x750=$75) | National Safety Signs: From, 600x600 or 750x750 | Seton: LOW conf - conflicting cache (also 183.95/169.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 750/900/1200mm | Jaybro: 750x750 exact | All Trades Group: 750mm triangular | eSafety Supplies: 750mm triangle | Safety Signs Australia: 750mm | SafetyXpress: 750mm | Traffic Control Products: 750mm | National Safety Signs: From, 750 or 900mm | Seton: LOW conf - 6-pack bulk tier price, single-unit unconfirmed</t>
+    <t xml:space="preserve">HiVis: 600x600/750x750/900x900 options | Jaybro: 600x600 exact | All Trades Group: 600mm (450/600/750 avail) | eSafety Supplies: 600x600 exact | Safety Signs Australia: 600x600 Class1 refl alu | SafetyXpress: range 84.67-127.50, midpoint used | Traffic Control Products: 600x600 'Hexagonal' CL1X (alt 750x750=$75) | National Safety Signs: From, 600x600 or 750x750 | Seton: LOW conf - conflicting cache (also 183.95/169.50) | Advanced Group: generic 'Stop Sign - Class 1 Reflective on Aluminium' (R1-1 family); specific 600mm size/variant price not independently confirmed on listing page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 750/900/1200mm | Jaybro: 750x750 exact | All Trades Group: 750mm triangular | eSafety Supplies: 750mm triangle | Safety Signs Australia: 750mm | SafetyXpress: 750mm | Traffic Control Products: 750mm | National Safety Signs: From, 750 or 900mm | Seton: LOW conf - 6-pack bulk tier price, single-unit unconfirmed | Advanced Group: generic 'Give Way Sign' (R1-2 family, triangle); 750mm size/variant not independently confirmed</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: 300x400/450x600/600x800 | Jaybro: 450x600 exact | All Trades Group: 600x450mm | eSafety Supplies: 450x600 exact, sale price (was 86.65) | Safety Signs Australia: 450x600 | SafetyXpress: 450x600 | Traffic Control Products: 450x600 | National Safety Signs: From, 400x300/600x450/800x600 | Seton: MEDIUM conf, 450x600</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: 600/750/900mm | Jaybro: 600mm exact | All Trades Group: 600x600 or 750x750 (W6-1, size differs from 600mm round) | eSafety Supplies: 600mm exact | Safety Signs Australia: 600mm dia | SafetyXpress: 600mm dia | Traffic Control Products: 600mm dia | National Safety Signs: From, 600 or 750mm round | Seton: MEDIUM conf, 600mm dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 10km/h, 450x600/600x800/900x1200 | Jaybro: 10km/h, 450x600 exact | All Trades Group: 10km/h, 300x225 or 600x450 | eSafety Supplies: 10km/h, 450x600 exact | Safety Signs Australia: 10km/h, 450x600 | SafetyXpress: 10km/h, upper of 25.64-31.19 range, 450x600 | Traffic Control Products: Not stocked - site only has 40-100km/h plates | National Safety Signs: From; custom-text R4-1 sign, speed typed in, shared across all speed rows | Seton: LOW conf, ~42-46 range, 450x600 Flute not alu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 450x750, size differs from 450x450 | Jaybro: 450x450 exact | All Trades Group: 600x450, size differs | eSafety Supplies: 450x450 exact | Safety Signs Australia: 450x450 exact | SafetyXpress: range 72.28-80.84, 450x450 exact | Traffic Control Products: 450x750, size differs | National Safety Signs: From, 450x450 avail | Seton: MEDIUM conf, 750x750 (not 450x450)</t>
+    <t xml:space="preserve">HiVis: 600/750/900mm | Jaybro: 600mm exact | All Trades Group: 600x600 or 750x750 (W6-1, size differs from 600mm round) | eSafety Supplies: 600mm exact | Safety Signs Australia: 600mm dia | SafetyXpress: 600mm dia | Traffic Control Products: 600mm dia | National Safety Signs: From, 600 or 750mm round | Seton: MEDIUM conf, 600mm dia | Advanced Group: 'Pedestrian Crossing Sign - Fluoro Reflective' (R3-1); colour/size variant not independently confirmed (listed as 'multiple sizes to choose from')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 10km/h, 450x600/600x800/900x1200 | Jaybro: 10km/h, 450x600 exact | All Trades Group: 10km/h, 300x225 or 600x450 | eSafety Supplies: 10km/h, 450x600 exact | Safety Signs Australia: 10km/h, 450x600 | SafetyXpress: 10km/h, upper of 25.64-31.19 range, 450x600 | Traffic Control Products: Not stocked - site only has 40-100km/h plates | National Safety Signs: From; custom-text R4-1 sign, speed typed in, shared across all speed rows | Seton: LOW conf, ~42-46 range, 450x600 Flute not alu | Advanced Group: generic 'Speed Limit (Speed Restriction) Sign' (R4-1), exact 450x600 size match; specific km value chosen at checkout, not SKU-confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 450x750, size differs from 450x450 | Jaybro: 450x450 exact | All Trades Group: 600x450, size differs | eSafety Supplies: 450x450 exact | Safety Signs Australia: 450x450 exact | SafetyXpress: range 72.28-80.84, 450x450 exact | Traffic Control Products: 450x750, size differs | National Safety Signs: From, 450x450 avail | Seton: MEDIUM conf, 750x750 (not 450x450) | Advanced Group: 'R2-4 No Entry Sign Reflective on Aluminium'; code matches (R2-4), exact size variant not stated on listing page</t>
   </si>
   <si>
     <t xml:space="preserve">Generic site/warehouse danger sign - no comparable product found at any of the 9 researched retailers (out of scope: these retailers focus on road/traffic signage).</t>
@@ -894,19 +902,19 @@
     <t xml:space="preserve">Jaybro: Not found | All Trades Group: 450x300 exact size option | eSafety Supplies: 300x450, 3mm ACP | Safety Signs Australia: 300x450, close | SafetyXpress: 300x450, close | Traffic Control Products: Not found | National Safety Signs: From | Seton: From, inc GST, 300x450</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: Not stocked (no 5km/h plate) | Jaybro: Not found separately | All Trades Group: Generic 5km/h reused, CL1 reflective not confirmed | eSafety Supplies: 5km/h, confirmed '1.6mm aluminium Class1 reflective' - good match | Safety Signs Australia: Generic 5km/h reused, size/spec differs | SafetyXpress: CL1/400 reflective alu, 450x600 - good match | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 20km/h, SKU reused across speeds | Jaybro: 20km/h, 450x600 exact | All Trades Group: 20km/h, 600x450 dedicated item | eSafety Supplies: 20km/h, 450x600 dedicated item | Safety Signs Australia: 20km/h, 450x600 | SafetyXpress: CL1/400 reflective, range 98.07-130.08, midpoint | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 1800x600, Boxed Edge STEEL not corflute - material/size differ | Jaybro: Not found (only POA corflute detour sign on site) | All Trades Group: Only $199.50 swing-stand version, not flat panel | eSafety Supplies: Not found | Safety Signs Australia: 300x1200, 6mm Corflute Class1 - exact match | SafetyXpress: 1200x300 corflute - good match | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: Not found</t>
+    <t xml:space="preserve">HiVis: Not stocked (no 5km/h plate) | Jaybro: Not found separately | All Trades Group: Generic 5km/h reused, CL1 reflective not confirmed | eSafety Supplies: 5km/h, confirmed '1.6mm aluminium Class1 reflective' - good match | Safety Signs Australia: Generic 5km/h reused, size/spec differs | SafetyXpress: CL1/400 reflective alu, 450x600 - good match | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Advanced Group: same generic 'Speed Limit (Speed Restriction) Sign' (R4-1) as other speed items, 600x450 = 450x600 rotated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 20km/h, SKU reused across speeds | Jaybro: 20km/h, 450x600 exact | All Trades Group: 20km/h, 600x450 dedicated item | eSafety Supplies: 20km/h, 450x600 dedicated item | Safety Signs Australia: 20km/h, 450x600 | SafetyXpress: CL1/400 reflective, range 98.07-130.08, midpoint | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Advanced Group: same generic 'Speed Limit (Speed Restriction) Sign' (R4-1) as other speed items, 600x450 = 450x600 rotated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 1800x600, Boxed Edge STEEL not corflute - material/size differ | Jaybro: Not found (only POA corflute detour sign on site) | All Trades Group: Only $199.50 swing-stand version, not flat panel | eSafety Supplies: Not found | Safety Signs Australia: 300x1200, 6mm Corflute Class1 - exact match | SafetyXpress: 1200x300 corflute - good match | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: Not found | Advanced Group: 'On Side Road - Corflute Sign 1200x300mm' (M123-T1-19); exact size/type match</t>
   </si>
   <si>
     <t xml:space="preserve">eSafety Supplies: Not found | Safety Signs Australia: 600x600, 6mm Corflute Class1 - exact match (confirms Jess's size assumption) | SafetyXpress: range 30.24-64.03 incl 600x600 | Traffic Control Products: Not found separately | National Safety Signs: From, was 70.65, 600x600 MM981, yellow colour not confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: 1200x900, Boxed Edge STEEL 'Workmen Ahead Digger Man' not corflute | All Trades Group: Only swing-stand version exists | Safety Signs Australia: 600x600, 'Workmen' closest wording, 6mm Corflute | SafetyXpress: range 58.84-114.86 incl 600x600 | Traffic Control Products: 600x600, 'Digger Workman' corflute MMS - good match | National Safety Signs: Not found (closest is different boxed-edge sign)</t>
+    <t xml:space="preserve">HiVis: 1200x900, Boxed Edge STEEL 'Workmen Ahead Digger Man' not corflute | All Trades Group: Only swing-stand version exists | Safety Signs Australia: 600x600, 'Workmen' closest wording, 6mm Corflute | SafetyXpress: range 58.84-114.86 incl 600x600 | Traffic Control Products: 600x600, 'Digger Workman' corflute MMS - good match | National Safety Signs: Not found (closest is different boxed-edge sign) | Advanced Group: 'Workers Ahead (Symbolic Worker) 600x600mm Corflute Sign' (M66-T1-5); exact size match, wording 'Workers Ahead' vs our 'Symbolic Worker'</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL '40,60km/h Roadwork' not corflute | Safety Signs Australia: 600x600, '60 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: Not found (TCP only has 40/END40, no plain 60) | National Safety Signs: From, was 70.65, MM916 '60 kph' 600x600</t>
@@ -915,10 +923,10 @@
     <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL, same SKU as 60km item | Safety Signs Australia: 600x600, '40 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: 600x600, '40 (Speed)' corflute MMS - exact match | National Safety Signs: From, was 70.65, MM915 '40 kph' 600x600</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: From; 900x600/1200x900, Boxed Edge STEEL not corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact size &amp; material | SafetyXpress: range 58.84-59.26, 600x600 or 1200x300 corflute | Traffic Control Products: 600x600, 'PTS' corflute MMS, size differs from 1200x300 | National Safety Signs: From, was 70.65, MM914, 600x600, size differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: From; 1800x600/2400x900, Boxed Edge STEEL not corflute | All Trades Group: 600x600, confirmed 6mm corflute, size differs from 1200x300 | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: range 57.75-90.17 incl 1200x300 | Traffic Control Products: 1200x300, corflute MMS reflective - exact match | National Safety Signs: From, was 70.65, MM920, 600x600, size differs</t>
+    <t xml:space="preserve">HiVis: From; 900x600/1200x900, Boxed Edge STEEL not corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact size &amp; material | SafetyXpress: range 58.84-59.26, 600x600 or 1200x300 corflute | Traffic Control Products: 600x600, 'PTS' corflute MMS, size differs from 1200x300 | National Safety Signs: From, was 70.65, MM914, 600x600, size differs | Advanced Group: 'Prepare To Stop - Corflute Sign 1200x300mm' (M123-T1-18); exact match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: From; 1800x600/2400x900, Boxed Edge STEEL not corflute | All Trades Group: 600x600, confirmed 6mm corflute, size differs from 1200x300 | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: range 57.75-90.17 incl 1200x300 | Traffic Control Products: 1200x300, corflute MMS reflective - exact match | National Safety Signs: From, was 70.65, MM920, 600x600, size differs | Advanced Group: 'Roadwork Ahead Sign 1200x300mm' (M123-T1-1); exact match</t>
   </si>
   <si>
     <t xml:space="preserve">Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: 1200x300, 'White on Blue' corflute MMS - exact match | National Safety Signs: Not found</t>
@@ -939,16 +947,25 @@
     <t xml:space="preserve">HiVis: 1200x300, 3mm aluminium Class400, not corflute but same size | eSafety Supplies: 1200x300, steel 3M Class1, NOT corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 MMS board, corflute | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: From, was 70.65, MM905 left variant, 600x600, size differs</t>
   </si>
   <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Security Sign This Area Is..450x300 Poly' (841756); exact size/material match, full wording truncated on listing (not independently confirmed as '24 hour surveillance')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 300x225 exact | All Trades Group: two fetches disagreed (42.50 vs 28.30); 300x225/450x300/600x450 avail | eSafety Supplies: 300x450, closest size | Safety Signs Australia: Not found - no exact wording/size/material match | SafetyXpress: 225x300, close | Traffic Control Products: Not found | National Safety Signs: From, M1890 | Seton: LOW conf, bulk tier range 31.16-34.28, 300x225 poly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 600x450 exact | All Trades Group: 600x450 exact | eSafety Supplies: 600x450 exact | Safety Signs Australia: 18.00(corflute)/33.50(metal) avg, 450x600 size differs slightly | SafetyXpress: Not found - only differently-worded 'Construction Site Office' sign | Traffic Control Products: 600x450 exact, poly | National Safety Signs: Not found (only differently-worded 'All Vehicles Report')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'Fire Naked Flame And..300x225 Poly' (840048); exact size/material, exact wording not confirmed (truncated on listing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Danger Construction..600x450 Polyp' (844510); size differs (600x450 vs our 600x400)</t>
+  </si>
+  <si>
     <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range.</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaybro: 300x225 exact | All Trades Group: two fetches disagreed (42.50 vs 28.30); 300x225/450x300/600x450 avail | eSafety Supplies: 300x450, closest size | Safety Signs Australia: Not found - no exact wording/size/material match | SafetyXpress: 225x300, close | Traffic Control Products: Not found | National Safety Signs: From, M1890 | Seton: LOW conf, bulk tier range 31.16-34.28, 300x225 poly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: 600x450 exact | All Trades Group: 600x450 exact | eSafety Supplies: 600x450 exact | Safety Signs Australia: 18.00(corflute)/33.50(metal) avg, 450x600 size differs slightly | SafetyXpress: Not found - only differently-worded 'Construction Site Office' sign | Traffic Control Products: 600x450 exact, poly | National Safety Signs: Not found (only differently-worded 'All Vehicles Report')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: wording lacks 'By Permit' | Safety Signs Australia: 300x450 poly, size differs slightly, wording lacks 'By Permit' | SafetyXpress: 225x300 or 450x600, no exact 450x300, 'By Permit Only' wording exact | Traffic Control Products: 300x225 metal not poly, size differs, 'By Permit Only' wording exact | National Safety Signs: Not found</t>
+    <t xml:space="preserve">Jaybro: wording lacks 'By Permit' | Safety Signs Australia: 300x450 poly, size differs slightly, wording lacks 'By Permit' | SafetyXpress: 225x300 or 450x600, no exact 450x300, 'By Permit Only' wording exact | Traffic Control Products: 300x225 metal not poly, size differs, 'By Permit Only' wording exact | National Safety Signs: Not found | Advanced Group: 'Confined Space Entry By..450x300 Poly' (835604); exact size/material match</t>
   </si>
   <si>
     <t xml:space="preserve">Jaybro: 225x300, size differs from 450x300 | All Trades Group: 450x300 exact size | eSafety Supplies: 300x450, size differs slightly, polypropylene | Safety Signs Australia: 300x450 poly, size differs slightly | SafetyXpress: range 25.15-44.87 incl 300x450 | Traffic Control Products: 19.50/26.50 two sizes (300x225/450x600), no exact 450x300 | National Safety Signs: From, E1217</t>
@@ -960,13 +977,19 @@
     <t xml:space="preserve">n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">All Trades Group: 900x600 corflute, size differs (larger) | Safety Signs Australia: 450x600 poly EXACT | SafetyXpress: 450x600 metal EXACT size, material differs | Traffic Control Products: 600x450, 'Danger Crane Working Overhead' - different wording, poly | National Safety Signs: From, D10279 | Seton: LOW conf, bulk tier range 33.21-36.91, 600x450 Flute</t>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'RESTR AREA AUTHORISED..600X450 POLY' (845084); wording differs (Restricted Area Authorised vs our Warning Authorised Personnel), same size/material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'Hazardous Materials Area..300x225 Poly' (840344); related hazard wording, not an exact match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Trades Group: 900x600 corflute, size differs (larger) | Safety Signs Australia: 450x600 poly EXACT | SafetyXpress: 450x600 metal EXACT size, material differs | Traffic Control Products: 600x450, 'Danger Crane Working Overhead' - different wording, poly | National Safety Signs: From, D10279 | Seton: LOW conf, bulk tier range 33.21-36.91, 600x450 Flute | Advanced Group: 'Danger Overhead Power Lines 450x600mm' (850599); size matches (rotated), material not stated on listing</t>
   </si>
   <si>
     <t xml:space="preserve">Items compared (60 total line items)</t>
   </si>
   <si>
-    <t xml:space="preserve">Total numeric price points captured across these 9 retailers (ex GST columns)</t>
+    <t xml:space="preserve">Total numeric price points captured across these 10 retailers (ex GST columns)</t>
   </si>
   <si>
     <t xml:space="preserve">Items where our 1200-Stock quote is cheaper than the cheapest of RSEA/competitors</t>
@@ -996,7 +1019,7 @@
     <t xml:space="preserve">Summary — Closest-Priced Competitor &amp; Where We're More Expensive</t>
   </si>
   <si>
-    <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. "$ Difference" and "% Difference" are now expressed as Us − Them: a positive (red) figure means we are MORE expensive than that competitor; a negative (green) figure means we are cheaper. Figures pulled from the 'Market Comparison' tab as of 15 October 2026 — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
+    <t xml:space="preserve">For each of our 60 line items: "Our Quoted Price" below is whichever is HIGHER of our 1200-stock or 1220-stock quoted price (shown in blue bold when the 1220-stock price was the higher/used figure, plain black when the 1200-stock price was used — e.g. for items with no 1220-stock price at all, such as the swing-stand products). Against that price, this sheet shows the competitor (or RSEA) whose ex-GST price is CLOSEST to ours — above or below — with the $ and % gap. Rows shaded amber are ones where that closest competitor (or, in some cases, a different cheaper one — see the call-out list below) is actually cheaper than us. "$ Difference" is expressed as Us − Them: a positive (red) figure means we are MORE expensive than that competitor; a negative (green) figure means we are cheaper. "% Difference" is that $ gap as a percentage of THEIR price (not ours). Figures pulled from the 'Market Comparison' tab, now including Advanced Group (advancedgroup.com.au) as a 10th competitor (added 15 October 2026) — re-run this summary if competitor prices there change. All $ / % figures compare ex-GST prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Closest-Priced
@@ -1016,7 +1039,7 @@
   </si>
   <si>
     <t xml:space="preserve">% Difference
-(Us vs Them)</t>
+(vs Their Price)</t>
   </si>
   <si>
     <t xml:space="preserve">Are We More
@@ -1057,6 +1080,9 @@
   </si>
   <si>
     <t xml:space="preserve">Safety Signs Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Group</t>
   </si>
   <si>
     <t xml:space="preserve">Items We're MORE EXPENSIVE On (our higher-of-1200/1220 quote vs the single cheapest alternative — 7 of 60 items)</t>
@@ -1317,14 +1343,14 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color theme="4" tint="0.3997"/>
+        <color theme="4" tint="0.3996"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.3997"/>
+        <color theme="4" tint="0.3996"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.3997"/>
+        <color theme="4" tint="0.3996"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1332,10 +1358,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.3997"/>
+        <color theme="4" tint="0.3996"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.3997"/>
+        <color theme="4" tint="0.3996"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1718,7 +1744,7 @@
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF1F6FEB"/>
-      <rgbColor rgb="FF45B1E1"/>
+      <rgbColor rgb="FF45B0E1"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -1749,9 +1775,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>404640</xdr:colOff>
+      <xdr:colOff>403920</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>261000</xdr:rowOff>
+      <xdr:rowOff>260280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1765,7 +1791,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2192400" cy="2338560"/>
+          <a:ext cx="2191680" cy="2337840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7340,7 +7366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AG77"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
@@ -7550,6 +7576,12 @@
       <c r="AE5" s="25" t="s">
         <v>256</v>
       </c>
+      <c r="AF5" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="AG5" s="25" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -7586,16 +7618,16 @@
         <v>39.0818181818182</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N6" s="11" t="n">
         <v>42.5</v>
@@ -7625,10 +7657,10 @@
         <v>28.3545454545455</v>
       </c>
       <c r="V6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W6" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X6" s="11" t="n">
         <v>10.29</v>
@@ -7644,20 +7676,22 @@
         <f aca="false">Z6/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB6" s="11" t="n">
-        <f aca="false">IF(COUNT(I6,K6,M6,O6,Q6,S6,U6,W6,Y6,AA6)=0,"N/A",MIN(I6,K6,M6,O6,Q6,S6,U6,W6,Y6,AA6))</f>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11" t="n">
+        <f aca="false">IF(COUNT(I6,J6,M6,O6,Q6,S6,U6,V6,Y6,AA6,AC6)=0,"N/A",MIN(I6,J6,M6,O6,Q6,S6,U6,V6,Y6,AA6,AC6))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC6" s="43" t="n">
-        <f aca="false">IF(OR(D6="",AB6="",AB6="N/A"),"N/A",D6/AB6-1)</f>
+      <c r="AE6" s="43" t="n">
+        <f aca="false">IF(OR(D6="",AD6="",AD6="N/A"),"N/A",D6/AD6-1)</f>
         <v>0.786297376093295</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <f aca="false">IF(OR(F6="",AB6="",AB6="N/A"),"N/A",F6/AB6-1)</f>
+      <c r="AF6" s="43" t="n">
+        <f aca="false">IF(OR(F6="",AD6="",AD6="N/A"),"N/A",F6/AD6-1)</f>
         <v>0.810109329446064</v>
       </c>
-      <c r="AE6" s="41" t="s">
-        <v>258</v>
+      <c r="AG6" s="41" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7689,52 +7723,52 @@
         <v>122.718181818182</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y7" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z7" s="45" t="n">
         <f aca="false">AA7*1.1</f>
@@ -7743,20 +7777,22 @@
       <c r="AA7" s="45" t="n">
         <v>128.75</v>
       </c>
-      <c r="AB7" s="11" t="n">
-        <f aca="false">IF(COUNT(I7,K7,M7,O7,Q7,S7,U7,W7,Y7,AA7)=0,"N/A",MIN(I7,K7,M7,O7,Q7,S7,U7,W7,Y7,AA7))</f>
+      <c r="AB7" s="45"/>
+      <c r="AC7" s="45"/>
+      <c r="AD7" s="11" t="n">
+        <f aca="false">IF(COUNT(I7,J7,M7,O7,Q7,S7,U7,V7,Y7,AA7,AC7)=0,"N/A",MIN(I7,J7,M7,O7,Q7,S7,U7,V7,Y7,AA7,AC7))</f>
         <v>122.718181818182</v>
       </c>
-      <c r="AC7" s="43" t="n">
-        <f aca="false">IF(OR(D7="",AB7="",AB7="N/A"),"N/A",D7/AB7-1)</f>
+      <c r="AE7" s="43" t="n">
+        <f aca="false">IF(OR(D7="",AD7="",AD7="N/A"),"N/A",D7/AD7-1)</f>
         <v>-0.455418919919994</v>
       </c>
-      <c r="AD7" s="43" t="str">
-        <f aca="false">IF(OR(F7="",AB7="",AB7="N/A"),"N/A",F7/AB7-1)</f>
+      <c r="AF7" s="43" t="str">
+        <f aca="false">IF(OR(F7="",AD7="",AD7="N/A"),"N/A",F7/AD7-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE7" s="41" t="s">
-        <v>259</v>
+      <c r="AG7" s="41" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7794,52 +7830,52 @@
         <v>152.718181818182</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y8" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z8" s="45" t="n">
         <f aca="false">AA8*1.1</f>
@@ -7848,20 +7884,22 @@
       <c r="AA8" s="45" t="n">
         <v>128.75</v>
       </c>
-      <c r="AB8" s="11" t="n">
-        <f aca="false">IF(COUNT(I8,K8,M8,O8,Q8,S8,U8,W8,Y8,AA8)=0,"N/A",MIN(I8,K8,M8,O8,Q8,S8,U8,W8,Y8,AA8))</f>
+      <c r="AB8" s="45"/>
+      <c r="AC8" s="45"/>
+      <c r="AD8" s="11" t="n">
+        <f aca="false">IF(COUNT(I8,J8,M8,O8,Q8,S8,U8,V8,Y8,AA8,AC8)=0,"N/A",MIN(I8,J8,M8,O8,Q8,S8,U8,V8,Y8,AA8,AC8))</f>
         <v>128.75</v>
       </c>
-      <c r="AC8" s="43" t="n">
-        <f aca="false">IF(OR(D8="",AB8="",AB8="N/A"),"N/A",D8/AB8-1)</f>
+      <c r="AE8" s="43" t="n">
+        <f aca="false">IF(OR(D8="",AD8="",AD8="N/A"),"N/A",D8/AD8-1)</f>
         <v>-0.653980582524272</v>
       </c>
-      <c r="AD8" s="43" t="str">
-        <f aca="false">IF(OR(F8="",AB8="",AB8="N/A"),"N/A",F8/AB8-1)</f>
+      <c r="AF8" s="43" t="str">
+        <f aca="false">IF(OR(F8="",AD8="",AD8="N/A"),"N/A",F8/AD8-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE8" s="41" t="s">
-        <v>259</v>
+      <c r="AG8" s="41" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7960,19 +7998,26 @@
         <v>117.1</v>
       </c>
       <c r="AB9" s="11" t="n">
-        <f aca="false">IF(COUNT(I9,K9,M9,O9,Q9,S9,U9,W9,Y9,AA9)=0,"N/A",MIN(I9,K9,M9,O9,Q9,S9,U9,W9,Y9,AA9))</f>
-        <v>62.95</v>
-      </c>
-      <c r="AC9" s="43" t="n">
-        <f aca="false">IF(OR(D9="",AB9="",AB9="N/A"),"N/A",D9/AB9-1)</f>
-        <v>-0.2922954725973</v>
-      </c>
-      <c r="AD9" s="43" t="n">
-        <f aca="false">IF(OR(F9="",AB9="",AB9="N/A"),"N/A",F9/AB9-1)</f>
-        <v>-0.28285941223193</v>
-      </c>
-      <c r="AE9" s="41" t="s">
-        <v>260</v>
+        <v>121</v>
+      </c>
+      <c r="AC9" s="11" t="n">
+        <f aca="false">AB9/1.1</f>
+        <v>110</v>
+      </c>
+      <c r="AD9" s="11" t="n">
+        <f aca="false">IF(COUNT(I9,J9,M9,O9,Q9,S9,U9,V9,Y9,AA9,AC9)=0,"N/A",MIN(I9,J9,M9,O9,Q9,S9,U9,V9,Y9,AA9,AC9))</f>
+        <v>69.245</v>
+      </c>
+      <c r="AE9" s="43" t="n">
+        <f aca="false">IF(OR(D9="",AD9="",AD9="N/A"),"N/A",D9/AD9-1)</f>
+        <v>-0.356632247815727</v>
+      </c>
+      <c r="AF9" s="43" t="n">
+        <f aca="false">IF(OR(F9="",AD9="",AD9="N/A"),"N/A",F9/AD9-1)</f>
+        <v>-0.348054011119937</v>
+      </c>
+      <c r="AG9" s="41" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8071,19 +8116,26 @@
         <v>200.836363636364</v>
       </c>
       <c r="AB10" s="11" t="n">
-        <f aca="false">IF(COUNT(I10,K10,M10,O10,Q10,S10,U10,W10,Y10,AA10)=0,"N/A",MIN(I10,K10,M10,O10,Q10,S10,U10,W10,Y10,AA10))</f>
-        <v>74</v>
-      </c>
-      <c r="AC10" s="43" t="n">
-        <f aca="false">IF(OR(D10="",AB10="",AB10="N/A"),"N/A",D10/AB10-1)</f>
-        <v>-0.0593243243243243</v>
-      </c>
-      <c r="AD10" s="43" t="n">
-        <f aca="false">IF(OR(F10="",AB10="",AB10="N/A"),"N/A",F10/AB10-1)</f>
-        <v>-0.0467820945945947</v>
-      </c>
-      <c r="AE10" s="41" t="s">
-        <v>261</v>
+        <v>137.5</v>
+      </c>
+      <c r="AC10" s="11" t="n">
+        <f aca="false">AB10/1.1</f>
+        <v>125</v>
+      </c>
+      <c r="AD10" s="11" t="n">
+        <f aca="false">IF(COUNT(I10,J10,M10,O10,Q10,S10,U10,V10,Y10,AA10,AC10)=0,"N/A",MIN(I10,J10,M10,O10,Q10,S10,U10,V10,Y10,AA10,AC10))</f>
+        <v>81.4</v>
+      </c>
+      <c r="AE10" s="43" t="n">
+        <f aca="false">IF(OR(D10="",AD10="",AD10="N/A"),"N/A",D10/AD10-1)</f>
+        <v>-0.144840294840295</v>
+      </c>
+      <c r="AF10" s="43" t="n">
+        <f aca="false">IF(OR(F10="",AD10="",AD10="N/A"),"N/A",F10/AD10-1)</f>
+        <v>-0.133438267813268</v>
+      </c>
+      <c r="AG10" s="41" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8181,20 +8233,22 @@
         <f aca="false">Z11/1.1</f>
         <v>158.163636363636</v>
       </c>
-      <c r="AB11" s="11" t="n">
-        <f aca="false">IF(COUNT(I11,K11,M11,O11,Q11,S11,U11,W11,Y11,AA11)=0,"N/A",MIN(I11,K11,M11,O11,Q11,S11,U11,W11,Y11,AA11))</f>
-        <v>40.19</v>
-      </c>
-      <c r="AC11" s="43" t="n">
-        <f aca="false">IF(OR(D11="",AB11="",AB11="N/A"),"N/A",D11/AB11-1)</f>
-        <v>-0.168698681263996</v>
-      </c>
-      <c r="AD11" s="43" t="n">
-        <f aca="false">IF(OR(F11="",AB11="",AB11="N/A"),"N/A",F11/AB11-1)</f>
-        <v>-0.157613834287136</v>
-      </c>
-      <c r="AE11" s="41" t="s">
-        <v>262</v>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11" t="n">
+        <f aca="false">IF(COUNT(I11,J11,M11,O11,Q11,S11,U11,V11,Y11,AA11,AC11)=0,"N/A",MIN(I11,J11,M11,O11,Q11,S11,U11,V11,Y11,AA11,AC11))</f>
+        <v>44.209</v>
+      </c>
+      <c r="AE11" s="43" t="n">
+        <f aca="false">IF(OR(D11="",AD11="",AD11="N/A"),"N/A",D11/AD11-1)</f>
+        <v>-0.244271528421815</v>
+      </c>
+      <c r="AF11" s="43" t="n">
+        <f aca="false">IF(OR(F11="",AD11="",AD11="N/A"),"N/A",F11/AD11-1)</f>
+        <v>-0.234194394806487</v>
+      </c>
+      <c r="AG11" s="41" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8293,19 +8347,26 @@
         <v>163.4</v>
       </c>
       <c r="AB12" s="11" t="n">
-        <f aca="false">IF(COUNT(I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12)=0,"N/A",MIN(I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12))</f>
+        <v>130.79</v>
+      </c>
+      <c r="AC12" s="11" t="n">
+        <f aca="false">AB12/1.1</f>
+        <v>118.9</v>
+      </c>
+      <c r="AD12" s="11" t="n">
+        <f aca="false">IF(COUNT(I12,J12,M12,O12,Q12,S12,U12,V12,Y12,AA12,AC12)=0,"N/A",MIN(I12,J12,M12,O12,Q12,S12,U12,V12,Y12,AA12,AC12))</f>
         <v>70.36</v>
       </c>
-      <c r="AC12" s="43" t="n">
-        <f aca="false">IF(OR(D12="",AB12="",AB12="N/A"),"N/A",D12/AB12-1)</f>
+      <c r="AE12" s="43" t="n">
+        <f aca="false">IF(OR(D12="",AD12="",AD12="N/A"),"N/A",D12/AD12-1)</f>
         <v>-0.366827743035816</v>
       </c>
-      <c r="AD12" s="43" t="n">
-        <f aca="false">IF(OR(F12="",AB12="",AB12="N/A"),"N/A",F12/AB12-1)</f>
+      <c r="AF12" s="43" t="n">
+        <f aca="false">IF(OR(F12="",AD12="",AD12="N/A"),"N/A",F12/AD12-1)</f>
         <v>-0.358385446276293</v>
       </c>
-      <c r="AE12" s="41" t="s">
-        <v>263</v>
+      <c r="AG12" s="41" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8383,10 +8444,10 @@
         <v>28.3545454545455</v>
       </c>
       <c r="V13" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W13" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X13" s="11" t="n">
         <v>110.1</v>
@@ -8403,19 +8464,26 @@
         <v>40</v>
       </c>
       <c r="AB13" s="11" t="n">
-        <f aca="false">IF(COUNT(I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13)=0,"N/A",MIN(I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13))</f>
+        <v>90.08</v>
+      </c>
+      <c r="AC13" s="11" t="n">
+        <f aca="false">AB13/1.1</f>
+        <v>81.8909090909091</v>
+      </c>
+      <c r="AD13" s="11" t="n">
+        <f aca="false">IF(COUNT(I13,J13,M13,O13,Q13,S13,U13,V13,Y13,AA13,AC13)=0,"N/A",MIN(I13,J13,M13,O13,Q13,S13,U13,V13,Y13,AA13,AC13))</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="AC13" s="43" t="n">
-        <f aca="false">IF(OR(D13="",AB13="",AB13="N/A"),"N/A",D13/AB13-1)</f>
+      <c r="AE13" s="43" t="n">
+        <f aca="false">IF(OR(D13="",AD13="",AD13="N/A"),"N/A",D13/AD13-1)</f>
         <v>0.1782943251042</v>
       </c>
-      <c r="AD13" s="43" t="n">
-        <f aca="false">IF(OR(F13="",AB13="",AB13="N/A"),"N/A",F13/AB13-1)</f>
+      <c r="AF13" s="43" t="n">
+        <f aca="false">IF(OR(F13="",AD13="",AD13="N/A"),"N/A",F13/AD13-1)</f>
         <v>0.194006091696056</v>
       </c>
-      <c r="AE13" s="41" t="s">
-        <v>264</v>
+      <c r="AG13" s="41" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8514,19 +8582,26 @@
         <v>144.763636363636</v>
       </c>
       <c r="AB14" s="11" t="n">
-        <f aca="false">IF(COUNT(I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14)=0,"N/A",MIN(I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14))</f>
+        <v>82.5</v>
+      </c>
+      <c r="AC14" s="11" t="n">
+        <f aca="false">AB14/1.1</f>
+        <v>75</v>
+      </c>
+      <c r="AD14" s="11" t="n">
+        <f aca="false">IF(COUNT(I14,J14,M14,O14,Q14,S14,U14,V14,Y14,AA14,AC14)=0,"N/A",MIN(I14,J14,M14,O14,Q14,S14,U14,V14,Y14,AA14,AC14))</f>
         <v>43.09</v>
       </c>
-      <c r="AC14" s="43" t="n">
-        <f aca="false">IF(OR(D14="",AB14="",AB14="N/A"),"N/A",D14/AB14-1)</f>
+      <c r="AE14" s="43" t="n">
+        <f aca="false">IF(OR(D14="",AD14="",AD14="N/A"),"N/A",D14/AD14-1)</f>
         <v>-0.418426549083314</v>
       </c>
-      <c r="AD14" s="43" t="n">
-        <f aca="false">IF(OR(F14="",AB14="",AB14="N/A"),"N/A",F14/AB14-1)</f>
+      <c r="AF14" s="43" t="n">
+        <f aca="false">IF(OR(F14="",AD14="",AD14="N/A"),"N/A",F14/AD14-1)</f>
         <v>-0.410672429798097</v>
       </c>
-      <c r="AE14" s="41" t="s">
-        <v>265</v>
+      <c r="AG14" s="41" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8564,52 +8639,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y15" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z15" s="45" t="n">
         <f aca="false">AA15*1.1</f>
@@ -8618,20 +8693,22 @@
       <c r="AA15" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB15" s="11" t="n">
-        <f aca="false">IF(COUNT(I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15)=0,"N/A",MIN(I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15))</f>
+      <c r="AB15" s="45"/>
+      <c r="AC15" s="45"/>
+      <c r="AD15" s="11" t="n">
+        <f aca="false">IF(COUNT(I15,J15,M15,O15,Q15,S15,U15,V15,Y15,AA15,AC15)=0,"N/A",MIN(I15,J15,M15,O15,Q15,S15,U15,V15,Y15,AA15,AC15))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC15" s="43" t="n">
-        <f aca="false">IF(OR(D15="",AB15="",AB15="N/A"),"N/A",D15/AB15-1)</f>
+      <c r="AE15" s="43" t="n">
+        <f aca="false">IF(OR(D15="",AD15="",AD15="N/A"),"N/A",D15/AD15-1)</f>
         <v>-0.721582297665959</v>
       </c>
-      <c r="AD15" s="43" t="n">
-        <f aca="false">IF(OR(F15="",AB15="",AB15="N/A"),"N/A",F15/AB15-1)</f>
+      <c r="AF15" s="43" t="n">
+        <f aca="false">IF(OR(F15="",AD15="",AD15="N/A"),"N/A",F15/AD15-1)</f>
         <v>-0.717868672324947</v>
       </c>
-      <c r="AE15" s="41" t="s">
-        <v>266</v>
+      <c r="AG15" s="41" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8669,52 +8746,52 @@
         <v>40.9</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y16" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z16" s="45" t="n">
         <f aca="false">AA16*1.1</f>
@@ -8723,20 +8800,22 @@
       <c r="AA16" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB16" s="11" t="n">
-        <f aca="false">IF(COUNT(I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16)=0,"N/A",MIN(I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16))</f>
+      <c r="AB16" s="45"/>
+      <c r="AC16" s="45"/>
+      <c r="AD16" s="11" t="n">
+        <f aca="false">IF(COUNT(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16)=0,"N/A",MIN(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16))</f>
         <v>40.9</v>
       </c>
-      <c r="AC16" s="43" t="n">
-        <f aca="false">IF(OR(D16="",AB16="",AB16="N/A"),"N/A",D16/AB16-1)</f>
+      <c r="AE16" s="43" t="n">
+        <f aca="false">IF(OR(D16="",AD16="",AD16="N/A"),"N/A",D16/AD16-1)</f>
         <v>-0.618826405867971</v>
       </c>
-      <c r="AD16" s="43" t="n">
-        <f aca="false">IF(OR(F16="",AB16="",AB16="N/A"),"N/A",F16/AB16-1)</f>
+      <c r="AF16" s="43" t="n">
+        <f aca="false">IF(OR(F16="",AD16="",AD16="N/A"),"N/A",F16/AD16-1)</f>
         <v>-0.613380195599022</v>
       </c>
-      <c r="AE16" s="41" t="s">
-        <v>267</v>
+      <c r="AG16" s="41" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8774,52 +8853,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y17" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z17" s="45" t="n">
         <f aca="false">AA17*1.1</f>
@@ -8828,20 +8907,22 @@
       <c r="AA17" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB17" s="11" t="n">
-        <f aca="false">IF(COUNT(I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17)=0,"N/A",MIN(I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17))</f>
+      <c r="AB17" s="45"/>
+      <c r="AC17" s="45"/>
+      <c r="AD17" s="11" t="n">
+        <f aca="false">IF(COUNT(I17,J17,M17,O17,Q17,S17,U17,V17,Y17,AA17,AC17)=0,"N/A",MIN(I17,J17,M17,O17,Q17,S17,U17,V17,Y17,AA17,AC17))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC17" s="43" t="n">
-        <f aca="false">IF(OR(D17="",AB17="",AB17="N/A"),"N/A",D17/AB17-1)</f>
+      <c r="AE17" s="43" t="n">
+        <f aca="false">IF(OR(D17="",AD17="",AD17="N/A"),"N/A",D17/AD17-1)</f>
         <v>-0.721582297665959</v>
       </c>
-      <c r="AD17" s="43" t="n">
-        <f aca="false">IF(OR(F17="",AB17="",AB17="N/A"),"N/A",F17/AB17-1)</f>
+      <c r="AF17" s="43" t="n">
+        <f aca="false">IF(OR(F17="",AD17="",AD17="N/A"),"N/A",F17/AD17-1)</f>
         <v>-0.717868672324947</v>
       </c>
-      <c r="AE17" s="41" t="s">
-        <v>268</v>
+      <c r="AG17" s="41" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8879,22 +8960,22 @@
         <v>63.6272727272727</v>
       </c>
       <c r="J18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P18" s="11" t="n">
         <v>57</v>
@@ -8917,10 +8998,10 @@
         <v>37.3909090909091</v>
       </c>
       <c r="V18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W18" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X18" s="11" t="n">
         <v>110.1</v>
@@ -8936,20 +9017,22 @@
       <c r="AA18" s="45" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB18" s="11" t="n">
-        <f aca="false">IF(COUNT(I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18)=0,"N/A",MIN(I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18))</f>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="11" t="n">
+        <f aca="false">IF(COUNT(I18,J18,M18,O18,Q18,S18,U18,V18,Y18,AA18,AC18)=0,"N/A",MIN(I18,J18,M18,O18,Q18,S18,U18,V18,Y18,AA18,AC18))</f>
         <v>37.3909090909091</v>
       </c>
-      <c r="AC18" s="43" t="n">
-        <f aca="false">IF(OR(D18="",AB18="",AB18="N/A"),"N/A",D18/AB18-1)</f>
+      <c r="AE18" s="43" t="n">
+        <f aca="false">IF(OR(D18="",AD18="",AD18="N/A"),"N/A",D18/AD18-1)</f>
         <v>-0.205689277899344</v>
       </c>
-      <c r="AD18" s="43" t="n">
-        <f aca="false">IF(OR(F18="",AB18="",AB18="N/A"),"N/A",F18/AB18-1)</f>
+      <c r="AF18" s="43" t="n">
+        <f aca="false">IF(OR(F18="",AD18="",AD18="N/A"),"N/A",F18/AD18-1)</f>
         <v>-0.193774617067834</v>
       </c>
-      <c r="AE18" s="41" t="s">
-        <v>269</v>
+      <c r="AG18" s="41" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8994,10 +9077,10 @@
         <v>99.23</v>
       </c>
       <c r="L19" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M19" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N19" s="11" t="n">
         <v>36.5</v>
@@ -9027,10 +9110,10 @@
         <v>28.3545454545455</v>
       </c>
       <c r="V19" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W19" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X19" s="11" t="n">
         <v>110.1</v>
@@ -9046,20 +9129,22 @@
       <c r="AA19" s="45" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB19" s="11" t="n">
-        <f aca="false">IF(COUNT(I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19)=0,"N/A",MIN(I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19))</f>
+      <c r="AB19" s="45"/>
+      <c r="AC19" s="45"/>
+      <c r="AD19" s="11" t="n">
+        <f aca="false">IF(COUNT(I19,J19,M19,O19,Q19,S19,U19,V19,Y19,AA19,AC19)=0,"N/A",MIN(I19,J19,M19,O19,Q19,S19,U19,V19,Y19,AA19,AC19))</f>
         <v>28.3545454545455</v>
       </c>
-      <c r="AC19" s="43" t="n">
-        <f aca="false">IF(OR(D19="",AB19="",AB19="N/A"),"N/A",D19/AB19-1)</f>
+      <c r="AE19" s="43" t="n">
+        <f aca="false">IF(OR(D19="",AD19="",AD19="N/A"),"N/A",D19/AD19-1)</f>
         <v>0.0474511061237577</v>
       </c>
-      <c r="AD19" s="43" t="n">
-        <f aca="false">IF(OR(F19="",AB19="",AB19="N/A"),"N/A",F19/AB19-1)</f>
+      <c r="AF19" s="43" t="n">
+        <f aca="false">IF(OR(F19="",AD19="",AD19="N/A"),"N/A",F19/AD19-1)</f>
         <v>0.0631628727156139</v>
       </c>
-      <c r="AE19" s="41" t="s">
-        <v>270</v>
+      <c r="AG19" s="41" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9137,10 +9222,10 @@
         <v>23.3090909090909</v>
       </c>
       <c r="V20" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W20" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X20" s="11" t="n">
         <v>26.77</v>
@@ -9156,20 +9241,22 @@
         <f aca="false">Z20/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB20" s="11" t="n">
-        <f aca="false">IF(COUNT(I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20)=0,"N/A",MIN(I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20))</f>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
+      <c r="AD20" s="11" t="n">
+        <f aca="false">IF(COUNT(I20,J20,M20,O20,Q20,S20,U20,V20,Y20,AA20,AC20)=0,"N/A",MIN(I20,J20,M20,O20,Q20,S20,U20,V20,Y20,AA20,AC20))</f>
         <v>23.3090909090909</v>
       </c>
-      <c r="AC20" s="43" t="n">
-        <f aca="false">IF(OR(D20="",AB20="",AB20="N/A"),"N/A",D20/AB20-1)</f>
+      <c r="AE20" s="43" t="n">
+        <f aca="false">IF(OR(D20="",AD20="",AD20="N/A"),"N/A",D20/AD20-1)</f>
         <v>-0.28311232449298</v>
       </c>
-      <c r="AD20" s="43" t="n">
-        <f aca="false">IF(OR(F20="",AB20="",AB20="N/A"),"N/A",F20/AB20-1)</f>
+      <c r="AF20" s="43" t="n">
+        <f aca="false">IF(OR(F20="",AD20="",AD20="N/A"),"N/A",F20/AD20-1)</f>
         <v>-0.27355596723869</v>
       </c>
-      <c r="AE20" s="41" t="s">
-        <v>271</v>
+      <c r="AG20" s="41" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9233,10 +9320,10 @@
         <v>40.91</v>
       </c>
       <c r="R21" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S21" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T21" s="11" t="n">
         <v>82.82</v>
@@ -9246,10 +9333,10 @@
         <v>75.2909090909091</v>
       </c>
       <c r="V21" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W21" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X21" s="11" t="n">
         <v>23.32</v>
@@ -9265,20 +9352,22 @@
       <c r="AA21" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB21" s="11" t="n">
-        <f aca="false">IF(COUNT(I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21)=0,"N/A",MIN(I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21))</f>
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="45"/>
+      <c r="AD21" s="11" t="n">
+        <f aca="false">IF(COUNT(I21,J21,M21,O21,Q21,S21,U21,V21,Y21,AA21,AC21)=0,"N/A",MIN(I21,J21,M21,O21,Q21,S21,U21,V21,Y21,AA21,AC21))</f>
         <v>21.2</v>
       </c>
-      <c r="AC21" s="43" t="n">
-        <f aca="false">IF(OR(D21="",AB21="",AB21="N/A"),"N/A",D21/AB21-1)</f>
+      <c r="AE21" s="43" t="n">
+        <f aca="false">IF(OR(D21="",AD21="",AD21="N/A"),"N/A",D21/AD21-1)</f>
         <v>0.575943396226415</v>
       </c>
-      <c r="AD21" s="43" t="n">
-        <f aca="false">IF(OR(F21="",AB21="",AB21="N/A"),"N/A",F21/AB21-1)</f>
+      <c r="AF21" s="43" t="n">
+        <f aca="false">IF(OR(F21="",AD21="",AD21="N/A"),"N/A",F21/AD21-1)</f>
         <v>0.596957547169811</v>
       </c>
-      <c r="AE21" s="41" t="s">
-        <v>272</v>
+      <c r="AG21" s="41" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9316,10 +9405,10 @@
         <v>40.9</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K22" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>29.61</v>
@@ -9355,10 +9444,10 @@
         <v>30.1090909090909</v>
       </c>
       <c r="V22" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W22" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X22" s="11" t="n">
         <v>23.32</v>
@@ -9374,20 +9463,22 @@
         <f aca="false">Z22/1.1</f>
         <v>44.4090909090909</v>
       </c>
-      <c r="AB22" s="11" t="n">
-        <f aca="false">IF(COUNT(I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22)=0,"N/A",MIN(I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22))</f>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
+      <c r="AD22" s="11" t="n">
+        <f aca="false">IF(COUNT(I22,J22,M22,O22,Q22,S22,U22,V22,Y22,AA22,AC22)=0,"N/A",MIN(I22,J22,M22,O22,Q22,S22,U22,V22,Y22,AA22,AC22))</f>
         <v>21.2</v>
       </c>
-      <c r="AC22" s="43" t="n">
-        <f aca="false">IF(OR(D22="",AB22="",AB22="N/A"),"N/A",D22/AB22-1)</f>
+      <c r="AE22" s="43" t="n">
+        <f aca="false">IF(OR(D22="",AD22="",AD22="N/A"),"N/A",D22/AD22-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD22" s="43" t="n">
-        <f aca="false">IF(OR(F22="",AB22="",AB22="N/A"),"N/A",F22/AB22-1)</f>
+      <c r="AF22" s="43" t="n">
+        <f aca="false">IF(OR(F22="",AD22="",AD22="N/A"),"N/A",F22/AD22-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE22" s="41" t="s">
-        <v>273</v>
+      <c r="AG22" s="41" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9465,10 +9556,10 @@
         <v>30.3</v>
       </c>
       <c r="V23" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W23" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X23" s="11" t="n">
         <v>23.32</v>
@@ -9483,20 +9574,22 @@
       <c r="AA23" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB23" s="11" t="n">
-        <f aca="false">IF(COUNT(I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23)=0,"N/A",MIN(I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23))</f>
+      <c r="AB23" s="45"/>
+      <c r="AC23" s="45"/>
+      <c r="AD23" s="11" t="n">
+        <f aca="false">IF(COUNT(I23,J23,M23,O23,Q23,S23,U23,V23,Y23,AA23,AC23)=0,"N/A",MIN(I23,J23,M23,O23,Q23,S23,U23,V23,Y23,AA23,AC23))</f>
         <v>21.2</v>
       </c>
-      <c r="AC23" s="43" t="n">
-        <f aca="false">IF(OR(D23="",AB23="",AB23="N/A"),"N/A",D23/AB23-1)</f>
+      <c r="AE23" s="43" t="n">
+        <f aca="false">IF(OR(D23="",AD23="",AD23="N/A"),"N/A",D23/AD23-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD23" s="43" t="n">
-        <f aca="false">IF(OR(F23="",AB23="",AB23="N/A"),"N/A",F23/AB23-1)</f>
+      <c r="AF23" s="43" t="n">
+        <f aca="false">IF(OR(F23="",AD23="",AD23="N/A"),"N/A",F23/AD23-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE23" s="41" t="s">
-        <v>274</v>
+      <c r="AG23" s="41" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9534,52 +9627,52 @@
         <v>34.5363636363636</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y24" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z24" s="45" t="n">
         <v>46.13</v>
@@ -9587,20 +9680,22 @@
       <c r="AA24" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB24" s="11" t="n">
-        <f aca="false">IF(COUNT(I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24)=0,"N/A",MIN(I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24))</f>
+      <c r="AB24" s="45"/>
+      <c r="AC24" s="45"/>
+      <c r="AD24" s="11" t="n">
+        <f aca="false">IF(COUNT(I24,J24,M24,O24,Q24,S24,U24,V24,Y24,AA24,AC24)=0,"N/A",MIN(I24,J24,M24,O24,Q24,S24,U24,V24,Y24,AA24,AC24))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC24" s="43" t="n">
-        <f aca="false">IF(OR(D24="",AB24="",AB24="N/A"),"N/A",D24/AB24-1)</f>
+      <c r="AE24" s="43" t="n">
+        <f aca="false">IF(OR(D24="",AD24="",AD24="N/A"),"N/A",D24/AD24-1)</f>
         <v>-0.829165569886812</v>
       </c>
-      <c r="AD24" s="43" t="n">
-        <f aca="false">IF(OR(F24="",AB24="",AB24="N/A"),"N/A",F24/AB24-1)</f>
+      <c r="AF24" s="43" t="n">
+        <f aca="false">IF(OR(F24="",AD24="",AD24="N/A"),"N/A",F24/AD24-1)</f>
         <v>-0.825940708081074</v>
       </c>
-      <c r="AE24" s="41" t="s">
-        <v>268</v>
+      <c r="AG24" s="41" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9638,16 +9733,16 @@
         <v>45.4454545454545</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K25" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L25" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>42.5</v>
@@ -9696,20 +9791,22 @@
       <c r="AA25" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB25" s="11" t="n">
-        <f aca="false">IF(COUNT(I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25)=0,"N/A",MIN(I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25))</f>
+      <c r="AB25" s="45"/>
+      <c r="AC25" s="45"/>
+      <c r="AD25" s="11" t="n">
+        <f aca="false">IF(COUNT(I25,J25,M25,O25,Q25,S25,U25,V25,Y25,AA25,AC25)=0,"N/A",MIN(I25,J25,M25,O25,Q25,S25,U25,V25,Y25,AA25,AC25))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC25" s="43" t="n">
-        <f aca="false">IF(OR(D25="",AB25="",AB25="N/A"),"N/A",D25/AB25-1)</f>
+      <c r="AE25" s="43" t="n">
+        <f aca="false">IF(OR(D25="",AD25="",AD25="N/A"),"N/A",D25/AD25-1)</f>
         <v>0.262487852283771</v>
       </c>
-      <c r="AD25" s="43" t="n">
-        <f aca="false">IF(OR(F25="",AB25="",AB25="N/A"),"N/A",F25/AB25-1)</f>
+      <c r="AF25" s="43" t="n">
+        <f aca="false">IF(OR(F25="",AD25="",AD25="N/A"),"N/A",F25/AD25-1)</f>
         <v>0.28629980563654</v>
       </c>
-      <c r="AE25" s="41" t="s">
-        <v>275</v>
+      <c r="AG25" s="41" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9747,16 +9844,16 @@
         <v>40.9</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>42.5</v>
@@ -9786,10 +9883,10 @@
         <v>28.3545454545455</v>
       </c>
       <c r="V26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W26" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X26" s="11" t="n">
         <v>10.29</v>
@@ -9805,20 +9902,22 @@
         <f aca="false">Z26/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB26" s="11" t="n">
-        <f aca="false">IF(COUNT(I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26)=0,"N/A",MIN(I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26))</f>
+      <c r="AB26" s="11"/>
+      <c r="AC26" s="11"/>
+      <c r="AD26" s="11" t="n">
+        <f aca="false">IF(COUNT(I26,J26,M26,O26,Q26,S26,U26,V26,Y26,AA26,AC26)=0,"N/A",MIN(I26,J26,M26,O26,Q26,S26,U26,V26,Y26,AA26,AC26))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC26" s="43" t="n">
-        <f aca="false">IF(OR(D26="",AB26="",AB26="N/A"),"N/A",D26/AB26-1)</f>
+      <c r="AE26" s="43" t="n">
+        <f aca="false">IF(OR(D26="",AD26="",AD26="N/A"),"N/A",D26/AD26-1)</f>
         <v>0.262487852283771</v>
       </c>
-      <c r="AD26" s="43" t="n">
-        <f aca="false">IF(OR(F26="",AB26="",AB26="N/A"),"N/A",F26/AB26-1)</f>
+      <c r="AF26" s="43" t="n">
+        <f aca="false">IF(OR(F26="",AD26="",AD26="N/A"),"N/A",F26/AD26-1)</f>
         <v>0.28629980563654</v>
       </c>
-      <c r="AE26" s="41" t="s">
-        <v>258</v>
+      <c r="AG26" s="41" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9826,7 +9925,7 @@
         <v>222</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>173</v>
@@ -9856,16 +9955,16 @@
         <v>40.9</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N27" s="11" t="n">
         <v>35.75</v>
@@ -9895,10 +9994,10 @@
         <v>27.3727272727273</v>
       </c>
       <c r="V27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W27" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X27" s="11" t="n">
         <v>23.32</v>
@@ -9914,20 +10013,22 @@
         <f aca="false">Z27/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB27" s="11" t="n">
-        <f aca="false">IF(COUNT(I27,K27,M27,O27,Q27,S27,U27,W27,Y27,AA27)=0,"N/A",MIN(I27,K27,M27,O27,Q27,S27,U27,W27,Y27,AA27))</f>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
+      <c r="AD27" s="11" t="n">
+        <f aca="false">IF(COUNT(I27,J27,M27,O27,Q27,S27,U27,V27,Y27,AA27,AC27)=0,"N/A",MIN(I27,J27,M27,O27,Q27,S27,U27,V27,Y27,AA27,AC27))</f>
         <v>21.2</v>
       </c>
-      <c r="AC27" s="43" t="n">
-        <f aca="false">IF(OR(D27="",AB27="",AB27="N/A"),"N/A",D27/AB27-1)</f>
+      <c r="AE27" s="43" t="n">
+        <f aca="false">IF(OR(D27="",AD27="",AD27="N/A"),"N/A",D27/AD27-1)</f>
         <v>-0.442924528301887</v>
       </c>
-      <c r="AD27" s="43" t="n">
-        <f aca="false">IF(OR(F27="",AB27="",AB27="N/A"),"N/A",F27/AB27-1)</f>
+      <c r="AF27" s="43" t="n">
+        <f aca="false">IF(OR(F27="",AD27="",AD27="N/A"),"N/A",F27/AD27-1)</f>
         <v>-0.432417452830189</v>
       </c>
-      <c r="AE27" s="41" t="s">
-        <v>277</v>
+      <c r="AG27" s="41" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9965,16 +10066,16 @@
         <v>129.990909090909</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>35.75</v>
@@ -10004,10 +10105,10 @@
         <v>89.1545454545454</v>
       </c>
       <c r="V28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X28" s="11" t="n">
         <v>110.1</v>
@@ -10017,25 +10118,32 @@
         <v>100.090909090909</v>
       </c>
       <c r="Z28" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA28" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB28" s="11" t="n">
-        <f aca="false">IF(COUNT(I28,K28,M28,O28,Q28,S28,U28,W28,Y28,AA28)=0,"N/A",MIN(I28,K28,M28,O28,Q28,S28,U28,W28,Y28,AA28))</f>
+        <v>259</v>
+      </c>
+      <c r="AB28" s="42" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="AC28" s="42" t="n">
+        <f aca="false">AB28/1.1</f>
+        <v>81.8909090909091</v>
+      </c>
+      <c r="AD28" s="11" t="n">
+        <f aca="false">IF(COUNT(I28,J28,M28,O28,Q28,S28,U28,V28,Y28,AA28,AC28)=0,"N/A",MIN(I28,J28,M28,O28,Q28,S28,U28,V28,Y28,AA28,AC28))</f>
         <v>32.5</v>
       </c>
-      <c r="AC28" s="43" t="n">
-        <f aca="false">IF(OR(D28="",AB28="",AB28="N/A"),"N/A",D28/AB28-1)</f>
+      <c r="AE28" s="43" t="n">
+        <f aca="false">IF(OR(D28="",AD28="",AD28="N/A"),"N/A",D28/AD28-1)</f>
         <v>0.0279999999999998</v>
       </c>
-      <c r="AD28" s="43" t="n">
-        <f aca="false">IF(OR(F28="",AB28="",AB28="N/A"),"N/A",F28/AB28-1)</f>
+      <c r="AF28" s="43" t="n">
+        <f aca="false">IF(OR(F28="",AD28="",AD28="N/A"),"N/A",F28/AD28-1)</f>
         <v>0.0417076923076922</v>
       </c>
-      <c r="AE28" s="41" t="s">
-        <v>278</v>
+      <c r="AG28" s="41" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10113,10 +10221,10 @@
         <v>103.709090909091</v>
       </c>
       <c r="V29" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W29" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X29" s="11" t="n">
         <v>110.1</v>
@@ -10132,20 +10240,27 @@
       <c r="AA29" s="45" t="n">
         <v>121.26</v>
       </c>
-      <c r="AB29" s="11" t="n">
-        <f aca="false">IF(COUNT(I29,K29,M29,O29,Q29,S29,U29,W29,Y29,AA29)=0,"N/A",MIN(I29,K29,M29,O29,Q29,S29,U29,W29,Y29,AA29))</f>
+      <c r="AB29" s="45" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="AC29" s="45" t="n">
+        <f aca="false">AB29/1.1</f>
+        <v>81.8909090909091</v>
+      </c>
+      <c r="AD29" s="11" t="n">
+        <f aca="false">IF(COUNT(I29,J29,M29,O29,Q29,S29,U29,V29,Y29,AA29,AC29)=0,"N/A",MIN(I29,J29,M29,O29,Q29,S29,U29,V29,Y29,AA29,AC29))</f>
         <v>45</v>
       </c>
-      <c r="AC29" s="43" t="n">
-        <f aca="false">IF(OR(D29="",AB29="",AB29="N/A"),"N/A",D29/AB29-1)</f>
+      <c r="AE29" s="43" t="n">
+        <f aca="false">IF(OR(D29="",AD29="",AD29="N/A"),"N/A",D29/AD29-1)</f>
         <v>-0.257555555555556</v>
       </c>
-      <c r="AD29" s="43" t="n">
-        <f aca="false">IF(OR(F29="",AB29="",AB29="N/A"),"N/A",F29/AB29-1)</f>
+      <c r="AF29" s="43" t="n">
+        <f aca="false">IF(OR(F29="",AD29="",AD29="N/A"),"N/A",F29/AD29-1)</f>
         <v>-0.247655555555555</v>
       </c>
-      <c r="AE29" s="41" t="s">
-        <v>279</v>
+      <c r="AG29" s="41" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10190,22 +10305,22 @@
         <v>149.18</v>
       </c>
       <c r="L30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R30" s="11" t="n">
         <v>34.1</v>
@@ -10229,31 +10344,38 @@
         <v>28</v>
       </c>
       <c r="X30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z30" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA30" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB30" s="11" t="n">
-        <f aca="false">IF(COUNT(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30)=0,"N/A",MIN(I30,K30,M30,O30,Q30,S30,U30,W30,Y30,AA30))</f>
-        <v>28</v>
-      </c>
-      <c r="AC30" s="43" t="n">
-        <f aca="false">IF(OR(D30="",AB30="",AB30="N/A"),"N/A",D30/AB30-1)</f>
-        <v>-0.533214285714286</v>
-      </c>
-      <c r="AD30" s="43" t="str">
-        <f aca="false">IF(OR(F30="",AB30="",AB30="N/A"),"N/A",F30/AB30-1)</f>
+        <v>259</v>
+      </c>
+      <c r="AB30" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC30" s="42" t="n">
+        <f aca="false">AB30/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
+      <c r="AD30" s="11" t="n">
+        <f aca="false">IF(COUNT(I30,J30,M30,O30,Q30,S30,U30,V30,Y30,AA30,AC30)=0,"N/A",MIN(I30,J30,M30,O30,Q30,S30,U30,V30,Y30,AA30,AC30))</f>
+        <v>30.8</v>
+      </c>
+      <c r="AE30" s="43" t="n">
+        <f aca="false">IF(OR(D30="",AD30="",AD30="N/A"),"N/A",D30/AD30-1)</f>
+        <v>-0.575649350649351</v>
+      </c>
+      <c r="AF30" s="43" t="str">
+        <f aca="false">IF(OR(F30="",AD30="",AD30="N/A"),"N/A",F30/AD30-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE30" s="41" t="s">
-        <v>280</v>
+      <c r="AG30" s="41" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10291,28 +10413,28 @@
         <v>40.9</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R31" s="11" t="n">
         <v>34.1</v>
@@ -10329,10 +10451,10 @@
         <v>42.8545454545455</v>
       </c>
       <c r="V31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X31" s="11" t="n">
         <v>53.22</v>
@@ -10342,25 +10464,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z31" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA31" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB31" s="11" t="n">
-        <f aca="false">IF(COUNT(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31)=0,"N/A",MIN(I31,K31,M31,O31,Q31,S31,U31,W31,Y31,AA31))</f>
+        <v>259</v>
+      </c>
+      <c r="AB31" s="42"/>
+      <c r="AC31" s="42"/>
+      <c r="AD31" s="11" t="n">
+        <f aca="false">IF(COUNT(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31)=0,"N/A",MIN(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31))</f>
         <v>31</v>
       </c>
-      <c r="AC31" s="43" t="n">
-        <f aca="false">IF(OR(D31="",AB31="",AB31="N/A"),"N/A",D31/AB31-1)</f>
+      <c r="AE31" s="43" t="n">
+        <f aca="false">IF(OR(D31="",AD31="",AD31="N/A"),"N/A",D31/AD31-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD31" s="43" t="str">
-        <f aca="false">IF(OR(F31="",AB31="",AB31="N/A"),"N/A",F31/AB31-1)</f>
+      <c r="AF31" s="43" t="str">
+        <f aca="false">IF(OR(F31="",AD31="",AD31="N/A"),"N/A",F31/AD31-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE31" s="41" t="s">
-        <v>281</v>
+      <c r="AG31" s="41" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10405,22 +10529,22 @@
         <v>145.35</v>
       </c>
       <c r="L32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R32" s="11" t="n">
         <v>34.1</v>
@@ -10444,31 +10568,38 @@
         <v>51.5</v>
       </c>
       <c r="X32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z32" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA32" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB32" s="11" t="n">
-        <f aca="false">IF(COUNT(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32)=0,"N/A",MIN(I32,K32,M32,O32,Q32,S32,U32,W32,Y32,AA32))</f>
+        <v>259</v>
+      </c>
+      <c r="AB32" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC32" s="42" t="n">
+        <f aca="false">AB32/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
+      <c r="AD32" s="11" t="n">
+        <f aca="false">IF(COUNT(I32,J32,M32,O32,Q32,S32,U32,V32,Y32,AA32,AC32)=0,"N/A",MIN(I32,J32,M32,O32,Q32,S32,U32,V32,Y32,AA32,AC32))</f>
         <v>31</v>
       </c>
-      <c r="AC32" s="43" t="n">
-        <f aca="false">IF(OR(D32="",AB32="",AB32="N/A"),"N/A",D32/AB32-1)</f>
+      <c r="AE32" s="43" t="n">
+        <f aca="false">IF(OR(D32="",AD32="",AD32="N/A"),"N/A",D32/AD32-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD32" s="43" t="str">
-        <f aca="false">IF(OR(F32="",AB32="",AB32="N/A"),"N/A",F32/AB32-1)</f>
+      <c r="AF32" s="43" t="str">
+        <f aca="false">IF(OR(F32="",AD32="",AD32="N/A"),"N/A",F32/AD32-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE32" s="41" t="s">
-        <v>282</v>
+      <c r="AG32" s="41" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10513,22 +10644,22 @@
         <v>182.14</v>
       </c>
       <c r="L33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R33" s="11" t="n">
         <v>34.1</v>
@@ -10545,10 +10676,10 @@
         <v>53.4909090909091</v>
       </c>
       <c r="V33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X33" s="11" t="n">
         <v>53.22</v>
@@ -10558,25 +10689,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z33" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA33" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB33" s="11" t="n">
-        <f aca="false">IF(COUNT(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33)=0,"N/A",MIN(I33,K33,M33,O33,Q33,S33,U33,W33,Y33,AA33))</f>
+        <v>259</v>
+      </c>
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="42"/>
+      <c r="AD33" s="11" t="n">
+        <f aca="false">IF(COUNT(I33,J33,M33,O33,Q33,S33,U33,V33,Y33,AA33,AC33)=0,"N/A",MIN(I33,J33,M33,O33,Q33,S33,U33,V33,Y33,AA33,AC33))</f>
         <v>31</v>
       </c>
-      <c r="AC33" s="43" t="n">
-        <f aca="false">IF(OR(D33="",AB33="",AB33="N/A"),"N/A",D33/AB33-1)</f>
+      <c r="AE33" s="43" t="n">
+        <f aca="false">IF(OR(D33="",AD33="",AD33="N/A"),"N/A",D33/AD33-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD33" s="43" t="str">
-        <f aca="false">IF(OR(F33="",AB33="",AB33="N/A"),"N/A",F33/AB33-1)</f>
+      <c r="AF33" s="43" t="str">
+        <f aca="false">IF(OR(F33="",AD33="",AD33="N/A"),"N/A",F33/AD33-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE33" s="41" t="s">
-        <v>283</v>
+      <c r="AG33" s="41" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10621,22 +10754,22 @@
         <v>182.14</v>
       </c>
       <c r="L34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R34" s="11" t="n">
         <v>34.1</v>
@@ -10667,25 +10800,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z34" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA34" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB34" s="11" t="n">
-        <f aca="false">IF(COUNT(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34)=0,"N/A",MIN(I34,K34,M34,O34,Q34,S34,U34,W34,Y34,AA34))</f>
+        <v>259</v>
+      </c>
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="42"/>
+      <c r="AD34" s="11" t="n">
+        <f aca="false">IF(COUNT(I34,J34,M34,O34,Q34,S34,U34,V34,Y34,AA34,AC34)=0,"N/A",MIN(I34,J34,M34,O34,Q34,S34,U34,V34,Y34,AA34,AC34))</f>
         <v>31</v>
       </c>
-      <c r="AC34" s="43" t="n">
-        <f aca="false">IF(OR(D34="",AB34="",AB34="N/A"),"N/A",D34/AB34-1)</f>
+      <c r="AE34" s="43" t="n">
+        <f aca="false">IF(OR(D34="",AD34="",AD34="N/A"),"N/A",D34/AD34-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD34" s="43" t="str">
-        <f aca="false">IF(OR(F34="",AB34="",AB34="N/A"),"N/A",F34/AB34-1)</f>
+      <c r="AF34" s="43" t="str">
+        <f aca="false">IF(OR(F34="",AD34="",AD34="N/A"),"N/A",F34/AD34-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE34" s="41" t="s">
-        <v>284</v>
+      <c r="AG34" s="41" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10730,22 +10865,22 @@
         <v>118.4</v>
       </c>
       <c r="L35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R35" s="11" t="n">
         <v>34.1</v>
@@ -10776,25 +10911,32 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z35" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA35" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB35" s="11" t="n">
-        <f aca="false">IF(COUNT(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35)=0,"N/A",MIN(I35,K35,M35,O35,Q35,S35,U35,W35,Y35,AA35))</f>
+        <v>259</v>
+      </c>
+      <c r="AB35" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC35" s="42" t="n">
+        <f aca="false">AB35/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
+      <c r="AD35" s="11" t="n">
+        <f aca="false">IF(COUNT(I35,J35,M35,O35,Q35,S35,U35,V35,Y35,AA35,AC35)=0,"N/A",MIN(I35,J35,M35,O35,Q35,S35,U35,V35,Y35,AA35,AC35))</f>
         <v>31</v>
       </c>
-      <c r="AC35" s="43" t="n">
-        <f aca="false">IF(OR(D35="",AB35="",AB35="N/A"),"N/A",D35/AB35-1)</f>
+      <c r="AE35" s="43" t="n">
+        <f aca="false">IF(OR(D35="",AD35="",AD35="N/A"),"N/A",D35/AD35-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD35" s="43" t="str">
-        <f aca="false">IF(OR(F35="",AB35="",AB35="N/A"),"N/A",F35/AB35-1)</f>
+      <c r="AF35" s="43" t="str">
+        <f aca="false">IF(OR(F35="",AD35="",AD35="N/A"),"N/A",F35/AD35-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE35" s="41" t="s">
-        <v>285</v>
+      <c r="AG35" s="41" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10839,10 +10981,10 @@
         <v>149.18</v>
       </c>
       <c r="L36" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M36" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N36" s="11" t="n">
         <v>46.6</v>
@@ -10852,10 +10994,10 @@
         <v>42.3636363636364</v>
       </c>
       <c r="P36" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q36" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R36" s="11" t="n">
         <v>34.1</v>
@@ -10886,25 +11028,32 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z36" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA36" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB36" s="11" t="n">
-        <f aca="false">IF(COUNT(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36)=0,"N/A",MIN(I36,K36,M36,O36,Q36,S36,U36,W36,Y36,AA36))</f>
+        <v>259</v>
+      </c>
+      <c r="AB36" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC36" s="42" t="n">
+        <f aca="false">AB36/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
+      <c r="AD36" s="11" t="n">
+        <f aca="false">IF(COUNT(I36,J36,M36,O36,Q36,S36,U36,V36,Y36,AA36,AC36)=0,"N/A",MIN(I36,J36,M36,O36,Q36,S36,U36,V36,Y36,AA36,AC36))</f>
         <v>31</v>
       </c>
-      <c r="AC36" s="43" t="n">
-        <f aca="false">IF(OR(D36="",AB36="",AB36="N/A"),"N/A",D36/AB36-1)</f>
+      <c r="AE36" s="43" t="n">
+        <f aca="false">IF(OR(D36="",AD36="",AD36="N/A"),"N/A",D36/AD36-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD36" s="43" t="str">
-        <f aca="false">IF(OR(F36="",AB36="",AB36="N/A"),"N/A",F36/AB36-1)</f>
+      <c r="AF36" s="43" t="str">
+        <f aca="false">IF(OR(F36="",AD36="",AD36="N/A"),"N/A",F36/AD36-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE36" s="41" t="s">
-        <v>286</v>
+      <c r="AG36" s="41" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10942,28 +11091,28 @@
         <v>54.5363636363636</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R37" s="11" t="n">
         <v>34.1</v>
@@ -10987,31 +11136,33 @@
         <v>47.5</v>
       </c>
       <c r="X37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z37" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA37" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB37" s="11" t="n">
-        <f aca="false">IF(COUNT(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37)=0,"N/A",MIN(I37,K37,M37,O37,Q37,S37,U37,W37,Y37,AA37))</f>
+        <v>259</v>
+      </c>
+      <c r="AB37" s="42"/>
+      <c r="AC37" s="42"/>
+      <c r="AD37" s="11" t="n">
+        <f aca="false">IF(COUNT(I37,J37,M37,O37,Q37,S37,U37,V37,Y37,AA37,AC37)=0,"N/A",MIN(I37,J37,M37,O37,Q37,S37,U37,V37,Y37,AA37,AC37))</f>
         <v>31</v>
       </c>
-      <c r="AC37" s="43" t="n">
-        <f aca="false">IF(OR(D37="",AB37="",AB37="N/A"),"N/A",D37/AB37-1)</f>
+      <c r="AE37" s="43" t="n">
+        <f aca="false">IF(OR(D37="",AD37="",AD37="N/A"),"N/A",D37/AD37-1)</f>
         <v>-0.48258064516129</v>
       </c>
-      <c r="AD37" s="43" t="str">
-        <f aca="false">IF(OR(F37="",AB37="",AB37="N/A"),"N/A",F37/AB37-1)</f>
+      <c r="AF37" s="43" t="str">
+        <f aca="false">IF(OR(F37="",AD37="",AD37="N/A"),"N/A",F37/AD37-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE37" s="41" t="s">
-        <v>287</v>
+      <c r="AG37" s="41" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11056,22 +11207,22 @@
         <v>92.77</v>
       </c>
       <c r="L38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R38" s="11" t="n">
         <v>34.1</v>
@@ -11088,10 +11239,10 @@
         <v>53.6818181818182</v>
       </c>
       <c r="V38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X38" s="11" t="n">
         <v>53.22</v>
@@ -11101,25 +11252,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z38" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA38" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB38" s="11" t="n">
-        <f aca="false">IF(COUNT(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38)=0,"N/A",MIN(I38,K38,M38,O38,Q38,S38,U38,W38,Y38,AA38))</f>
+        <v>259</v>
+      </c>
+      <c r="AB38" s="42"/>
+      <c r="AC38" s="42"/>
+      <c r="AD38" s="11" t="n">
+        <f aca="false">IF(COUNT(I38,J38,M38,O38,Q38,S38,U38,V38,Y38,AA38,AC38)=0,"N/A",MIN(I38,J38,M38,O38,Q38,S38,U38,V38,Y38,AA38,AC38))</f>
         <v>31</v>
       </c>
-      <c r="AC38" s="43" t="n">
-        <f aca="false">IF(OR(D38="",AB38="",AB38="N/A"),"N/A",D38/AB38-1)</f>
+      <c r="AE38" s="43" t="n">
+        <f aca="false">IF(OR(D38="",AD38="",AD38="N/A"),"N/A",D38/AD38-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD38" s="43" t="str">
-        <f aca="false">IF(OR(F38="",AB38="",AB38="N/A"),"N/A",F38/AB38-1)</f>
+      <c r="AF38" s="43" t="str">
+        <f aca="false">IF(OR(F38="",AD38="",AD38="N/A"),"N/A",F38/AD38-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE38" s="41" t="s">
-        <v>288</v>
+      <c r="AG38" s="41" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11164,10 +11317,10 @@
         <v>65.81</v>
       </c>
       <c r="L39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N39" s="11" t="n">
         <v>115.9</v>
@@ -11177,10 +11330,10 @@
         <v>105.363636363636</v>
       </c>
       <c r="P39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R39" s="11" t="n">
         <v>34.1</v>
@@ -11197,10 +11350,10 @@
         <v>55.4909090909091</v>
       </c>
       <c r="V39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X39" s="11" t="n">
         <v>124.21</v>
@@ -11210,25 +11363,27 @@
         <v>112.918181818182</v>
       </c>
       <c r="Z39" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA39" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB39" s="11" t="n">
-        <f aca="false">IF(COUNT(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39)=0,"N/A",MIN(I39,K39,M39,O39,Q39,S39,U39,W39,Y39,AA39))</f>
+        <v>259</v>
+      </c>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="11" t="n">
+        <f aca="false">IF(COUNT(I39,J39,M39,O39,Q39,S39,U39,V39,Y39,AA39,AC39)=0,"N/A",MIN(I39,J39,M39,O39,Q39,S39,U39,V39,Y39,AA39,AC39))</f>
         <v>31</v>
       </c>
-      <c r="AC39" s="43" t="n">
-        <f aca="false">IF(OR(D39="",AB39="",AB39="N/A"),"N/A",D39/AB39-1)</f>
+      <c r="AE39" s="43" t="n">
+        <f aca="false">IF(OR(D39="",AD39="",AD39="N/A"),"N/A",D39/AD39-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD39" s="43" t="str">
-        <f aca="false">IF(OR(F39="",AB39="",AB39="N/A"),"N/A",F39/AB39-1)</f>
+      <c r="AF39" s="43" t="str">
+        <f aca="false">IF(OR(F39="",AD39="",AD39="N/A"),"N/A",F39/AD39-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE39" s="41" t="s">
-        <v>289</v>
+      <c r="AG39" s="41" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11273,10 +11428,10 @@
         <v>65.81</v>
       </c>
       <c r="L40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>115.9</v>
@@ -11286,10 +11441,10 @@
         <v>105.363636363636</v>
       </c>
       <c r="P40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R40" s="11" t="n">
         <v>34.1</v>
@@ -11306,10 +11461,10 @@
         <v>55.4909090909091</v>
       </c>
       <c r="V40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X40" s="11" t="n">
         <v>124.21</v>
@@ -11319,25 +11474,27 @@
         <v>112.918181818182</v>
       </c>
       <c r="Z40" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA40" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB40" s="11" t="n">
-        <f aca="false">IF(COUNT(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40)=0,"N/A",MIN(I40,K40,M40,O40,Q40,S40,U40,W40,Y40,AA40))</f>
+        <v>259</v>
+      </c>
+      <c r="AB40" s="42"/>
+      <c r="AC40" s="42"/>
+      <c r="AD40" s="11" t="n">
+        <f aca="false">IF(COUNT(I40,J40,M40,O40,Q40,S40,U40,V40,Y40,AA40,AC40)=0,"N/A",MIN(I40,J40,M40,O40,Q40,S40,U40,V40,Y40,AA40,AC40))</f>
         <v>31</v>
       </c>
-      <c r="AC40" s="43" t="n">
-        <f aca="false">IF(OR(D40="",AB40="",AB40="N/A"),"N/A",D40/AB40-1)</f>
+      <c r="AE40" s="43" t="n">
+        <f aca="false">IF(OR(D40="",AD40="",AD40="N/A"),"N/A",D40/AD40-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD40" s="43" t="str">
-        <f aca="false">IF(OR(F40="",AB40="",AB40="N/A"),"N/A",F40/AB40-1)</f>
+      <c r="AF40" s="43" t="str">
+        <f aca="false">IF(OR(F40="",AD40="",AD40="N/A"),"N/A",F40/AD40-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE40" s="41" t="s">
-        <v>290</v>
+      <c r="AG40" s="41" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11382,16 +11539,16 @@
         <v>98.33</v>
       </c>
       <c r="L41" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M41" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O41" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P41" s="11" t="n">
         <v>96.1</v>
@@ -11428,25 +11585,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z41" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA41" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB41" s="11" t="n">
-        <f aca="false">IF(COUNT(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41)=0,"N/A",MIN(I41,K41,M41,O41,Q41,S41,U41,W41,Y41,AA41))</f>
+        <v>259</v>
+      </c>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="42"/>
+      <c r="AD41" s="11" t="n">
+        <f aca="false">IF(COUNT(I41,J41,M41,O41,Q41,S41,U41,V41,Y41,AA41,AC41)=0,"N/A",MIN(I41,J41,M41,O41,Q41,S41,U41,V41,Y41,AA41,AC41))</f>
         <v>31</v>
       </c>
-      <c r="AC41" s="43" t="n">
-        <f aca="false">IF(OR(D41="",AB41="",AB41="N/A"),"N/A",D41/AB41-1)</f>
+      <c r="AE41" s="43" t="n">
+        <f aca="false">IF(OR(D41="",AD41="",AD41="N/A"),"N/A",D41/AD41-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD41" s="43" t="str">
-        <f aca="false">IF(OR(F41="",AB41="",AB41="N/A"),"N/A",F41/AB41-1)</f>
+      <c r="AF41" s="43" t="str">
+        <f aca="false">IF(OR(F41="",AD41="",AD41="N/A"),"N/A",F41/AD41-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE41" s="41" t="s">
-        <v>291</v>
+      <c r="AG41" s="41" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11491,16 +11650,16 @@
         <v>98.33</v>
       </c>
       <c r="L42" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M42" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N42" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O42" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P42" s="11" t="n">
         <v>96.1</v>
@@ -11537,25 +11696,27 @@
         <v>48.3818181818182</v>
       </c>
       <c r="Z42" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA42" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB42" s="11" t="n">
-        <f aca="false">IF(COUNT(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42)=0,"N/A",MIN(I42,K42,M42,O42,Q42,S42,U42,W42,Y42,AA42))</f>
+        <v>259</v>
+      </c>
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="42"/>
+      <c r="AD42" s="11" t="n">
+        <f aca="false">IF(COUNT(I42,J42,M42,O42,Q42,S42,U42,V42,Y42,AA42,AC42)=0,"N/A",MIN(I42,J42,M42,O42,Q42,S42,U42,V42,Y42,AA42,AC42))</f>
         <v>31</v>
       </c>
-      <c r="AC42" s="43" t="n">
-        <f aca="false">IF(OR(D42="",AB42="",AB42="N/A"),"N/A",D42/AB42-1)</f>
+      <c r="AE42" s="43" t="n">
+        <f aca="false">IF(OR(D42="",AD42="",AD42="N/A"),"N/A",D42/AD42-1)</f>
         <v>-0.578387096774194</v>
       </c>
-      <c r="AD42" s="43" t="str">
-        <f aca="false">IF(OR(F42="",AB42="",AB42="N/A"),"N/A",F42/AB42-1)</f>
+      <c r="AF42" s="43" t="str">
+        <f aca="false">IF(OR(F42="",AD42="",AD42="N/A"),"N/A",F42/AD42-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE42" s="41" t="s">
-        <v>292</v>
+      <c r="AG42" s="41" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11593,69 +11754,76 @@
         <v>34.5363636363636</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y43" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z43" s="42"/>
       <c r="AA43" s="42"/>
-      <c r="AB43" s="11" t="n">
-        <f aca="false">IF(COUNT(I43,K43,M43,O43,Q43,S43,U43,W43,Y43,AA43)=0,"N/A",MIN(I43,K43,M43,O43,Q43,S43,U43,W43,Y43,AA43))</f>
-        <v>34.5363636363636</v>
-      </c>
-      <c r="AC43" s="43" t="n">
-        <f aca="false">IF(OR(D43="",AB43="",AB43="N/A"),"N/A",D43/AB43-1)</f>
-        <v>-0.84509081337194</v>
-      </c>
-      <c r="AD43" s="43" t="str">
-        <f aca="false">IF(OR(F43="",AB43="",AB43="N/A"),"N/A",F43/AB43-1)</f>
+      <c r="AB43" s="42" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AC43" s="42" t="n">
+        <f aca="false">AB43/1.1</f>
+        <v>32.6363636363636</v>
+      </c>
+      <c r="AD43" s="11" t="n">
+        <f aca="false">IF(COUNT(I43,J43,M43,O43,Q43,S43,U43,V43,Y43,AA43,AC43)=0,"N/A",MIN(I43,J43,M43,O43,Q43,S43,U43,V43,Y43,AA43,AC43))</f>
+        <v>32.6363636363636</v>
+      </c>
+      <c r="AE43" s="43" t="n">
+        <f aca="false">IF(OR(D43="",AD43="",AD43="N/A"),"N/A",D43/AD43-1)</f>
+        <v>-0.836072423398329</v>
+      </c>
+      <c r="AF43" s="43" t="str">
+        <f aca="false">IF(OR(F43="",AD43="",AD43="N/A"),"N/A",F43/AD43-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE43" s="41" t="s">
-        <v>293</v>
+      <c r="AG43" s="41" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11693,10 +11861,10 @@
         <v>22.7181818181818</v>
       </c>
       <c r="J44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L44" s="11" t="n">
         <v>34.67</v>
@@ -11718,10 +11886,10 @@
         <v>22</v>
       </c>
       <c r="R44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T44" s="11" t="n">
         <v>21.12</v>
@@ -11731,10 +11899,10 @@
         <v>19.2</v>
       </c>
       <c r="V44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W44" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X44" s="11" t="n">
         <v>10.29</v>
@@ -11750,20 +11918,22 @@
         <f aca="false">Z44/1.1</f>
         <v>29.7454545454545</v>
       </c>
-      <c r="AB44" s="11" t="n">
-        <f aca="false">IF(COUNT(I44,K44,M44,O44,Q44,S44,U44,W44,Y44,AA44)=0,"N/A",MIN(I44,K44,M44,O44,Q44,S44,U44,W44,Y44,AA44))</f>
+      <c r="AB44" s="11"/>
+      <c r="AC44" s="11"/>
+      <c r="AD44" s="11" t="n">
+        <f aca="false">IF(COUNT(I44,J44,M44,O44,Q44,S44,U44,V44,Y44,AA44,AC44)=0,"N/A",MIN(I44,J44,M44,O44,Q44,S44,U44,V44,Y44,AA44,AC44))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC44" s="43" t="n">
-        <f aca="false">IF(OR(D44="",AB44="",AB44="N/A"),"N/A",D44/AB44-1)</f>
+      <c r="AE44" s="43" t="n">
+        <f aca="false">IF(OR(D44="",AD44="",AD44="N/A"),"N/A",D44/AD44-1)</f>
         <v>-0.714577259475219</v>
       </c>
-      <c r="AD44" s="43" t="str">
-        <f aca="false">IF(OR(F44="",AB44="",AB44="N/A"),"N/A",F44/AB44-1)</f>
+      <c r="AF44" s="43" t="str">
+        <f aca="false">IF(OR(F44="",AD44="",AD44="N/A"),"N/A",F44/AD44-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE44" s="41" t="s">
-        <v>294</v>
+      <c r="AG44" s="41" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11801,10 +11971,10 @@
         <v>40.9</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L45" s="11" t="n">
         <v>39.58</v>
@@ -11833,10 +12003,10 @@
         <v>23.4090909090909</v>
       </c>
       <c r="T45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V45" s="11" t="n">
         <f aca="false">W45*1.1</f>
@@ -11846,10 +12016,10 @@
         <v>26.5</v>
       </c>
       <c r="X45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y45" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z45" s="45" t="n">
         <f aca="false">AA45*1.1</f>
@@ -11858,20 +12028,22 @@
       <c r="AA45" s="45" t="n">
         <v>65.64</v>
       </c>
-      <c r="AB45" s="11" t="n">
-        <f aca="false">IF(COUNT(I45,K45,M45,O45,Q45,S45,U45,W45,Y45,AA45)=0,"N/A",MIN(I45,K45,M45,O45,Q45,S45,U45,W45,Y45,AA45))</f>
+      <c r="AB45" s="45"/>
+      <c r="AC45" s="45"/>
+      <c r="AD45" s="11" t="n">
+        <f aca="false">IF(COUNT(I45,J45,M45,O45,Q45,S45,U45,V45,Y45,AA45,AC45)=0,"N/A",MIN(I45,J45,M45,O45,Q45,S45,U45,V45,Y45,AA45,AC45))</f>
         <v>23.4090909090909</v>
       </c>
-      <c r="AC45" s="43" t="n">
-        <f aca="false">IF(OR(D45="",AB45="",AB45="N/A"),"N/A",D45/AB45-1)</f>
+      <c r="AE45" s="43" t="n">
+        <f aca="false">IF(OR(D45="",AD45="",AD45="N/A"),"N/A",D45/AD45-1)</f>
         <v>-0.543339805825243</v>
       </c>
-      <c r="AD45" s="43" t="str">
-        <f aca="false">IF(OR(F45="",AB45="",AB45="N/A"),"N/A",F45/AB45-1)</f>
+      <c r="AF45" s="43" t="str">
+        <f aca="false">IF(OR(F45="",AD45="",AD45="N/A"),"N/A",F45/AD45-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE45" s="41" t="s">
-        <v>295</v>
+      <c r="AG45" s="41" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11909,52 +12081,52 @@
         <v>22.7181818181818</v>
       </c>
       <c r="J46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y46" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z46" s="45" t="n">
         <f aca="false">AA46*1.1</f>
@@ -11963,20 +12135,27 @@
       <c r="AA46" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB46" s="11" t="n">
-        <f aca="false">IF(COUNT(I46,K46,M46,O46,Q46,S46,U46,W46,Y46,AA46)=0,"N/A",MIN(I46,K46,M46,O46,Q46,S46,U46,W46,Y46,AA46))</f>
+      <c r="AB46" s="45" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC46" s="45" t="n">
+        <f aca="false">AB46/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
+      <c r="AD46" s="11" t="n">
+        <f aca="false">IF(COUNT(I46,J46,M46,O46,Q46,S46,U46,V46,Y46,AA46,AC46)=0,"N/A",MIN(I46,J46,M46,O46,Q46,S46,U46,V46,Y46,AA46,AC46))</f>
         <v>22.7181818181818</v>
       </c>
-      <c r="AC46" s="43" t="n">
-        <f aca="false">IF(OR(D46="",AB46="",AB46="N/A"),"N/A",D46/AB46-1)</f>
+      <c r="AE46" s="43" t="n">
+        <f aca="false">IF(OR(D46="",AD46="",AD46="N/A"),"N/A",D46/AD46-1)</f>
         <v>-0.882472989195678</v>
       </c>
-      <c r="AD46" s="43" t="str">
-        <f aca="false">IF(OR(F46="",AB46="",AB46="N/A"),"N/A",F46/AB46-1)</f>
+      <c r="AF46" s="43" t="str">
+        <f aca="false">IF(OR(F46="",AD46="",AD46="N/A"),"N/A",F46/AD46-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE46" s="41" t="s">
-        <v>293</v>
+      <c r="AG46" s="41" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12014,52 +12193,52 @@
         <v>40.9</v>
       </c>
       <c r="J47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y47" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z47" s="45" t="n">
         <f aca="false">AA47*1.1</f>
@@ -12068,20 +12247,27 @@
       <c r="AA47" s="45" t="n">
         <v>43.81</v>
       </c>
-      <c r="AB47" s="11" t="n">
-        <f aca="false">IF(COUNT(I47,K47,M47,O47,Q47,S47,U47,W47,Y47,AA47)=0,"N/A",MIN(I47,K47,M47,O47,Q47,S47,U47,W47,Y47,AA47))</f>
-        <v>40.9</v>
-      </c>
-      <c r="AC47" s="43" t="n">
-        <f aca="false">IF(OR(D47="",AB47="",AB47="N/A"),"N/A",D47/AB47-1)</f>
-        <v>-0.767726161369193</v>
-      </c>
-      <c r="AD47" s="43" t="str">
-        <f aca="false">IF(OR(F47="",AB47="",AB47="N/A"),"N/A",F47/AB47-1)</f>
+      <c r="AB47" s="45" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="AC47" s="45" t="n">
+        <f aca="false">AB47/1.1</f>
+        <v>25.5818181818182</v>
+      </c>
+      <c r="AD47" s="11" t="n">
+        <f aca="false">IF(COUNT(I47,J47,M47,O47,Q47,S47,U47,V47,Y47,AA47,AC47)=0,"N/A",MIN(I47,J47,M47,O47,Q47,S47,U47,V47,Y47,AA47,AC47))</f>
+        <v>25.5818181818182</v>
+      </c>
+      <c r="AE47" s="43" t="n">
+        <f aca="false">IF(OR(D47="",AD47="",AD47="N/A"),"N/A",D47/AD47-1)</f>
+        <v>-0.62864250177683</v>
+      </c>
+      <c r="AF47" s="43" t="str">
+        <f aca="false">IF(OR(F47="",AD47="",AD47="N/A"),"N/A",F47/AD47-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE47" s="41" t="s">
-        <v>293</v>
+      <c r="AG47" s="41" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12119,52 +12305,52 @@
         <v>40.9</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y48" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z48" s="45" t="n">
         <f aca="false">AA48*1.1</f>
@@ -12173,20 +12359,22 @@
       <c r="AA48" s="45" t="n">
         <v>150.22</v>
       </c>
-      <c r="AB48" s="11" t="n">
-        <f aca="false">IF(COUNT(I48,K48,M48,O48,Q48,S48,U48,W48,Y48,AA48)=0,"N/A",MIN(I48,K48,M48,O48,Q48,S48,U48,W48,Y48,AA48))</f>
+      <c r="AB48" s="45"/>
+      <c r="AC48" s="45"/>
+      <c r="AD48" s="11" t="n">
+        <f aca="false">IF(COUNT(I48,J48,M48,O48,Q48,S48,U48,V48,Y48,AA48,AC48)=0,"N/A",MIN(I48,J48,M48,O48,Q48,S48,U48,V48,Y48,AA48,AC48))</f>
         <v>40.9</v>
       </c>
-      <c r="AC48" s="43" t="n">
-        <f aca="false">IF(OR(D48="",AB48="",AB48="N/A"),"N/A",D48/AB48-1)</f>
+      <c r="AE48" s="43" t="n">
+        <f aca="false">IF(OR(D48="",AD48="",AD48="N/A"),"N/A",D48/AD48-1)</f>
         <v>-0.738630806845966</v>
       </c>
-      <c r="AD48" s="43" t="str">
-        <f aca="false">IF(OR(F48="",AB48="",AB48="N/A"),"N/A",F48/AB48-1)</f>
+      <c r="AF48" s="43" t="str">
+        <f aca="false">IF(OR(F48="",AD48="",AD48="N/A"),"N/A",F48/AD48-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE48" s="41" t="s">
-        <v>293</v>
+      <c r="AG48" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12224,10 +12412,10 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L49" s="11" t="n">
         <v>34.67</v>
@@ -12236,16 +12424,16 @@
         <v>31.52</v>
       </c>
       <c r="N49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R49" s="11" t="n">
         <v>23</v>
@@ -12269,10 +12457,10 @@
         <v>21.9</v>
       </c>
       <c r="X49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y49" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z49" s="45" t="n">
         <f aca="false">AA49*1.1</f>
@@ -12281,20 +12469,27 @@
       <c r="AA49" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB49" s="11" t="n">
-        <f aca="false">IF(COUNT(I49,K49,M49,O49,Q49,S49,U49,W49,Y49,AA49)=0,"N/A",MIN(I49,K49,M49,O49,Q49,S49,U49,W49,Y49,AA49))</f>
+      <c r="AB49" s="45" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AC49" s="45" t="n">
+        <f aca="false">AB49/1.1</f>
+        <v>32.6363636363636</v>
+      </c>
+      <c r="AD49" s="11" t="n">
+        <f aca="false">IF(COUNT(I49,J49,M49,O49,Q49,S49,U49,V49,Y49,AA49,AC49)=0,"N/A",MIN(I49,J49,M49,O49,Q49,S49,U49,V49,Y49,AA49,AC49))</f>
         <v>20.9090909090909</v>
       </c>
-      <c r="AC49" s="43" t="n">
-        <f aca="false">IF(OR(D49="",AB49="",AB49="N/A"),"N/A",D49/AB49-1)</f>
+      <c r="AE49" s="43" t="n">
+        <f aca="false">IF(OR(D49="",AD49="",AD49="N/A"),"N/A",D49/AD49-1)</f>
         <v>-0.744130434782609</v>
       </c>
-      <c r="AD49" s="43" t="str">
-        <f aca="false">IF(OR(F49="",AB49="",AB49="N/A"),"N/A",F49/AB49-1)</f>
+      <c r="AF49" s="43" t="str">
+        <f aca="false">IF(OR(F49="",AD49="",AD49="N/A"),"N/A",F49/AD49-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE49" s="41" t="s">
-        <v>296</v>
+      <c r="AG49" s="41" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12332,10 +12527,10 @@
         <v>45.4454545454545</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K50" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L50" s="11" t="n">
         <v>34.67</v>
@@ -12391,20 +12586,22 @@
       <c r="AA50" s="45" t="n">
         <v>57.92</v>
       </c>
-      <c r="AB50" s="11" t="n">
-        <f aca="false">IF(COUNT(I50,K50,M50,O50,Q50,S50,U50,W50,Y50,AA50)=0,"N/A",MIN(I50,K50,M50,O50,Q50,S50,U50,W50,Y50,AA50))</f>
+      <c r="AB50" s="45"/>
+      <c r="AC50" s="45"/>
+      <c r="AD50" s="11" t="n">
+        <f aca="false">IF(COUNT(I50,J50,M50,O50,Q50,S50,U50,V50,Y50,AA50,AC50)=0,"N/A",MIN(I50,J50,M50,O50,Q50,S50,U50,V50,Y50,AA50,AC50))</f>
         <v>9.35454545454545</v>
       </c>
-      <c r="AC50" s="43" t="n">
-        <f aca="false">IF(OR(D50="",AB50="",AB50="N/A"),"N/A",D50/AB50-1)</f>
+      <c r="AE50" s="43" t="n">
+        <f aca="false">IF(OR(D50="",AD50="",AD50="N/A"),"N/A",D50/AD50-1)</f>
         <v>-0.428085519922255</v>
       </c>
-      <c r="AD50" s="43" t="str">
-        <f aca="false">IF(OR(F50="",AB50="",AB50="N/A"),"N/A",F50/AB50-1)</f>
+      <c r="AF50" s="43" t="str">
+        <f aca="false">IF(OR(F50="",AD50="",AD50="N/A"),"N/A",F50/AD50-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE50" s="41" t="s">
-        <v>297</v>
+      <c r="AG50" s="41" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12442,52 +12639,52 @@
         <v>25.4454545454545</v>
       </c>
       <c r="J51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y51" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z51" s="45" t="n">
         <f aca="false">AA51*1.1</f>
@@ -12496,20 +12693,22 @@
       <c r="AA51" s="45" t="n">
         <v>57.92</v>
       </c>
-      <c r="AB51" s="11" t="n">
-        <f aca="false">IF(COUNT(I51,K51,M51,O51,Q51,S51,U51,W51,Y51,AA51)=0,"N/A",MIN(I51,K51,M51,O51,Q51,S51,U51,W51,Y51,AA51))</f>
+      <c r="AB51" s="45"/>
+      <c r="AC51" s="45"/>
+      <c r="AD51" s="11" t="n">
+        <f aca="false">IF(COUNT(I51,J51,M51,O51,Q51,S51,U51,V51,Y51,AA51,AC51)=0,"N/A",MIN(I51,J51,M51,O51,Q51,S51,U51,V51,Y51,AA51,AC51))</f>
         <v>25.4454545454545</v>
       </c>
-      <c r="AC51" s="43" t="n">
-        <f aca="false">IF(OR(D51="",AB51="",AB51="N/A"),"N/A",D51/AB51-1)</f>
+      <c r="AE51" s="43" t="n">
+        <f aca="false">IF(OR(D51="",AD51="",AD51="N/A"),"N/A",D51/AD51-1)</f>
         <v>-0.895069667738478</v>
       </c>
-      <c r="AD51" s="43" t="str">
-        <f aca="false">IF(OR(F51="",AB51="",AB51="N/A"),"N/A",F51/AB51-1)</f>
+      <c r="AF51" s="43" t="str">
+        <f aca="false">IF(OR(F51="",AD51="",AD51="N/A"),"N/A",F51/AD51-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE51" s="41" t="s">
-        <v>293</v>
+      <c r="AG51" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12547,52 +12746,52 @@
         <v>40.9</v>
       </c>
       <c r="J52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y52" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z52" s="45" t="n">
         <f aca="false">AA52*1.1</f>
@@ -12601,20 +12800,22 @@
       <c r="AA52" s="45" t="n">
         <v>70.25</v>
       </c>
-      <c r="AB52" s="11" t="n">
-        <f aca="false">IF(COUNT(I52,K52,M52,O52,Q52,S52,U52,W52,Y52,AA52)=0,"N/A",MIN(I52,K52,M52,O52,Q52,S52,U52,W52,Y52,AA52))</f>
+      <c r="AB52" s="45"/>
+      <c r="AC52" s="45"/>
+      <c r="AD52" s="11" t="n">
+        <f aca="false">IF(COUNT(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52)=0,"N/A",MIN(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52))</f>
         <v>40.9</v>
       </c>
-      <c r="AC52" s="43" t="n">
-        <f aca="false">IF(OR(D52="",AB52="",AB52="N/A"),"N/A",D52/AB52-1)</f>
+      <c r="AE52" s="43" t="n">
+        <f aca="false">IF(OR(D52="",AD52="",AD52="N/A"),"N/A",D52/AD52-1)</f>
         <v>-0.767726161369193</v>
       </c>
-      <c r="AD52" s="43" t="str">
-        <f aca="false">IF(OR(F52="",AB52="",AB52="N/A"),"N/A",F52/AB52-1)</f>
+      <c r="AF52" s="43" t="str">
+        <f aca="false">IF(OR(F52="",AD52="",AD52="N/A"),"N/A",F52/AD52-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE52" s="41" t="s">
-        <v>293</v>
+      <c r="AG52" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12652,10 +12853,10 @@
         <v>45.4454545454545</v>
       </c>
       <c r="J53" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K53" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L53" s="11" t="n">
         <v>21.51</v>
@@ -12691,10 +12892,10 @@
         <v>20.1090909090909</v>
       </c>
       <c r="V53" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W53" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X53" s="11" t="n">
         <v>10.29</v>
@@ -12710,20 +12911,22 @@
         <f aca="false">Z53/1.1</f>
         <v>55.7545454545455</v>
       </c>
-      <c r="AB53" s="11" t="n">
-        <f aca="false">IF(COUNT(I53,K53,M53,O53,Q53,S53,U53,W53,Y53,AA53)=0,"N/A",MIN(I53,K53,M53,O53,Q53,S53,U53,W53,Y53,AA53))</f>
+      <c r="AB53" s="11"/>
+      <c r="AC53" s="11"/>
+      <c r="AD53" s="11" t="n">
+        <f aca="false">IF(COUNT(I53,J53,M53,O53,Q53,S53,U53,V53,Y53,AA53,AC53)=0,"N/A",MIN(I53,J53,M53,O53,Q53,S53,U53,V53,Y53,AA53,AC53))</f>
         <v>7.81818181818182</v>
       </c>
-      <c r="AC53" s="43" t="n">
-        <f aca="false">IF(OR(D53="",AB53="",AB53="N/A"),"N/A",D53/AB53-1)</f>
+      <c r="AE53" s="43" t="n">
+        <f aca="false">IF(OR(D53="",AD53="",AD53="N/A"),"N/A",D53/AD53-1)</f>
         <v>-0.744186046511628</v>
       </c>
-      <c r="AD53" s="43" t="str">
-        <f aca="false">IF(OR(F53="",AB53="",AB53="N/A"),"N/A",F53/AB53-1)</f>
+      <c r="AF53" s="43" t="str">
+        <f aca="false">IF(OR(F53="",AD53="",AD53="N/A"),"N/A",F53/AD53-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE53" s="41" t="s">
-        <v>298</v>
+      <c r="AG53" s="41" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12761,52 +12964,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y54" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z54" s="45" t="n">
         <f aca="false">1.1*AA54</f>
@@ -12815,20 +13018,22 @@
       <c r="AA54" s="45" t="n">
         <v>51.27</v>
       </c>
-      <c r="AB54" s="11" t="n">
-        <f aca="false">IF(COUNT(I54,K54,M54,O54,Q54,S54,U54,W54,Y54,AA54)=0,"N/A",MIN(I54,K54,M54,O54,Q54,S54,U54,W54,Y54,AA54))</f>
+      <c r="AB54" s="45"/>
+      <c r="AC54" s="45"/>
+      <c r="AD54" s="11" t="n">
+        <f aca="false">IF(COUNT(I54,J54,M54,O54,Q54,S54,U54,V54,Y54,AA54,AC54)=0,"N/A",MIN(I54,J54,M54,O54,Q54,S54,U54,V54,Y54,AA54,AC54))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC54" s="43" t="n">
-        <f aca="false">IF(OR(D54="",AB54="",AB54="N/A"),"N/A",D54/AB54-1)</f>
+      <c r="AE54" s="43" t="n">
+        <f aca="false">IF(OR(D54="",AD54="",AD54="N/A"),"N/A",D54/AD54-1)</f>
         <v>-0.910973022127918</v>
       </c>
-      <c r="AD54" s="43" t="str">
-        <f aca="false">IF(OR(F54="",AB54="",AB54="N/A"),"N/A",F54/AB54-1)</f>
+      <c r="AF54" s="43" t="str">
+        <f aca="false">IF(OR(F54="",AD54="",AD54="N/A"),"N/A",F54/AD54-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE54" s="41" t="s">
-        <v>293</v>
+      <c r="AG54" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12866,73 +13071,75 @@
         <v>34.5363636363636</v>
       </c>
       <c r="J55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z55" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA55" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="AB55" s="11" t="n">
-        <f aca="false">IF(COUNT(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55)=0,"N/A",MIN(I55,K55,M55,O55,Q55,S55,U55,W55,Y55,AA55))</f>
+        <v>304</v>
+      </c>
+      <c r="AB55" s="42"/>
+      <c r="AC55" s="42"/>
+      <c r="AD55" s="11" t="n">
+        <f aca="false">IF(COUNT(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55)=0,"N/A",MIN(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC55" s="43" t="n">
-        <f aca="false">IF(OR(D55="",AB55="",AB55="N/A"),"N/A",D55/AB55-1)</f>
+      <c r="AE55" s="43" t="n">
+        <f aca="false">IF(OR(D55="",AD55="",AD55="N/A"),"N/A",D55/AD55-1)</f>
         <v>-0.883890497499342</v>
       </c>
-      <c r="AD55" s="43" t="str">
-        <f aca="false">IF(OR(F55="",AB55="",AB55="N/A"),"N/A",F55/AB55-1)</f>
+      <c r="AF55" s="43" t="str">
+        <f aca="false">IF(OR(F55="",AD55="",AD55="N/A"),"N/A",F55/AD55-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE55" s="41" t="s">
-        <v>293</v>
+      <c r="AG55" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12970,73 +13177,75 @@
         <v>34.5363636363636</v>
       </c>
       <c r="J56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z56" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AA56" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB56" s="11" t="n">
-        <f aca="false">IF(COUNT(I56,K56,M56,O56,Q56,S56,U56,W56,Y56,AA56)=0,"N/A",MIN(I56,K56,M56,O56,Q56,S56,U56,W56,Y56,AA56))</f>
+        <v>259</v>
+      </c>
+      <c r="AB56" s="42"/>
+      <c r="AC56" s="42"/>
+      <c r="AD56" s="11" t="n">
+        <f aca="false">IF(COUNT(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56)=0,"N/A",MIN(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC56" s="43" t="n">
-        <f aca="false">IF(OR(D56="",AB56="",AB56="N/A"),"N/A",D56/AB56-1)</f>
+      <c r="AE56" s="43" t="n">
+        <f aca="false">IF(OR(D56="",AD56="",AD56="N/A"),"N/A",D56/AD56-1)</f>
         <v>-0.690471176625428</v>
       </c>
-      <c r="AD56" s="43" t="str">
-        <f aca="false">IF(OR(F56="",AB56="",AB56="N/A"),"N/A",F56/AB56-1)</f>
+      <c r="AF56" s="43" t="str">
+        <f aca="false">IF(OR(F56="",AD56="",AD56="N/A"),"N/A",F56/AD56-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE56" s="41" t="s">
-        <v>293</v>
+      <c r="AG56" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13074,52 +13283,52 @@
         <v>34.5363636363636</v>
       </c>
       <c r="J57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y57" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z57" s="45" t="n">
         <f aca="false">1.1*AA57</f>
@@ -13128,20 +13337,22 @@
       <c r="AA57" s="45" t="n">
         <v>70.25</v>
       </c>
-      <c r="AB57" s="11" t="n">
-        <f aca="false">IF(COUNT(I57,K57,M57,O57,Q57,S57,U57,W57,Y57,AA57)=0,"N/A",MIN(I57,K57,M57,O57,Q57,S57,U57,W57,Y57,AA57))</f>
+      <c r="AB57" s="45"/>
+      <c r="AC57" s="45"/>
+      <c r="AD57" s="11" t="n">
+        <f aca="false">IF(COUNT(I57,J57,M57,O57,Q57,S57,U57,V57,Y57,AA57,AC57)=0,"N/A",MIN(I57,J57,M57,O57,Q57,S57,U57,V57,Y57,AA57,AC57))</f>
         <v>34.5363636363636</v>
       </c>
-      <c r="AC57" s="43" t="n">
-        <f aca="false">IF(OR(D57="",AB57="",AB57="N/A"),"N/A",D57/AB57-1)</f>
+      <c r="AE57" s="43" t="n">
+        <f aca="false">IF(OR(D57="",AD57="",AD57="N/A"),"N/A",D57/AD57-1)</f>
         <v>-0.690471176625428</v>
       </c>
-      <c r="AD57" s="43" t="str">
-        <f aca="false">IF(OR(F57="",AB57="",AB57="N/A"),"N/A",F57/AB57-1)</f>
+      <c r="AF57" s="43" t="str">
+        <f aca="false">IF(OR(F57="",AD57="",AD57="N/A"),"N/A",F57/AD57-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE57" s="41" t="s">
-        <v>293</v>
+      <c r="AG57" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13179,52 +13390,52 @@
         <v>40.9</v>
       </c>
       <c r="J58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y58" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z58" s="45" t="n">
         <f aca="false">1.1*AA58</f>
@@ -13233,20 +13444,27 @@
       <c r="AA58" s="45" t="n">
         <v>43.81</v>
       </c>
-      <c r="AB58" s="11" t="n">
-        <f aca="false">IF(COUNT(I58,K58,M58,O58,Q58,S58,U58,W58,Y58,AA58)=0,"N/A",MIN(I58,K58,M58,O58,Q58,S58,U58,W58,Y58,AA58))</f>
-        <v>40.9</v>
-      </c>
-      <c r="AC58" s="43" t="n">
-        <f aca="false">IF(OR(D58="",AB58="",AB58="N/A"),"N/A",D58/AB58-1)</f>
-        <v>-0.738630806845966</v>
-      </c>
-      <c r="AD58" s="43" t="str">
-        <f aca="false">IF(OR(F58="",AB58="",AB58="N/A"),"N/A",F58/AB58-1)</f>
+      <c r="AB58" s="45" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AC58" s="45" t="n">
+        <f aca="false">AB58/1.1</f>
+        <v>38.8636363636364</v>
+      </c>
+      <c r="AD58" s="11" t="n">
+        <f aca="false">IF(COUNT(I58,J58,M58,O58,Q58,S58,U58,V58,Y58,AA58,AC58)=0,"N/A",MIN(I58,J58,M58,O58,Q58,S58,U58,V58,Y58,AA58,AC58))</f>
+        <v>38.8636363636364</v>
+      </c>
+      <c r="AE58" s="43" t="n">
+        <f aca="false">IF(OR(D58="",AD58="",AD58="N/A"),"N/A",D58/AD58-1)</f>
+        <v>-0.72493567251462</v>
+      </c>
+      <c r="AF58" s="43" t="str">
+        <f aca="false">IF(OR(F58="",AD58="",AD58="N/A"),"N/A",F58/AD58-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE58" s="41" t="s">
-        <v>293</v>
+      <c r="AG58" s="41" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13284,52 +13502,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y59" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z59" s="45" t="n">
         <f aca="false">1.1*AA59</f>
@@ -13338,20 +13556,22 @@
       <c r="AA59" s="45" t="n">
         <v>47.44</v>
       </c>
-      <c r="AB59" s="11" t="n">
-        <f aca="false">IF(COUNT(I59,K59,M59,O59,Q59,S59,U59,W59,Y59,AA59)=0,"N/A",MIN(I59,K59,M59,O59,Q59,S59,U59,W59,Y59,AA59))</f>
+      <c r="AB59" s="45"/>
+      <c r="AC59" s="45"/>
+      <c r="AD59" s="11" t="n">
+        <f aca="false">IF(COUNT(I59,J59,M59,O59,Q59,S59,U59,V59,Y59,AA59,AC59)=0,"N/A",MIN(I59,J59,M59,O59,Q59,S59,U59,V59,Y59,AA59,AC59))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC59" s="43" t="n">
-        <f aca="false">IF(OR(D59="",AB59="",AB59="N/A"),"N/A",D59/AB59-1)</f>
+      <c r="AE59" s="43" t="n">
+        <f aca="false">IF(OR(D59="",AD59="",AD59="N/A"),"N/A",D59/AD59-1)</f>
         <v>-0.903637465898757</v>
       </c>
-      <c r="AD59" s="43" t="str">
-        <f aca="false">IF(OR(F59="",AB59="",AB59="N/A"),"N/A",F59/AB59-1)</f>
+      <c r="AF59" s="43" t="str">
+        <f aca="false">IF(OR(F59="",AD59="",AD59="N/A"),"N/A",F59/AD59-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE59" s="41" t="s">
-        <v>293</v>
+      <c r="AG59" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13389,52 +13609,52 @@
         <v>45.4454545454545</v>
       </c>
       <c r="J60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y60" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z60" s="45" t="n">
         <f aca="false">1.1*AA60</f>
@@ -13443,20 +13663,22 @@
       <c r="AA60" s="45" t="n">
         <v>83.86</v>
       </c>
-      <c r="AB60" s="11" t="n">
-        <f aca="false">IF(COUNT(I60,K60,M60,O60,Q60,S60,U60,W60,Y60,AA60)=0,"N/A",MIN(I60,K60,M60,O60,Q60,S60,U60,W60,Y60,AA60))</f>
+      <c r="AB60" s="45"/>
+      <c r="AC60" s="45"/>
+      <c r="AD60" s="11" t="n">
+        <f aca="false">IF(COUNT(I60,J60,M60,O60,Q60,S60,U60,V60,Y60,AA60,AC60)=0,"N/A",MIN(I60,J60,M60,O60,Q60,S60,U60,V60,Y60,AA60,AC60))</f>
         <v>45.4454545454545</v>
       </c>
-      <c r="AC60" s="43" t="n">
-        <f aca="false">IF(OR(D60="",AB60="",AB60="N/A"),"N/A",D60/AB60-1)</f>
+      <c r="AE60" s="43" t="n">
+        <f aca="false">IF(OR(D60="",AD60="",AD60="N/A"),"N/A",D60/AD60-1)</f>
         <v>-0.957311462292458</v>
       </c>
-      <c r="AD60" s="43" t="str">
-        <f aca="false">IF(OR(F60="",AB60="",AB60="N/A"),"N/A",F60/AB60-1)</f>
+      <c r="AF60" s="43" t="str">
+        <f aca="false">IF(OR(F60="",AD60="",AD60="N/A"),"N/A",F60/AD60-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE60" s="41" t="s">
-        <v>293</v>
+      <c r="AG60" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13494,52 +13716,52 @@
         <v>45.4454545454545</v>
       </c>
       <c r="J61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y61" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z61" s="45" t="n">
         <f aca="false">1.1*AA61</f>
@@ -13548,20 +13770,22 @@
       <c r="AA61" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB61" s="11" t="n">
-        <f aca="false">IF(COUNT(I61,K61,M61,O61,Q61,S61,U61,W61,Y61,AA61)=0,"N/A",MIN(I61,K61,M61,O61,Q61,S61,U61,W61,Y61,AA61))</f>
+      <c r="AB61" s="45"/>
+      <c r="AC61" s="45"/>
+      <c r="AD61" s="11" t="n">
+        <f aca="false">IF(COUNT(I61,J61,M61,O61,Q61,S61,U61,V61,Y61,AA61,AC61)=0,"N/A",MIN(I61,J61,M61,O61,Q61,S61,U61,V61,Y61,AA61,AC61))</f>
         <v>43.55</v>
       </c>
-      <c r="AC61" s="43" t="n">
-        <f aca="false">IF(OR(D61="",AB61="",AB61="N/A"),"N/A",D61/AB61-1)</f>
+      <c r="AE61" s="43" t="n">
+        <f aca="false">IF(OR(D61="",AD61="",AD61="N/A"),"N/A",D61/AD61-1)</f>
         <v>-0.754535017221584</v>
       </c>
-      <c r="AD61" s="43" t="str">
-        <f aca="false">IF(OR(F61="",AB61="",AB61="N/A"),"N/A",F61/AB61-1)</f>
+      <c r="AF61" s="43" t="str">
+        <f aca="false">IF(OR(F61="",AD61="",AD61="N/A"),"N/A",F61/AD61-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE61" s="41" t="s">
-        <v>293</v>
+      <c r="AG61" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13599,52 +13823,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y62" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z62" s="45" t="n">
         <f aca="false">1.1*AA62</f>
@@ -13653,20 +13877,22 @@
       <c r="AA62" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB62" s="11" t="n">
-        <f aca="false">IF(COUNT(I62,K62,M62,O62,Q62,S62,U62,W62,Y62,AA62)=0,"N/A",MIN(I62,K62,M62,O62,Q62,S62,U62,W62,Y62,AA62))</f>
+      <c r="AB62" s="45"/>
+      <c r="AC62" s="45"/>
+      <c r="AD62" s="11" t="n">
+        <f aca="false">IF(COUNT(I62,J62,M62,O62,Q62,S62,U62,V62,Y62,AA62,AC62)=0,"N/A",MIN(I62,J62,M62,O62,Q62,S62,U62,V62,Y62,AA62,AC62))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC62" s="43" t="n">
-        <f aca="false">IF(OR(D62="",AB62="",AB62="N/A"),"N/A",D62/AB62-1)</f>
+      <c r="AE62" s="43" t="n">
+        <f aca="false">IF(OR(D62="",AD62="",AD62="N/A"),"N/A",D62/AD62-1)</f>
         <v>-0.893267656865717</v>
       </c>
-      <c r="AD62" s="43" t="str">
-        <f aca="false">IF(OR(F62="",AB62="",AB62="N/A"),"N/A",F62/AB62-1)</f>
+      <c r="AF62" s="43" t="str">
+        <f aca="false">IF(OR(F62="",AD62="",AD62="N/A"),"N/A",F62/AD62-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE62" s="41" t="s">
-        <v>293</v>
+      <c r="AG62" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13704,52 +13930,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y63" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z63" s="45" t="n">
         <f aca="false">1.1*AA63</f>
@@ -13758,20 +13984,22 @@
       <c r="AA63" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB63" s="11" t="n">
-        <f aca="false">IF(COUNT(I63,K63,M63,O63,Q63,S63,U63,W63,Y63,AA63)=0,"N/A",MIN(I63,K63,M63,O63,Q63,S63,U63,W63,Y63,AA63))</f>
+      <c r="AB63" s="45"/>
+      <c r="AC63" s="45"/>
+      <c r="AD63" s="11" t="n">
+        <f aca="false">IF(COUNT(I63,J63,M63,O63,Q63,S63,U63,V63,Y63,AA63,AC63)=0,"N/A",MIN(I63,J63,M63,O63,Q63,S63,U63,V63,Y63,AA63,AC63))</f>
         <v>29.9909090909091</v>
       </c>
-      <c r="AC63" s="43" t="n">
-        <f aca="false">IF(OR(D63="",AB63="",AB63="N/A"),"N/A",D63/AB63-1)</f>
+      <c r="AE63" s="43" t="n">
+        <f aca="false">IF(OR(D63="",AD63="",AD63="N/A"),"N/A",D63/AD63-1)</f>
         <v>-0.821612609881782</v>
       </c>
-      <c r="AD63" s="43" t="str">
-        <f aca="false">IF(OR(F63="",AB63="",AB63="N/A"),"N/A",F63/AB63-1)</f>
+      <c r="AF63" s="43" t="str">
+        <f aca="false">IF(OR(F63="",AD63="",AD63="N/A"),"N/A",F63/AD63-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE63" s="41" t="s">
-        <v>293</v>
+      <c r="AG63" s="41" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13809,52 +14037,52 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="V64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="X64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y64" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z64" s="45" t="n">
         <f aca="false">1.1*AA64</f>
@@ -13863,20 +14091,27 @@
       <c r="AA64" s="45" t="n">
         <v>34.78</v>
       </c>
-      <c r="AB64" s="11" t="n">
-        <f aca="false">IF(COUNT(I64,K64,M64,O64,Q64,S64,U64,W64,Y64,AA64)=0,"N/A",MIN(I64,K64,M64,O64,Q64,S64,U64,W64,Y64,AA64))</f>
-        <v>29.9909090909091</v>
-      </c>
-      <c r="AC64" s="43" t="n">
-        <f aca="false">IF(OR(D64="",AB64="",AB64="N/A"),"N/A",D64/AB64-1)</f>
-        <v>-0.910973022127918</v>
-      </c>
-      <c r="AD64" s="43" t="str">
-        <f aca="false">IF(OR(F64="",AB64="",AB64="N/A"),"N/A",F64/AB64-1)</f>
+      <c r="AB64" s="45" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC64" s="45" t="n">
+        <f aca="false">AB64/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
+      <c r="AD64" s="11" t="n">
+        <f aca="false">IF(COUNT(I64,J64,M64,O64,Q64,S64,U64,V64,Y64,AA64,AC64)=0,"N/A",MIN(I64,J64,M64,O64,Q64,S64,U64,V64,Y64,AA64,AC64))</f>
+        <v>27.9727272727273</v>
+      </c>
+      <c r="AE64" s="43" t="n">
+        <f aca="false">IF(OR(D64="",AD64="",AD64="N/A"),"N/A",D64/AD64-1)</f>
+        <v>-0.904549886252844</v>
+      </c>
+      <c r="AF64" s="43" t="str">
+        <f aca="false">IF(OR(F64="",AD64="",AD64="N/A"),"N/A",F64/AD64-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE64" s="41" t="s">
-        <v>293</v>
+      <c r="AG64" s="41" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13914,16 +14149,16 @@
         <v>29.9909090909091</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N65" s="11" t="n">
         <v>108.6</v>
@@ -13933,10 +14168,10 @@
         <v>98.7272727272727</v>
       </c>
       <c r="P65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q65" s="42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R65" s="11" t="n">
         <v>30</v>
@@ -13974,19 +14209,26 @@
         <v>31.8727272727273</v>
       </c>
       <c r="AB65" s="11" t="n">
-        <f aca="false">IF(COUNT(I65,K65,M65,O65,Q65,S65,U65,W65,Y65,AA65)=0,"N/A",MIN(I65,K65,M65,O65,Q65,S65,U65,W65,Y65,AA65))</f>
+        <v>46.99</v>
+      </c>
+      <c r="AC65" s="11" t="n">
+        <f aca="false">AB65/1.1</f>
+        <v>42.7181818181818</v>
+      </c>
+      <c r="AD65" s="11" t="n">
+        <f aca="false">IF(COUNT(I65,J65,M65,O65,Q65,S65,U65,V65,Y65,AA65,AC65)=0,"N/A",MIN(I65,J65,M65,O65,Q65,S65,U65,V65,Y65,AA65,AC65))</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="AC65" s="43" t="n">
-        <f aca="false">IF(OR(D65="",AB65="",AB65="N/A"),"N/A",D65/AB65-1)</f>
+      <c r="AE65" s="43" t="n">
+        <f aca="false">IF(OR(D65="",AD65="",AD65="N/A"),"N/A",D65/AD65-1)</f>
         <v>-0.608033333333333</v>
       </c>
-      <c r="AD65" s="43" t="str">
-        <f aca="false">IF(OR(F65="",AB65="",AB65="N/A"),"N/A",F65/AB65-1)</f>
+      <c r="AF65" s="43" t="str">
+        <f aca="false">IF(OR(F65="",AD65="",AD65="N/A"),"N/A",F65/AD65-1)</f>
         <v>N/A</v>
       </c>
-      <c r="AE65" s="41" t="s">
-        <v>300</v>
+      <c r="AG65" s="41" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13996,7 +14238,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="35" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
@@ -14007,100 +14249,100 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="35" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="n">
-        <f aca="false">COUNTIF(K6:K65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(W6:W65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")</f>
-        <v>251</v>
+        <f aca="false">COUNTIF(J6:J65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(V6:V65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")+COUNTIF(AC6:AC65,"&gt;0")</f>
+        <v>269</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="35" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="n">
-        <f aca="false">COUNTIF(AC6:AC65,"&lt;0")</f>
+        <f aca="false">COUNTIF(AE6:AE65,"&lt;0")</f>
         <v>53</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="35" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="n">
-        <f aca="false">COUNTIF(AC6:AC65,"&gt;0")</f>
+        <f aca="false">COUNTIF(AE6:AE65,"&gt;0")</f>
         <v>7</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="35" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
       <c r="D72" s="47" t="n">
-        <f aca="false">AVERAGE(AC6:AC65)</f>
-        <v>-0.501166129687786</v>
+        <f aca="false">AVERAGE(AE6:AE65)</f>
+        <v>-0.502826801988701</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="35" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
       <c r="D73" s="47" t="n">
-        <f aca="false">MEDIAN(AC6:AC65)</f>
+        <f aca="false">MEDIAN(AE6:AE65)</f>
         <v>-0.578387096774194</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="35" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="n">
-        <f aca="false">COUNTIF(AD6:AD65,"&lt;0")</f>
+        <f aca="false">COUNTIF(AF6:AF65,"&lt;0")</f>
         <v>15</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="35" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="n">
-        <f aca="false">COUNTIF(AD6:AD65,"&gt;0")</f>
+        <f aca="false">COUNTIF(AF6:AF65,"&gt;0")</f>
         <v>7</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="35" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
       <c r="D76" s="47" t="n">
-        <f aca="false">AVERAGE(AD6:AD65)</f>
-        <v>-0.175684855421017</v>
+        <f aca="false">AVERAGE(AF6:AF65)</f>
+        <v>-0.186068097813109</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="35" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
       <c r="D77" s="47" t="n">
-        <f aca="false">MEDIAN(AD6:AD65)</f>
+        <f aca="false">MEDIAN(AF6:AF65)</f>
         <v>-0.260605761397123</v>
       </c>
     </row>
@@ -14152,7 +14394,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -14166,7 +14408,7 @@
     </row>
     <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B2" s="49"/>
       <c r="C2" s="49"/>
@@ -14189,22 +14431,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E4" s="50" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="G4" s="50" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="H4" s="50" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="I4" s="50" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J4" s="50" t="s">
         <v>221</v>
@@ -14221,7 +14463,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E5" s="52" t="n">
         <v>20.05</v>
@@ -14233,10 +14475,10 @@
         <v>-3.11725</v>
       </c>
       <c r="H5" s="55" t="n">
-        <v>-0.184095908815757</v>
+        <v>-0.155473815461347</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J5" s="51"/>
     </row>
@@ -14251,7 +14493,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E6" s="52" t="n">
         <v>122.718181818182</v>
@@ -14263,10 +14505,10 @@
         <v>-55.888181818182</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>-0.836273856324735</v>
+        <v>-0.455418919919995</v>
       </c>
       <c r="I6" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J6" s="51"/>
     </row>
@@ -14281,7 +14523,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E7" s="52" t="n">
         <v>128.75</v>
@@ -14293,10 +14535,10 @@
         <v>-84.2</v>
       </c>
       <c r="H7" s="55" t="n">
-        <v>-1.89001122334456</v>
+        <v>-0.653980582524272</v>
       </c>
       <c r="I7" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J7" s="51"/>
     </row>
@@ -14311,7 +14553,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E8" s="52" t="n">
         <v>69.245</v>
@@ -14323,10 +14565,10 @@
         <v>-24.101</v>
       </c>
       <c r="H8" s="55" t="n">
-        <v>-0.533869395711501</v>
+        <v>-0.348054011119937</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J8" s="51"/>
     </row>
@@ -14341,7 +14583,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E9" s="52" t="n">
         <v>81.4</v>
@@ -14353,10 +14595,10 @@
         <v>-10.861875</v>
       </c>
       <c r="H9" s="55" t="n">
-        <v>-0.153985876432072</v>
+        <v>-0.133438267813268</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J9" s="51"/>
     </row>
@@ -14371,7 +14613,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E10" s="52" t="n">
         <v>44.209</v>
@@ -14383,10 +14625,10 @@
         <v>-10.3535</v>
       </c>
       <c r="H10" s="55" t="n">
-        <v>-0.305814417155263</v>
+        <v>-0.234194394806487</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J10" s="51"/>
     </row>
@@ -14401,7 +14643,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E11" s="52" t="n">
         <v>70.36</v>
@@ -14413,10 +14655,10 @@
         <v>-25.216</v>
       </c>
       <c r="H11" s="55" t="n">
-        <v>-0.558568137515506</v>
+        <v>-0.358385446276293</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J11" s="51"/>
     </row>
@@ -14431,7 +14673,7 @@
         <v>80</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E12" s="59" t="n">
         <v>33.1818181818182</v>
@@ -14443,10 +14685,10 @@
         <v>0.673681818181798</v>
       </c>
       <c r="H12" s="62" t="n">
-        <v>0.019898740771272</v>
+        <v>0.0203027397260268</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J12" s="57"/>
     </row>
@@ -14461,7 +14703,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E13" s="52" t="n">
         <v>43.09</v>
@@ -14473,10 +14715,10 @@
         <v>-17.695875</v>
       </c>
       <c r="H13" s="55" t="n">
-        <v>-0.696849172790951</v>
+        <v>-0.410672429798097</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J13" s="51"/>
     </row>
@@ -14491,7 +14733,7 @@
         <v>102</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E14" s="52" t="n">
         <v>29.9909090909091</v>
@@ -14503,10 +14745,10 @@
         <v>-21.5295340909091</v>
       </c>
       <c r="H14" s="55" t="n">
-        <v>-2.54444863759248</v>
+        <v>-0.717868672324947</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J14" s="51"/>
     </row>
@@ -14521,7 +14763,7 @@
         <v>108</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E15" s="52" t="n">
         <v>40.9</v>
@@ -14533,10 +14775,10 @@
         <v>-25.08725</v>
       </c>
       <c r="H15" s="55" t="n">
-        <v>-1.58652037121943</v>
+        <v>-0.613380195599022</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J15" s="51"/>
     </row>
@@ -14551,7 +14793,7 @@
         <v>118</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E16" s="52" t="n">
         <v>29.9909090909091</v>
@@ -14563,10 +14805,10 @@
         <v>-21.5295340909091</v>
       </c>
       <c r="H16" s="55" t="n">
-        <v>-2.54444863759248</v>
+        <v>-0.717868672324947</v>
       </c>
       <c r="I16" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J16" s="51"/>
     </row>
@@ -14581,7 +14823,7 @@
         <v>128</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E17" s="52" t="n">
         <v>37.3909090909091</v>
@@ -14593,10 +14835,10 @@
         <v>-7.2454090909091</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>-0.240347948811899</v>
+        <v>-0.193774617067834</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J17" s="51"/>
     </row>
@@ -14611,7 +14853,7 @@
         <v>132</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E18" s="59" t="n">
         <v>28.3545454545455</v>
@@ -14623,10 +14865,10 @@
         <v>1.7909545454545</v>
       </c>
       <c r="H18" s="62" t="n">
-        <v>0.0594103446768007</v>
+        <v>0.0631628727156122</v>
       </c>
       <c r="I18" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J18" s="57"/>
     </row>
@@ -14641,7 +14883,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E19" s="52" t="n">
         <v>23.3090909090909</v>
@@ -14653,10 +14895,10 @@
         <v>-6.3763409090909</v>
       </c>
       <c r="H19" s="55" t="n">
-        <v>-0.376568537838857</v>
+        <v>-0.273555967238689</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J19" s="51"/>
     </row>
@@ -14671,7 +14913,7 @@
         <v>142</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E20" s="59" t="n">
         <v>28.99</v>
@@ -14683,10 +14925,10 @@
         <v>4.8655</v>
       </c>
       <c r="H20" s="62" t="n">
-        <v>0.14371372450562</v>
+        <v>0.167833735770956</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J20" s="57"/>
     </row>
@@ -14701,7 +14943,7 @@
         <v>148</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E21" s="52" t="n">
         <v>21.2</v>
@@ -14713,10 +14955,10 @@
         <v>-9.16725</v>
       </c>
       <c r="H21" s="55" t="n">
-        <v>-0.761858261827097</v>
+        <v>-0.432417452830189</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J21" s="51"/>
     </row>
@@ -14731,7 +14973,7 @@
         <v>152</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E22" s="52" t="n">
         <v>21.2</v>
@@ -14743,10 +14985,10 @@
         <v>-9.16725</v>
       </c>
       <c r="H22" s="55" t="n">
-        <v>-0.761858261827097</v>
+        <v>-0.432417452830189</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J22" s="51"/>
     </row>
@@ -14761,7 +15003,7 @@
         <v>154</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E23" s="52" t="n">
         <v>34.5363636363636</v>
@@ -14773,10 +15015,10 @@
         <v>-28.5249886363636</v>
       </c>
       <c r="H23" s="55" t="n">
-        <v>-4.74516872368861</v>
+        <v>-0.825940708081074</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J23" s="51"/>
     </row>
@@ -14791,7 +15033,7 @@
         <v>160</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E24" s="59" t="n">
         <v>9.35454545454545</v>
@@ -14803,10 +15045,10 @@
         <v>2.67820454545455</v>
       </c>
       <c r="H24" s="62" t="n">
-        <v>0.222576264399622</v>
+        <v>0.286299805636541</v>
       </c>
       <c r="I24" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J24" s="57"/>
     </row>
@@ -14821,7 +15063,7 @@
         <v>172</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E25" s="59" t="n">
         <v>9.35454545454545</v>
@@ -14833,10 +15075,10 @@
         <v>2.67820454545455</v>
       </c>
       <c r="H25" s="62" t="n">
-        <v>0.222576264399622</v>
+        <v>0.286299805636541</v>
       </c>
       <c r="I25" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J25" s="57"/>
     </row>
@@ -14845,13 +15087,13 @@
         <v>222</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>173</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E26" s="52" t="n">
         <v>21.2</v>
@@ -14863,10 +15105,10 @@
         <v>-9.16725</v>
       </c>
       <c r="H26" s="55" t="n">
-        <v>-0.761858261827097</v>
+        <v>-0.432417452830189</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J26" s="51"/>
     </row>
@@ -14881,7 +15123,7 @@
         <v>168</v>
       </c>
       <c r="D27" s="57" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E27" s="59" t="n">
         <v>32.5</v>
@@ -14893,10 +15135,10 @@
         <v>1.3555</v>
       </c>
       <c r="H27" s="62" t="n">
-        <v>0.0400378077417258</v>
+        <v>0.0417076923076923</v>
       </c>
       <c r="I27" s="63" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J27" s="57"/>
     </row>
@@ -14911,7 +15153,7 @@
         <v>175</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E28" s="52" t="n">
         <v>45</v>
@@ -14923,10 +15165,10 @@
         <v>-11.1445</v>
       </c>
       <c r="H28" s="55" t="n">
-        <v>-0.329178420049918</v>
+        <v>-0.247655555555556</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J28" s="51"/>
     </row>
@@ -14941,7 +15183,7 @@
         <v>50</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E29" s="52" t="n">
         <v>30.8</v>
@@ -14953,10 +15195,10 @@
         <v>-17.73</v>
       </c>
       <c r="H29" s="55" t="n">
-        <v>-1.35654169854629</v>
+        <v>-0.575649350649351</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J29" s="51"/>
     </row>
@@ -14971,7 +15213,7 @@
         <v>52</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E30" s="52" t="n">
         <v>31</v>
@@ -14983,10 +15225,10 @@
         <v>-17.93</v>
       </c>
       <c r="H30" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J30" s="51"/>
     </row>
@@ -15001,7 +15243,7 @@
         <v>54</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E31" s="52" t="n">
         <v>31</v>
@@ -15013,10 +15255,10 @@
         <v>-14.96</v>
       </c>
       <c r="H31" s="55" t="n">
-        <v>-0.932668329177057</v>
+        <v>-0.48258064516129</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J31" s="51"/>
     </row>
@@ -15031,7 +15273,7 @@
         <v>56</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E32" s="52" t="n">
         <v>31</v>
@@ -15043,10 +15285,10 @@
         <v>-14.96</v>
       </c>
       <c r="H32" s="55" t="n">
-        <v>-0.932668329177057</v>
+        <v>-0.48258064516129</v>
       </c>
       <c r="I32" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J32" s="51"/>
     </row>
@@ -15061,7 +15303,7 @@
         <v>58</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E33" s="52" t="n">
         <v>31</v>
@@ -15073,10 +15315,10 @@
         <v>-14.96</v>
       </c>
       <c r="H33" s="55" t="n">
-        <v>-0.932668329177057</v>
+        <v>-0.48258064516129</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J33" s="51"/>
     </row>
@@ -15091,7 +15333,7 @@
         <v>60</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E34" s="52" t="n">
         <v>31</v>
@@ -15103,10 +15345,10 @@
         <v>-14.96</v>
       </c>
       <c r="H34" s="55" t="n">
-        <v>-0.932668329177057</v>
+        <v>-0.48258064516129</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J34" s="51"/>
     </row>
@@ -15121,7 +15363,7 @@
         <v>62</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E35" s="52" t="n">
         <v>31</v>
@@ -15133,10 +15375,10 @@
         <v>-17.93</v>
       </c>
       <c r="H35" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J35" s="51"/>
     </row>
@@ -15151,7 +15393,7 @@
         <v>64</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E36" s="52" t="n">
         <v>31</v>
@@ -15163,10 +15405,10 @@
         <v>-14.96</v>
       </c>
       <c r="H36" s="55" t="n">
-        <v>-0.932668329177057</v>
+        <v>-0.48258064516129</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J36" s="51"/>
     </row>
@@ -15181,7 +15423,7 @@
         <v>66</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E37" s="52" t="n">
         <v>31</v>
@@ -15193,10 +15435,10 @@
         <v>-17.93</v>
       </c>
       <c r="H37" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J37" s="51"/>
     </row>
@@ -15211,7 +15453,7 @@
         <v>68</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E38" s="52" t="n">
         <v>31</v>
@@ -15223,10 +15465,10 @@
         <v>-17.93</v>
       </c>
       <c r="H38" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I38" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J38" s="51"/>
     </row>
@@ -15241,7 +15483,7 @@
         <v>70</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E39" s="52" t="n">
         <v>31</v>
@@ -15253,10 +15495,10 @@
         <v>-17.93</v>
       </c>
       <c r="H39" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J39" s="51"/>
     </row>
@@ -15271,7 +15513,7 @@
         <v>72</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E40" s="52" t="n">
         <v>31</v>
@@ -15283,10 +15525,10 @@
         <v>-17.93</v>
       </c>
       <c r="H40" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I40" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J40" s="51"/>
     </row>
@@ -15301,7 +15543,7 @@
         <v>74</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E41" s="52" t="n">
         <v>31</v>
@@ -15313,10 +15555,10 @@
         <v>-17.93</v>
       </c>
       <c r="H41" s="55" t="n">
-        <v>-1.37184391736802</v>
+        <v>-0.578387096774194</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J41" s="51"/>
     </row>
@@ -15331,22 +15573,22 @@
         <v>5</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="E42" s="52" t="n">
-        <v>34.5363636363636</v>
+        <v>32.6363636363636</v>
       </c>
       <c r="F42" s="56" t="n">
         <v>5.35</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>-29.1863636363636</v>
+        <v>-27.2863636363636</v>
       </c>
       <c r="H42" s="55" t="n">
-        <v>-5.4553950722175</v>
+        <v>-0.836072423398328</v>
       </c>
       <c r="I42" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J42" s="51"/>
     </row>
@@ -15361,7 +15603,7 @@
         <v>96</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E43" s="52" t="n">
         <v>9.35454545454545</v>
@@ -15373,10 +15615,10 @@
         <v>-6.68454545454545</v>
       </c>
       <c r="H43" s="55" t="n">
-        <v>-2.50357507660878</v>
+        <v>-0.714577259475219</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J43" s="51"/>
     </row>
@@ -15391,7 +15633,7 @@
         <v>98</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E44" s="52" t="n">
         <v>23.4090909090909</v>
@@ -15403,10 +15645,10 @@
         <v>-12.7190909090909</v>
       </c>
       <c r="H44" s="55" t="n">
-        <v>-1.18981205884854</v>
+        <v>-0.543339805825243</v>
       </c>
       <c r="I44" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J44" s="51"/>
     </row>
@@ -15421,7 +15663,7 @@
         <v>100</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E45" s="52" t="n">
         <v>22.7181818181818</v>
@@ -15433,10 +15675,10 @@
         <v>-20.0481818181818</v>
       </c>
       <c r="H45" s="55" t="n">
-        <v>-7.50868232890704</v>
+        <v>-0.882472989195678</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J45" s="51"/>
     </row>
@@ -15451,22 +15693,22 @@
         <v>104</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="E46" s="52" t="n">
-        <v>40.9</v>
+        <v>25.5818181818182</v>
       </c>
       <c r="F46" s="56" t="n">
         <v>9.5</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>-31.4</v>
+        <v>-16.0818181818182</v>
       </c>
       <c r="H46" s="55" t="n">
-        <v>-3.30526315789474</v>
+        <v>-0.62864250177683</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J46" s="51"/>
     </row>
@@ -15481,7 +15723,7 @@
         <v>106</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E47" s="52" t="n">
         <v>40.9</v>
@@ -15493,10 +15735,10 @@
         <v>-30.21</v>
       </c>
       <c r="H47" s="55" t="n">
-        <v>-2.82600561272217</v>
+        <v>-0.738630806845966</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J47" s="51"/>
     </row>
@@ -15511,7 +15753,7 @@
         <v>110</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E48" s="52" t="n">
         <v>20.9090909090909</v>
@@ -15523,10 +15765,10 @@
         <v>-15.5590909090909</v>
       </c>
       <c r="H48" s="55" t="n">
-        <v>-2.90824129141886</v>
+        <v>-0.744130434782609</v>
       </c>
       <c r="I48" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J48" s="51"/>
     </row>
@@ -15541,7 +15783,7 @@
         <v>112</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E49" s="52" t="n">
         <v>9.35454545454545</v>
@@ -15553,10 +15795,10 @@
         <v>-4.00454545454545</v>
       </c>
       <c r="H49" s="55" t="n">
-        <v>-0.748513169073916</v>
+        <v>-0.428085519922254</v>
       </c>
       <c r="I49" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J49" s="51"/>
     </row>
@@ -15571,7 +15813,7 @@
         <v>116</v>
       </c>
       <c r="D50" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E50" s="52" t="n">
         <v>25.4454545454545</v>
@@ -15583,10 +15825,10 @@
         <v>-22.7754545454545</v>
       </c>
       <c r="H50" s="55" t="n">
-        <v>-8.53013278855974</v>
+        <v>-0.895069667738478</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J50" s="51"/>
     </row>
@@ -15601,7 +15843,7 @@
         <v>120</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E51" s="52" t="n">
         <v>40.9</v>
@@ -15613,10 +15855,10 @@
         <v>-31.4</v>
       </c>
       <c r="H51" s="55" t="n">
-        <v>-3.30526315789474</v>
+        <v>-0.767726161369193</v>
       </c>
       <c r="I51" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J51" s="51"/>
     </row>
@@ -15631,7 +15873,7 @@
         <v>122</v>
       </c>
       <c r="D52" s="51" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E52" s="52" t="n">
         <v>7.81818181818182</v>
@@ -15643,10 +15885,10 @@
         <v>-5.81818181818182</v>
       </c>
       <c r="H52" s="55" t="n">
-        <v>-2.90909090909091</v>
+        <v>-0.744186046511628</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J52" s="51"/>
     </row>
@@ -15661,7 +15903,7 @@
         <v>124</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E53" s="52" t="n">
         <v>29.9909090909091</v>
@@ -15673,10 +15915,10 @@
         <v>-27.3209090909091</v>
       </c>
       <c r="H53" s="55" t="n">
-        <v>-10.2325502213143</v>
+        <v>-0.910973022127918</v>
       </c>
       <c r="I53" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J53" s="51"/>
     </row>
@@ -15691,7 +15933,7 @@
         <v>126</v>
       </c>
       <c r="D54" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E54" s="52" t="n">
         <v>34.5363636363636</v>
@@ -15703,10 +15945,10 @@
         <v>-30.5263636363636</v>
       </c>
       <c r="H54" s="55" t="n">
-        <v>-7.61255951031511</v>
+        <v>-0.883890497499342</v>
       </c>
       <c r="I54" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J54" s="51"/>
     </row>
@@ -15721,7 +15963,7 @@
         <v>130</v>
       </c>
       <c r="D55" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E55" s="52" t="n">
         <v>34.5363636363636</v>
@@ -15733,10 +15975,10 @@
         <v>-23.8463636363636</v>
       </c>
       <c r="H55" s="55" t="n">
-        <v>-2.23071689769538</v>
+        <v>-0.690471176625428</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J55" s="51"/>
     </row>
@@ -15751,7 +15993,7 @@
         <v>134</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E56" s="52" t="n">
         <v>34.5363636363636</v>
@@ -15763,10 +16005,10 @@
         <v>-23.8463636363636</v>
       </c>
       <c r="H56" s="55" t="n">
-        <v>-2.23071689769538</v>
+        <v>-0.690471176625428</v>
       </c>
       <c r="I56" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J56" s="51"/>
     </row>
@@ -15781,22 +16023,22 @@
         <v>136</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="E57" s="52" t="n">
-        <v>40.9</v>
+        <v>38.8636363636364</v>
       </c>
       <c r="F57" s="56" t="n">
         <v>10.69</v>
       </c>
       <c r="G57" s="54" t="n">
-        <v>-30.21</v>
+        <v>-28.1736363636364</v>
       </c>
       <c r="H57" s="55" t="n">
-        <v>-2.82600561272217</v>
+        <v>-0.72493567251462</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J57" s="51"/>
     </row>
@@ -15811,7 +16053,7 @@
         <v>140</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E58" s="52" t="n">
         <v>29.9909090909091</v>
@@ -15823,10 +16065,10 @@
         <v>-27.1009090909091</v>
       </c>
       <c r="H58" s="55" t="n">
-        <v>-9.37747719408619</v>
+        <v>-0.903637465898757</v>
       </c>
       <c r="I58" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J58" s="51"/>
     </row>
@@ -15841,7 +16083,7 @@
         <v>144</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E59" s="52" t="n">
         <v>45.4454545454545</v>
@@ -15853,10 +16095,10 @@
         <v>-43.5054545454545</v>
       </c>
       <c r="H59" s="55" t="n">
-        <v>-22.4254920337394</v>
+        <v>-0.957311462292458</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J59" s="51"/>
     </row>
@@ -15871,7 +16113,7 @@
         <v>150</v>
       </c>
       <c r="D60" s="51" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E60" s="52" t="n">
         <v>43.55</v>
@@ -15883,10 +16125,10 @@
         <v>-32.86</v>
       </c>
       <c r="H60" s="55" t="n">
-        <v>-3.07390084190833</v>
+        <v>-0.754535017221584</v>
       </c>
       <c r="I60" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J60" s="51"/>
     </row>
@@ -15901,7 +16143,7 @@
         <v>156</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E61" s="52" t="n">
         <v>29.9909090909091</v>
@@ -15913,10 +16155,10 @@
         <v>-26.7899090909091</v>
       </c>
       <c r="H61" s="55" t="n">
-        <v>-8.36923120615717</v>
+        <v>-0.893267656865717</v>
       </c>
       <c r="I61" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J61" s="51"/>
     </row>
@@ -15931,7 +16173,7 @@
         <v>158</v>
       </c>
       <c r="D62" s="51" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E62" s="52" t="n">
         <v>29.9909090909091</v>
@@ -15943,10 +16185,10 @@
         <v>-24.6409090909091</v>
       </c>
       <c r="H62" s="55" t="n">
-        <v>-4.60577740016993</v>
+        <v>-0.821612609881782</v>
       </c>
       <c r="I62" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J62" s="51"/>
     </row>
@@ -15961,22 +16203,22 @@
         <v>162</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="E63" s="52" t="n">
-        <v>29.9909090909091</v>
+        <v>27.9727272727273</v>
       </c>
       <c r="F63" s="56" t="n">
         <v>2.67</v>
       </c>
       <c r="G63" s="54" t="n">
-        <v>-27.3209090909091</v>
+        <v>-25.3027272727273</v>
       </c>
       <c r="H63" s="55" t="n">
-        <v>-10.2325502213143</v>
+        <v>-0.904549886252844</v>
       </c>
       <c r="I63" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J63" s="51"/>
     </row>
@@ -15991,7 +16233,7 @@
         <v>164</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E64" s="52" t="n">
         <v>27.2727272727273</v>
@@ -16003,16 +16245,16 @@
         <v>-16.5827272727273</v>
       </c>
       <c r="H64" s="55" t="n">
-        <v>-1.55123735011481</v>
+        <v>-0.608033333333334</v>
       </c>
       <c r="I64" s="51" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J64" s="51"/>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="64" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B66" s="64"/>
       <c r="C66" s="64"/>
@@ -16032,19 +16274,19 @@
         <v>1</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G67" s="50" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16055,7 +16297,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D68" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16078,7 +16320,7 @@
         <v>142</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D69" s="59" t="n">
         <v>21.2</v>
@@ -16101,7 +16343,7 @@
         <v>160</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D70" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16124,7 +16366,7 @@
         <v>172</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D71" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16147,7 +16389,7 @@
         <v>80</v>
       </c>
       <c r="C72" s="57" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D72" s="59" t="n">
         <v>28.3545454545455</v>
@@ -16170,7 +16412,7 @@
         <v>132</v>
       </c>
       <c r="C73" s="57" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D73" s="59" t="n">
         <v>28.3545454545455</v>
@@ -16193,7 +16435,7 @@
         <v>168</v>
       </c>
       <c r="C74" s="57" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D74" s="59" t="n">
         <v>32.5</v>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -869,7 +869,7 @@
     <t xml:space="preserve">Generic site/warehouse danger sign - no comparable product found at any of the 9 researched retailers (out of scope: these retailers focus on road/traffic signage).</t>
   </si>
   <si>
-    <t xml:space="preserve">No metal-sign equivalent found at the 9 researched retailers for this specific size/material. See RSEA 685265 (Poly, Confined Space Entry By Permit) below for comparable market data.</t>
+    <t xml:space="preserve">Advanced Group: 'Confined Space Entry By Permit Only - Danger Signs - Metal (colorbond steel) - 450 x 300' (832249), $38.45 Inc GST; exact size and material match.</t>
   </si>
   <si>
     <t xml:space="preserve">Generic site/warehouse safety sign - no comparable product found at any of the 9 researched retailers.</t>
@@ -1070,6 +1070,9 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
+    <t xml:space="preserve">Advanced Group</t>
+  </si>
+  <si>
     <t xml:space="preserve">SafetyXpress</t>
   </si>
   <si>
@@ -1080,9 +1083,6 @@
   </si>
   <si>
     <t xml:space="preserve">Safety Signs Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Group</t>
   </si>
   <si>
     <t xml:space="preserve">Items We're MORE EXPENSIVE On (our higher-of-1200/1220 quote vs the single cheapest alternative — 7 of 60 items)</t>
@@ -1775,9 +1775,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>403920</xdr:colOff>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>260280</xdr:rowOff>
+      <xdr:rowOff>258840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1791,7 +1791,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2191680" cy="2337840"/>
+          <a:ext cx="2190240" cy="2336400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8800,19 +8800,24 @@
       <c r="AA16" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB16" s="45"/>
-      <c r="AC16" s="45"/>
+      <c r="AB16" s="45" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC16" s="45" t="n">
+        <f aca="false">AB16/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD16" s="11" t="n">
         <f aca="false">IF(COUNT(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16)=0,"N/A",MIN(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16))</f>
-        <v>40.9</v>
+        <v>34.9545454545455</v>
       </c>
       <c r="AE16" s="43" t="n">
         <f aca="false">IF(OR(D16="",AD16="",AD16="N/A"),"N/A",D16/AD16-1)</f>
-        <v>-0.618826405867971</v>
+        <v>-0.553992197659298</v>
       </c>
       <c r="AF16" s="43" t="n">
         <f aca="false">IF(OR(F16="",AD16="",AD16="N/A"),"N/A",F16/AD16-1)</f>
-        <v>-0.613380195599022</v>
+        <v>-0.547619635890767</v>
       </c>
       <c r="AG16" s="41" t="s">
         <v>269</v>
@@ -14255,7 +14260,7 @@
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="n">
         <f aca="false">COUNTIF(J6:J65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(V6:V65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")+COUNTIF(AC6:AC65,"&gt;0")</f>
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14288,7 +14293,7 @@
       <c r="C72" s="35"/>
       <c r="D72" s="47" t="n">
         <f aca="false">AVERAGE(AE6:AE65)</f>
-        <v>-0.502826801988701</v>
+        <v>-0.50174623185189</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14332,7 +14337,7 @@
       <c r="C76" s="35"/>
       <c r="D76" s="47" t="n">
         <f aca="false">AVERAGE(AF6:AF65)</f>
-        <v>-0.186068097813109</v>
+        <v>-0.183078981462734</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14763,19 +14768,19 @@
         <v>108</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E15" s="52" t="n">
-        <v>40.9</v>
+        <v>34.9545454545455</v>
       </c>
       <c r="F15" s="53" t="n">
         <v>15.81275</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>-25.08725</v>
+        <v>-19.1417954545455</v>
       </c>
       <c r="H15" s="55" t="n">
-        <v>-0.613380195599022</v>
+        <v>-0.547619635890768</v>
       </c>
       <c r="I15" s="51" t="s">
         <v>327</v>
@@ -14823,7 +14828,7 @@
         <v>128</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E17" s="52" t="n">
         <v>37.3909090909091</v>
@@ -14853,7 +14858,7 @@
         <v>132</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E18" s="59" t="n">
         <v>28.3545454545455</v>
@@ -14883,7 +14888,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E19" s="52" t="n">
         <v>23.3090909090909</v>
@@ -14913,7 +14918,7 @@
         <v>142</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E20" s="59" t="n">
         <v>28.99</v>
@@ -14943,7 +14948,7 @@
         <v>148</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E21" s="52" t="n">
         <v>21.2</v>
@@ -14973,7 +14978,7 @@
         <v>152</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E22" s="52" t="n">
         <v>21.2</v>
@@ -15033,7 +15038,7 @@
         <v>160</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E24" s="59" t="n">
         <v>9.35454545454545</v>
@@ -15063,7 +15068,7 @@
         <v>172</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E25" s="59" t="n">
         <v>9.35454545454545</v>
@@ -15093,7 +15098,7 @@
         <v>173</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E26" s="52" t="n">
         <v>21.2</v>
@@ -15213,7 +15218,7 @@
         <v>52</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E30" s="52" t="n">
         <v>31</v>
@@ -15243,7 +15248,7 @@
         <v>54</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E31" s="52" t="n">
         <v>31</v>
@@ -15273,7 +15278,7 @@
         <v>56</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E32" s="52" t="n">
         <v>31</v>
@@ -15303,7 +15308,7 @@
         <v>58</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E33" s="52" t="n">
         <v>31</v>
@@ -15333,7 +15338,7 @@
         <v>60</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E34" s="52" t="n">
         <v>31</v>
@@ -15363,7 +15368,7 @@
         <v>62</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E35" s="52" t="n">
         <v>31</v>
@@ -15393,7 +15398,7 @@
         <v>64</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E36" s="52" t="n">
         <v>31</v>
@@ -15423,7 +15428,7 @@
         <v>66</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E37" s="52" t="n">
         <v>31</v>
@@ -15453,7 +15458,7 @@
         <v>68</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E38" s="52" t="n">
         <v>31</v>
@@ -15483,7 +15488,7 @@
         <v>70</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E39" s="52" t="n">
         <v>31</v>
@@ -15513,7 +15518,7 @@
         <v>72</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E40" s="52" t="n">
         <v>31</v>
@@ -15543,7 +15548,7 @@
         <v>74</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E41" s="52" t="n">
         <v>31</v>
@@ -15573,7 +15578,7 @@
         <v>5</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E42" s="52" t="n">
         <v>32.6363636363636</v>
@@ -15603,7 +15608,7 @@
         <v>96</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E43" s="52" t="n">
         <v>9.35454545454545</v>
@@ -15633,7 +15638,7 @@
         <v>98</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E44" s="52" t="n">
         <v>23.4090909090909</v>
@@ -15693,7 +15698,7 @@
         <v>104</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E46" s="52" t="n">
         <v>25.5818181818182</v>
@@ -15753,7 +15758,7 @@
         <v>110</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E48" s="52" t="n">
         <v>20.9090909090909</v>
@@ -15783,7 +15788,7 @@
         <v>112</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E49" s="52" t="n">
         <v>9.35454545454545</v>
@@ -16023,7 +16028,7 @@
         <v>136</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E57" s="52" t="n">
         <v>38.8636363636364</v>
@@ -16203,7 +16208,7 @@
         <v>162</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E63" s="52" t="n">
         <v>27.9727272727273</v>
@@ -16233,7 +16238,7 @@
         <v>164</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E64" s="52" t="n">
         <v>27.2727272727273</v>
@@ -16297,7 +16302,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D68" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16320,7 +16325,7 @@
         <v>142</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D69" s="59" t="n">
         <v>21.2</v>
@@ -16343,7 +16348,7 @@
         <v>160</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D70" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16366,7 +16371,7 @@
         <v>172</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D71" s="59" t="n">
         <v>9.35454545454545</v>
@@ -16389,7 +16394,7 @@
         <v>80</v>
       </c>
       <c r="C72" s="57" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D72" s="59" t="n">
         <v>28.3545454545455</v>
@@ -16412,7 +16417,7 @@
         <v>132</v>
       </c>
       <c r="C73" s="57" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D73" s="59" t="n">
         <v>28.3545454545455</v>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="356">
   <si>
     <t xml:space="preserve">RSEA Code</t>
   </si>
@@ -736,7 +736,7 @@
     <t xml:space="preserve">Market-Wide Price Comparison — Our Pricing, RSEA &amp; 10 Retailers (All GST Bases Confirmed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Methodology: all 9 retailers' GST treatment is now confirmed (4 stated it directly on-site; the remaining 5 — Safety Signs Australia, SafetyXpress, Traffic Control Products, National Safety Signs, Seton — were confirmed by direct check). Safety Signs Australia, SafetyXpress, National Safety Signs and Seton display prices INC GST; Traffic Control Products displays EX GST; HiVis displays EX GST; Jaybro and eSafety Supplies display both inc and ex GST directly; All Trades Group marks its prices "Tax included" (INC GST). Every price below is shown both ex and inc GST, with whichever figure is NOT the retailer's own displayed figure calculated (×1.1 or ÷1.1). Our Quoted Price (both 1200- and 1220-stock) and the RSEA Website Price are pulled by formula from the 'RSEA vs Quoted Comparison' tab; competitor figures were captured live from each retailer's own website on 14 October 2026 and are hardcoded (not formulas) since they come from outside this workbook. Advanced Group (advancedgroup.com.au) was added on 15 October 2026 as a 10th competitor: its per-item prices are individually labelled 'Inc GST' (a generic 'all prices are GST exclusive' banner also appears on some of its category pages but conflicts with every per-item label, so it is treated as boilerplate and the per-item Inc-GST label is used, same convention as the other as-shown-inc retailers above). Its catalogue runs to 200+ paginated categories, so research there was a representative sample, not exhaustive — rows with no Advanced Group price are genuinely unresearched (left blank), not confirmed-absent.</t>
+    <t xml:space="preserve">Methodology: all 9 retailers' GST treatment is now confirmed (4 stated it directly on-site; the remaining 5 — Safety Signs Australia, SafetyXpress, Traffic Control Products, National Safety Signs, Seton — were confirmed by direct check). Safety Signs Australia, SafetyXpress, National Safety Signs and Seton display prices INC GST; Traffic Control Products displays EX GST; HiVis displays EX GST; Jaybro and eSafety Supplies display both inc and ex GST directly; All Trades Group marks its prices "Tax included" (INC GST). Every price below is shown both ex and inc GST, with whichever figure is NOT the retailer's own displayed figure calculated (×1.1 or ÷1.1). Our Quoted Price (both 1200- and 1220-stock) and the RSEA Website Price are pulled by formula from the 'RSEA vs Quoted Comparison' tab; competitor figures were captured live from each retailer's own website on 14 October 2026 and are hardcoded (not formulas) since they come from outside this workbook. Advanced Group (advancedgroup.com.au) was added on 15 October 2026 as a 10th competitor: its per-item prices are individually labelled 'Inc GST' (a generic 'all prices are GST exclusive' banner also appears on some of its category pages but conflicts with every per-item label, so it is treated as boilerplate and the per-item Inc-GST label is used, same convention as the other as-shown-inc retailers above). Its catalogue runs to 200+ paginated categories, so research there was a representative sample, not exhaustive — rows with no Advanced Group price are genuinely unresearched (left blank), not confirmed-absent. A deeper re-check pass (16 October 2026) went beyond the retailers' obvious category pages and crawled each site's full product sitemap (or, where blocked, its native search) to re-test every cell that had been marked blank/N/A — this filled in 140 previously-missing price points across 8 of the 9 researched competitors (Seton excluded, bot-blocked). Where no exact size/material match exists, the closest equivalent is used and flagged in the Notes column, same convention as before. Cells still blank after this deeper pass are either genuinely confirmed absent by the retailer (e.g. a whole product line it doesn't stock, confirmed via full-catalogue search) or remain simply unresearched — Notes/the original research log should be checked before assuming either way.</t>
   </si>
   <si>
     <t xml:space="preserve">Where a retailer did not carry the exact size/material of our line item, the closest equivalent sign TYPE was used instead and the mismatch is flagged in the Notes column — treat those rows as directionally indicative, not an exact apples-to-apples match. "N/A" means that retailer does not appear to carry a comparable product (confirmed via the research, not a blank/forgotten cell). Seton additionally blocked direct automated access (403/bot protection) during research, so its prices were recovered from search-engine cache only and are flagged LOW CONFIDENCE in the Notes column — that is a data-reliability flag, separate from its (confirmed) GST treatment. Sources: hivis.com/collections/signage · jaybro.com.au/road-traffic/permanent-signs/regulatory-signs/ · alltradesgroup.net.au/collections/site-safety-signage-roads-traffic-signs · esafetysupplies.com.au/collections/traffic-road-safety-sign · safetysigns.com.au/collections/road-car-park-signs · safetyxpress.com.au/traffic-signs/ · trafficcontrolproducts.com.au/collections/road-signs-traffic · nationalsafetysigns.com.au/product-category/road-and-traffic-signs/road-signs/ · seton.net.au · advancedgroup.com.au (Advanced Group, captured 15 October 2026, representative sample only — see methodology above). Captured 14 October 2026 unless noted.</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">All Trades Group: 300x225 poly or 600x450; no exact 450x300 | eSafety Supplies: 600x450 also stocked | Safety Signs Australia: 450x600, size differs | SafetyXpress: 3 sizes incl 300x450 | National Safety Signs: From, S2870 | Seton: LOW conf; 'Video Surveillance In Use', 300-450mm range</t>
+    <t xml:space="preserve">All Trades Group: 300x225 poly or 600x450; no exact 450x300 | eSafety Supplies: 600x450 also stocked | Safety Signs Australia: 450x600, size differs | SafetyXpress: 3 sizes incl 300x450 | National Safety Signs: From, S2870 | Seton: LOW conf; 'Video Surveillance In Use', 300-450mm range | Advanced Group: Security Notice: This Building Under 24hr Surveillance, Metal 300x450(=450x300) (closest-equiv (wording)) https://www.advancedgroup.com.au/SURV-SIGN-THIS-BUILDING-IS-UNDER-24-MTL-p/843695.htm</t>
   </si>
   <si>
     <t xml:space="preserve">Swing-stand temporary traffic-control sign - no comparable product found at any of the 9 researched retailers.</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">HiVis: 750/900/1200mm | Jaybro: 750x750 exact | All Trades Group: 750mm triangular | eSafety Supplies: 750mm triangle | Safety Signs Australia: 750mm | SafetyXpress: 750mm | Traffic Control Products: 750mm | National Safety Signs: From, 750 or 900mm | Seton: LOW conf - 6-pack bulk tier price, single-unit unconfirmed | Advanced Group: generic 'Give Way Sign' (R1-2 family, triangle); 750mm size/variant not independently confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: 300x400/450x600/600x800 | Jaybro: 450x600 exact | All Trades Group: 600x450mm | eSafety Supplies: 450x600 exact, sale price (was 86.65) | Safety Signs Australia: 450x600 | SafetyXpress: 450x600 | Traffic Control Products: 450x600 | National Safety Signs: From, 400x300/600x450/800x600 | Seton: MEDIUM conf, 450x600</t>
+    <t xml:space="preserve">HiVis: 300x400/450x600/600x800 | Jaybro: 450x600 exact | All Trades Group: 600x450mm | eSafety Supplies: 450x600 exact, sale price (was 86.65) | Safety Signs Australia: 450x600 | SafetyXpress: 450x600 | Traffic Control Products: 450x600 | National Safety Signs: From, 400x300/600x450/800x600 | Seton: MEDIUM conf, 450x600 | Advanced Group: Keep Left Sign A Size Aluminium 450x600mm (R2-3AL) (EXACT) https://www.advancedgroup.com.au/product-p/r2-3al.htm</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: 600/750/900mm | Jaybro: 600mm exact | All Trades Group: 600x600 or 750x750 (W6-1, size differs from 600mm round) | eSafety Supplies: 600mm exact | Safety Signs Australia: 600mm dia | SafetyXpress: 600mm dia | Traffic Control Products: 600mm dia | National Safety Signs: From, 600 or 750mm round | Seton: MEDIUM conf, 600mm dia | Advanced Group: 'Pedestrian Crossing Sign - Fluoro Reflective' (R3-1); colour/size variant not independently confirmed (listed as 'multiple sizes to choose from')</t>
@@ -866,40 +866,46 @@
     <t xml:space="preserve">HiVis: 450x750, size differs from 450x450 | Jaybro: 450x450 exact | All Trades Group: 600x450, size differs | eSafety Supplies: 450x450 exact | Safety Signs Australia: 450x450 exact | SafetyXpress: range 72.28-80.84, 450x450 exact | Traffic Control Products: 450x750, size differs | National Safety Signs: From, 450x450 avail | Seton: MEDIUM conf, 750x750 (not 450x450) | Advanced Group: 'R2-4 No Entry Sign Reflective on Aluminium'; code matches (R2-4), exact size variant not stated on listing page</t>
   </si>
   <si>
-    <t xml:space="preserve">Generic site/warehouse danger sign - no comparable product found at any of the 9 researched retailers (out of scope: these retailers focus on road/traffic signage).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Group: 'Confined Space Entry By Permit Only - Danger Signs - Metal (colorbond steel) - 450 x 300' (832249), $38.45 Inc GST; exact size and material match.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic site/warehouse safety sign - no comparable product found at any of the 9 researched retailers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eSafety Supplies: 5km/h, 450x600 (combined with item 16), not 600x400 | Safety Signs Australia: 5km/h, 450x600, not 600x400 | SafetyXpress: 5km/h plain metal, 450x600 | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Seton: Not confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 10km/h SKU reused, size differs (600x800 etc not 600x400) | All Trades Group: 10km/h SKU reused, size differs | eSafety Supplies: 10km/h, 450x600 (combined with item 5), not 600x400 | Safety Signs Australia: 10km/h SKU reused, size differs | SafetyXpress: 10km/h, size differs | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 225x450, size differs from 450x300 | Jaybro: 225x450, size differs | All Trades Group: 300x225, size differs | eSafety Supplies: 225x450, closest size | Safety Signs Australia: 300x450, size differs | SafetyXpress: 300x450, size differs | Traffic Control Products: Not found | National Safety Signs: From | Seton: From, inc GST, 300x450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 225x450, much smaller than 600x450 target | Jaybro: 225x450, size differs | All Trades Group: 225x450, size differs | eSafety Supplies: 300x450 shown / 600x450 also stocked | Safety Signs Australia: Not found - only 300x450 exists | SafetyXpress: 600x450 variant, exact size | Traffic Control Products: Only directional-arrow variants stocked | National Safety Signs: From, generic RD124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: 225x450, size differs from 300x450 | All Trades Group: 'No Stopping' dual arrow closest wording, 225x450 | eSafety Supplies: 300x450 exact | Safety Signs Australia: 300x450 exact | SafetyXpress: 300x450 exact (upper of range) | Traffic Control Products: Not found | National Safety Signs: From, 'Bi-Directional' closest to double arrow | Seton: LOW conf - promo pricing, 300x450 exact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 225x450, close to 450x300 | Jaybro: 225x450, close | All Trades Group: 225x450, same SKU as 686503 | eSafety Supplies: 300x450, close | Safety Signs Australia: 300x450, close | SafetyXpress: 300x450, close | Traffic Control Products: Not found | National Safety Signs: From, shared with 686503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: Found differently-worded 'No Entry Authorised Prohibition' 600x450 $39.58inc/$35.98ex - size differs, see notes | All Trades Group: 450x300 exact size option available | eSafety Supplies: 300x450, 600x450 also stocked | Safety Signs Australia: 450x600, size differs | SafetyXpress: range 33.19-35.73, no exact 450x300 | Traffic Control Products: 450x300 exact, poly | National Safety Signs: From, R2543 'Restricted Area Do Not Enter'</t>
+    <t xml:space="preserve">Generic site/warehouse danger sign - no comparable product found at any of the 9 researched retailers (out of scope: these retailers focus on road/traffic signage). | Advanced Group: Danger Forklift Operating Area 300x225 Metal (EXACT) https://www.advancedgroup.com.au/DANGER-FORKLIFT-OPERATING-300X225-MTL-p/841659.htm | All Trades Group: Danger Forklift Operating Area Site Sign, 300x225 Metal (EXACT) https://alltradesgroup.net.au/products/danger-forklift-operating-area-site-sign | eSafety Supplies: Danger Forklift Operating Area, 300x450 Poly (closest-equiv, material Poly/ACP not Metal) https://esafetysupplies.com.au/products/danger-sign-forklift-operating-area | Safety Signs Australia: Danger Sign Forklift Operating Area, 225x300 Metal (EXACT) https://www.safetysigns.com.au/products/danger-forklift | National Safety Signs: Forklift Area D1076, 300x225 Aluminium (EXACT) https://nationalsafetysigns.com.au/safety-signs/forklift-area-d1076/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Group: 'Confined Space Entry By Permit Only - Danger Signs - Metal (colorbond steel) - 450 x 300' (832249), $38.45 Inc GST; exact size and material match. | Jaybro: Confined Space Entry By Permit Only Danger Sign Metal (closest-equiv, size 225x300 (need 450x300)) https://www.jaybro.com.au/safety-signs/confined-space-entry-by-permit-only-danger-sign-metal-225x300mm/ | All Trades Group: Danger Confined Space Sign, 450x300 Metal (closest-equiv, wording (no "Entry By Permit")) https://alltradesgroup.net.au/products/danger-confined-space-sign | eSafety Supplies: Danger Confined Space Entry By Permit Only, 300x450(=450x300) Poly (closest-equiv, material Poly/ACP not Metal) https://esafetysupplies.com.au/products/danger-sign-confined-space-entry-by-permit-only-600-x-450mm | Safety Signs Australia: Danger Sign Confined Space Hazardous Atmosphere Entry By Permit, 300x450 Metal (closest-equiv, wording adds "Hazardous Atmosphere") https://www.safetysigns.com.au/products/danger-confined-space-permit | Traffic Control Products: Danger Confined Space Entry By Permit Only, Metal (closest-equiv, size 225x300 (need 450x300)) https://trafficcontrolproducts.com.au/products/danger-confined-space-300x225-metal | National Safety Signs: Confined Space Permit Only Sign D1037, 450x300 Aluminium (EXACT) https://nationalsafetysigns.com.au/safety-signs/danger-confined-space-d1037/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic site/warehouse safety sign - no comparable product found at any of the 9 researched retailers. | Advanced Group: Emergency Eye Wash 300x225 Metal (size/material match) https://www.advancedgroup.com.au/EMERGENCY-EYE-WASH-300X225-MTL-p/841538.htm | Jaybro: Emergency Eye Wash Emergency Sign Metal 300x225mm (EXACT) https://www.jaybro.com.au/safety-signs/emergency-eye-wash-emergency-sign-metal-300x225mm/ | All Trades Group: Emergency Eyewash Sign, 300x225 Metal (closest-equiv, wording (no "First Aid" prefix)) https://alltradesgroup.net.au/products/emergency-eyewash-sign | eSafety Supplies: Emergency Eye Wash Sign, Poly (closest-equiv, material Poly not Metal, size 300x450) https://esafetysupplies.com.au/products/emergency-eye-wash-sign-300-x-450-mm | Safety Signs Australia: Emergency Sign Emergency Eye Wash, 225x300 Metal (EXACT) https://www.safetysigns.com.au/products/emergency-eye-wash | National Safety Signs: Emergency Eyewash E1212, 300x225 Metal (EXACT) https://nationalsafetysigns.com.au/safety-signs/emergency-eyewash-e1212/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eSafety Supplies: 5km/h, 450x600 (combined with item 16), not 600x400 | Safety Signs Australia: 5km/h, 450x600, not 600x400 | SafetyXpress: 5km/h plain metal, 450x600 | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Seton: Not confirmed | Advanced Group: Speed Limit Sign Speed 5, Metal (closest-equiv, size differs (450x600 not 600x400)) https://www.advancedgroup.com.au/SPEED-LIMIT-SIGN-SPEED-5-450X600-MTL-p/832056.htm | All Trades Group: 5km/h Speed Limit Road Sign, Metal (closest-equiv, size 600x450 (need 600x400)) https://alltradesgroup.net.au/products/5-km-h-speed-limit-road-sign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 10km/h SKU reused, size differs (600x800 etc not 600x400) | All Trades Group: 10km/h SKU reused, size differs | eSafety Supplies: 10km/h, 450x600 (combined with item 5), not 600x400 | Safety Signs Australia: 10km/h SKU reused, size differs | SafetyXpress: 10km/h, size differs | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Advanced Group: Speed Limit Sign Speed 10, Metal (closest-equiv, size differs (450x600 not 600x400)) https://www.advancedgroup.com.au/SPEED-LIMIT-SIGN-SPEED-10-450X600-MTL-p/832057.htm | Jaybro: 10km/h Class 1 Aluminium (closest-equiv, size 450x600 (need 600x400)) https://www.jaybro.com.au/regulatory-signs/10km-h-class-1-aluminium-450x600mm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 225x450, size differs from 450x300 | Jaybro: 225x450, size differs | All Trades Group: 300x225, size differs | eSafety Supplies: 225x450, closest size | Safety Signs Australia: 300x450, size differs | SafetyXpress: 300x450, size differs | Traffic Control Products: Not found | National Safety Signs: From | Seton: From, inc GST, 300x450 | Advanced Group: Access Sign Disabled Parking 300x450 Metal (EXACT (size-order)) https://www.advancedgroup.com.au/ACCESS-SIGN-DISABLED-PARKING-300X450-MTL-p/842283.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 225x450, much smaller than 600x450 target | Jaybro: 225x450, size differs | All Trades Group: 225x450, size differs | eSafety Supplies: 300x450 shown / 600x450 also stocked | Safety Signs Australia: Not found - only 300x450 exists | SafetyXpress: 600x450 variant, exact size | Traffic Control Products: Only directional-arrow variants stocked | National Safety Signs: From, generic RD124 | Advanced Group: Restricted Area No Parking 600x450 Metal (closest-equiv, wording differs) https://www.advancedgroup.com.au/RESTRICTED-AREA-NO-PARKING-600X450-MTL-p/854975.htm | Safety Signs Australia: No Parking Sign (SKU R47A), Aluminium (closest-equiv, size 450x225 (need 600x450)) https://www.safetysigns.com.au/products/road-parking-no-parking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 225x450, size differs from 300x450 | All Trades Group: 'No Stopping' dual arrow closest wording, 225x450 | eSafety Supplies: 300x450 exact | Safety Signs Australia: 300x450 exact | SafetyXpress: 300x450 exact (upper of range) | Traffic Control Products: Not found | National Safety Signs: From, 'Bi-Directional' closest to double arrow | Seton: LOW conf - promo pricing, 300x450 exact | Advanced Group: No Standing Dbl Arr 300x450 Metal (EXACT) https://www.advancedgroup.com.au/NO-STANDING-DBL-ARR-300X450-MTL-p/843289.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 225x450, close to 450x300 | Jaybro: 225x450, close | All Trades Group: 225x450, same SKU as 686503 | eSafety Supplies: 300x450, close | Safety Signs Australia: 300x450, close | SafetyXpress: 300x450, close | Traffic Control Products: Not found | National Safety Signs: From, shared with 686503 | Advanced Group: T&amp;P Sign No Parking 300x450 Metal (EXACT (SKU 840307 match)) https://www.advancedgroup.com.au/T-P-SIGN-NO-PARKING-300X450-MTL-p/840307.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic site/warehouse safety sign - no comparable product found at any of the 9 researched retailers. | Advanced Group: No Smoking In This Area 300x225 Metal (EXACT (SKU 841090 match)) https://www.advancedgroup.com.au/NO-SMOKING-IN-THIS-AREA-300X225-MTL-p/841090.htm | Jaybro: No Smoking Prohibition Sign Metal 300x225mm (closest-equiv, wording) https://www.jaybro.com.au/safety-signs/no-smoking-prohibition-sign-metal-300x225mm/ | All Trades Group: No Smoking Sign, 300x225 Metal (closest-equiv, wording (generic, no "In This Area")) https://alltradesgroup.net.au/products/no-smoking-sign | eSafety Supplies: Prohibition Sign This Is A No Smoking Area, Poly (closest-equiv, material Poly/ACP not Metal) https://esafetysupplies.com.au/products/prohibition-sign-this-is-a-no-smoking-area | Safety Signs Australia: Prohibition Sign No Smoking In This Area, 225x300 Metal (EXACT) https://www.safetysigns.com.au/products/no-smoking-in-area-portrait | SafetyXpress: No Smoking In This Area Sign, 225x300 Metal (EXACT) https://www.safetyxpress.com.au/signs-posts-fixings/safety-signs/no-smoking-in-this-area-sign-225mm-x-300mm-metal/ | National Safety Signs: No Smoking In This Area P2223, Aluminium (closest-equiv, size 420x180 (need 300x225, no exact size exists)) https://nationalsafetysigns.com.au/safety-signs/no-smoking-in-this-area-p2223/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: Found differently-worded 'No Entry Authorised Prohibition' 600x450 $39.58inc/$35.98ex - size differs, see notes | All Trades Group: 450x300 exact size option available | eSafety Supplies: 300x450, 600x450 also stocked | Safety Signs Australia: 450x600, size differs | SafetyXpress: range 33.19-35.73, no exact 450x300 | Traffic Control Products: 450x300 exact, poly | National Safety Signs: From, R2543 'Restricted Area Do Not Enter' | Advanced Group: Restricted Area Authorised Persons - Admittance Sign (EXACT (SKU 832221 match)) https://www.advancedgroup.com.au/RESTR-AREA-AUTHORISED-450X300-MTL-p/832221.htm | Jaybro: No Entry Authorised Prohibition Sign Metal 450x300mm (closest-equiv, wording (currently OUT OF STOCK)) https://www.jaybro.com.au/safety-signs/no-entry-authorised-prohibition-sign-metal-450x300mm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Trades Group: 300x225 poly or 600x450; no exact 450x300 | eSafety Supplies: 600x450 also stocked | Safety Signs Australia: 450x600, size differs | SafetyXpress: 3 sizes incl 300x450 | National Safety Signs: From, S2870 | Seton: LOW conf; 'Video Surveillance In Use', 300-450mm range | Advanced Group: Security Notice: These Premises Are Protected By.. Metal 300x450(=450x300) (closest-equiv (wording)) https://www.advancedgroup.com.au/SURV-SIGN-THESE-PREMISES-ARE-PROT-MTL-p/844010.htm</t>
   </si>
   <si>
     <t xml:space="preserve">869339</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaybro: Not found | All Trades Group: 450x300 exact size option | eSafety Supplies: 300x450, 3mm ACP | Safety Signs Australia: 300x450, close | SafetyXpress: 300x450, close | Traffic Control Products: Not found | National Safety Signs: From | Seton: From, inc GST, 300x450</t>
+    <t xml:space="preserve">Jaybro: Not found | All Trades Group: 450x300 exact size option | eSafety Supplies: 300x450, 3mm ACP | Safety Signs Australia: 300x450, close | SafetyXpress: 300x450, close | Traffic Control Products: Not found | National Safety Signs: From | Seton: From, inc GST, 300x450 | Advanced Group: Reverse Parking Only Sign 300x450mm Metal (EXACT (size-order)) https://www.advancedgroup.com.au/Reverse-Parking-Only-Sign-300x450mm-MTL-p/856850.htm | Jaybro: Reverse Parking Only Notice Sign Poly 600x450mm (closest-equiv, material Poly not Metal, size 600x450 (need 450x300)) https://www.jaybro.com.au/safety-signs/reverse-parking-only-notice-sign-poly-600x450mm/</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: Not stocked (no 5km/h plate) | Jaybro: Not found separately | All Trades Group: Generic 5km/h reused, CL1 reflective not confirmed | eSafety Supplies: 5km/h, confirmed '1.6mm aluminium Class1 reflective' - good match | Safety Signs Australia: Generic 5km/h reused, size/spec differs | SafetyXpress: CL1/400 reflective alu, 450x600 - good match | Traffic Control Products: Not stocked | National Safety Signs: From; shared custom-text speed sign | Advanced Group: same generic 'Speed Limit (Speed Restriction) Sign' (R4-1) as other speed items, 600x450 = 450x600 rotated</t>
@@ -911,16 +917,16 @@
     <t xml:space="preserve">HiVis: 1800x600, Boxed Edge STEEL not corflute - material/size differ | Jaybro: Not found (only POA corflute detour sign on site) | All Trades Group: Only $199.50 swing-stand version, not flat panel | eSafety Supplies: Not found | Safety Signs Australia: 300x1200, 6mm Corflute Class1 - exact match | SafetyXpress: 1200x300 corflute - good match | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: Not found | Advanced Group: 'On Side Road - Corflute Sign 1200x300mm' (M123-T1-19); exact size/type match</t>
   </si>
   <si>
-    <t xml:space="preserve">eSafety Supplies: Not found | Safety Signs Australia: 600x600, 6mm Corflute Class1 - exact match (confirms Jess's size assumption) | SafetyXpress: range 30.24-64.03 incl 600x600 | Traffic Control Products: Not found separately | National Safety Signs: From, was 70.65, 600x600 MM981, yellow colour not confirmed</t>
+    <t xml:space="preserve">eSafety Supplies: Not found | Safety Signs Australia: 600x600, 6mm Corflute Class1 - exact match (confirms Jess's size assumption) | SafetyXpress: range 30.24-64.03 incl 600x600 | Traffic Control Products: Not found separately | National Safety Signs: From, was 70.65, 600x600 MM981, yellow colour not confirmed | Traffic Control Products: Multi Message Corflute Blank 1200x300 Yellow (closest-equiv, plausible match for UNISAF blank) https://trafficcontrolproducts.com.au/products/multi-message-blank-1200x300mm-corflute-yellow-3m</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: 1200x900, Boxed Edge STEEL 'Workmen Ahead Digger Man' not corflute | All Trades Group: Only swing-stand version exists | Safety Signs Australia: 600x600, 'Workmen' closest wording, 6mm Corflute | SafetyXpress: range 58.84-114.86 incl 600x600 | Traffic Control Products: 600x600, 'Digger Workman' corflute MMS - good match | National Safety Signs: Not found (closest is different boxed-edge sign) | Advanced Group: 'Workers Ahead (Symbolic Worker) 600x600mm Corflute Sign' (M66-T1-5); exact size match, wording 'Workers Ahead' vs our 'Symbolic Worker'</t>
   </si>
   <si>
-    <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL '40,60km/h Roadwork' not corflute | Safety Signs Australia: 600x600, '60 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: Not found (TCP only has 40/END40, no plain 60) | National Safety Signs: From, was 70.65, MM916 '60 kph' 600x600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL, same SKU as 60km item | Safety Signs Australia: 600x600, '40 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: 600x600, '40 (Speed)' corflute MMS - exact match | National Safety Signs: From, was 70.65, MM915 '40 kph' 600x600</t>
+    <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL '40,60km/h Roadwork' not corflute | Safety Signs Australia: 600x600, '60 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: Not found (TCP only has 40/END40, no plain 60) | National Safety Signs: From, was 70.65, MM916 '60 kph' 600x600 | Advanced Group: Speed Limit (Speed Restriction) 60Kmh 600x600mm, Corflute (closest-equiv naming) https://www.advancedgroup.com.au/product-p/m66-t4-1-60.htm | All Trades Group: Multi Message Speed Limit Sign, 600x600 Corflute (closest-equiv naming ("60km/h Ahead")) https://alltradesgroup.net.au/products/multi-message-speed-limit-sign-reflective | Traffic Control Products: 60 (Speed) 600x600x5mm Corflute MMS Reflective (EXACT) https://trafficcontrolproducts.com.au/products/60-speed-600-x-600-sign-corflute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 900x1200, Boxed Edge STEEL, same SKU as 60km item | Safety Signs Australia: 600x600, '40 KM' 6mm Corflute - exact match | SafetyXpress: 600x600 corflute - exact match | Traffic Control Products: 600x600, '40 (Speed)' corflute MMS - exact match | National Safety Signs: From, was 70.65, MM915 '40 kph' 600x600 | Advanced Group: Speed Limit (Speed Restriction) 40Kmh 600x600mm, Corflute (closest-equiv naming) https://www.advancedgroup.com.au/Speed-Limit-Speed-Restriction-40Kmh-p/m66-t4-1-40.htm</t>
   </si>
   <si>
     <t xml:space="preserve">HiVis: From; 900x600/1200x900, Boxed Edge STEEL not corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact size &amp; material | SafetyXpress: range 58.84-59.26, 600x600 or 1200x300 corflute | Traffic Control Products: 600x600, 'PTS' corflute MMS, size differs from 1200x300 | National Safety Signs: From, was 70.65, MM914, 600x600, size differs | Advanced Group: 'Prepare To Stop - Corflute Sign 1200x300mm' (M123-T1-18); exact match</t>
@@ -929,61 +935,94 @@
     <t xml:space="preserve">HiVis: From; 1800x600/2400x900, Boxed Edge STEEL not corflute | All Trades Group: 600x600, confirmed 6mm corflute, size differs from 1200x300 | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: range 57.75-90.17 incl 1200x300 | Traffic Control Products: 1200x300, corflute MMS reflective - exact match | National Safety Signs: From, was 70.65, MM920, 600x600, size differs | Advanced Group: 'Roadwork Ahead Sign 1200x300mm' (M123-T1-1); exact match</t>
   </si>
   <si>
-    <t xml:space="preserve">Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: 1200x300, 'White on Blue' corflute MMS - exact match | National Safety Signs: Not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 1800x300, Boxed Edge STEEL not corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: range 58.84-59.26, 600x600 or 1200x300 corflute | Traffic Control Products: Not found (TCP has 900x600/1200x900/1800x300/600x600, none at 1200x300 corflute) | National Safety Signs: From, was 70.65, MM901, 600x600, '1.6mm alu OR 6mm corflute' choice, size differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: From; 1200x300/1800x450, material likely alu/boxed-edge not corflute | All Trades Group: 1200x300 Class1, 'boxed edge' material not confirmed as corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: Only alu Boxed Edge ~$109.65, not corflute | National Safety Signs: INC GST; T5-1BL boxed-edge ALU not corflute, ~900x600 size differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: From; same as left-arrow SKU | All Trades Group: same note as detour left | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: Only alu Boxed Edge ~$109.65, not corflute | National Safety Signs: INC GST; T5-1BR boxed-edge ALU not corflute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 1200x300, 3mm aluminium Class400, not corflute but same size | eSafety Supplies: 1200x300, steel 3M Class1, NOT corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 MMS board, corflute | Traffic Control Products: 1200x300, Boxed Edge, NOT corflute | National Safety Signs: From, was 70.65, MM905 right variant, 600x600, size differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiVis: 1200x300, 3mm aluminium Class400, not corflute but same size | eSafety Supplies: 1200x300, steel 3M Class1, NOT corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 MMS board, corflute | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: From, was 70.65, MM905 left variant, 600x600, size differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Security Sign This Area Is..450x300 Poly' (841756); exact size/material match, full wording truncated on listing (not independently confirmed as '24 hour surveillance')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: 300x225 exact | All Trades Group: two fetches disagreed (42.50 vs 28.30); 300x225/450x300/600x450 avail | eSafety Supplies: 300x450, closest size | Safety Signs Australia: Not found - no exact wording/size/material match | SafetyXpress: 225x300, close | Traffic Control Products: Not found | National Safety Signs: From, M1890 | Seton: LOW conf, bulk tier range 31.16-34.28, 300x225 poly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: 600x450 exact | All Trades Group: 600x450 exact | eSafety Supplies: 600x450 exact | Safety Signs Australia: 18.00(corflute)/33.50(metal) avg, 450x600 size differs slightly | SafetyXpress: Not found - only differently-worded 'Construction Site Office' sign | Traffic Control Products: 600x450 exact, poly | National Safety Signs: Not found (only differently-worded 'All Vehicles Report')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'Fire Naked Flame And..300x225 Poly' (840048); exact size/material, exact wording not confirmed (truncated on listing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Danger Construction..600x450 Polyp' (844510); size differs (600x450 vs our 600x400)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: wording lacks 'By Permit' | Safety Signs Australia: 300x450 poly, size differs slightly, wording lacks 'By Permit' | SafetyXpress: 225x300 or 450x600, no exact 450x300, 'By Permit Only' wording exact | Traffic Control Products: 300x225 metal not poly, size differs, 'By Permit Only' wording exact | National Safety Signs: Not found | Advanced Group: 'Confined Space Entry By..450x300 Poly' (835604); exact size/material match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaybro: 225x300, size differs from 450x300 | All Trades Group: 450x300 exact size | eSafety Supplies: 300x450, size differs slightly, polypropylene | Safety Signs Australia: 300x450 poly, size differs slightly | SafetyXpress: range 25.15-44.87 incl 300x450 | Traffic Control Products: 19.50/26.50 two sizes (300x225/450x600), no exact 450x300 | National Safety Signs: From, E1217</t>
+    <t xml:space="preserve">Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: 1200x300, 'White on Blue' corflute MMS - exact match | National Safety Signs: Not found | Advanced Group: Drive Safely Sign Corflute 1200x300mm (EXACT ("Safely" vs "Safety")) https://www.advancedgroup.com.au/Drive-Safely-Sign-Corflute-1200x300mm-p/m123-t2-101.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 1800x300, Boxed Edge STEEL not corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: range 58.84-59.26, 600x600 or 1200x300 corflute | Traffic Control Products: Not found (TCP has 900x600/1200x900/1800x300/600x600, none at 1200x300 corflute) | National Safety Signs: From, was 70.65, MM901, 600x600, '1.6mm alu OR 6mm corflute' choice, size differs | Advanced Group: Road Closed 1200x300mm Corflute Sign (EXACT) https://www.advancedgroup.com.au/Road-Closed-Corflute-Sign-p/m123-t2-4.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: From; 1200x300/1800x450, material likely alu/boxed-edge not corflute | All Trades Group: 1200x300 Class1, 'boxed edge' material not confirmed as corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: Only alu Boxed Edge ~$109.65, not corflute | National Safety Signs: INC GST; T5-1BL boxed-edge ALU not corflute, ~900x600 size differs | Advanced Group: Detour W Left Arrow 1200x300mm, Corflute (EXACT) https://www.advancedgroup.com.au/DETOUR-with-Left-Arrow-Sign-p/m123-t5-1(l).htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: From; same as left-arrow SKU | All Trades Group: same note as detour left | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 corflute - exact match | Traffic Control Products: Only alu Boxed Edge ~$109.65, not corflute | National Safety Signs: INC GST; T5-1BR boxed-edge ALU not corflute | Advanced Group: Detour W Right Arrow 1200x300mm, Corflute (EXACT) https://www.advancedgroup.com.au/DETOUR-with-Right-Arrow-Sign-p/m123-t5-1(r).htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 1200x300, 3mm aluminium Class400, not corflute but same size | eSafety Supplies: 1200x300, steel 3M Class1, NOT corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 MMS board, corflute | Traffic Control Products: 1200x300, Boxed Edge, NOT corflute | National Safety Signs: From, was 70.65, MM905 right variant, 600x600, size differs | Advanced Group: Pedestrians with Right Arrow Corflute 1200x300mm (EXACT (not the aluminium variant)) https://www.advancedgroup.com.au/product-p/m123-t8-2r.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiVis: 1200x300, 3mm aluminium Class400, not corflute but same size | eSafety Supplies: 1200x300, steel 3M Class1, NOT corflute | Safety Signs Australia: 300x1200, 6mm Corflute - exact match | SafetyXpress: 1200x300 MMS board, corflute | Traffic Control Products: 1200x300 corflute, SOLD OUT at capture | National Safety Signs: From, was 70.65, MM905 left variant, 600x600, size differs | Advanced Group: Pedestrians with Left Arrow Corflute 1200x300mm (EXACT (not the aluminium variant)) https://www.advancedgroup.com.au/product-p/m123-t8-2l.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Security Sign This Area Is..450x300 Poly' (841756); exact size/material match, full wording truncated on listing (not independently confirmed as '24 hour surveillance') | eSafety Supplies: Security Notice This Area Is Under 24 Hour Surveillance, Poly (closest-equiv, size 300x450(=450x300)) https://esafetysupplies.com.au/products/security-notice-this-area-is-under-24-hour-surveillance | Safety Signs Australia: Security Sign This Area Is Under 24 Hour Surveillance, 300x450 Metal (closest-equiv, material Metal not Poly) https://www.safetysigns.com.au/products/security-24-hour-surveillance | National Safety Signs: Security CCTV Camera 24hr Surveillance S2883, 450x300 Poly (closest-equiv, wording) https://nationalsafetysigns.com.au/safety-signs/security-cctv-camera-24hr-surveillance-sign-s2883/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 300x225 exact | All Trades Group: two fetches disagreed (42.50 vs 28.30); 300x225/450x300/600x450 avail | eSafety Supplies: 300x450, closest size | Safety Signs Australia: Not found - no exact wording/size/material match | SafetyXpress: 225x300, close | Traffic Control Products: Not found | National Safety Signs: From, M1890 | Seton: LOW conf, bulk tier range 31.16-34.28, 300x225 poly | Advanced Group: Eye Protection Must Be Worn, 300x225 Poly (EXACT) https://www.advancedgroup.com.au/EYE-PROTECTION-MUST-BE-300X225-POLY-p/840599.htm | Safety Signs Australia: Mandatory Sign Eye Protection Must Be Worn In This Area, 225x300 Poly (closest-equiv, wording adds "In This Area") https://www.safetysigns.com.au/products/eye-protection-worn-area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 600x450 exact | All Trades Group: 600x450 exact | eSafety Supplies: 600x450 exact | Safety Signs Australia: 18.00(corflute)/33.50(metal) avg, 450x600 size differs slightly | SafetyXpress: Not found - only differently-worded 'Construction Site Office' sign | Traffic Control Products: 600x450 exact, poly | National Safety Signs: Not found (only differently-worded 'All Vehicles Report') | Advanced Group: All Visitors Must Report To Site Office, 600x450 Poly (EXACT) https://www.advancedgroup.com.au/ALL-VISITORS-MUST-REPORT-600X450-POLY-p/844553.htm | National Safety Signs: All Visitors Report to Office N2005, 600x450 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/all-visitors-report-to-office-n2005/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: No Smoking No Naked Flame, 300x225 Poly (SKU 840750) (EXACT now) https://www.advancedgroup.com.au/NO-SMOKING-NO-NAKED-FLAM-300X225-POLY-p/840750.htm | Jaybro: Danger No Smoking No Naked Flames Poly 600x450mm (closest-equiv, size 600x450 (need 300x225)) https://www.jaybro.com.au/safety-signs/danger-no-smoking-no-naked-flames-danger-sign-poly-600x450mm/ | All Trades Group: Danger No Smoking No Naked Flames No Matches, 300x225 Poly (EXACT) https://alltradesgroup.net.au/products/danger-no-smoking-no-naked-flames-no-matches-sign | Safety Signs Australia: Danger Sign No Smoking No Naked Flames No Matches, 225x300 Poly (EXACT) https://www.safetysigns.com.au/products/danger-no-smoking | National Safety Signs: No Smoking No Naked Flame D10376, 300x225 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/no-smoking-no-naked-flame-d10376/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: 'Danger Construction..600x450 Polyp' (844510); size differs (600x450 vs our 600x400) | Jaybro: Construction Site Danger Sign Poly 600x450mm (closest-equiv, size 600x450 (need 600x400)) https://www.jaybro.com.au/safety-signs/construction-site-danger-sign-poly-600x450mm/ | All Trades Group: Danger Construction Site Sign, 600x450 Poly (closest-equiv, size+wording (no "Do Not Enter")) https://alltradesgroup.net.au/products/danger-construction-site-sign | eSafety Supplies: Danger Construction Site Do Not Enter, 600x450 Poly (closest-equiv, size 600x450 (need 600x400)) https://esafetysupplies.com.au/products/danger-sign-construction-site-do-not-enter | Safety Signs Australia: Danger Sign Construction Site Do Not Enter, 450x600 Poly (closest-equiv, size 450x600 (need 600x400)) https://www.safetysigns.com.au/products/danger-construction-site | SafetyXpress: Danger Sign Construction Site Do Not Enter, Poly (closest-equiv, size 450x600 (need 600x400)) https://www.safetyxpress.com.au/site-signage-posts-fixings/danger-sign-construction-site-do-not-enter-450mm-x-600mm-poly/ | Traffic Control Products: Danger Construction Site Do Not Enter, 600x450 Poly (closest-equiv, size 600x450 (need 600x400) - currently SOLD OUT) https://trafficcontrolproducts.com.au/products/danger-construct-site-do-not-enter-600x450-poly | National Safety Signs: Construction Site No Entry D10261, 600x450 Poly (closest-equiv, size 600x450 (need 600x400), wording "No Entry" vs "Do Not Enter") https://nationalsafetysigns.com.au/safety-signs/construction-site-no-entry-d10261/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Danger Demolition Work In Progress, 600x450 Poly (EXACT (SKU US-223LP match)) https://www.advancedgroup.com.au/Danger-Demolition-Work-in-Progress-600X450-POLY-p/us-223lp.htm | Jaybro: Danger Demolition Work In Progress 600x450mm Poly (EXACT) https://www.jaybro.com.au/safety-signs/danger-demolition-work-in-progress-600x450mm/ | All Trades Group: Danger Demolition Work In Progress, 600x450 Poly (EXACT) https://alltradesgroup.net.au/products/danger-demolition-work-in-progress-sign | eSafety Supplies: Danger Demolition Work In Progress, 600x450 Poly (EXACT) https://esafetysupplies.com.au/products/danger-sign-demolition-work-in-progress | Safety Signs Australia: Danger Sign Demolition Work In Progress, 450x600 Metal (closest-equiv, material Metal not Poly) https://www.safetysigns.com.au/products/danger-demolition | SafetyXpress: Danger Sign Demolition Work In Progress, 450x600 Poly (EXACT) https://www.safetyxpress.com.au/signs-posts-fixings/safety-signs/danger-sign-demolition-work-in-progress-450mm-x-600mm-poly/ | Traffic Control Products: Danger Demolition Work In Progress, 600x450mm Poly (EXACT) https://trafficcontrolproducts.com.au/products/danger-demolition-work-in-progress-600x450mm-poly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: wording lacks 'By Permit' | Safety Signs Australia: 300x450 poly, size differs slightly, wording lacks 'By Permit' | SafetyXpress: 225x300 or 450x600, no exact 450x300, 'By Permit Only' wording exact | Traffic Control Products: 300x225 metal not poly, size differs, 'By Permit Only' wording exact | National Safety Signs: Not found | Advanced Group: 'Confined Space Entry By..450x300 Poly' (835604); exact size/material match | All Trades Group: Danger Confined Space Sign, 450x300 Poly (closest-equiv, wording (generic)) https://alltradesgroup.net.au/products/danger-confined-space-sign | eSafety Supplies: Danger Confined Space Entry By Permit Only, 300x450(=450x300) Poly (EXACT (size equiv via rotation)) https://esafetysupplies.com.au/products/danger-sign-confined-space-entry-by-permit-only-600-x-450mm | National Safety Signs: Confined Space Permit Only Sign D1037, 450x300 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/danger-confined-space-d1037/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaybro: 225x300, size differs from 450x300 | All Trades Group: 450x300 exact size | eSafety Supplies: 300x450, size differs slightly, polypropylene | Safety Signs Australia: 300x450 poly, size differs slightly | SafetyXpress: range 25.15-44.87 incl 300x450 | Traffic Control Products: 19.50/26.50 two sizes (300x225/450x600), no exact 450x300 | National Safety Signs: From, E1217 | Advanced Group: First Aid 450x300 Poly (EXACT (SKU 835331 match)) https://www.advancedgroup.com.au/FIRST-AID-450X300-POLY-p/835331.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: First Aid Station 300x225 Poly (EXACT) https://www.advancedgroup.com.au/FIRST-AID-STATION-300X225-POLY-p/840003.htm | Jaybro: First Aid Emergency Sign Poly 225x300mm (closest-equiv, wording "Emergency" not "Station") https://www.jaybro.com.au/safety-signs/first-aid-emergency-sign-poly-225x300mm/ | All Trades Group: First Aid Site Sign, 300x225 Poly (closest-equiv, wording "Site" vs "Station") https://alltradesgroup.net.au/products/first-aid-site-sign | eSafety Supplies: First Aid Sign, 300x450 Poly (closest-equiv, size 300x450 (need 300x225)) https://esafetysupplies.com.au/products/first-aid-sign-300-x-450-mm | Safety Signs Australia: Emergency Sign First Aid Station, 225x300 Poly (EXACT) https://www.safetysigns.com.au/products/first-aid-station | SafetyXpress: First Aid Sign Polypropylene, 225x300 (EXACT (confirmed default variant)) https://www.safetyxpress.com.au/signs-posts-fixings/safety-signs/first-aid-sign-polypropylene/ | Traffic Control Products: First Aid Sign, 300x225 Poly (closest-equiv, wording "Sign" vs "Station") https://trafficcontrolproducts.com.au/products/first-aid-sign-300-x-225-poly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Jaybro: Emergency Assembly Point Emergency Sign Poly 600x450mm (closest-equiv, size 600x450 (need 600x400), wording "Point" not "Area") https://www.jaybro.com.au/safety-signs/emergency-assembly-point-emergency-sign-poly-600x450mm/ | All Trades Group: Emergency Assembly Point Sign, 600x450 Poly (closest-equiv, size+wording ("Point" not "Area")) https://alltradesgroup.net.au/products/emergency-assembly-point-sign | eSafety Supplies: Information Sign Emergency Assembly Point, 450x600 Aluminium (closest-equiv, material Aluminium not Poly) https://esafetysupplies.com.au/products/information-sign-emergency-assembly-point-450-x-600mm | Safety Signs Australia: Emergency Sign Emergency Assembly Area, Metal (closest-equiv, material Metal not Poly, size 450x600 (need 600x400)) https://www.safetysigns.com.au/products/emergency-assembly-area | Traffic Control Products: Emergency Assembly Point, 600x450mm Poly (closest-equiv, wording "Point" vs "Area", size needs 600x400) https://trafficcontrolproducts.com.au/products/emergency-assembly-point-600mm-x-450mm-poly | National Safety Signs: Emergency Assembly Area E1266, 600x450 Poly (closest-equiv, size 600x450 (need 600x400)) https://nationalsafetysigns.com.au/safety-signs/emergency-assembly-area-e1266/</t>
   </si>
   <si>
     <t xml:space="preserve">Jaybro: 150x150, size differs from 225x225 | All Trades Group: 150x225, size differs | eSafety Supplies: 300x450, closest, '600x450 also stocked' | Safety Signs Australia: 225x225 poly EXACT, double-sided | SafetyXpress: range 21.11-23.12, 225x300 size differs slightly | Traffic Control Products: Only physical extinguisher unit stocked, not a wall sign | National Safety Signs: From, F1411, 225x225 not confirmed | Seton: MEDIUM conf, 225x225 poly EXACT, inc GST (55.75 ex)</t>
   </si>
   <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Fire Sign Fire Hose Reel Poly, 300x225 (closest-equiv ("&amp;Picto" unconfirmed)) https://www.advancedgroup.com.au/FIRE-SIGN-FIRE-HOSE-REEL-POLY-p/840698.htm | Jaybro: Fire Hose Reel Sign Poly 225x300mm (EXACT (225x300=300x225)) https://www.jaybro.com.au/safety-signs/fire-hose-reel-sign-poly-225x300mm/ | All Trades Group: Fire Hose Reel Sign, 300x225 Poly (EXACT) https://alltradesgroup.net.au/products/fire-hose-reel-sign | Safety Signs Australia: Fire Hose Reel Sign, 225x300 Poly (EXACT) https://www.safetysigns.com.au/products/fire-hose-reel-portrait | National Safety Signs: Fire Hose Reel Sign F1433, 300x225 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/fire-hose-reel-sign-f1433/</t>
+  </si>
+  <si>
     <t xml:space="preserve">n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'RESTR AREA AUTHORISED..600X450 POLY' (845084); wording differs (Restricted Area Authorised vs our Warning Authorised Personnel), same size/material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: closest equivalent 'Hazardous Materials Area..300x225 Poly' (840344); related hazard wording, not an exact match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Trades Group: 900x600 corflute, size differs (larger) | Safety Signs Australia: 450x600 poly EXACT | SafetyXpress: 450x600 metal EXACT size, material differs | Traffic Control Products: 600x450, 'Danger Crane Working Overhead' - different wording, poly | National Safety Signs: From, D10279 | Seton: LOW conf, bulk tier range 33.21-36.91, 600x450 Flute | Advanced Group: 'Danger Overhead Power Lines 450x600mm' (850599); size matches (rotated), material not stated on listing</t>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Safety Signs Australia: Arrow Sign, 200x450 Poly (EXACT) https://www.safetysigns.com.au/products/arrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | eSafety Supplies: Car Park Sign Forklift Speed Limit 5km/h, 600x450 Poly (size/material match, wording differs slightly) https://esafetysupplies.com.au/products/carpark-sign-forklift-speed-limit-5 | Safety Signs Australia: Speed Limit Sign 5km, 450x600 Metal (closest-equiv, material Metal not Poly) https://www.safetysigns.com.au/products/speed-limit-5 | National Safety Signs: Speed Limit 5 KPH Sign R2402, 600x450 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/speed-limit-5-kph-sign-r2402/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Watch Out For Pedestrians 600x450 Poly (closest-equiv wording differs) https://www.advancedgroup.com.au/WATCH-OUT-FOR-PEDESTRIANS-600X450-POLY-p/844439.htm | Jaybro: Beware Of Pedestrians Warning Sign Poly 600x450mm (EXACT) https://www.jaybro.com.au/safety-signs/beware-of-pedestrians-warning-sign-poly-600x450mm/ | Safety Signs Australia: Warning Sign Watch Out For Pedestrians, 450x600 Poly (closest-equiv, wording) https://www.safetysigns.com.au/products/watch-for-pedestrians | National Safety Signs: Watch Out For Pedestrians RD126, 600x450 Poly (closest-equiv, wording) https://nationalsafetysigns.com.au/safety-signs/watch-out-for-pedestrians-rd126/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Authorised Personnel, 600x450 Poly (SKU 835253) (better wording match) https://www.advancedgroup.com.au/AUTHORISED-PERSONNEL-600X450-POLY-p/835253.htm | All Trades Group: Authorised Personnel Only Prohibition Sign, 600x450 Poly (closest-equiv, category label) https://alltradesgroup.net.au/products/authorised-personnel-only-prohibition-sign | eSafety Supplies: Danger No Entry Authorised Personnel Only, 600x450 Poly (size/material match, "Danger" vs "Warning") https://esafetysupplies.com.au/products/danger-sign-no-entry-authorised-personnel-only-600-x-450mm | Safety Signs Australia: Prohibition Sign Authorised Personnel Only, 450x600 Poly (closest-equiv, category "Prohibition" vs "Warning") https://www.safetysigns.com.au/products/authorised-personnel-only | National Safety Signs: Restricted Area Authorised Personnel Only W30286, 600x450 Poly (closest-equiv, wording adds "Restricted Area") https://nationalsafetysigns.com.au/safety-signs/restricted-area-authorised-personnel-only-sign-w30286/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Corrosive 8 Labels 270mm Poly (EXACT (SKU 835630 match)) https://www.advancedgroup.com.au/CORROSIVE-8-LABELS-270MM-POLY-p/835630.htm | All Trades Group: Corrosive Dangerous Goods Sign, 270x270 Poly (closest-equiv (AS1216 Class 8, not labelled "Hazchem")) https://alltradesgroup.net.au/products/corrosive-dangerous-goods-sign | Safety Signs Australia: Hazchem Sign 8 Corrosive, 270x270 Poly (EXACT) https://www.safetysigns.com.au/products/dg-corrosive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Exit &amp; Evac Sign Arr/DL Exit Lum Poly (closest-equiv, size differs (350x180 not 350x140)) https://www.advancedgroup.com.au/EXIT-EVAC-SIGN-ARR-DL-EXIT-LUM-POLY-p/843034.htm | National Safety Signs: Luminous Emergency Exit Sign With Symbol E12137, Poly (closest-equiv, size 270x135 (need 350x140, reasonably close)) https://nationalsafetysigns.com.au/safety-signs/luminous-emergency-exit-sign-with-symbol-e12137/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Danger Workers Above, 600x450 Poly (EXACT) https://www.advancedgroup.com.au/DANGER-WORKERS-ABOVE-600X450-POLY-p/835818.htm | Jaybro: Danger Workers Overhead Danger Sign 600x450mm Poly (closest-equiv, wording "Overhead" vs "Above") https://www.jaybro.com.au/safety-signs/danger-workers-overhead-danger-sign-600x450mm/ | All Trades Group: Danger Workers Above, 600x450 Poly (EXACT) https://alltradesgroup.net.au/products/danger-workers-above-sign | Safety Signs Australia: Danger Sign Workers Above, 450x600 Poly (EXACT) https://www.safetysigns.com.au/products/danger-workers-above | National Safety Signs: Workers Above D10181, 600x450 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/workers-above-d10181/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: No Pedestrian Access, 300x225 Poly (EXACT (SKU 840223 match)) https://www.advancedgroup.com.au/NO-PEDESTRIAN-ACCESS-300X225-POLY-p/840223.htm | Jaybro: No Pedestrian Access Prohibition Sign Poly 600x450mm (closest-equiv, size 600x450 (need 300x225)) https://www.jaybro.com.au/safety-signs/no-pedestrian-access-prohibition-sign-poly-600x450mm/ | All Trades Group: No Pedestrian Access Prohibition Sign, 300x225 Poly (EXACT) https://alltradesgroup.net.au/products/no-pedestrian-access-prohibition-sign | eSafety Supplies: Prohibition Sign No Pedestrian Access, Poly (closest-equiv, size 300x450/600x450 (need 300x225)) https://esafetysupplies.com.au/products/prohibition-sign-no-pedestrian-access | Safety Signs Australia: Prohibition Sign No Pedestrian Access, 225x300 Poly (EXACT) https://www.safetysigns.com.au/products/no-pedestrian-access | National Safety Signs: No Pedestrian Access P22102, 300x225 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/no-pedestrian-access-sign-p22102/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Lunch Room, 450x180 Poly (closest-equiv, size differs (450x180 not 450x300)) https://www.advancedgroup.com.au/LUNCH-ROOM-450X180-POLY-p/840023.htm | Jaybro: Lunch Room Information Sign Poly 600x450mm (closest-equiv, size 600x450 (need 450x300)) https://www.jaybro.com.au/safety-signs/lunch-room-information-sign-poly-600x450mm/ | eSafety Supplies: General Sign Lunch Room, 300x450(=450x300) Poly (EXACT (size equiv via rotation)) https://esafetysupplies.com.au/products/lunch-room-sign | Safety Signs Australia: Construction Sign Lunch Room, 200x450 Poly (closest-equiv, size 200x450 (need 450x300)) https://www.safetysigns.com.au/products/lunch-room | National Safety Signs: Lunch Room S2802, 450x300 Poly (EXACT) https://nationalsafetysigns.com.au/safety-signs/lunch-room-s2802/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No comparable product found at any of the 9 researched retailers - likely generic site-safety signage outside their core road/traffic-sign range. | Advanced Group: Flammable Material Storage, 300x225 Poly (SKU 840747) (EXACT now) https://www.advancedgroup.com.au/FLAMMABLE-MATERIAL-STORAGE-300X225-POLY-p/840747.htm | Jaybro: Danger Flammable Materials Danger Sign Poly 600x450mm (closest-equiv, size 600x450 (need 300x225)) https://www.jaybro.com.au/safety-signs/danger-flammable-materials-danger-sign-poly-600x450mm/ | All Trades Group: Danger Flammable Materials Sign, 300x225 Poly (closest-equiv, wording (no "Storage Area")) https://alltradesgroup.net.au/products/danger-flammable-materials-sign | eSafety Supplies: Danger Sign Flammable Materials, Poly (closest-equiv, size+wording (no "Storage Area")) https://esafetysupplies.com.au/products/danger-sign-flammable-materials | Safety Signs Australia: Danger Sign Flammable Material Storage Keep Heat Away, 225x300 Poly (closest-equiv, wording adds "Keep Heat Away") https://www.safetysigns.com.au/products/danger-flammable-storage | National Safety Signs: Flammable Material D10324, 300x225 Poly (closest-equiv, wording (no "Storage Area")) https://nationalsafetysigns.com.au/safety-signs/flammable-material-sign-d10324/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Trades Group: 900x600 corflute, size differs (larger) | Safety Signs Australia: 450x600 poly EXACT | SafetyXpress: 450x600 metal EXACT size, material differs | Traffic Control Products: 600x450, 'Danger Crane Working Overhead' - different wording, poly | National Safety Signs: From, D10279 | Seton: LOW conf, bulk tier range 33.21-36.91, 600x450 Flute | Advanced Group: 'Danger Overhead Power Lines 450x600mm' (850599); size matches (rotated), material not stated on listing | Jaybro: Overhead Powerlines Danger Sign Poly 450x600mm (closest-equiv, material Poly not Corflute) https://www.jaybro.com.au/safety-signs/overhead-powerlines-danger-sign-poly-450x600mm/</t>
   </si>
   <si>
     <t xml:space="preserve">Items compared (60 total line items)</t>
@@ -1070,19 +1109,13 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Advanced Group</t>
-  </si>
-  <si>
     <t xml:space="preserve">SafetyXpress</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaybro</t>
+    <t xml:space="preserve">Safety Signs Australia</t>
   </si>
   <si>
     <t xml:space="preserve">National Safety Signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety Signs Australia</t>
   </si>
   <si>
     <t xml:space="preserve">Items We're MORE EXPENSIVE On (our higher-of-1200/1220 quote vs the single cheapest alternative — 7 of 60 items)</t>
@@ -1107,14 +1140,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1406,7 +1438,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1611,31 +1643,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1643,23 +1667,23 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1775,9 +1799,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>402480</xdr:colOff>
+      <xdr:colOff>401400</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>258840</xdr:rowOff>
+      <xdr:rowOff>257760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1791,7 +1815,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2190240" cy="2336400"/>
+          <a:ext cx="2189160" cy="2335320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7676,8 +7700,13 @@
         <f aca="false">Z6/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
+      <c r="AB6" s="11" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC6" s="11" t="n">
+        <f aca="false">AB6/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD6" s="11" t="n">
         <f aca="false">IF(COUNT(I6,J6,M6,O6,Q6,S6,U6,V6,Y6,AA6,AC6)=0,"N/A",MIN(I6,J6,M6,O6,Q6,S6,U6,V6,Y6,AA6,AC6))</f>
         <v>9.35454545454545</v>
@@ -8233,8 +8262,13 @@
         <f aca="false">Z11/1.1</f>
         <v>158.163636363636</v>
       </c>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
+      <c r="AB11" s="11" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="AC11" s="11" t="n">
+        <f aca="false">AB11/1.1</f>
+        <v>77.9090909090909</v>
+      </c>
       <c r="AD11" s="11" t="n">
         <f aca="false">IF(COUNT(I11,J11,M11,O11,Q11,S11,U11,V11,Y11,AA11,AC11)=0,"N/A",MIN(I11,J11,M11,O11,Q11,S11,U11,V11,Y11,AA11,AC11))</f>
         <v>44.209</v>
@@ -8650,23 +8684,25 @@
       <c r="M15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S15" s="42" t="s">
-        <v>259</v>
+      <c r="N15" s="42" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O15" s="42" t="n">
+        <f aca="false">N15/1.1</f>
+        <v>32.4545454545455</v>
+      </c>
+      <c r="P15" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q15" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R15" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="S15" s="42" t="n">
+        <f aca="false">R15/1.1</f>
+        <v>22.7272727272727</v>
       </c>
       <c r="T15" s="42" t="s">
         <v>259</v>
@@ -8680,11 +8716,12 @@
       <c r="W15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X15" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y15" s="42" t="s">
-        <v>259</v>
+      <c r="X15" s="42" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="Y15" s="42" t="n">
+        <f aca="false">X15/1.1</f>
+        <v>31.8818181818182</v>
       </c>
       <c r="Z15" s="45" t="n">
         <f aca="false">AA15*1.1</f>
@@ -8693,19 +8730,24 @@
       <c r="AA15" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB15" s="45"/>
-      <c r="AC15" s="45"/>
+      <c r="AB15" s="45" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="AC15" s="45" t="n">
+        <f aca="false">AB15/1.1</f>
+        <v>31.8727272727273</v>
+      </c>
       <c r="AD15" s="11" t="n">
         <f aca="false">IF(COUNT(I15,J15,M15,O15,Q15,S15,U15,V15,Y15,AA15,AC15)=0,"N/A",MIN(I15,J15,M15,O15,Q15,S15,U15,V15,Y15,AA15,AC15))</f>
-        <v>29.9909090909091</v>
+        <v>22</v>
       </c>
       <c r="AE15" s="43" t="n">
         <f aca="false">IF(OR(D15="",AD15="",AD15="N/A"),"N/A",D15/AD15-1)</f>
-        <v>-0.721582297665959</v>
+        <v>-0.620454545454546</v>
       </c>
       <c r="AF15" s="43" t="n">
         <f aca="false">IF(OR(F15="",AD15="",AD15="N/A"),"N/A",F15/AD15-1)</f>
-        <v>-0.717868672324947</v>
+        <v>-0.615392045454545</v>
       </c>
       <c r="AG15" s="41" t="s">
         <v>268</v>
@@ -8751,29 +8793,31 @@
       <c r="K16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S16" s="42" t="s">
-        <v>259</v>
+      <c r="L16" s="42" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <f aca="false">N16/1.1</f>
+        <v>36.3181818181818</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <f aca="false">R16/1.1</f>
+        <v>25</v>
       </c>
       <c r="T16" s="42" t="s">
         <v>259</v>
@@ -8781,17 +8825,19 @@
       <c r="U16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="X16" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y16" s="42" t="s">
-        <v>259</v>
+      <c r="V16" s="42" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="W16" s="42" t="n">
+        <f aca="false">V16*1.1</f>
+        <v>24.09</v>
+      </c>
+      <c r="X16" s="42" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="Y16" s="42" t="n">
+        <f aca="false">X16/1.1</f>
+        <v>38.8636363636364</v>
       </c>
       <c r="Z16" s="45" t="n">
         <f aca="false">AA16*1.1</f>
@@ -8809,15 +8855,15 @@
       </c>
       <c r="AD16" s="11" t="n">
         <f aca="false">IF(COUNT(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16)=0,"N/A",MIN(I16,J16,M16,O16,Q16,S16,U16,V16,Y16,AA16,AC16))</f>
-        <v>34.9545454545455</v>
+        <v>21.9</v>
       </c>
       <c r="AE16" s="43" t="n">
         <f aca="false">IF(OR(D16="",AD16="",AD16="N/A"),"N/A",D16/AD16-1)</f>
-        <v>-0.553992197659298</v>
+        <v>-0.288127853881279</v>
       </c>
       <c r="AF16" s="43" t="n">
         <f aca="false">IF(OR(F16="",AD16="",AD16="N/A"),"N/A",F16/AD16-1)</f>
-        <v>-0.547619635890767</v>
+        <v>-0.277956621004566</v>
       </c>
       <c r="AG16" s="41" t="s">
         <v>269</v>
@@ -8863,29 +8909,31 @@
       <c r="K17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S17" s="42" t="s">
-        <v>259</v>
+      <c r="L17" s="42" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O17" s="42" t="n">
+        <f aca="false">N17/1.1</f>
+        <v>32.4545454545455</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R17" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="S17" s="42" t="n">
+        <f aca="false">R17/1.1</f>
+        <v>22.7272727272727</v>
       </c>
       <c r="T17" s="42" t="s">
         <v>259</v>
@@ -8899,11 +8947,12 @@
       <c r="W17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X17" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y17" s="42" t="s">
-        <v>259</v>
+      <c r="X17" s="42" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="Y17" s="42" t="n">
+        <f aca="false">X17/1.1</f>
+        <v>31.8818181818182</v>
       </c>
       <c r="Z17" s="45" t="n">
         <f aca="false">AA17*1.1</f>
@@ -8912,19 +8961,24 @@
       <c r="AA17" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB17" s="45"/>
-      <c r="AC17" s="45"/>
+      <c r="AB17" s="45" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="AC17" s="45" t="n">
+        <f aca="false">AB17/1.1</f>
+        <v>31.8727272727273</v>
+      </c>
       <c r="AD17" s="11" t="n">
         <f aca="false">IF(COUNT(I17,J17,M17,O17,Q17,S17,U17,V17,Y17,AA17,AC17)=0,"N/A",MIN(I17,J17,M17,O17,Q17,S17,U17,V17,Y17,AA17,AC17))</f>
-        <v>29.9909090909091</v>
+        <v>10.5</v>
       </c>
       <c r="AE17" s="43" t="n">
         <f aca="false">IF(OR(D17="",AD17="",AD17="N/A"),"N/A",D17/AD17-1)</f>
-        <v>-0.721582297665959</v>
+        <v>-0.204761904761905</v>
       </c>
       <c r="AF17" s="43" t="n">
         <f aca="false">IF(OR(F17="",AD17="",AD17="N/A"),"N/A",F17/AD17-1)</f>
-        <v>-0.717868672324947</v>
+        <v>-0.194154761904762</v>
       </c>
       <c r="AG17" s="41" t="s">
         <v>270</v>
@@ -8976,11 +9030,12 @@
       <c r="M18" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N18" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O18" s="42" t="s">
-        <v>259</v>
+      <c r="N18" s="42" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="O18" s="42" t="n">
+        <f aca="false">N18/1.1</f>
+        <v>45</v>
       </c>
       <c r="P18" s="11" t="n">
         <v>57</v>
@@ -9022,8 +9077,13 @@
       <c r="AA18" s="45" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
+      <c r="AB18" s="45" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="AC18" s="45" t="n">
+        <f aca="false">AB18/1.1</f>
+        <v>42.7181818181818</v>
+      </c>
       <c r="AD18" s="11" t="n">
         <f aca="false">IF(COUNT(I18,J18,M18,O18,Q18,S18,U18,V18,Y18,AA18,AC18)=0,"N/A",MIN(I18,J18,M18,O18,Q18,S18,U18,V18,Y18,AA18,AC18))</f>
         <v>37.3909090909091</v>
@@ -9081,11 +9141,11 @@
       <c r="K19" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L19" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M19" s="42" t="s">
-        <v>259</v>
+      <c r="L19" s="42" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="M19" s="42" t="n">
+        <v>55.99</v>
       </c>
       <c r="N19" s="11" t="n">
         <v>36.5</v>
@@ -9134,8 +9194,13 @@
       <c r="AA19" s="45" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB19" s="45"/>
-      <c r="AC19" s="45"/>
+      <c r="AB19" s="45" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="AC19" s="45" t="n">
+        <f aca="false">AB19/1.1</f>
+        <v>42.7181818181818</v>
+      </c>
       <c r="AD19" s="11" t="n">
         <f aca="false">IF(COUNT(I19,J19,M19,O19,Q19,S19,U19,V19,Y19,AA19,AC19)=0,"N/A",MIN(I19,J19,M19,O19,Q19,S19,U19,V19,Y19,AA19,AC19))</f>
         <v>28.3545454545455</v>
@@ -9246,8 +9311,13 @@
         <f aca="false">Z20/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
+      <c r="AB20" s="11" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC20" s="11" t="n">
+        <f aca="false">AB20/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD20" s="11" t="n">
         <f aca="false">IF(COUNT(I20,J20,M20,O20,Q20,S20,U20,V20,Y20,AA20,AC20)=0,"N/A",MIN(I20,J20,M20,O20,Q20,S20,U20,V20,Y20,AA20,AC20))</f>
         <v>23.3090909090909</v>
@@ -9324,11 +9394,12 @@
       <c r="Q21" s="11" t="n">
         <v>40.91</v>
       </c>
-      <c r="R21" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S21" s="42" t="s">
-        <v>259</v>
+      <c r="R21" s="42" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="S21" s="42" t="n">
+        <f aca="false">R21/1.1</f>
+        <v>33.7</v>
       </c>
       <c r="T21" s="11" t="n">
         <v>82.82</v>
@@ -9357,8 +9428,13 @@
       <c r="AA21" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB21" s="45"/>
-      <c r="AC21" s="45"/>
+      <c r="AB21" s="45" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="AC21" s="45" t="n">
+        <f aca="false">AB21/1.1</f>
+        <v>42.7181818181818</v>
+      </c>
       <c r="AD21" s="11" t="n">
         <f aca="false">IF(COUNT(I21,J21,M21,O21,Q21,S21,U21,V21,Y21,AA21,AC21)=0,"N/A",MIN(I21,J21,M21,O21,Q21,S21,U21,V21,Y21,AA21,AC21))</f>
         <v>21.2</v>
@@ -9468,8 +9544,13 @@
         <f aca="false">Z22/1.1</f>
         <v>44.4090909090909</v>
       </c>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
+      <c r="AB22" s="11" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC22" s="11" t="n">
+        <f aca="false">AB22/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD22" s="11" t="n">
         <f aca="false">IF(COUNT(I22,J22,M22,O22,Q22,S22,U22,V22,Y22,AA22,AC22)=0,"N/A",MIN(I22,J22,M22,O22,Q22,S22,U22,V22,Y22,AA22,AC22))</f>
         <v>21.2</v>
@@ -9579,8 +9660,13 @@
       <c r="AA23" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB23" s="45"/>
-      <c r="AC23" s="45"/>
+      <c r="AB23" s="45" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC23" s="45" t="n">
+        <f aca="false">AB23/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD23" s="11" t="n">
         <f aca="false">IF(COUNT(I23,J23,M23,O23,Q23,S23,U23,V23,Y23,AA23,AC23)=0,"N/A",MIN(I23,J23,M23,O23,Q23,S23,U23,V23,Y23,AA23,AC23))</f>
         <v>21.2</v>
@@ -9637,35 +9723,38 @@
       <c r="K24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="T24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="U24" s="42" t="s">
-        <v>259</v>
+      <c r="L24" s="42" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="M24" s="42" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="N24" s="42" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="O24" s="42" t="n">
+        <f aca="false">N24/1.1</f>
+        <v>32.5</v>
+      </c>
+      <c r="P24" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q24" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R24" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="S24" s="42" t="n">
+        <f aca="false">R24/1.1</f>
+        <v>22.7272727272727</v>
+      </c>
+      <c r="T24" s="42" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="U24" s="42" t="n">
+        <f aca="false">T24/1.1</f>
+        <v>30.1727272727273</v>
       </c>
       <c r="V24" s="42" t="s">
         <v>259</v>
@@ -9673,11 +9762,12 @@
       <c r="W24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X24" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y24" s="42" t="s">
-        <v>259</v>
+      <c r="X24" s="42" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="Y24" s="42" t="n">
+        <f aca="false">X24/1.1</f>
+        <v>32.6363636363636</v>
       </c>
       <c r="Z24" s="45" t="n">
         <v>46.13</v>
@@ -9685,22 +9775,27 @@
       <c r="AA24" s="45" t="n">
         <v>41.94</v>
       </c>
-      <c r="AB24" s="45"/>
-      <c r="AC24" s="45"/>
+      <c r="AB24" s="45" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="AC24" s="45" t="n">
+        <f aca="false">AB24/1.1</f>
+        <v>31.8727272727273</v>
+      </c>
       <c r="AD24" s="11" t="n">
         <f aca="false">IF(COUNT(I24,J24,M24,O24,Q24,S24,U24,V24,Y24,AA24,AC24)=0,"N/A",MIN(I24,J24,M24,O24,Q24,S24,U24,V24,Y24,AA24,AC24))</f>
-        <v>34.5363636363636</v>
+        <v>22</v>
       </c>
       <c r="AE24" s="43" t="n">
         <f aca="false">IF(OR(D24="",AD24="",AD24="N/A"),"N/A",D24/AD24-1)</f>
-        <v>-0.829165569886812</v>
+        <v>-0.731818181818182</v>
       </c>
       <c r="AF24" s="43" t="n">
         <f aca="false">IF(OR(F24="",AD24="",AD24="N/A"),"N/A",F24/AD24-1)</f>
-        <v>-0.825940708081074</v>
+        <v>-0.726755681818182</v>
       </c>
       <c r="AG24" s="41" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9743,11 +9838,11 @@
       <c r="K25" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L25" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M25" s="42" t="s">
-        <v>259</v>
+      <c r="L25" s="42" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="M25" s="42" t="n">
+        <v>42.08</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>42.5</v>
@@ -9796,8 +9891,13 @@
       <c r="AA25" s="45" t="n">
         <v>44.41</v>
       </c>
-      <c r="AB25" s="45"/>
-      <c r="AC25" s="45"/>
+      <c r="AB25" s="45" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC25" s="45" t="n">
+        <f aca="false">AB25/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD25" s="11" t="n">
         <f aca="false">IF(COUNT(I25,J25,M25,O25,Q25,S25,U25,V25,Y25,AA25,AC25)=0,"N/A",MIN(I25,J25,M25,O25,Q25,S25,U25,V25,Y25,AA25,AC25))</f>
         <v>9.35454545454545</v>
@@ -9811,7 +9911,7 @@
         <v>0.28629980563654</v>
       </c>
       <c r="AG25" s="41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9907,8 +10007,13 @@
         <f aca="false">Z26/1.1</f>
         <v>59.6636363636364</v>
       </c>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
+      <c r="AB26" s="11" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC26" s="11" t="n">
+        <f aca="false">AB26/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD26" s="11" t="n">
         <f aca="false">IF(COUNT(I26,J26,M26,O26,Q26,S26,U26,V26,Y26,AA26,AC26)=0,"N/A",MIN(I26,J26,M26,O26,Q26,S26,U26,V26,Y26,AA26,AC26))</f>
         <v>9.35454545454545</v>
@@ -9922,7 +10027,7 @@
         <v>0.28629980563654</v>
       </c>
       <c r="AG26" s="41" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9930,7 +10035,7 @@
         <v>222</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>173</v>
@@ -9965,11 +10070,11 @@
       <c r="K27" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L27" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M27" s="42" t="s">
-        <v>259</v>
+      <c r="L27" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M27" s="42" t="n">
+        <v>35.98</v>
       </c>
       <c r="N27" s="11" t="n">
         <v>35.75</v>
@@ -10018,8 +10123,13 @@
         <f aca="false">Z27/1.1</f>
         <v>45.2545454545455</v>
       </c>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
+      <c r="AB27" s="11" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AC27" s="11" t="n">
+        <f aca="false">AB27/1.1</f>
+        <v>34.9545454545455</v>
+      </c>
       <c r="AD27" s="11" t="n">
         <f aca="false">IF(COUNT(I27,J27,M27,O27,Q27,S27,U27,V27,Y27,AA27,AC27)=0,"N/A",MIN(I27,J27,M27,O27,Q27,S27,U27,V27,Y27,AA27,AC27))</f>
         <v>21.2</v>
@@ -10033,7 +10143,7 @@
         <v>-0.432417452830189</v>
       </c>
       <c r="AG27" s="41" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10148,7 +10258,7 @@
         <v>0.0417076923076922</v>
       </c>
       <c r="AG28" s="41" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10265,7 +10375,7 @@
         <v>-0.247655555555555</v>
       </c>
       <c r="AG29" s="41" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10380,7 +10490,7 @@
         <v>N/A</v>
       </c>
       <c r="AG30" s="41" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10455,11 +10565,12 @@
         <f aca="false">T31/1.1</f>
         <v>42.8545454545455</v>
       </c>
-      <c r="V31" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W31" s="42" t="s">
-        <v>259</v>
+      <c r="V31" s="42" t="n">
+        <v>28</v>
+      </c>
+      <c r="W31" s="42" t="n">
+        <f aca="false">V31*1.1</f>
+        <v>30.8</v>
       </c>
       <c r="X31" s="11" t="n">
         <v>53.22</v>
@@ -10478,18 +10589,18 @@
       <c r="AC31" s="42"/>
       <c r="AD31" s="11" t="n">
         <f aca="false">IF(COUNT(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31)=0,"N/A",MIN(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31))</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AE31" s="43" t="n">
         <f aca="false">IF(OR(D31="",AD31="",AD31="N/A"),"N/A",D31/AD31-1)</f>
-        <v>-0.578387096774194</v>
+        <v>-0.533214285714286</v>
       </c>
       <c r="AF31" s="43" t="str">
         <f aca="false">IF(OR(F31="",AD31="",AD31="N/A"),"N/A",F31/AD31-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG31" s="41" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10604,7 +10715,7 @@
         <v>N/A</v>
       </c>
       <c r="AG32" s="41" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10654,11 +10765,12 @@
       <c r="M33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N33" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O33" s="42" t="s">
-        <v>259</v>
+      <c r="N33" s="42" t="n">
+        <v>51</v>
+      </c>
+      <c r="O33" s="42" t="n">
+        <f aca="false">N33/1.1</f>
+        <v>46.3636363636364</v>
       </c>
       <c r="P33" s="42" t="s">
         <v>259</v>
@@ -10680,11 +10792,12 @@
         <f aca="false">T33/1.1</f>
         <v>53.4909090909091</v>
       </c>
-      <c r="V33" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W33" s="42" t="s">
-        <v>259</v>
+      <c r="V33" s="42" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="W33" s="42" t="n">
+        <f aca="false">V33*1.1</f>
+        <v>56.65</v>
       </c>
       <c r="X33" s="11" t="n">
         <v>53.22</v>
@@ -10699,8 +10812,13 @@
       <c r="AA33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB33" s="42"/>
-      <c r="AC33" s="42"/>
+      <c r="AB33" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC33" s="42" t="n">
+        <f aca="false">AB33/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD33" s="11" t="n">
         <f aca="false">IF(COUNT(I33,J33,M33,O33,Q33,S33,U33,V33,Y33,AA33,AC33)=0,"N/A",MIN(I33,J33,M33,O33,Q33,S33,U33,V33,Y33,AA33,AC33))</f>
         <v>31</v>
@@ -10714,7 +10832,7 @@
         <v>N/A</v>
       </c>
       <c r="AG33" s="41" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10810,8 +10928,13 @@
       <c r="AA34" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB34" s="42"/>
-      <c r="AC34" s="42"/>
+      <c r="AB34" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC34" s="42" t="n">
+        <f aca="false">AB34/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD34" s="11" t="n">
         <f aca="false">IF(COUNT(I34,J34,M34,O34,Q34,S34,U34,V34,Y34,AA34,AC34)=0,"N/A",MIN(I34,J34,M34,O34,Q34,S34,U34,V34,Y34,AA34,AC34))</f>
         <v>31</v>
@@ -10825,7 +10948,7 @@
         <v>N/A</v>
       </c>
       <c r="AG34" s="41" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10941,7 +11064,7 @@
         <v>N/A</v>
       </c>
       <c r="AG35" s="41" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11058,7 +11181,7 @@
         <v>N/A</v>
       </c>
       <c r="AG36" s="41" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11152,8 +11275,13 @@
       <c r="AA37" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB37" s="42"/>
-      <c r="AC37" s="42"/>
+      <c r="AB37" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC37" s="42" t="n">
+        <f aca="false">AB37/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD37" s="11" t="n">
         <f aca="false">IF(COUNT(I37,J37,M37,O37,Q37,S37,U37,V37,Y37,AA37,AC37)=0,"N/A",MIN(I37,J37,M37,O37,Q37,S37,U37,V37,Y37,AA37,AC37))</f>
         <v>31</v>
@@ -11167,7 +11295,7 @@
         <v>N/A</v>
       </c>
       <c r="AG37" s="41" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11262,8 +11390,13 @@
       <c r="AA38" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB38" s="42"/>
-      <c r="AC38" s="42"/>
+      <c r="AB38" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC38" s="42" t="n">
+        <f aca="false">AB38/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD38" s="11" t="n">
         <f aca="false">IF(COUNT(I38,J38,M38,O38,Q38,S38,U38,V38,Y38,AA38,AC38)=0,"N/A",MIN(I38,J38,M38,O38,Q38,S38,U38,V38,Y38,AA38,AC38))</f>
         <v>31</v>
@@ -11277,7 +11410,7 @@
         <v>N/A</v>
       </c>
       <c r="AG38" s="41" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11373,8 +11506,13 @@
       <c r="AA39" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
+      <c r="AB39" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC39" s="42" t="n">
+        <f aca="false">AB39/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD39" s="11" t="n">
         <f aca="false">IF(COUNT(I39,J39,M39,O39,Q39,S39,U39,V39,Y39,AA39,AC39)=0,"N/A",MIN(I39,J39,M39,O39,Q39,S39,U39,V39,Y39,AA39,AC39))</f>
         <v>31</v>
@@ -11388,7 +11526,7 @@
         <v>N/A</v>
       </c>
       <c r="AG39" s="41" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11484,8 +11622,13 @@
       <c r="AA40" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB40" s="42"/>
-      <c r="AC40" s="42"/>
+      <c r="AB40" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC40" s="42" t="n">
+        <f aca="false">AB40/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD40" s="11" t="n">
         <f aca="false">IF(COUNT(I40,J40,M40,O40,Q40,S40,U40,V40,Y40,AA40,AC40)=0,"N/A",MIN(I40,J40,M40,O40,Q40,S40,U40,V40,Y40,AA40,AC40))</f>
         <v>31</v>
@@ -11499,7 +11642,7 @@
         <v>N/A</v>
       </c>
       <c r="AG40" s="41" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11595,8 +11738,13 @@
       <c r="AA41" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB41" s="42"/>
-      <c r="AC41" s="42"/>
+      <c r="AB41" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC41" s="42" t="n">
+        <f aca="false">AB41/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD41" s="11" t="n">
         <f aca="false">IF(COUNT(I41,J41,M41,O41,Q41,S41,U41,V41,Y41,AA41,AC41)=0,"N/A",MIN(I41,J41,M41,O41,Q41,S41,U41,V41,Y41,AA41,AC41))</f>
         <v>31</v>
@@ -11610,7 +11758,7 @@
         <v>N/A</v>
       </c>
       <c r="AG41" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11706,8 +11854,13 @@
       <c r="AA42" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB42" s="42"/>
-      <c r="AC42" s="42"/>
+      <c r="AB42" s="42" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AC42" s="42" t="n">
+        <f aca="false">AB42/1.1</f>
+        <v>37.1181818181818</v>
+      </c>
       <c r="AD42" s="11" t="n">
         <f aca="false">IF(COUNT(I42,J42,M42,O42,Q42,S42,U42,V42,Y42,AA42,AC42)=0,"N/A",MIN(I42,J42,M42,O42,Q42,S42,U42,V42,Y42,AA42,AC42))</f>
         <v>31</v>
@@ -11721,7 +11874,7 @@
         <v>N/A</v>
       </c>
       <c r="AG42" s="41" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11776,17 +11929,18 @@
       <c r="O43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P43" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q43" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R43" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S43" s="42" t="s">
-        <v>259</v>
+      <c r="P43" s="42" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="Q43" s="42" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="R43" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S43" s="42" t="n">
+        <f aca="false">R43/1.1</f>
+        <v>25</v>
       </c>
       <c r="T43" s="42" t="s">
         <v>259</v>
@@ -11800,11 +11954,12 @@
       <c r="W43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X43" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y43" s="42" t="s">
-        <v>259</v>
+      <c r="X43" s="42" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="Y43" s="42" t="n">
+        <f aca="false">X43/1.1</f>
+        <v>29.0545454545455</v>
       </c>
       <c r="Z43" s="42"/>
       <c r="AA43" s="42"/>
@@ -11817,18 +11972,18 @@
       </c>
       <c r="AD43" s="11" t="n">
         <f aca="false">IF(COUNT(I43,J43,M43,O43,Q43,S43,U43,V43,Y43,AA43,AC43)=0,"N/A",MIN(I43,J43,M43,O43,Q43,S43,U43,V43,Y43,AA43,AC43))</f>
-        <v>32.6363636363636</v>
+        <v>20.05</v>
       </c>
       <c r="AE43" s="43" t="n">
         <f aca="false">IF(OR(D43="",AD43="",AD43="N/A"),"N/A",D43/AD43-1)</f>
-        <v>-0.836072423398329</v>
+        <v>-0.733167082294264</v>
       </c>
       <c r="AF43" s="43" t="str">
         <f aca="false">IF(OR(F43="",AD43="",AD43="N/A"),"N/A",F43/AD43-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG43" s="41" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11890,11 +12045,12 @@
       <c r="Q44" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R44" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S44" s="42" t="s">
-        <v>259</v>
+      <c r="R44" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S44" s="42" t="n">
+        <f aca="false">R44/1.1</f>
+        <v>20.4545454545455</v>
       </c>
       <c r="T44" s="11" t="n">
         <v>21.12</v>
@@ -11923,8 +12079,13 @@
         <f aca="false">Z44/1.1</f>
         <v>29.7454545454545</v>
       </c>
-      <c r="AB44" s="11"/>
-      <c r="AC44" s="11"/>
+      <c r="AB44" s="11" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC44" s="11" t="n">
+        <f aca="false">AB44/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
       <c r="AD44" s="11" t="n">
         <f aca="false">IF(COUNT(I44,J44,M44,O44,Q44,S44,U44,V44,Y44,AA44,AC44)=0,"N/A",MIN(I44,J44,M44,O44,Q44,S44,U44,V44,Y44,AA44,AC44))</f>
         <v>9.35454545454545</v>
@@ -11938,7 +12099,7 @@
         <v>N/A</v>
       </c>
       <c r="AG44" s="41" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12020,11 +12181,12 @@
       <c r="W45" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="X45" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y45" s="42" t="s">
-        <v>259</v>
+      <c r="X45" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y45" s="42" t="n">
+        <f aca="false">X45/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z45" s="45" t="n">
         <f aca="false">AA45*1.1</f>
@@ -12033,8 +12195,13 @@
       <c r="AA45" s="45" t="n">
         <v>65.64</v>
       </c>
-      <c r="AB45" s="45"/>
-      <c r="AC45" s="45"/>
+      <c r="AB45" s="45" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AC45" s="45" t="n">
+        <f aca="false">AB45/1.1</f>
+        <v>38.8636363636364</v>
+      </c>
       <c r="AD45" s="11" t="n">
         <f aca="false">IF(COUNT(I45,J45,M45,O45,Q45,S45,U45,V45,Y45,AA45,AC45)=0,"N/A",MIN(I45,J45,M45,O45,Q45,S45,U45,V45,Y45,AA45,AC45))</f>
         <v>23.4090909090909</v>
@@ -12048,7 +12215,7 @@
         <v>N/A</v>
       </c>
       <c r="AG45" s="41" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12091,17 +12258,18 @@
       <c r="K46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L46" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M46" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N46" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O46" s="42" t="s">
-        <v>259</v>
+      <c r="L46" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M46" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N46" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O46" s="42" t="n">
+        <f aca="false">N46/1.1</f>
+        <v>25</v>
       </c>
       <c r="P46" s="42" t="s">
         <v>259</v>
@@ -12109,11 +12277,12 @@
       <c r="Q46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R46" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S46" s="42" t="s">
-        <v>259</v>
+      <c r="R46" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S46" s="42" t="n">
+        <f aca="false">R46/1.1</f>
+        <v>20.4545454545455</v>
       </c>
       <c r="T46" s="42" t="s">
         <v>259</v>
@@ -12127,11 +12296,12 @@
       <c r="W46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X46" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y46" s="42" t="s">
-        <v>259</v>
+      <c r="X46" s="42" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Y46" s="42" t="n">
+        <f aca="false">X46/1.1</f>
+        <v>22.6909090909091</v>
       </c>
       <c r="Z46" s="45" t="n">
         <f aca="false">AA46*1.1</f>
@@ -12149,18 +12319,18 @@
       </c>
       <c r="AD46" s="11" t="n">
         <f aca="false">IF(COUNT(I46,J46,M46,O46,Q46,S46,U46,V46,Y46,AA46,AC46)=0,"N/A",MIN(I46,J46,M46,O46,Q46,S46,U46,V46,Y46,AA46,AC46))</f>
-        <v>22.7181818181818</v>
+        <v>20.4545454545455</v>
       </c>
       <c r="AE46" s="43" t="n">
         <f aca="false">IF(OR(D46="",AD46="",AD46="N/A"),"N/A",D46/AD46-1)</f>
-        <v>-0.882472989195678</v>
+        <v>-0.869466666666667</v>
       </c>
       <c r="AF46" s="43" t="str">
         <f aca="false">IF(OR(F46="",AD46="",AD46="N/A"),"N/A",F46/AD46-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG46" s="41" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12203,47 +12373,52 @@
       <c r="K47" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="T47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="U47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="V47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="X47" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y47" s="42" t="s">
-        <v>259</v>
+      <c r="L47" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M47" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N47" s="42" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="O47" s="42" t="n">
+        <f aca="false">N47/1.1</f>
+        <v>38.6363636363636</v>
+      </c>
+      <c r="P47" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q47" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R47" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="S47" s="42" t="n">
+        <f aca="false">R47/1.1</f>
+        <v>27.2727272727273</v>
+      </c>
+      <c r="T47" s="42" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="U47" s="42" t="n">
+        <f aca="false">T47/1.1</f>
+        <v>26.0545454545455</v>
+      </c>
+      <c r="V47" s="42" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="W47" s="42" t="n">
+        <f aca="false">V47*1.1</f>
+        <v>40.15</v>
+      </c>
+      <c r="X47" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y47" s="42" t="n">
+        <f aca="false">X47/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z47" s="45" t="n">
         <f aca="false">AA47*1.1</f>
@@ -12261,18 +12436,18 @@
       </c>
       <c r="AD47" s="11" t="n">
         <f aca="false">IF(COUNT(I47,J47,M47,O47,Q47,S47,U47,V47,Y47,AA47,AC47)=0,"N/A",MIN(I47,J47,M47,O47,Q47,S47,U47,V47,Y47,AA47,AC47))</f>
-        <v>25.5818181818182</v>
+        <v>22</v>
       </c>
       <c r="AE47" s="43" t="n">
         <f aca="false">IF(OR(D47="",AD47="",AD47="N/A"),"N/A",D47/AD47-1)</f>
-        <v>-0.62864250177683</v>
+        <v>-0.568181818181818</v>
       </c>
       <c r="AF47" s="43" t="str">
         <f aca="false">IF(OR(F47="",AD47="",AD47="N/A"),"N/A",F47/AD47-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG47" s="41" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12315,41 +12490,45 @@
       <c r="K48" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="T48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="U48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="V48" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W48" s="42" t="s">
-        <v>259</v>
+      <c r="L48" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M48" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N48" s="42" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="O48" s="42" t="n">
+        <f aca="false">N48/1.1</f>
+        <v>38.6363636363636</v>
+      </c>
+      <c r="P48" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q48" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R48" s="42" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="S48" s="42" t="n">
+        <f aca="false">R48/1.1</f>
+        <v>30.4545454545455</v>
+      </c>
+      <c r="T48" s="42" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="U48" s="42" t="n">
+        <f aca="false">T48/1.1</f>
+        <v>16.7363636363636</v>
+      </c>
+      <c r="V48" s="42" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W48" s="42" t="n">
+        <f aca="false">V48*1.1</f>
+        <v>31.35</v>
       </c>
       <c r="X48" s="42" t="s">
         <v>259</v>
@@ -12364,22 +12543,27 @@
       <c r="AA48" s="45" t="n">
         <v>150.22</v>
       </c>
-      <c r="AB48" s="45"/>
-      <c r="AC48" s="45"/>
+      <c r="AB48" s="45" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="AC48" s="45" t="n">
+        <f aca="false">AB48/1.1</f>
+        <v>33.9</v>
+      </c>
       <c r="AD48" s="11" t="n">
         <f aca="false">IF(COUNT(I48,J48,M48,O48,Q48,S48,U48,V48,Y48,AA48,AC48)=0,"N/A",MIN(I48,J48,M48,O48,Q48,S48,U48,V48,Y48,AA48,AC48))</f>
-        <v>40.9</v>
+        <v>16.7363636363636</v>
       </c>
       <c r="AE48" s="43" t="n">
         <f aca="false">IF(OR(D48="",AD48="",AD48="N/A"),"N/A",D48/AD48-1)</f>
-        <v>-0.738630806845966</v>
+        <v>-0.361271048343292</v>
       </c>
       <c r="AF48" s="43" t="str">
         <f aca="false">IF(OR(F48="",AD48="",AD48="N/A"),"N/A",F48/AD48-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG48" s="41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12428,17 +12612,18 @@
       <c r="M49" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N49" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O49" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P49" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q49" s="42" t="s">
-        <v>259</v>
+      <c r="N49" s="42" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O49" s="42" t="n">
+        <f aca="false">N49/1.1</f>
+        <v>32.1818181818182</v>
+      </c>
+      <c r="P49" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q49" s="42" t="n">
+        <v>22</v>
       </c>
       <c r="R49" s="11" t="n">
         <v>23</v>
@@ -12461,11 +12646,12 @@
       <c r="W49" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X49" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y49" s="42" t="s">
-        <v>259</v>
+      <c r="X49" s="42" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="Y49" s="42" t="n">
+        <f aca="false">X49/1.1</f>
+        <v>29.0545454545455</v>
       </c>
       <c r="Z49" s="45" t="n">
         <f aca="false">AA49*1.1</f>
@@ -12494,7 +12680,7 @@
         <v>N/A</v>
       </c>
       <c r="AG49" s="41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12591,8 +12777,13 @@
       <c r="AA50" s="45" t="n">
         <v>57.92</v>
       </c>
-      <c r="AB50" s="45"/>
-      <c r="AC50" s="45"/>
+      <c r="AB50" s="45" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AC50" s="45" t="n">
+        <f aca="false">AB50/1.1</f>
+        <v>32.6363636363636</v>
+      </c>
       <c r="AD50" s="11" t="n">
         <f aca="false">IF(COUNT(I50,J50,M50,O50,Q50,S50,U50,V50,Y50,AA50,AC50)=0,"N/A",MIN(I50,J50,M50,O50,Q50,S50,U50,V50,Y50,AA50,AC50))</f>
         <v>9.35454545454545</v>
@@ -12606,7 +12797,7 @@
         <v>N/A</v>
       </c>
       <c r="AG50" s="41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12649,41 +12840,45 @@
       <c r="K51" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="T51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="U51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="V51" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W51" s="42" t="s">
-        <v>259</v>
+      <c r="L51" s="42" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="M51" s="42" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="N51" s="42" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="O51" s="42" t="n">
+        <f aca="false">N51/1.1</f>
+        <v>25.7272727272727</v>
+      </c>
+      <c r="P51" s="42" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="Q51" s="42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R51" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S51" s="42" t="n">
+        <f aca="false">R51/1.1</f>
+        <v>20.4545454545455</v>
+      </c>
+      <c r="T51" s="42" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="U51" s="42" t="n">
+        <f aca="false">T51/1.1</f>
+        <v>30.0363636363636</v>
+      </c>
+      <c r="V51" s="42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W51" s="42" t="n">
+        <f aca="false">V51*1.1</f>
+        <v>21.45</v>
       </c>
       <c r="X51" s="42" t="s">
         <v>259</v>
@@ -12698,22 +12893,27 @@
       <c r="AA51" s="45" t="n">
         <v>57.92</v>
       </c>
-      <c r="AB51" s="45"/>
-      <c r="AC51" s="45"/>
+      <c r="AB51" s="45" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC51" s="45" t="n">
+        <f aca="false">AB51/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
       <c r="AD51" s="11" t="n">
         <f aca="false">IF(COUNT(I51,J51,M51,O51,Q51,S51,U51,V51,Y51,AA51,AC51)=0,"N/A",MIN(I51,J51,M51,O51,Q51,S51,U51,V51,Y51,AA51,AC51))</f>
-        <v>25.4454545454545</v>
+        <v>10.5</v>
       </c>
       <c r="AE51" s="43" t="n">
         <f aca="false">IF(OR(D51="",AD51="",AD51="N/A"),"N/A",D51/AD51-1)</f>
-        <v>-0.895069667738478</v>
+        <v>-0.745714285714286</v>
       </c>
       <c r="AF51" s="43" t="str">
         <f aca="false">IF(OR(F51="",AD51="",AD51="N/A"),"N/A",F51/AD51-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG51" s="41" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12756,29 +12956,31 @@
       <c r="K52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S52" s="42" t="s">
-        <v>259</v>
+      <c r="L52" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M52" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N52" s="42" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="O52" s="42" t="n">
+        <f aca="false">N52/1.1</f>
+        <v>38.6363636363636</v>
+      </c>
+      <c r="P52" s="42" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="Q52" s="42" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="R52" s="42" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="S52" s="42" t="n">
+        <f aca="false">R52/1.1</f>
+        <v>30.4545454545455</v>
       </c>
       <c r="T52" s="42" t="s">
         <v>259</v>
@@ -12786,17 +12988,19 @@
       <c r="U52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="W52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="X52" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y52" s="42" t="s">
-        <v>259</v>
+      <c r="V52" s="42" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="W52" s="42" t="n">
+        <f aca="false">V52*1.1</f>
+        <v>29.15</v>
+      </c>
+      <c r="X52" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y52" s="42" t="n">
+        <f aca="false">X52/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z52" s="45" t="n">
         <f aca="false">AA52*1.1</f>
@@ -12809,18 +13013,18 @@
       <c r="AC52" s="45"/>
       <c r="AD52" s="11" t="n">
         <f aca="false">IF(COUNT(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52)=0,"N/A",MIN(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52))</f>
-        <v>40.9</v>
+        <v>26.5</v>
       </c>
       <c r="AE52" s="43" t="n">
         <f aca="false">IF(OR(D52="",AD52="",AD52="N/A"),"N/A",D52/AD52-1)</f>
-        <v>-0.767726161369193</v>
+        <v>-0.641509433962264</v>
       </c>
       <c r="AF52" s="43" t="str">
         <f aca="false">IF(OR(F52="",AD52="",AD52="N/A"),"N/A",F52/AD52-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG52" s="41" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12931,7 +13135,7 @@
         <v>N/A</v>
       </c>
       <c r="AG53" s="41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12974,17 +13178,18 @@
       <c r="K54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L54" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M54" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N54" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O54" s="42" t="s">
-        <v>259</v>
+      <c r="L54" s="42" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="M54" s="42" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="N54" s="42" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="O54" s="42" t="n">
+        <f aca="false">N54/1.1</f>
+        <v>25.7272727272727</v>
       </c>
       <c r="P54" s="42" t="s">
         <v>259</v>
@@ -12992,11 +13197,12 @@
       <c r="Q54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R54" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S54" s="42" t="s">
-        <v>259</v>
+      <c r="R54" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S54" s="42" t="n">
+        <f aca="false">R54/1.1</f>
+        <v>20.4545454545455</v>
       </c>
       <c r="T54" s="42" t="s">
         <v>259</v>
@@ -13010,11 +13216,12 @@
       <c r="W54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X54" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y54" s="42" t="s">
-        <v>259</v>
+      <c r="X54" s="42" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Y54" s="42" t="n">
+        <f aca="false">X54/1.1</f>
+        <v>22.6909090909091</v>
       </c>
       <c r="Z54" s="45" t="n">
         <f aca="false">1.1*AA54</f>
@@ -13023,22 +13230,27 @@
       <c r="AA54" s="45" t="n">
         <v>51.27</v>
       </c>
-      <c r="AB54" s="45"/>
-      <c r="AC54" s="45"/>
+      <c r="AB54" s="45" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC54" s="45" t="n">
+        <f aca="false">AB54/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
       <c r="AD54" s="11" t="n">
         <f aca="false">IF(COUNT(I54,J54,M54,O54,Q54,S54,U54,V54,Y54,AA54,AC54)=0,"N/A",MIN(I54,J54,M54,O54,Q54,S54,U54,V54,Y54,AA54,AC54))</f>
-        <v>29.9909090909091</v>
+        <v>20.4545454545455</v>
       </c>
       <c r="AE54" s="43" t="n">
         <f aca="false">IF(OR(D54="",AD54="",AD54="N/A"),"N/A",D54/AD54-1)</f>
-        <v>-0.910973022127918</v>
+        <v>-0.869466666666667</v>
       </c>
       <c r="AF54" s="43" t="str">
         <f aca="false">IF(OR(F54="",AD54="",AD54="N/A"),"N/A",F54/AD54-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG54" s="41" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13099,11 +13311,12 @@
       <c r="Q55" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R55" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S55" s="42" t="s">
-        <v>259</v>
+      <c r="R55" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="S55" s="42" t="n">
+        <f aca="false">R55/1.1</f>
+        <v>20.9090909090909</v>
       </c>
       <c r="T55" s="42" t="s">
         <v>259</v>
@@ -13127,24 +13340,24 @@
         <v>259</v>
       </c>
       <c r="AA55" s="42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AB55" s="42"/>
       <c r="AC55" s="42"/>
       <c r="AD55" s="11" t="n">
         <f aca="false">IF(COUNT(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55)=0,"N/A",MIN(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55))</f>
-        <v>34.5363636363636</v>
+        <v>20.9090909090909</v>
       </c>
       <c r="AE55" s="43" t="n">
         <f aca="false">IF(OR(D55="",AD55="",AD55="N/A"),"N/A",D55/AD55-1)</f>
-        <v>-0.883890497499342</v>
+        <v>-0.808217391304348</v>
       </c>
       <c r="AF55" s="43" t="str">
         <f aca="false">IF(OR(F55="",AD55="",AD55="N/A"),"N/A",F55/AD55-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG55" s="41" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13199,17 +13412,18 @@
       <c r="O56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P56" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q56" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R56" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S56" s="42" t="s">
-        <v>259</v>
+      <c r="P56" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q56" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R56" s="42" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="S56" s="42" t="n">
+        <f aca="false">R56/1.1</f>
+        <v>30.4545454545455</v>
       </c>
       <c r="T56" s="42" t="s">
         <v>259</v>
@@ -13223,11 +13437,12 @@
       <c r="W56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X56" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y56" s="42" t="s">
-        <v>259</v>
+      <c r="X56" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y56" s="42" t="n">
+        <f aca="false">X56/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z56" s="42" t="s">
         <v>259</v>
@@ -13239,18 +13454,18 @@
       <c r="AC56" s="42"/>
       <c r="AD56" s="11" t="n">
         <f aca="false">IF(COUNT(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56)=0,"N/A",MIN(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56))</f>
-        <v>34.5363636363636</v>
+        <v>22</v>
       </c>
       <c r="AE56" s="43" t="n">
         <f aca="false">IF(OR(D56="",AD56="",AD56="N/A"),"N/A",D56/AD56-1)</f>
-        <v>-0.690471176625428</v>
+        <v>-0.514090909090909</v>
       </c>
       <c r="AF56" s="43" t="str">
         <f aca="false">IF(OR(F56="",AD56="",AD56="N/A"),"N/A",F56/AD56-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG56" s="41" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13293,11 +13508,11 @@
       <c r="K57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L57" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M57" s="42" t="s">
-        <v>259</v>
+      <c r="L57" s="42" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="M57" s="42" t="n">
+        <v>35.88</v>
       </c>
       <c r="N57" s="42" t="s">
         <v>259</v>
@@ -13311,11 +13526,12 @@
       <c r="Q57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R57" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S57" s="42" t="s">
-        <v>259</v>
+      <c r="R57" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="S57" s="42" t="n">
+        <f aca="false">R57/1.1</f>
+        <v>27.2727272727273</v>
       </c>
       <c r="T57" s="42" t="s">
         <v>259</v>
@@ -13329,11 +13545,12 @@
       <c r="W57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X57" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y57" s="42" t="s">
-        <v>259</v>
+      <c r="X57" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y57" s="42" t="n">
+        <f aca="false">X57/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z57" s="45" t="n">
         <f aca="false">1.1*AA57</f>
@@ -13342,22 +13559,27 @@
       <c r="AA57" s="45" t="n">
         <v>70.25</v>
       </c>
-      <c r="AB57" s="45"/>
-      <c r="AC57" s="45"/>
+      <c r="AB57" s="45" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AC57" s="45" t="n">
+        <f aca="false">AB57/1.1</f>
+        <v>38.8636363636364</v>
+      </c>
       <c r="AD57" s="11" t="n">
         <f aca="false">IF(COUNT(I57,J57,M57,O57,Q57,S57,U57,V57,Y57,AA57,AC57)=0,"N/A",MIN(I57,J57,M57,O57,Q57,S57,U57,V57,Y57,AA57,AC57))</f>
-        <v>34.5363636363636</v>
+        <v>27.2727272727273</v>
       </c>
       <c r="AE57" s="43" t="n">
         <f aca="false">IF(OR(D57="",AD57="",AD57="N/A"),"N/A",D57/AD57-1)</f>
-        <v>-0.690471176625428</v>
+        <v>-0.608033333333333</v>
       </c>
       <c r="AF57" s="43" t="str">
         <f aca="false">IF(OR(F57="",AD57="",AD57="N/A"),"N/A",F57/AD57-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG57" s="41" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13406,23 +13628,25 @@
       <c r="M58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S58" s="42" t="s">
-        <v>259</v>
+      <c r="N58" s="42" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="O58" s="42" t="n">
+        <f aca="false">N58/1.1</f>
+        <v>38.6363636363636</v>
+      </c>
+      <c r="P58" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q58" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R58" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="S58" s="42" t="n">
+        <f aca="false">R58/1.1</f>
+        <v>27.2727272727273</v>
       </c>
       <c r="T58" s="42" t="s">
         <v>259</v>
@@ -13436,11 +13660,12 @@
       <c r="W58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X58" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y58" s="42" t="s">
-        <v>259</v>
+      <c r="X58" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y58" s="42" t="n">
+        <f aca="false">X58/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z58" s="45" t="n">
         <f aca="false">1.1*AA58</f>
@@ -13458,18 +13683,18 @@
       </c>
       <c r="AD58" s="11" t="n">
         <f aca="false">IF(COUNT(I58,J58,M58,O58,Q58,S58,U58,V58,Y58,AA58,AC58)=0,"N/A",MIN(I58,J58,M58,O58,Q58,S58,U58,V58,Y58,AA58,AC58))</f>
-        <v>38.8636363636364</v>
+        <v>22</v>
       </c>
       <c r="AE58" s="43" t="n">
         <f aca="false">IF(OR(D58="",AD58="",AD58="N/A"),"N/A",D58/AD58-1)</f>
-        <v>-0.72493567251462</v>
+        <v>-0.514090909090909</v>
       </c>
       <c r="AF58" s="43" t="str">
         <f aca="false">IF(OR(F58="",AD58="",AD58="N/A"),"N/A",F58/AD58-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG58" s="41" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13518,11 +13743,12 @@
       <c r="M59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N59" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O59" s="42" t="s">
-        <v>259</v>
+      <c r="N59" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O59" s="42" t="n">
+        <f aca="false">N59/1.1</f>
+        <v>25</v>
       </c>
       <c r="P59" s="42" t="s">
         <v>259</v>
@@ -13530,11 +13756,12 @@
       <c r="Q59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R59" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S59" s="42" t="s">
-        <v>259</v>
+      <c r="R59" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="S59" s="42" t="n">
+        <f aca="false">R59/1.1</f>
+        <v>20</v>
       </c>
       <c r="T59" s="42" t="s">
         <v>259</v>
@@ -13561,22 +13788,27 @@
       <c r="AA59" s="45" t="n">
         <v>47.44</v>
       </c>
-      <c r="AB59" s="45"/>
-      <c r="AC59" s="45"/>
+      <c r="AB59" s="45" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="AC59" s="45" t="n">
+        <f aca="false">AB59/1.1</f>
+        <v>33.7636363636364</v>
+      </c>
       <c r="AD59" s="11" t="n">
         <f aca="false">IF(COUNT(I59,J59,M59,O59,Q59,S59,U59,V59,Y59,AA59,AC59)=0,"N/A",MIN(I59,J59,M59,O59,Q59,S59,U59,V59,Y59,AA59,AC59))</f>
-        <v>29.9909090909091</v>
+        <v>20</v>
       </c>
       <c r="AE59" s="43" t="n">
         <f aca="false">IF(OR(D59="",AD59="",AD59="N/A"),"N/A",D59/AD59-1)</f>
-        <v>-0.903637465898757</v>
+        <v>-0.8555</v>
       </c>
       <c r="AF59" s="43" t="str">
         <f aca="false">IF(OR(F59="",AD59="",AD59="N/A"),"N/A",F59/AD59-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG59" s="41" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13655,11 +13887,12 @@
       <c r="W60" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X60" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y60" s="42" t="s">
-        <v>259</v>
+      <c r="X60" s="42" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="Y60" s="42" t="n">
+        <f aca="false">X60/1.1</f>
+        <v>37.6363636363636</v>
       </c>
       <c r="Z60" s="45" t="n">
         <f aca="false">1.1*AA60</f>
@@ -13668,22 +13901,27 @@
       <c r="AA60" s="45" t="n">
         <v>83.86</v>
       </c>
-      <c r="AB60" s="45"/>
-      <c r="AC60" s="45"/>
+      <c r="AB60" s="45" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="AC60" s="45" t="n">
+        <f aca="false">AB60/1.1</f>
+        <v>49.2636363636364</v>
+      </c>
       <c r="AD60" s="11" t="n">
         <f aca="false">IF(COUNT(I60,J60,M60,O60,Q60,S60,U60,V60,Y60,AA60,AC60)=0,"N/A",MIN(I60,J60,M60,O60,Q60,S60,U60,V60,Y60,AA60,AC60))</f>
-        <v>45.4454545454545</v>
+        <v>37.6363636363636</v>
       </c>
       <c r="AE60" s="43" t="n">
         <f aca="false">IF(OR(D60="",AD60="",AD60="N/A"),"N/A",D60/AD60-1)</f>
-        <v>-0.957311462292458</v>
+        <v>-0.948454106280193</v>
       </c>
       <c r="AF60" s="43" t="str">
         <f aca="false">IF(OR(F60="",AD60="",AD60="N/A"),"N/A",F60/AD60-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG60" s="41" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13726,17 +13964,18 @@
       <c r="K61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L61" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M61" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N61" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O61" s="42" t="s">
-        <v>259</v>
+      <c r="L61" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M61" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N61" s="42" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="O61" s="42" t="n">
+        <f aca="false">N61/1.1</f>
+        <v>38.6363636363636</v>
       </c>
       <c r="P61" s="42" t="s">
         <v>259</v>
@@ -13744,11 +13983,12 @@
       <c r="Q61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R61" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S61" s="42" t="s">
-        <v>259</v>
+      <c r="R61" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="S61" s="42" t="n">
+        <f aca="false">R61/1.1</f>
+        <v>27.2727272727273</v>
       </c>
       <c r="T61" s="42" t="s">
         <v>259</v>
@@ -13762,11 +14002,12 @@
       <c r="W61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X61" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y61" s="42" t="s">
-        <v>259</v>
+      <c r="X61" s="42" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="Y61" s="42" t="n">
+        <f aca="false">X61/1.1</f>
+        <v>41.6</v>
       </c>
       <c r="Z61" s="45" t="n">
         <f aca="false">1.1*AA61</f>
@@ -13775,22 +14016,27 @@
       <c r="AA61" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB61" s="45"/>
-      <c r="AC61" s="45"/>
+      <c r="AB61" s="45" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AC61" s="45" t="n">
+        <f aca="false">AB61/1.1</f>
+        <v>38.8636363636364</v>
+      </c>
       <c r="AD61" s="11" t="n">
         <f aca="false">IF(COUNT(I61,J61,M61,O61,Q61,S61,U61,V61,Y61,AA61,AC61)=0,"N/A",MIN(I61,J61,M61,O61,Q61,S61,U61,V61,Y61,AA61,AC61))</f>
-        <v>43.55</v>
+        <v>27.2727272727273</v>
       </c>
       <c r="AE61" s="43" t="n">
         <f aca="false">IF(OR(D61="",AD61="",AD61="N/A"),"N/A",D61/AD61-1)</f>
-        <v>-0.754535017221584</v>
+        <v>-0.608033333333333</v>
       </c>
       <c r="AF61" s="43" t="str">
         <f aca="false">IF(OR(F61="",AD61="",AD61="N/A"),"N/A",F61/AD61-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG61" s="41" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13833,29 +14079,31 @@
       <c r="K62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S62" s="42" t="s">
-        <v>259</v>
+      <c r="L62" s="42" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="M62" s="42" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="N62" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O62" s="42" t="n">
+        <f aca="false">N62/1.1</f>
+        <v>25</v>
+      </c>
+      <c r="P62" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q62" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R62" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S62" s="42" t="n">
+        <f aca="false">R62/1.1</f>
+        <v>20.4545454545455</v>
       </c>
       <c r="T62" s="42" t="s">
         <v>259</v>
@@ -13869,11 +14117,12 @@
       <c r="W62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y62" s="42" t="s">
-        <v>259</v>
+      <c r="X62" s="42" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Y62" s="42" t="n">
+        <f aca="false">X62/1.1</f>
+        <v>22.6909090909091</v>
       </c>
       <c r="Z62" s="45" t="n">
         <f aca="false">1.1*AA62</f>
@@ -13882,22 +14131,27 @@
       <c r="AA62" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB62" s="45"/>
-      <c r="AC62" s="45"/>
+      <c r="AB62" s="45" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AC62" s="45" t="n">
+        <f aca="false">AB62/1.1</f>
+        <v>27.9727272727273</v>
+      </c>
       <c r="AD62" s="11" t="n">
         <f aca="false">IF(COUNT(I62,J62,M62,O62,Q62,S62,U62,V62,Y62,AA62,AC62)=0,"N/A",MIN(I62,J62,M62,O62,Q62,S62,U62,V62,Y62,AA62,AC62))</f>
-        <v>29.9909090909091</v>
+        <v>20.4545454545455</v>
       </c>
       <c r="AE62" s="43" t="n">
         <f aca="false">IF(OR(D62="",AD62="",AD62="N/A"),"N/A",D62/AD62-1)</f>
-        <v>-0.893267656865717</v>
+        <v>-0.843506666666667</v>
       </c>
       <c r="AF62" s="43" t="str">
         <f aca="false">IF(OR(F62="",AD62="",AD62="N/A"),"N/A",F62/AD62-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG62" s="41" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13940,11 +14194,11 @@
       <c r="K63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L63" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M63" s="42" t="s">
-        <v>259</v>
+      <c r="L63" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M63" s="42" t="n">
+        <v>35.98</v>
       </c>
       <c r="N63" s="42" t="s">
         <v>259</v>
@@ -13952,17 +14206,18 @@
       <c r="O63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P63" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q63" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R63" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S63" s="42" t="s">
-        <v>259</v>
+      <c r="P63" s="42" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q63" s="42" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="R63" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="S63" s="42" t="n">
+        <f aca="false">R63/1.1</f>
+        <v>20.9090909090909</v>
       </c>
       <c r="T63" s="42" t="s">
         <v>259</v>
@@ -13976,11 +14231,12 @@
       <c r="W63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X63" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y63" s="42" t="s">
-        <v>259</v>
+      <c r="X63" s="42" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="Y63" s="42" t="n">
+        <f aca="false">X63/1.1</f>
+        <v>29.0545454545455</v>
       </c>
       <c r="Z63" s="45" t="n">
         <f aca="false">1.1*AA63</f>
@@ -13989,22 +14245,27 @@
       <c r="AA63" s="45" t="n">
         <v>43.55</v>
       </c>
-      <c r="AB63" s="45"/>
-      <c r="AC63" s="45"/>
+      <c r="AB63" s="45" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="AC63" s="45" t="n">
+        <f aca="false">AB63/1.1</f>
+        <v>35.6090909090909</v>
+      </c>
       <c r="AD63" s="11" t="n">
         <f aca="false">IF(COUNT(I63,J63,M63,O63,Q63,S63,U63,V63,Y63,AA63,AC63)=0,"N/A",MIN(I63,J63,M63,O63,Q63,S63,U63,V63,Y63,AA63,AC63))</f>
-        <v>29.9909090909091</v>
+        <v>20.55</v>
       </c>
       <c r="AE63" s="43" t="n">
         <f aca="false">IF(OR(D63="",AD63="",AD63="N/A"),"N/A",D63/AD63-1)</f>
-        <v>-0.821612609881782</v>
+        <v>-0.739659367396594</v>
       </c>
       <c r="AF63" s="43" t="str">
         <f aca="false">IF(OR(F63="",AD63="",AD63="N/A"),"N/A",F63/AD63-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG63" s="41" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14047,29 +14308,31 @@
       <c r="K64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="N64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="O64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="P64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="R64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="S64" s="42" t="s">
-        <v>259</v>
+      <c r="L64" s="42" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="M64" s="42" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="N64" s="42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O64" s="42" t="n">
+        <f aca="false">N64/1.1</f>
+        <v>25</v>
+      </c>
+      <c r="P64" s="42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q64" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R64" s="42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S64" s="42" t="n">
+        <f aca="false">R64/1.1</f>
+        <v>20.4545454545455</v>
       </c>
       <c r="T64" s="42" t="s">
         <v>259</v>
@@ -14083,11 +14346,12 @@
       <c r="W64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X64" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y64" s="42" t="s">
-        <v>259</v>
+      <c r="X64" s="42" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Y64" s="42" t="n">
+        <f aca="false">X64/1.1</f>
+        <v>22.6909090909091</v>
       </c>
       <c r="Z64" s="45" t="n">
         <f aca="false">1.1*AA64</f>
@@ -14105,18 +14369,18 @@
       </c>
       <c r="AD64" s="11" t="n">
         <f aca="false">IF(COUNT(I64,J64,M64,O64,Q64,S64,U64,V64,Y64,AA64,AC64)=0,"N/A",MIN(I64,J64,M64,O64,Q64,S64,U64,V64,Y64,AA64,AC64))</f>
-        <v>27.9727272727273</v>
+        <v>20.4545454545455</v>
       </c>
       <c r="AE64" s="43" t="n">
         <f aca="false">IF(OR(D64="",AD64="",AD64="N/A"),"N/A",D64/AD64-1)</f>
-        <v>-0.904549886252844</v>
+        <v>-0.869466666666667</v>
       </c>
       <c r="AF64" s="43" t="str">
         <f aca="false">IF(OR(F64="",AD64="",AD64="N/A"),"N/A",F64/AD64-1)</f>
         <v>N/A</v>
       </c>
       <c r="AG64" s="41" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14159,11 +14423,11 @@
       <c r="K65" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L65" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="M65" s="42" t="s">
-        <v>259</v>
+      <c r="L65" s="42" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="M65" s="42" t="n">
+        <v>35.88</v>
       </c>
       <c r="N65" s="11" t="n">
         <v>108.6</v>
@@ -14233,7 +14497,7 @@
         <v>N/A</v>
       </c>
       <c r="AG65" s="41" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14243,7 +14507,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="35" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
@@ -14254,18 +14518,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="35" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="n">
         <f aca="false">COUNTIF(J6:J65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(V6:V65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")+COUNTIF(AC6:AC65,"&gt;0")</f>
-        <v>270</v>
+        <v>407</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="35" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
@@ -14276,7 +14540,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="35" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
@@ -14287,29 +14551,29 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="35" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
       <c r="D72" s="47" t="n">
         <f aca="false">AVERAGE(AE6:AE65)</f>
-        <v>-0.50174623185189</v>
+        <v>-0.454866678565887</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="35" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
       <c r="D73" s="47" t="n">
         <f aca="false">MEDIAN(AE6:AE65)</f>
-        <v>-0.578387096774194</v>
+        <v>-0.523652597402597</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="35" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
@@ -14320,7 +14584,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="35" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -14331,24 +14595,24 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="35" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
       <c r="D76" s="47" t="n">
         <f aca="false">AVERAGE(AF6:AF65)</f>
-        <v>-0.183078981462734</v>
+        <v>-0.137849955170021</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="35" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
       <c r="D77" s="47" t="n">
         <f aca="false">MEDIAN(AF6:AF65)</f>
-        <v>-0.260605761397123</v>
+        <v>-0.240924975181021</v>
       </c>
     </row>
   </sheetData>
@@ -14385,21 +14649,21 @@
   <dimension ref="A1:J74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -14413,7 +14677,7 @@
     </row>
     <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B2" s="49"/>
       <c r="C2" s="49"/>
@@ -14436,1840 +14700,1786 @@
         <v>1</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E4" s="50" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="G4" s="50" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H4" s="50" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="I4" s="50" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="J4" s="50" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="s">
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="E5" s="52" t="n">
+      <c r="D5" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="51" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G5" s="54" t="n">
+      <c r="G5" s="52" t="n">
         <v>-3.11725</v>
       </c>
-      <c r="H5" s="55" t="n">
+      <c r="H5" s="53" t="n">
         <v>-0.155473815461347</v>
       </c>
-      <c r="I5" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J5" s="51"/>
-    </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
+      <c r="I5" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E6" s="52" t="n">
+      <c r="D6" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>122.718181818182</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="54" t="n">
         <v>66.83</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="52" t="n">
         <v>-55.888181818182</v>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="53" t="n">
         <v>-0.455418919919995</v>
       </c>
-      <c r="I6" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J6" s="51"/>
-    </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
+      <c r="I6" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="E7" s="52" t="n">
+      <c r="D7" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>128.75</v>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="54" t="n">
         <v>44.55</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="52" t="n">
         <v>-84.2</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="53" t="n">
         <v>-0.653980582524272</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J7" s="51"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="s">
+      <c r="I7" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="E8" s="52" t="n">
+      <c r="D8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="11" t="n">
         <v>69.245</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="51" t="n">
         <v>45.144</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="52" t="n">
         <v>-24.101</v>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="53" t="n">
         <v>-0.348054011119937</v>
       </c>
-      <c r="I8" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J8" s="51"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
+      <c r="I8" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="E9" s="52" t="n">
+      <c r="D9" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>81.4</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="51" t="n">
         <v>70.538125</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="52" t="n">
         <v>-10.861875</v>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="53" t="n">
         <v>-0.133438267813268</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J9" s="51"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
+      <c r="I9" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="E10" s="52" t="n">
+      <c r="D10" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>44.209</v>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="51" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G10" s="54" t="n">
+      <c r="G10" s="52" t="n">
         <v>-10.3535</v>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="53" t="n">
         <v>-0.234194394806487</v>
       </c>
-      <c r="I10" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J10" s="51"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
+      <c r="I10" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="D11" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>70.36</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="51" t="n">
         <v>45.144</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="52" t="n">
         <v>-25.216</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="53" t="n">
         <v>-0.358385446276293</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J11" s="51"/>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="57" t="s">
+      <c r="I11" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="57" t="s">
-        <v>332</v>
-      </c>
-      <c r="E12" s="59" t="n">
+      <c r="D12" s="55" t="s">
+        <v>345</v>
+      </c>
+      <c r="E12" s="57" t="n">
         <v>33.1818181818182</v>
       </c>
-      <c r="F12" s="60" t="n">
+      <c r="F12" s="58" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="59" t="n">
         <v>0.673681818181798</v>
       </c>
-      <c r="H12" s="62" t="n">
+      <c r="H12" s="60" t="n">
         <v>0.0203027397260268</v>
       </c>
-      <c r="I12" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="s">
+      <c r="I12" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="E13" s="52" t="n">
+      <c r="D13" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>43.09</v>
       </c>
-      <c r="F13" s="53" t="n">
+      <c r="F13" s="51" t="n">
         <v>25.394125</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G13" s="52" t="n">
         <v>-17.695875</v>
       </c>
-      <c r="H13" s="55" t="n">
+      <c r="H13" s="53" t="n">
         <v>-0.410672429798097</v>
       </c>
-      <c r="I13" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J13" s="51"/>
-    </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
+      <c r="I13" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E14" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F14" s="53" t="n">
+      <c r="D14" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="51" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G14" s="54" t="n">
-        <v>-21.5295340909091</v>
-      </c>
-      <c r="H14" s="55" t="n">
-        <v>-0.717868672324947</v>
-      </c>
-      <c r="I14" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J14" s="51"/>
-    </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="s">
+      <c r="G14" s="52" t="n">
+        <v>-13.538625</v>
+      </c>
+      <c r="H14" s="53" t="n">
+        <v>-0.615392045454545</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E15" s="52" t="n">
-        <v>34.9545454545455</v>
-      </c>
-      <c r="F15" s="53" t="n">
+      <c r="D15" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F15" s="51" t="n">
         <v>15.81275</v>
       </c>
-      <c r="G15" s="54" t="n">
-        <v>-19.1417954545455</v>
-      </c>
-      <c r="H15" s="55" t="n">
-        <v>-0.547619635890768</v>
-      </c>
-      <c r="I15" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="s">
+      <c r="G15" s="52" t="n">
+        <v>-6.08725</v>
+      </c>
+      <c r="H15" s="53" t="n">
+        <v>-0.277956621004566</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F16" s="53" t="n">
+      <c r="D16" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F16" s="51" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G16" s="54" t="n">
-        <v>-21.5295340909091</v>
-      </c>
-      <c r="H16" s="55" t="n">
-        <v>-0.717868672324947</v>
-      </c>
-      <c r="I16" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
+      <c r="G16" s="52" t="n">
+        <v>-2.038625</v>
+      </c>
+      <c r="H16" s="53" t="n">
+        <v>-0.194154761904762</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="E17" s="52" t="n">
+      <c r="D17" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>37.3909090909091</v>
       </c>
-      <c r="F17" s="53" t="n">
+      <c r="F17" s="51" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G17" s="54" t="n">
+      <c r="G17" s="52" t="n">
         <v>-7.2454090909091</v>
       </c>
-      <c r="H17" s="55" t="n">
+      <c r="H17" s="53" t="n">
         <v>-0.193774617067834</v>
       </c>
-      <c r="I17" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57" t="s">
+      <c r="I17" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="E18" s="59" t="n">
+      <c r="D18" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="E18" s="57" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="F18" s="60" t="n">
+      <c r="F18" s="58" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G18" s="61" t="n">
+      <c r="G18" s="59" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="H18" s="62" t="n">
+      <c r="H18" s="60" t="n">
         <v>0.0631628727156122</v>
       </c>
-      <c r="I18" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J18" s="57"/>
-    </row>
-    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="s">
+      <c r="I18" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J18" s="55"/>
+    </row>
+    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C19" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="E19" s="52" t="n">
+      <c r="D19" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>23.3090909090909</v>
       </c>
-      <c r="F19" s="53" t="n">
+      <c r="F19" s="51" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G19" s="54" t="n">
+      <c r="G19" s="52" t="n">
         <v>-6.3763409090909</v>
       </c>
-      <c r="H19" s="55" t="n">
+      <c r="H19" s="53" t="n">
         <v>-0.273555967238689</v>
       </c>
-      <c r="I19" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J19" s="51"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="57" t="s">
+      <c r="I19" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="57" t="s">
-        <v>336</v>
-      </c>
-      <c r="E20" s="59" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="F20" s="60" t="n">
+      <c r="D20" s="55" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="57" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F20" s="58" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G20" s="61" t="n">
-        <v>4.8655</v>
-      </c>
-      <c r="H20" s="62" t="n">
-        <v>0.167833735770956</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J20" s="57"/>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="s">
+      <c r="G20" s="59" t="n">
+        <v>0.155499999999996</v>
+      </c>
+      <c r="H20" s="60" t="n">
+        <v>0.00461424332344203</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J20" s="55"/>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="E21" s="52" t="n">
+      <c r="D21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="53" t="n">
+      <c r="F21" s="51" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G21" s="54" t="n">
+      <c r="G21" s="52" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H21" s="55" t="n">
+      <c r="H21" s="53" t="n">
         <v>-0.432417452830189</v>
       </c>
-      <c r="I21" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J21" s="51"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="s">
+      <c r="I21" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C22" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="E22" s="52" t="n">
+      <c r="D22" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F22" s="53" t="n">
+      <c r="F22" s="51" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G22" s="54" t="n">
+      <c r="G22" s="52" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H22" s="55" t="n">
+      <c r="H22" s="53" t="n">
         <v>-0.432417452830189</v>
       </c>
-      <c r="I22" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J22" s="51"/>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="s">
+      <c r="I22" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C23" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E23" s="52" t="n">
-        <v>34.5363636363636</v>
-      </c>
-      <c r="F23" s="53" t="n">
+      <c r="D23" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="51" t="n">
         <v>6.011375</v>
       </c>
-      <c r="G23" s="54" t="n">
-        <v>-28.5249886363636</v>
-      </c>
-      <c r="H23" s="55" t="n">
-        <v>-0.825940708081074</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J23" s="51"/>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="57" t="s">
+      <c r="G23" s="52" t="n">
+        <v>-15.988625</v>
+      </c>
+      <c r="H23" s="53" t="n">
+        <v>-0.726755681818182</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="E24" s="59" t="n">
+      <c r="D24" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="E24" s="57" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F24" s="60" t="n">
+      <c r="F24" s="58" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G24" s="61" t="n">
+      <c r="G24" s="59" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="60" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I24" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J24" s="57"/>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="s">
+      <c r="I24" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J24" s="55"/>
+    </row>
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="E25" s="59" t="n">
+      <c r="D25" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="E25" s="57" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F25" s="60" t="n">
+      <c r="F25" s="58" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G25" s="61" t="n">
+      <c r="G25" s="59" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H25" s="62" t="n">
+      <c r="H25" s="60" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I25" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J25" s="57"/>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="s">
+      <c r="I25" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J25" s="55"/>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B26" s="51" t="s">
-        <v>278</v>
+      <c r="B26" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="E26" s="52" t="n">
+      <c r="D26" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="51" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G26" s="54" t="n">
+      <c r="G26" s="52" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H26" s="55" t="n">
+      <c r="H26" s="53" t="n">
         <v>-0.432417452830189</v>
       </c>
-      <c r="I26" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J26" s="51"/>
-    </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="57" t="s">
+      <c r="I26" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="57" t="s">
-        <v>332</v>
-      </c>
-      <c r="E27" s="59" t="n">
+      <c r="D27" s="55" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27" s="57" t="n">
         <v>32.5</v>
       </c>
-      <c r="F27" s="60" t="n">
+      <c r="F27" s="58" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G27" s="61" t="n">
+      <c r="G27" s="59" t="n">
         <v>1.3555</v>
       </c>
-      <c r="H27" s="62" t="n">
+      <c r="H27" s="60" t="n">
         <v>0.0417076923076923</v>
       </c>
-      <c r="I27" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="J27" s="57"/>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51" t="s">
+      <c r="I27" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="J27" s="55"/>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="E28" s="52" t="n">
+      <c r="D28" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="51" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G28" s="54" t="n">
+      <c r="G28" s="52" t="n">
         <v>-11.1445</v>
       </c>
-      <c r="H28" s="55" t="n">
+      <c r="H28" s="53" t="n">
         <v>-0.247655555555556</v>
       </c>
-      <c r="I28" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J28" s="51"/>
-    </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="s">
+      <c r="I28" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="E29" s="52" t="n">
+      <c r="D29" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E29" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G29" s="54" t="n">
+      <c r="G29" s="52" t="n">
         <v>-17.73</v>
       </c>
-      <c r="H29" s="55" t="n">
+      <c r="H29" s="53" t="n">
         <v>-0.575649350649351</v>
       </c>
-      <c r="I29" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J29" s="51"/>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="s">
+      <c r="I29" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E30" s="52" t="n">
-        <v>31</v>
-      </c>
-      <c r="F30" s="56" t="n">
+      <c r="D30" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="F30" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G30" s="54" t="n">
-        <v>-17.93</v>
-      </c>
-      <c r="H30" s="55" t="n">
-        <v>-0.578387096774194</v>
-      </c>
-      <c r="I30" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J30" s="51"/>
-    </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
+      <c r="G30" s="52" t="n">
+        <v>-14.93</v>
+      </c>
+      <c r="H30" s="53" t="n">
+        <v>-0.533214285714286</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E31" s="52" t="n">
+      <c r="D31" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F31" s="56" t="n">
+      <c r="F31" s="54" t="n">
         <v>16.04</v>
       </c>
-      <c r="G31" s="54" t="n">
+      <c r="G31" s="52" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H31" s="55" t="n">
+      <c r="H31" s="53" t="n">
         <v>-0.48258064516129</v>
       </c>
-      <c r="I31" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J31" s="51"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="s">
+      <c r="I31" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E32" s="52" t="n">
+      <c r="D32" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F32" s="56" t="n">
+      <c r="F32" s="54" t="n">
         <v>16.04</v>
       </c>
-      <c r="G32" s="54" t="n">
+      <c r="G32" s="52" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H32" s="55" t="n">
+      <c r="H32" s="53" t="n">
         <v>-0.48258064516129</v>
       </c>
-      <c r="I32" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J32" s="51"/>
-    </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="s">
+      <c r="I32" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E33" s="52" t="n">
+      <c r="D33" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="54" t="n">
         <v>16.04</v>
       </c>
-      <c r="G33" s="54" t="n">
+      <c r="G33" s="52" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H33" s="55" t="n">
+      <c r="H33" s="53" t="n">
         <v>-0.48258064516129</v>
       </c>
-      <c r="I33" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J33" s="51"/>
-    </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="s">
+      <c r="I33" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E34" s="52" t="n">
+      <c r="D34" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E34" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F34" s="56" t="n">
+      <c r="F34" s="54" t="n">
         <v>16.04</v>
       </c>
-      <c r="G34" s="54" t="n">
+      <c r="G34" s="52" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H34" s="55" t="n">
+      <c r="H34" s="53" t="n">
         <v>-0.48258064516129</v>
       </c>
-      <c r="I34" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J34" s="51"/>
-    </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="s">
+      <c r="I34" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E35" s="52" t="n">
+      <c r="D35" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F35" s="56" t="n">
+      <c r="F35" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G35" s="54" t="n">
+      <c r="G35" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H35" s="55" t="n">
+      <c r="H35" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I35" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J35" s="51"/>
-    </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="51" t="s">
+      <c r="I35" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E36" s="52" t="n">
+      <c r="D36" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E36" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F36" s="56" t="n">
+      <c r="F36" s="54" t="n">
         <v>16.04</v>
       </c>
-      <c r="G36" s="54" t="n">
+      <c r="G36" s="52" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H36" s="55" t="n">
+      <c r="H36" s="53" t="n">
         <v>-0.48258064516129</v>
       </c>
-      <c r="I36" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J36" s="51"/>
-    </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51" t="s">
+      <c r="I36" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C37" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E37" s="52" t="n">
+      <c r="D37" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E37" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F37" s="56" t="n">
+      <c r="F37" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G37" s="54" t="n">
+      <c r="G37" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H37" s="55" t="n">
+      <c r="H37" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I37" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J37" s="51"/>
-    </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51" t="s">
+      <c r="I37" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="52" t="n">
+      <c r="D38" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F38" s="56" t="n">
+      <c r="F38" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G38" s="54" t="n">
+      <c r="G38" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H38" s="55" t="n">
+      <c r="H38" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I38" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J38" s="51"/>
-    </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="51" t="s">
+      <c r="I38" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B39" s="51" t="s">
+      <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E39" s="52" t="n">
+      <c r="D39" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E39" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F39" s="56" t="n">
+      <c r="F39" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G39" s="54" t="n">
+      <c r="G39" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H39" s="55" t="n">
+      <c r="H39" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I39" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J39" s="51"/>
-    </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="51" t="s">
+      <c r="I39" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B40" s="51" t="s">
+      <c r="B40" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C40" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E40" s="52" t="n">
+      <c r="D40" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F40" s="56" t="n">
+      <c r="F40" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G40" s="54" t="n">
+      <c r="G40" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H40" s="55" t="n">
+      <c r="H40" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I40" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J40" s="51"/>
-    </row>
-    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="51" t="s">
+      <c r="I40" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E41" s="52" t="n">
+      <c r="D41" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F41" s="56" t="n">
+      <c r="F41" s="54" t="n">
         <v>13.07</v>
       </c>
-      <c r="G41" s="54" t="n">
+      <c r="G41" s="52" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H41" s="55" t="n">
+      <c r="H41" s="53" t="n">
         <v>-0.578387096774194</v>
       </c>
-      <c r="I41" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J41" s="51"/>
-    </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="51" t="s">
+      <c r="I41" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C42" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E42" s="52" t="n">
-        <v>32.6363636363636</v>
-      </c>
-      <c r="F42" s="56" t="n">
+      <c r="D42" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="F42" s="54" t="n">
         <v>5.35</v>
       </c>
-      <c r="G42" s="54" t="n">
-        <v>-27.2863636363636</v>
-      </c>
-      <c r="H42" s="55" t="n">
-        <v>-0.836072423398328</v>
-      </c>
-      <c r="I42" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J42" s="51"/>
-    </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="51" t="s">
+      <c r="G42" s="52" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="H42" s="53" t="n">
+        <v>-0.733167082294264</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C43" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="E43" s="52" t="n">
+      <c r="D43" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F43" s="56" t="n">
+      <c r="F43" s="54" t="n">
         <v>2.67</v>
       </c>
-      <c r="G43" s="54" t="n">
+      <c r="G43" s="52" t="n">
         <v>-6.68454545454545</v>
       </c>
-      <c r="H43" s="55" t="n">
+      <c r="H43" s="53" t="n">
         <v>-0.714577259475219</v>
       </c>
-      <c r="I43" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J43" s="51"/>
-    </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="51" t="s">
+      <c r="I43" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E44" s="52" t="n">
+      <c r="D44" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E44" s="11" t="n">
         <v>23.4090909090909</v>
       </c>
-      <c r="F44" s="56" t="n">
+      <c r="F44" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G44" s="54" t="n">
+      <c r="G44" s="52" t="n">
         <v>-12.7190909090909</v>
       </c>
-      <c r="H44" s="55" t="n">
+      <c r="H44" s="53" t="n">
         <v>-0.543339805825243</v>
       </c>
-      <c r="I44" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J44" s="51"/>
-    </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="51" t="s">
+      <c r="I44" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C45" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E45" s="52" t="n">
-        <v>22.7181818181818</v>
-      </c>
-      <c r="F45" s="56" t="n">
+      <c r="D45" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="F45" s="54" t="n">
         <v>2.67</v>
       </c>
-      <c r="G45" s="54" t="n">
-        <v>-20.0481818181818</v>
-      </c>
-      <c r="H45" s="55" t="n">
-        <v>-0.882472989195678</v>
-      </c>
-      <c r="I45" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J45" s="51"/>
-    </row>
-    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="51" t="s">
+      <c r="G45" s="52" t="n">
+        <v>-17.7845454545455</v>
+      </c>
+      <c r="H45" s="53" t="n">
+        <v>-0.869466666666667</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C46" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E46" s="52" t="n">
-        <v>25.5818181818182</v>
-      </c>
-      <c r="F46" s="56" t="n">
+      <c r="D46" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" s="54" t="n">
         <v>9.5</v>
       </c>
-      <c r="G46" s="54" t="n">
-        <v>-16.0818181818182</v>
-      </c>
-      <c r="H46" s="55" t="n">
-        <v>-0.62864250177683</v>
-      </c>
-      <c r="I46" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J46" s="51"/>
-    </row>
-    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="51" t="s">
+      <c r="G46" s="52" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H46" s="53" t="n">
+        <v>-0.568181818181818</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C47" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E47" s="52" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F47" s="56" t="n">
+      <c r="D47" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>16.7363636363636</v>
+      </c>
+      <c r="F47" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G47" s="54" t="n">
-        <v>-30.21</v>
-      </c>
-      <c r="H47" s="55" t="n">
-        <v>-0.738630806845966</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J47" s="51"/>
-    </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="51" t="s">
+      <c r="G47" s="52" t="n">
+        <v>-6.0463636363636</v>
+      </c>
+      <c r="H47" s="53" t="n">
+        <v>-0.36127104834329</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E48" s="52" t="n">
+      <c r="D48" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E48" s="11" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="F48" s="56" t="n">
+      <c r="F48" s="54" t="n">
         <v>5.35</v>
       </c>
-      <c r="G48" s="54" t="n">
+      <c r="G48" s="52" t="n">
         <v>-15.5590909090909</v>
       </c>
-      <c r="H48" s="55" t="n">
+      <c r="H48" s="53" t="n">
         <v>-0.744130434782609</v>
       </c>
-      <c r="I48" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J48" s="51"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="51" t="s">
+      <c r="I48" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="E49" s="52" t="n">
+      <c r="D49" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E49" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F49" s="56" t="n">
+      <c r="F49" s="54" t="n">
         <v>5.35</v>
       </c>
-      <c r="G49" s="54" t="n">
+      <c r="G49" s="52" t="n">
         <v>-4.00454545454545</v>
       </c>
-      <c r="H49" s="55" t="n">
+      <c r="H49" s="53" t="n">
         <v>-0.428085519922254</v>
       </c>
-      <c r="I49" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J49" s="51"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51" t="s">
+      <c r="I49" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B50" s="51" t="s">
+      <c r="B50" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C50" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E50" s="52" t="n">
-        <v>25.4454545454545</v>
-      </c>
-      <c r="F50" s="56" t="n">
+      <c r="D50" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F50" s="54" t="n">
         <v>2.67</v>
       </c>
-      <c r="G50" s="54" t="n">
-        <v>-22.7754545454545</v>
-      </c>
-      <c r="H50" s="55" t="n">
-        <v>-0.895069667738478</v>
-      </c>
-      <c r="I50" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J50" s="51"/>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="51" t="s">
+      <c r="G50" s="52" t="n">
+        <v>-7.83</v>
+      </c>
+      <c r="H50" s="53" t="n">
+        <v>-0.745714285714286</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C51" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E51" s="52" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F51" s="56" t="n">
+      <c r="D51" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F51" s="54" t="n">
         <v>9.5</v>
       </c>
-      <c r="G51" s="54" t="n">
-        <v>-31.4</v>
-      </c>
-      <c r="H51" s="55" t="n">
-        <v>-0.767726161369193</v>
-      </c>
-      <c r="I51" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J51" s="51"/>
-    </row>
-    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="51" t="s">
+      <c r="G51" s="52" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H51" s="53" t="n">
+        <v>-0.641509433962264</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B52" s="51" t="s">
+      <c r="B52" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="E52" s="52" t="n">
+      <c r="D52" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E52" s="11" t="n">
         <v>7.81818181818182</v>
       </c>
-      <c r="F52" s="56" t="n">
+      <c r="F52" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="54" t="n">
+      <c r="G52" s="52" t="n">
         <v>-5.81818181818182</v>
       </c>
-      <c r="H52" s="55" t="n">
+      <c r="H52" s="53" t="n">
         <v>-0.744186046511628</v>
       </c>
-      <c r="I52" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J52" s="51"/>
-    </row>
-    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="51" t="s">
+      <c r="I52" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B53" s="51" t="s">
+      <c r="B53" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D53" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E53" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F53" s="56" t="n">
+      <c r="D53" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="F53" s="54" t="n">
         <v>2.67</v>
       </c>
-      <c r="G53" s="54" t="n">
-        <v>-27.3209090909091</v>
-      </c>
-      <c r="H53" s="55" t="n">
-        <v>-0.910973022127918</v>
-      </c>
-      <c r="I53" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J53" s="51"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="51" t="s">
+      <c r="G53" s="52" t="n">
+        <v>-17.7845454545455</v>
+      </c>
+      <c r="H53" s="53" t="n">
+        <v>-0.869466666666667</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B54" s="51" t="s">
+      <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C54" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E54" s="52" t="n">
-        <v>34.5363636363636</v>
-      </c>
-      <c r="F54" s="56" t="n">
+      <c r="D54" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>20.9090909090909</v>
+      </c>
+      <c r="F54" s="54" t="n">
         <v>4.01</v>
       </c>
-      <c r="G54" s="54" t="n">
-        <v>-30.5263636363636</v>
-      </c>
-      <c r="H54" s="55" t="n">
-        <v>-0.883890497499342</v>
-      </c>
-      <c r="I54" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J54" s="51"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51" t="s">
+      <c r="G54" s="52" t="n">
+        <v>-16.8990909090909</v>
+      </c>
+      <c r="H54" s="53" t="n">
+        <v>-0.808217391304348</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B55" s="51" t="s">
+      <c r="B55" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C55" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D55" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E55" s="52" t="n">
-        <v>34.5363636363636</v>
-      </c>
-      <c r="F55" s="56" t="n">
+      <c r="D55" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F55" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G55" s="54" t="n">
-        <v>-23.8463636363636</v>
-      </c>
-      <c r="H55" s="55" t="n">
-        <v>-0.690471176625428</v>
-      </c>
-      <c r="I55" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J55" s="51"/>
-    </row>
-    <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="51" t="s">
+      <c r="G55" s="52" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="H55" s="53" t="n">
+        <v>-0.514090909090909</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B56" s="51" t="s">
+      <c r="B56" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C56" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E56" s="52" t="n">
-        <v>34.5363636363636</v>
-      </c>
-      <c r="F56" s="56" t="n">
+      <c r="D56" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>27.2727272727273</v>
+      </c>
+      <c r="F56" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G56" s="54" t="n">
-        <v>-23.8463636363636</v>
-      </c>
-      <c r="H56" s="55" t="n">
-        <v>-0.690471176625428</v>
-      </c>
-      <c r="I56" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J56" s="51"/>
-    </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="51" t="s">
+      <c r="G56" s="52" t="n">
+        <v>-16.5827272727273</v>
+      </c>
+      <c r="H56" s="53" t="n">
+        <v>-0.608033333333334</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E57" s="52" t="n">
-        <v>38.8636363636364</v>
-      </c>
-      <c r="F57" s="56" t="n">
+      <c r="D57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F57" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G57" s="54" t="n">
-        <v>-28.1736363636364</v>
-      </c>
-      <c r="H57" s="55" t="n">
-        <v>-0.72493567251462</v>
-      </c>
-      <c r="I57" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J57" s="51"/>
-    </row>
-    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="51" t="s">
+      <c r="G57" s="52" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="H57" s="53" t="n">
+        <v>-0.514090909090909</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B58" s="51" t="s">
+      <c r="B58" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C58" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E58" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F58" s="56" t="n">
+      <c r="D58" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="54" t="n">
         <v>2.89</v>
       </c>
-      <c r="G58" s="54" t="n">
-        <v>-27.1009090909091</v>
-      </c>
-      <c r="H58" s="55" t="n">
-        <v>-0.903637465898757</v>
-      </c>
-      <c r="I58" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J58" s="51"/>
-    </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="51" t="s">
+      <c r="G58" s="52" t="n">
+        <v>-17.11</v>
+      </c>
+      <c r="H58" s="53" t="n">
+        <v>-0.8555</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C59" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E59" s="52" t="n">
-        <v>45.4454545454545</v>
-      </c>
-      <c r="F59" s="56" t="n">
+      <c r="D59" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>37.6363636363636</v>
+      </c>
+      <c r="F59" s="54" t="n">
         <v>1.94</v>
       </c>
-      <c r="G59" s="54" t="n">
-        <v>-43.5054545454545</v>
-      </c>
-      <c r="H59" s="55" t="n">
-        <v>-0.957311462292458</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J59" s="51"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="51" t="s">
+      <c r="G59" s="52" t="n">
+        <v>-35.6963636363636</v>
+      </c>
+      <c r="H59" s="53" t="n">
+        <v>-0.948454106280193</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B60" s="51" t="s">
+      <c r="B60" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C60" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D60" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="E60" s="52" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="F60" s="56" t="n">
+      <c r="D60" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>27.2727272727273</v>
+      </c>
+      <c r="F60" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G60" s="54" t="n">
-        <v>-32.86</v>
-      </c>
-      <c r="H60" s="55" t="n">
-        <v>-0.754535017221584</v>
-      </c>
-      <c r="I60" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J60" s="51"/>
-    </row>
-    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="51" t="s">
+      <c r="G60" s="52" t="n">
+        <v>-16.5827272727273</v>
+      </c>
+      <c r="H60" s="53" t="n">
+        <v>-0.608033333333334</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B61" s="51" t="s">
+      <c r="B61" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E61" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F61" s="56" t="n">
+      <c r="D61" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="F61" s="54" t="n">
         <v>3.201</v>
       </c>
-      <c r="G61" s="54" t="n">
-        <v>-26.7899090909091</v>
-      </c>
-      <c r="H61" s="55" t="n">
-        <v>-0.893267656865717</v>
-      </c>
-      <c r="I61" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J61" s="51"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="51" t="s">
+      <c r="G61" s="52" t="n">
+        <v>-17.2535454545455</v>
+      </c>
+      <c r="H61" s="53" t="n">
+        <v>-0.843506666666667</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B62" s="51" t="s">
+      <c r="B62" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C62" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D62" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="E62" s="52" t="n">
-        <v>29.9909090909091</v>
-      </c>
-      <c r="F62" s="56" t="n">
+      <c r="D62" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="F62" s="54" t="n">
         <v>5.35</v>
       </c>
-      <c r="G62" s="54" t="n">
-        <v>-24.6409090909091</v>
-      </c>
-      <c r="H62" s="55" t="n">
-        <v>-0.821612609881782</v>
-      </c>
-      <c r="I62" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J62" s="51"/>
-    </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="51" t="s">
+      <c r="G62" s="52" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="H62" s="53" t="n">
+        <v>-0.739659367396594</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="51" t="s">
+      <c r="B63" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C63" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E63" s="52" t="n">
-        <v>27.9727272727273</v>
-      </c>
-      <c r="F63" s="56" t="n">
+      <c r="D63" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="F63" s="54" t="n">
         <v>2.67</v>
       </c>
-      <c r="G63" s="54" t="n">
-        <v>-25.3027272727273</v>
-      </c>
-      <c r="H63" s="55" t="n">
-        <v>-0.904549886252844</v>
-      </c>
-      <c r="I63" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J63" s="51"/>
-    </row>
-    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="51" t="s">
+      <c r="G63" s="52" t="n">
+        <v>-17.7845454545455</v>
+      </c>
+      <c r="H63" s="53" t="n">
+        <v>-0.869466666666667</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C64" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D64" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="E64" s="52" t="n">
+      <c r="D64" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E64" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F64" s="56" t="n">
+      <c r="F64" s="54" t="n">
         <v>10.69</v>
       </c>
-      <c r="G64" s="54" t="n">
+      <c r="G64" s="52" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H64" s="55" t="n">
+      <c r="H64" s="53" t="n">
         <v>-0.608033333333334</v>
       </c>
-      <c r="I64" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="J64" s="51"/>
+      <c r="I64" s="1" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="64" t="s">
-        <v>339</v>
-      </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="64"/>
-      <c r="G66" s="64"/>
-      <c r="H66" s="64"/>
-      <c r="I66" s="64"/>
-      <c r="J66" s="64"/>
+      <c r="A66" s="62" t="s">
+        <v>350</v>
+      </c>
+      <c r="B66" s="62"/>
+      <c r="C66" s="62"/>
+      <c r="D66" s="62"/>
+      <c r="E66" s="62"/>
+      <c r="F66" s="62"/>
+      <c r="G66" s="62"/>
+      <c r="H66" s="62"/>
+      <c r="I66" s="62"/>
+      <c r="J66" s="62"/>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="50" t="s">
@@ -16279,179 +16489,179 @@
         <v>1</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="G67" s="50" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="57" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="D68" s="59" t="n">
+      <c r="C68" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="57" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E68" s="59" t="n">
+      <c r="E68" s="57" t="n">
         <v>16.93275</v>
       </c>
-      <c r="F68" s="61" t="n">
+      <c r="F68" s="59" t="n">
         <v>7.57820454545455</v>
       </c>
-      <c r="G68" s="62" t="n">
+      <c r="G68" s="60" t="n">
         <v>0.447547181967167</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="57" t="s">
+    <row r="69" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="58" t="s">
+      <c r="B69" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="D69" s="59" t="n">
+      <c r="C69" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" s="57" t="n">
         <v>21.2</v>
       </c>
-      <c r="E69" s="59" t="n">
+      <c r="E69" s="57" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F69" s="61" t="n">
+      <c r="F69" s="59" t="n">
         <v>12.6555</v>
       </c>
-      <c r="G69" s="62" t="n">
+      <c r="G69" s="60" t="n">
         <v>0.373809277665372</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="57" t="s">
+    <row r="70" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="58" t="s">
+      <c r="B70" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="C70" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="D70" s="59" t="n">
+      <c r="C70" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D70" s="57" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E70" s="59" t="n">
+      <c r="E70" s="57" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F70" s="61" t="n">
+      <c r="F70" s="59" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G70" s="62" t="n">
+      <c r="G70" s="60" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="57" t="s">
+    <row r="71" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="58" t="s">
+      <c r="B71" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="D71" s="59" t="n">
+      <c r="C71" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D71" s="57" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E71" s="59" t="n">
+      <c r="E71" s="57" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F71" s="61" t="n">
+      <c r="F71" s="59" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G71" s="62" t="n">
+      <c r="G71" s="60" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="57" t="s">
+    <row r="72" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="58" t="s">
+      <c r="B72" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="D72" s="59" t="n">
+      <c r="C72" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="D72" s="57" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E72" s="59" t="n">
+      <c r="E72" s="57" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F72" s="61" t="n">
+      <c r="F72" s="59" t="n">
         <v>5.5009545454545</v>
       </c>
-      <c r="G72" s="62" t="n">
+      <c r="G72" s="60" t="n">
         <v>0.162483334922081</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="57" t="s">
+    <row r="73" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="58" t="s">
+      <c r="B73" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="C73" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="D73" s="59" t="n">
+      <c r="C73" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="D73" s="57" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E73" s="59" t="n">
+      <c r="E73" s="57" t="n">
         <v>30.1455</v>
       </c>
-      <c r="F73" s="61" t="n">
+      <c r="F73" s="59" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="G73" s="62" t="n">
+      <c r="G73" s="60" t="n">
         <v>0.0594103446768007</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="57" t="s">
+    <row r="74" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="58" t="s">
+      <c r="B74" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="57" t="s">
-        <v>332</v>
-      </c>
-      <c r="D74" s="59" t="n">
+      <c r="C74" s="55" t="s">
+        <v>345</v>
+      </c>
+      <c r="D74" s="57" t="n">
         <v>32.5</v>
       </c>
-      <c r="E74" s="59" t="n">
+      <c r="E74" s="57" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F74" s="61" t="n">
+      <c r="F74" s="59" t="n">
         <v>1.3555</v>
       </c>
-      <c r="G74" s="62" t="n">
+      <c r="G74" s="60" t="n">
         <v>0.0400378077417258</v>
       </c>
     </row>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -1140,15 +1140,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1248,13 +1249,21 @@
     <font>
       <i val="true"/>
       <sz val="11"/>
-      <color rgb="FF9B9B9B"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
       <sz val="11"/>
+      <color rgb="FF9B9B9B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1438,7 +1447,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1619,7 +1628,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1631,31 +1648,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1671,23 +1688,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1700,7 +1717,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1723,6 +1740,11 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
     </dxf>
   </dxfs>
   <colors>
@@ -1799,9 +1821,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>401400</xdr:colOff>
+      <xdr:colOff>401040</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>257760</xdr:rowOff>
+      <xdr:rowOff>257400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1815,7 +1837,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2189160" cy="2335320"/>
+          <a:ext cx="2188800" cy="2334960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8684,23 +8706,23 @@
       <c r="M15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N15" s="42" t="n">
+      <c r="N15" s="46" t="n">
         <v>35.7</v>
       </c>
-      <c r="O15" s="42" t="n">
+      <c r="O15" s="46" t="n">
         <f aca="false">N15/1.1</f>
         <v>32.4545454545455</v>
       </c>
-      <c r="P15" s="42" t="n">
+      <c r="P15" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q15" s="42" t="n">
+      <c r="Q15" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R15" s="42" t="n">
+      <c r="R15" s="46" t="n">
         <v>25</v>
       </c>
-      <c r="S15" s="42" t="n">
+      <c r="S15" s="46" t="n">
         <f aca="false">R15/1.1</f>
         <v>22.7272727272727</v>
       </c>
@@ -8716,10 +8738,10 @@
       <c r="W15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X15" s="42" t="n">
+      <c r="X15" s="46" t="n">
         <v>35.07</v>
       </c>
-      <c r="Y15" s="42" t="n">
+      <c r="Y15" s="46" t="n">
         <f aca="false">X15/1.1</f>
         <v>31.8818181818182</v>
       </c>
@@ -8793,29 +8815,29 @@
       <c r="K16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L16" s="42" t="n">
+      <c r="L16" s="46" t="n">
         <v>48.29</v>
       </c>
-      <c r="M16" s="42" t="n">
+      <c r="M16" s="46" t="n">
         <v>43.9</v>
       </c>
-      <c r="N16" s="42" t="n">
+      <c r="N16" s="46" t="n">
         <v>39.95</v>
       </c>
-      <c r="O16" s="42" t="n">
+      <c r="O16" s="46" t="n">
         <f aca="false">N16/1.1</f>
         <v>36.3181818181818</v>
       </c>
-      <c r="P16" s="42" t="n">
+      <c r="P16" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q16" s="42" t="n">
+      <c r="Q16" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R16" s="42" t="n">
+      <c r="R16" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="S16" s="42" t="n">
+      <c r="S16" s="46" t="n">
         <f aca="false">R16/1.1</f>
         <v>25</v>
       </c>
@@ -8825,17 +8847,17 @@
       <c r="U16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V16" s="42" t="n">
+      <c r="V16" s="46" t="n">
         <v>21.9</v>
       </c>
-      <c r="W16" s="42" t="n">
+      <c r="W16" s="46" t="n">
         <f aca="false">V16*1.1</f>
         <v>24.09</v>
       </c>
-      <c r="X16" s="42" t="n">
+      <c r="X16" s="46" t="n">
         <v>42.75</v>
       </c>
-      <c r="Y16" s="42" t="n">
+      <c r="Y16" s="46" t="n">
         <f aca="false">X16/1.1</f>
         <v>38.8636363636364</v>
       </c>
@@ -8909,29 +8931,29 @@
       <c r="K17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L17" s="42" t="n">
+      <c r="L17" s="46" t="n">
         <v>53.63</v>
       </c>
-      <c r="M17" s="42" t="n">
+      <c r="M17" s="46" t="n">
         <v>48.75</v>
       </c>
-      <c r="N17" s="42" t="n">
+      <c r="N17" s="46" t="n">
         <v>35.7</v>
       </c>
-      <c r="O17" s="42" t="n">
+      <c r="O17" s="46" t="n">
         <f aca="false">N17/1.1</f>
         <v>32.4545454545455</v>
       </c>
-      <c r="P17" s="42" t="n">
+      <c r="P17" s="46" t="n">
         <v>11.55</v>
       </c>
-      <c r="Q17" s="42" t="n">
+      <c r="Q17" s="46" t="n">
         <v>10.5</v>
       </c>
-      <c r="R17" s="42" t="n">
+      <c r="R17" s="46" t="n">
         <v>25</v>
       </c>
-      <c r="S17" s="42" t="n">
+      <c r="S17" s="46" t="n">
         <f aca="false">R17/1.1</f>
         <v>22.7272727272727</v>
       </c>
@@ -8947,10 +8969,10 @@
       <c r="W17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X17" s="42" t="n">
+      <c r="X17" s="46" t="n">
         <v>35.07</v>
       </c>
-      <c r="Y17" s="42" t="n">
+      <c r="Y17" s="46" t="n">
         <f aca="false">X17/1.1</f>
         <v>31.8818181818182</v>
       </c>
@@ -9030,10 +9052,10 @@
       <c r="M18" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N18" s="42" t="n">
+      <c r="N18" s="46" t="n">
         <v>49.5</v>
       </c>
-      <c r="O18" s="42" t="n">
+      <c r="O18" s="46" t="n">
         <f aca="false">N18/1.1</f>
         <v>45</v>
       </c>
@@ -9141,10 +9163,10 @@
       <c r="K19" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L19" s="42" t="n">
+      <c r="L19" s="46" t="n">
         <v>61.59</v>
       </c>
-      <c r="M19" s="42" t="n">
+      <c r="M19" s="46" t="n">
         <v>55.99</v>
       </c>
       <c r="N19" s="11" t="n">
@@ -9394,10 +9416,10 @@
       <c r="Q21" s="11" t="n">
         <v>40.91</v>
       </c>
-      <c r="R21" s="42" t="n">
+      <c r="R21" s="46" t="n">
         <v>37.07</v>
       </c>
-      <c r="S21" s="42" t="n">
+      <c r="S21" s="46" t="n">
         <f aca="false">R21/1.1</f>
         <v>33.7</v>
       </c>
@@ -9723,36 +9745,36 @@
       <c r="K24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L24" s="42" t="n">
+      <c r="L24" s="46" t="n">
         <v>43.15</v>
       </c>
-      <c r="M24" s="42" t="n">
+      <c r="M24" s="46" t="n">
         <v>39.23</v>
       </c>
-      <c r="N24" s="42" t="n">
+      <c r="N24" s="46" t="n">
         <v>35.75</v>
       </c>
-      <c r="O24" s="42" t="n">
+      <c r="O24" s="46" t="n">
         <f aca="false">N24/1.1</f>
         <v>32.5</v>
       </c>
-      <c r="P24" s="42" t="n">
+      <c r="P24" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q24" s="42" t="n">
+      <c r="Q24" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R24" s="42" t="n">
+      <c r="R24" s="46" t="n">
         <v>25</v>
       </c>
-      <c r="S24" s="42" t="n">
+      <c r="S24" s="46" t="n">
         <f aca="false">R24/1.1</f>
         <v>22.7272727272727</v>
       </c>
-      <c r="T24" s="42" t="n">
+      <c r="T24" s="46" t="n">
         <v>33.19</v>
       </c>
-      <c r="U24" s="42" t="n">
+      <c r="U24" s="46" t="n">
         <f aca="false">T24/1.1</f>
         <v>30.1727272727273</v>
       </c>
@@ -9762,10 +9784,10 @@
       <c r="W24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X24" s="42" t="n">
+      <c r="X24" s="46" t="n">
         <v>35.9</v>
       </c>
-      <c r="Y24" s="42" t="n">
+      <c r="Y24" s="46" t="n">
         <f aca="false">X24/1.1</f>
         <v>32.6363636363636</v>
       </c>
@@ -9838,10 +9860,10 @@
       <c r="K25" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L25" s="42" t="n">
+      <c r="L25" s="46" t="n">
         <v>46.29</v>
       </c>
-      <c r="M25" s="42" t="n">
+      <c r="M25" s="46" t="n">
         <v>42.08</v>
       </c>
       <c r="N25" s="11" t="n">
@@ -10070,10 +10092,10 @@
       <c r="K27" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L27" s="42" t="n">
+      <c r="L27" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M27" s="42" t="n">
+      <c r="M27" s="46" t="n">
         <v>35.98</v>
       </c>
       <c r="N27" s="11" t="n">
@@ -10238,10 +10260,10 @@
       <c r="AA28" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB28" s="42" t="n">
+      <c r="AB28" s="46" t="n">
         <v>90.08</v>
       </c>
-      <c r="AC28" s="42" t="n">
+      <c r="AC28" s="46" t="n">
         <f aca="false">AB28/1.1</f>
         <v>81.8909090909091</v>
       </c>
@@ -10470,10 +10492,10 @@
       <c r="AA30" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB30" s="42" t="n">
+      <c r="AB30" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC30" s="42" t="n">
+      <c r="AC30" s="46" t="n">
         <f aca="false">AB30/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10565,10 +10587,10 @@
         <f aca="false">T31/1.1</f>
         <v>42.8545454545455</v>
       </c>
-      <c r="V31" s="42" t="n">
+      <c r="V31" s="46" t="n">
         <v>28</v>
       </c>
-      <c r="W31" s="42" t="n">
+      <c r="W31" s="46" t="n">
         <f aca="false">V31*1.1</f>
         <v>30.8</v>
       </c>
@@ -10585,8 +10607,8 @@
       <c r="AA31" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB31" s="42"/>
-      <c r="AC31" s="42"/>
+      <c r="AB31" s="47"/>
+      <c r="AC31" s="47"/>
       <c r="AD31" s="11" t="n">
         <f aca="false">IF(COUNT(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31)=0,"N/A",MIN(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31))</f>
         <v>28</v>
@@ -10695,10 +10717,10 @@
       <c r="AA32" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB32" s="42" t="n">
+      <c r="AB32" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC32" s="42" t="n">
+      <c r="AC32" s="46" t="n">
         <f aca="false">AB32/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10765,10 +10787,10 @@
       <c r="M33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N33" s="42" t="n">
+      <c r="N33" s="46" t="n">
         <v>51</v>
       </c>
-      <c r="O33" s="42" t="n">
+      <c r="O33" s="46" t="n">
         <f aca="false">N33/1.1</f>
         <v>46.3636363636364</v>
       </c>
@@ -10792,10 +10814,10 @@
         <f aca="false">T33/1.1</f>
         <v>53.4909090909091</v>
       </c>
-      <c r="V33" s="42" t="n">
+      <c r="V33" s="46" t="n">
         <v>51.5</v>
       </c>
-      <c r="W33" s="42" t="n">
+      <c r="W33" s="46" t="n">
         <f aca="false">V33*1.1</f>
         <v>56.65</v>
       </c>
@@ -10812,10 +10834,10 @@
       <c r="AA33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB33" s="42" t="n">
+      <c r="AB33" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC33" s="42" t="n">
+      <c r="AC33" s="46" t="n">
         <f aca="false">AB33/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10928,10 +10950,10 @@
       <c r="AA34" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB34" s="42" t="n">
+      <c r="AB34" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC34" s="42" t="n">
+      <c r="AC34" s="46" t="n">
         <f aca="false">AB34/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11044,10 +11066,10 @@
       <c r="AA35" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB35" s="42" t="n">
+      <c r="AB35" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC35" s="42" t="n">
+      <c r="AC35" s="46" t="n">
         <f aca="false">AB35/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11161,10 +11183,10 @@
       <c r="AA36" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB36" s="42" t="n">
+      <c r="AB36" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC36" s="42" t="n">
+      <c r="AC36" s="46" t="n">
         <f aca="false">AB36/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11275,10 +11297,10 @@
       <c r="AA37" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB37" s="42" t="n">
+      <c r="AB37" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC37" s="42" t="n">
+      <c r="AC37" s="46" t="n">
         <f aca="false">AB37/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11390,10 +11412,10 @@
       <c r="AA38" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB38" s="42" t="n">
+      <c r="AB38" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC38" s="42" t="n">
+      <c r="AC38" s="46" t="n">
         <f aca="false">AB38/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11506,10 +11528,10 @@
       <c r="AA39" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB39" s="42" t="n">
+      <c r="AB39" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC39" s="42" t="n">
+      <c r="AC39" s="46" t="n">
         <f aca="false">AB39/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11622,10 +11644,10 @@
       <c r="AA40" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB40" s="42" t="n">
+      <c r="AB40" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC40" s="42" t="n">
+      <c r="AC40" s="46" t="n">
         <f aca="false">AB40/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11738,10 +11760,10 @@
       <c r="AA41" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB41" s="42" t="n">
+      <c r="AB41" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC41" s="42" t="n">
+      <c r="AC41" s="46" t="n">
         <f aca="false">AB41/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11854,10 +11876,10 @@
       <c r="AA42" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB42" s="42" t="n">
+      <c r="AB42" s="46" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC42" s="42" t="n">
+      <c r="AC42" s="46" t="n">
         <f aca="false">AB42/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11929,16 +11951,16 @@
       <c r="O43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P43" s="42" t="n">
+      <c r="P43" s="46" t="n">
         <v>22.05</v>
       </c>
-      <c r="Q43" s="42" t="n">
+      <c r="Q43" s="46" t="n">
         <v>20.05</v>
       </c>
-      <c r="R43" s="42" t="n">
+      <c r="R43" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="S43" s="42" t="n">
+      <c r="S43" s="46" t="n">
         <f aca="false">R43/1.1</f>
         <v>25</v>
       </c>
@@ -11954,19 +11976,19 @@
       <c r="W43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X43" s="42" t="n">
+      <c r="X43" s="46" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y43" s="42" t="n">
+      <c r="Y43" s="46" t="n">
         <f aca="false">X43/1.1</f>
         <v>29.0545454545455</v>
       </c>
-      <c r="Z43" s="42"/>
-      <c r="AA43" s="42"/>
-      <c r="AB43" s="42" t="n">
+      <c r="Z43" s="47"/>
+      <c r="AA43" s="47"/>
+      <c r="AB43" s="46" t="n">
         <v>35.9</v>
       </c>
-      <c r="AC43" s="42" t="n">
+      <c r="AC43" s="46" t="n">
         <f aca="false">AB43/1.1</f>
         <v>32.6363636363636</v>
       </c>
@@ -12045,10 +12067,10 @@
       <c r="Q44" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R44" s="42" t="n">
+      <c r="R44" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S44" s="42" t="n">
+      <c r="S44" s="46" t="n">
         <f aca="false">R44/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -12181,10 +12203,10 @@
       <c r="W45" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="X45" s="42" t="n">
+      <c r="X45" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y45" s="42" t="n">
+      <c r="Y45" s="46" t="n">
         <f aca="false">X45/1.1</f>
         <v>41.6</v>
       </c>
@@ -12258,16 +12280,16 @@
       <c r="K46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L46" s="42" t="n">
+      <c r="L46" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M46" s="42" t="n">
+      <c r="M46" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N46" s="42" t="n">
+      <c r="N46" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="O46" s="42" t="n">
+      <c r="O46" s="46" t="n">
         <f aca="false">N46/1.1</f>
         <v>25</v>
       </c>
@@ -12277,10 +12299,10 @@
       <c r="Q46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R46" s="42" t="n">
+      <c r="R46" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S46" s="42" t="n">
+      <c r="S46" s="46" t="n">
         <f aca="false">R46/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -12296,10 +12318,10 @@
       <c r="W46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X46" s="42" t="n">
+      <c r="X46" s="46" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y46" s="42" t="n">
+      <c r="Y46" s="46" t="n">
         <f aca="false">X46/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -12373,50 +12395,50 @@
       <c r="K47" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L47" s="42" t="n">
+      <c r="L47" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M47" s="42" t="n">
+      <c r="M47" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N47" s="42" t="n">
+      <c r="N47" s="46" t="n">
         <v>42.5</v>
       </c>
-      <c r="O47" s="42" t="n">
+      <c r="O47" s="46" t="n">
         <f aca="false">N47/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P47" s="42" t="n">
+      <c r="P47" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q47" s="42" t="n">
+      <c r="Q47" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R47" s="42" t="n">
+      <c r="R47" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="S47" s="42" t="n">
+      <c r="S47" s="46" t="n">
         <f aca="false">R47/1.1</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="T47" s="42" t="n">
+      <c r="T47" s="46" t="n">
         <v>28.66</v>
       </c>
-      <c r="U47" s="42" t="n">
+      <c r="U47" s="46" t="n">
         <f aca="false">T47/1.1</f>
         <v>26.0545454545455</v>
       </c>
-      <c r="V47" s="42" t="n">
+      <c r="V47" s="46" t="n">
         <v>36.5</v>
       </c>
-      <c r="W47" s="42" t="n">
+      <c r="W47" s="46" t="n">
         <f aca="false">V47*1.1</f>
         <v>40.15</v>
       </c>
-      <c r="X47" s="42" t="n">
+      <c r="X47" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y47" s="42" t="n">
+      <c r="Y47" s="46" t="n">
         <f aca="false">X47/1.1</f>
         <v>41.6</v>
       </c>
@@ -12490,43 +12512,43 @@
       <c r="K48" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L48" s="42" t="n">
+      <c r="L48" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M48" s="42" t="n">
+      <c r="M48" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N48" s="42" t="n">
+      <c r="N48" s="46" t="n">
         <v>42.5</v>
       </c>
-      <c r="O48" s="42" t="n">
+      <c r="O48" s="46" t="n">
         <f aca="false">N48/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P48" s="42" t="n">
+      <c r="P48" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q48" s="42" t="n">
+      <c r="Q48" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R48" s="42" t="n">
+      <c r="R48" s="46" t="n">
         <v>33.5</v>
       </c>
-      <c r="S48" s="42" t="n">
+      <c r="S48" s="46" t="n">
         <f aca="false">R48/1.1</f>
         <v>30.4545454545455</v>
       </c>
-      <c r="T48" s="42" t="n">
+      <c r="T48" s="46" t="n">
         <v>18.41</v>
       </c>
-      <c r="U48" s="42" t="n">
+      <c r="U48" s="46" t="n">
         <f aca="false">T48/1.1</f>
         <v>16.7363636363636</v>
       </c>
-      <c r="V48" s="42" t="n">
+      <c r="V48" s="46" t="n">
         <v>28.5</v>
       </c>
-      <c r="W48" s="42" t="n">
+      <c r="W48" s="46" t="n">
         <f aca="false">V48*1.1</f>
         <v>31.35</v>
       </c>
@@ -12612,17 +12634,17 @@
       <c r="M49" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N49" s="42" t="n">
+      <c r="N49" s="46" t="n">
         <v>35.4</v>
       </c>
-      <c r="O49" s="42" t="n">
+      <c r="O49" s="46" t="n">
         <f aca="false">N49/1.1</f>
         <v>32.1818181818182</v>
       </c>
-      <c r="P49" s="42" t="n">
+      <c r="P49" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q49" s="42" t="n">
+      <c r="Q49" s="46" t="n">
         <v>22</v>
       </c>
       <c r="R49" s="11" t="n">
@@ -12646,10 +12668,10 @@
       <c r="W49" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X49" s="42" t="n">
+      <c r="X49" s="46" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y49" s="42" t="n">
+      <c r="Y49" s="46" t="n">
         <f aca="false">X49/1.1</f>
         <v>29.0545454545455</v>
       </c>
@@ -12840,43 +12862,43 @@
       <c r="K51" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L51" s="42" t="n">
+      <c r="L51" s="46" t="n">
         <v>34.67</v>
       </c>
-      <c r="M51" s="42" t="n">
+      <c r="M51" s="46" t="n">
         <v>31.52</v>
       </c>
-      <c r="N51" s="42" t="n">
+      <c r="N51" s="46" t="n">
         <v>28.3</v>
       </c>
-      <c r="O51" s="42" t="n">
+      <c r="O51" s="46" t="n">
         <f aca="false">N51/1.1</f>
         <v>25.7272727272727</v>
       </c>
-      <c r="P51" s="42" t="n">
+      <c r="P51" s="46" t="n">
         <v>11.55</v>
       </c>
-      <c r="Q51" s="42" t="n">
+      <c r="Q51" s="46" t="n">
         <v>10.5</v>
       </c>
-      <c r="R51" s="42" t="n">
+      <c r="R51" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S51" s="42" t="n">
+      <c r="S51" s="46" t="n">
         <f aca="false">R51/1.1</f>
         <v>20.4545454545455</v>
       </c>
-      <c r="T51" s="42" t="n">
+      <c r="T51" s="46" t="n">
         <v>33.04</v>
       </c>
-      <c r="U51" s="42" t="n">
+      <c r="U51" s="46" t="n">
         <f aca="false">T51/1.1</f>
         <v>30.0363636363636</v>
       </c>
-      <c r="V51" s="42" t="n">
+      <c r="V51" s="46" t="n">
         <v>19.5</v>
       </c>
-      <c r="W51" s="42" t="n">
+      <c r="W51" s="46" t="n">
         <f aca="false">V51*1.1</f>
         <v>21.45</v>
       </c>
@@ -12956,29 +12978,29 @@
       <c r="K52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L52" s="42" t="n">
+      <c r="L52" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M52" s="42" t="n">
+      <c r="M52" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N52" s="42" t="n">
+      <c r="N52" s="46" t="n">
         <v>42.5</v>
       </c>
-      <c r="O52" s="42" t="n">
+      <c r="O52" s="46" t="n">
         <f aca="false">N52/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P52" s="42" t="n">
+      <c r="P52" s="46" t="n">
         <v>45.15</v>
       </c>
-      <c r="Q52" s="42" t="n">
+      <c r="Q52" s="46" t="n">
         <v>41.05</v>
       </c>
-      <c r="R52" s="42" t="n">
+      <c r="R52" s="46" t="n">
         <v>33.5</v>
       </c>
-      <c r="S52" s="42" t="n">
+      <c r="S52" s="46" t="n">
         <f aca="false">R52/1.1</f>
         <v>30.4545454545455</v>
       </c>
@@ -12988,17 +13010,17 @@
       <c r="U52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V52" s="42" t="n">
+      <c r="V52" s="46" t="n">
         <v>26.5</v>
       </c>
-      <c r="W52" s="42" t="n">
+      <c r="W52" s="46" t="n">
         <f aca="false">V52*1.1</f>
         <v>29.15</v>
       </c>
-      <c r="X52" s="42" t="n">
+      <c r="X52" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y52" s="42" t="n">
+      <c r="Y52" s="46" t="n">
         <f aca="false">X52/1.1</f>
         <v>41.6</v>
       </c>
@@ -13178,16 +13200,16 @@
       <c r="K54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L54" s="42" t="n">
+      <c r="L54" s="46" t="n">
         <v>34.67</v>
       </c>
-      <c r="M54" s="42" t="n">
+      <c r="M54" s="46" t="n">
         <v>31.52</v>
       </c>
-      <c r="N54" s="42" t="n">
+      <c r="N54" s="46" t="n">
         <v>28.3</v>
       </c>
-      <c r="O54" s="42" t="n">
+      <c r="O54" s="46" t="n">
         <f aca="false">N54/1.1</f>
         <v>25.7272727272727</v>
       </c>
@@ -13197,10 +13219,10 @@
       <c r="Q54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R54" s="42" t="n">
+      <c r="R54" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S54" s="42" t="n">
+      <c r="S54" s="46" t="n">
         <f aca="false">R54/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -13216,10 +13238,10 @@
       <c r="W54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X54" s="42" t="n">
+      <c r="X54" s="46" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y54" s="42" t="n">
+      <c r="Y54" s="46" t="n">
         <f aca="false">X54/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -13311,10 +13333,10 @@
       <c r="Q55" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R55" s="42" t="n">
+      <c r="R55" s="46" t="n">
         <v>23</v>
       </c>
-      <c r="S55" s="42" t="n">
+      <c r="S55" s="46" t="n">
         <f aca="false">R55/1.1</f>
         <v>20.9090909090909</v>
       </c>
@@ -13342,8 +13364,8 @@
       <c r="AA55" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="AB55" s="42"/>
-      <c r="AC55" s="42"/>
+      <c r="AB55" s="47"/>
+      <c r="AC55" s="47"/>
       <c r="AD55" s="11" t="n">
         <f aca="false">IF(COUNT(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55)=0,"N/A",MIN(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55))</f>
         <v>20.9090909090909</v>
@@ -13412,16 +13434,16 @@
       <c r="O56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P56" s="42" t="n">
+      <c r="P56" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q56" s="42" t="n">
+      <c r="Q56" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R56" s="42" t="n">
+      <c r="R56" s="46" t="n">
         <v>33.5</v>
       </c>
-      <c r="S56" s="42" t="n">
+      <c r="S56" s="46" t="n">
         <f aca="false">R56/1.1</f>
         <v>30.4545454545455</v>
       </c>
@@ -13437,10 +13459,10 @@
       <c r="W56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X56" s="42" t="n">
+      <c r="X56" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y56" s="42" t="n">
+      <c r="Y56" s="46" t="n">
         <f aca="false">X56/1.1</f>
         <v>41.6</v>
       </c>
@@ -13450,8 +13472,8 @@
       <c r="AA56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB56" s="42"/>
-      <c r="AC56" s="42"/>
+      <c r="AB56" s="47"/>
+      <c r="AC56" s="47"/>
       <c r="AD56" s="11" t="n">
         <f aca="false">IF(COUNT(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56)=0,"N/A",MIN(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56))</f>
         <v>22</v>
@@ -13508,10 +13530,10 @@
       <c r="K57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L57" s="42" t="n">
+      <c r="L57" s="46" t="n">
         <v>39.47</v>
       </c>
-      <c r="M57" s="42" t="n">
+      <c r="M57" s="46" t="n">
         <v>35.88</v>
       </c>
       <c r="N57" s="42" t="s">
@@ -13526,10 +13548,10 @@
       <c r="Q57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R57" s="42" t="n">
+      <c r="R57" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="S57" s="42" t="n">
+      <c r="S57" s="46" t="n">
         <f aca="false">R57/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -13545,10 +13567,10 @@
       <c r="W57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X57" s="42" t="n">
+      <c r="X57" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y57" s="42" t="n">
+      <c r="Y57" s="46" t="n">
         <f aca="false">X57/1.1</f>
         <v>41.6</v>
       </c>
@@ -13628,23 +13650,23 @@
       <c r="M58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N58" s="42" t="n">
+      <c r="N58" s="46" t="n">
         <v>42.5</v>
       </c>
-      <c r="O58" s="42" t="n">
+      <c r="O58" s="46" t="n">
         <f aca="false">N58/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P58" s="42" t="n">
+      <c r="P58" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q58" s="42" t="n">
+      <c r="Q58" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R58" s="42" t="n">
+      <c r="R58" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="S58" s="42" t="n">
+      <c r="S58" s="46" t="n">
         <f aca="false">R58/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -13660,10 +13682,10 @@
       <c r="W58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X58" s="42" t="n">
+      <c r="X58" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y58" s="42" t="n">
+      <c r="Y58" s="46" t="n">
         <f aca="false">X58/1.1</f>
         <v>41.6</v>
       </c>
@@ -13743,10 +13765,10 @@
       <c r="M59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N59" s="42" t="n">
+      <c r="N59" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="O59" s="42" t="n">
+      <c r="O59" s="46" t="n">
         <f aca="false">N59/1.1</f>
         <v>25</v>
       </c>
@@ -13756,10 +13778,10 @@
       <c r="Q59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R59" s="42" t="n">
+      <c r="R59" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="S59" s="42" t="n">
+      <c r="S59" s="46" t="n">
         <f aca="false">R59/1.1</f>
         <v>20</v>
       </c>
@@ -13887,10 +13909,10 @@
       <c r="W60" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X60" s="42" t="n">
+      <c r="X60" s="46" t="n">
         <v>41.4</v>
       </c>
-      <c r="Y60" s="42" t="n">
+      <c r="Y60" s="46" t="n">
         <f aca="false">X60/1.1</f>
         <v>37.6363636363636</v>
       </c>
@@ -13964,16 +13986,16 @@
       <c r="K61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L61" s="42" t="n">
+      <c r="L61" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M61" s="42" t="n">
+      <c r="M61" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N61" s="42" t="n">
+      <c r="N61" s="46" t="n">
         <v>42.5</v>
       </c>
-      <c r="O61" s="42" t="n">
+      <c r="O61" s="46" t="n">
         <f aca="false">N61/1.1</f>
         <v>38.6363636363636</v>
       </c>
@@ -13983,10 +14005,10 @@
       <c r="Q61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R61" s="42" t="n">
+      <c r="R61" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="S61" s="42" t="n">
+      <c r="S61" s="46" t="n">
         <f aca="false">R61/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -14002,10 +14024,10 @@
       <c r="W61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X61" s="42" t="n">
+      <c r="X61" s="46" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y61" s="42" t="n">
+      <c r="Y61" s="46" t="n">
         <f aca="false">X61/1.1</f>
         <v>41.6</v>
       </c>
@@ -14079,29 +14101,29 @@
       <c r="K62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="42" t="n">
+      <c r="L62" s="46" t="n">
         <v>39.47</v>
       </c>
-      <c r="M62" s="42" t="n">
+      <c r="M62" s="46" t="n">
         <v>35.88</v>
       </c>
-      <c r="N62" s="42" t="n">
+      <c r="N62" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="O62" s="42" t="n">
+      <c r="O62" s="46" t="n">
         <f aca="false">N62/1.1</f>
         <v>25</v>
       </c>
-      <c r="P62" s="42" t="n">
+      <c r="P62" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q62" s="42" t="n">
+      <c r="Q62" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R62" s="42" t="n">
+      <c r="R62" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S62" s="42" t="n">
+      <c r="S62" s="46" t="n">
         <f aca="false">R62/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -14117,10 +14139,10 @@
       <c r="W62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X62" s="42" t="n">
+      <c r="X62" s="46" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y62" s="42" t="n">
+      <c r="Y62" s="46" t="n">
         <f aca="false">X62/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -14194,10 +14216,10 @@
       <c r="K63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L63" s="42" t="n">
+      <c r="L63" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M63" s="42" t="n">
+      <c r="M63" s="46" t="n">
         <v>35.98</v>
       </c>
       <c r="N63" s="42" t="s">
@@ -14206,16 +14228,16 @@
       <c r="O63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P63" s="42" t="n">
+      <c r="P63" s="46" t="n">
         <v>22.6</v>
       </c>
-      <c r="Q63" s="42" t="n">
+      <c r="Q63" s="46" t="n">
         <v>20.55</v>
       </c>
-      <c r="R63" s="42" t="n">
+      <c r="R63" s="46" t="n">
         <v>23</v>
       </c>
-      <c r="S63" s="42" t="n">
+      <c r="S63" s="46" t="n">
         <f aca="false">R63/1.1</f>
         <v>20.9090909090909</v>
       </c>
@@ -14231,10 +14253,10 @@
       <c r="W63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X63" s="42" t="n">
+      <c r="X63" s="46" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y63" s="42" t="n">
+      <c r="Y63" s="46" t="n">
         <f aca="false">X63/1.1</f>
         <v>29.0545454545455</v>
       </c>
@@ -14308,29 +14330,29 @@
       <c r="K64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L64" s="42" t="n">
+      <c r="L64" s="46" t="n">
         <v>39.58</v>
       </c>
-      <c r="M64" s="42" t="n">
+      <c r="M64" s="46" t="n">
         <v>35.98</v>
       </c>
-      <c r="N64" s="42" t="n">
+      <c r="N64" s="46" t="n">
         <v>27.5</v>
       </c>
-      <c r="O64" s="42" t="n">
+      <c r="O64" s="46" t="n">
         <f aca="false">N64/1.1</f>
         <v>25</v>
       </c>
-      <c r="P64" s="42" t="n">
+      <c r="P64" s="46" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q64" s="42" t="n">
+      <c r="Q64" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="R64" s="42" t="n">
+      <c r="R64" s="46" t="n">
         <v>22.5</v>
       </c>
-      <c r="S64" s="42" t="n">
+      <c r="S64" s="46" t="n">
         <f aca="false">R64/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -14346,10 +14368,10 @@
       <c r="W64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X64" s="42" t="n">
+      <c r="X64" s="46" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y64" s="42" t="n">
+      <c r="Y64" s="46" t="n">
         <f aca="false">X64/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -14423,10 +14445,10 @@
       <c r="K65" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L65" s="42" t="n">
+      <c r="L65" s="46" t="n">
         <v>39.47</v>
       </c>
-      <c r="M65" s="42" t="n">
+      <c r="M65" s="46" t="n">
         <v>35.88</v>
       </c>
       <c r="N65" s="11" t="n">
@@ -14511,7 +14533,7 @@
       </c>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
-      <c r="D68" s="46" t="n">
+      <c r="D68" s="48" t="n">
         <f aca="false">COUNTA(B6:B65)</f>
         <v>60</v>
       </c>
@@ -14522,7 +14544,7 @@
       </c>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
-      <c r="D69" s="46" t="n">
+      <c r="D69" s="48" t="n">
         <f aca="false">COUNTIF(J6:J65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(V6:V65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")+COUNTIF(AC6:AC65,"&gt;0")</f>
         <v>407</v>
       </c>
@@ -14533,7 +14555,7 @@
       </c>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
-      <c r="D70" s="46" t="n">
+      <c r="D70" s="48" t="n">
         <f aca="false">COUNTIF(AE6:AE65,"&lt;0")</f>
         <v>53</v>
       </c>
@@ -14544,7 +14566,7 @@
       </c>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
-      <c r="D71" s="46" t="n">
+      <c r="D71" s="48" t="n">
         <f aca="false">COUNTIF(AE6:AE65,"&gt;0")</f>
         <v>7</v>
       </c>
@@ -14555,7 +14577,7 @@
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
-      <c r="D72" s="47" t="n">
+      <c r="D72" s="49" t="n">
         <f aca="false">AVERAGE(AE6:AE65)</f>
         <v>-0.454866678565887</v>
       </c>
@@ -14566,7 +14588,7 @@
       </c>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
-      <c r="D73" s="47" t="n">
+      <c r="D73" s="49" t="n">
         <f aca="false">MEDIAN(AE6:AE65)</f>
         <v>-0.523652597402597</v>
       </c>
@@ -14577,7 +14599,7 @@
       </c>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
-      <c r="D74" s="46" t="n">
+      <c r="D74" s="48" t="n">
         <f aca="false">COUNTIF(AF6:AF65,"&lt;0")</f>
         <v>15</v>
       </c>
@@ -14588,7 +14610,7 @@
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
-      <c r="D75" s="46" t="n">
+      <c r="D75" s="48" t="n">
         <f aca="false">COUNTIF(AF6:AF65,"&gt;0")</f>
         <v>7</v>
       </c>
@@ -14599,7 +14621,7 @@
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
-      <c r="D76" s="47" t="n">
+      <c r="D76" s="49" t="n">
         <f aca="false">AVERAGE(AF6:AF65)</f>
         <v>-0.137849955170021</v>
       </c>
@@ -14610,7 +14632,7 @@
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
-      <c r="D77" s="47" t="n">
+      <c r="D77" s="49" t="n">
         <f aca="false">MEDIAN(AF6:AF65)</f>
         <v>-0.240924975181021</v>
       </c>
@@ -14631,6 +14653,21 @@
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A77:C77"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD6:AD65">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>EXACT(AD6,"N/A")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AE65">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>EXACT(AE6,"N/A")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF6:AF65">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>EXACT(AF6,"N/A")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14662,62 +14699,62 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="52" t="s">
         <v>333</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="52" t="s">
         <v>334</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="52" t="s">
         <v>335</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="52" t="s">
         <v>336</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="52" t="s">
         <v>337</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="J4" s="50" t="s">
+      <c r="J4" s="52" t="s">
         <v>221</v>
       </c>
     </row>
@@ -14737,13 +14774,13 @@
       <c r="E5" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="53" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="54" t="n">
         <v>-3.11725</v>
       </c>
-      <c r="H5" s="53" t="n">
+      <c r="H5" s="55" t="n">
         <v>-0.155473815461347</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -14766,13 +14803,13 @@
       <c r="E6" s="11" t="n">
         <v>122.718181818182</v>
       </c>
-      <c r="F6" s="54" t="n">
+      <c r="F6" s="56" t="n">
         <v>66.83</v>
       </c>
-      <c r="G6" s="52" t="n">
+      <c r="G6" s="54" t="n">
         <v>-55.888181818182</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="55" t="n">
         <v>-0.455418919919995</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -14795,13 +14832,13 @@
       <c r="E7" s="11" t="n">
         <v>128.75</v>
       </c>
-      <c r="F7" s="54" t="n">
+      <c r="F7" s="56" t="n">
         <v>44.55</v>
       </c>
-      <c r="G7" s="52" t="n">
+      <c r="G7" s="54" t="n">
         <v>-84.2</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="55" t="n">
         <v>-0.653980582524272</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -14824,13 +14861,13 @@
       <c r="E8" s="11" t="n">
         <v>69.245</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="53" t="n">
         <v>45.144</v>
       </c>
-      <c r="G8" s="52" t="n">
+      <c r="G8" s="54" t="n">
         <v>-24.101</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="55" t="n">
         <v>-0.348054011119937</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -14853,13 +14890,13 @@
       <c r="E9" s="11" t="n">
         <v>81.4</v>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="53" t="n">
         <v>70.538125</v>
       </c>
-      <c r="G9" s="52" t="n">
+      <c r="G9" s="54" t="n">
         <v>-10.861875</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="55" t="n">
         <v>-0.133438267813268</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -14882,13 +14919,13 @@
       <c r="E10" s="11" t="n">
         <v>44.209</v>
       </c>
-      <c r="F10" s="51" t="n">
+      <c r="F10" s="53" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G10" s="52" t="n">
+      <c r="G10" s="54" t="n">
         <v>-10.3535</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="55" t="n">
         <v>-0.234194394806487</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -14911,13 +14948,13 @@
       <c r="E11" s="11" t="n">
         <v>70.36</v>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="53" t="n">
         <v>45.144</v>
       </c>
-      <c r="G11" s="52" t="n">
+      <c r="G11" s="54" t="n">
         <v>-25.216</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="55" t="n">
         <v>-0.358385446276293</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -14925,34 +14962,34 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="E12" s="57" t="n">
+      <c r="E12" s="59" t="n">
         <v>33.1818181818182</v>
       </c>
-      <c r="F12" s="58" t="n">
+      <c r="F12" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G12" s="59" t="n">
+      <c r="G12" s="61" t="n">
         <v>0.673681818181798</v>
       </c>
-      <c r="H12" s="60" t="n">
+      <c r="H12" s="62" t="n">
         <v>0.0203027397260268</v>
       </c>
-      <c r="I12" s="61" t="s">
+      <c r="I12" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J12" s="55"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -14970,13 +15007,13 @@
       <c r="E13" s="11" t="n">
         <v>43.09</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="53" t="n">
         <v>25.394125</v>
       </c>
-      <c r="G13" s="52" t="n">
+      <c r="G13" s="54" t="n">
         <v>-17.695875</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="55" t="n">
         <v>-0.410672429798097</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -14999,13 +15036,13 @@
       <c r="E14" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="53" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G14" s="52" t="n">
+      <c r="G14" s="54" t="n">
         <v>-13.538625</v>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H14" s="55" t="n">
         <v>-0.615392045454545</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -15028,13 +15065,13 @@
       <c r="E15" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="F15" s="51" t="n">
+      <c r="F15" s="53" t="n">
         <v>15.81275</v>
       </c>
-      <c r="G15" s="52" t="n">
+      <c r="G15" s="54" t="n">
         <v>-6.08725</v>
       </c>
-      <c r="H15" s="53" t="n">
+      <c r="H15" s="55" t="n">
         <v>-0.277956621004566</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -15057,13 +15094,13 @@
       <c r="E16" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="F16" s="51" t="n">
+      <c r="F16" s="53" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G16" s="52" t="n">
+      <c r="G16" s="54" t="n">
         <v>-2.038625</v>
       </c>
-      <c r="H16" s="53" t="n">
+      <c r="H16" s="55" t="n">
         <v>-0.194154761904762</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -15086,13 +15123,13 @@
       <c r="E17" s="11" t="n">
         <v>37.3909090909091</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="53" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G17" s="52" t="n">
+      <c r="G17" s="54" t="n">
         <v>-7.2454090909091</v>
       </c>
-      <c r="H17" s="53" t="n">
+      <c r="H17" s="55" t="n">
         <v>-0.193774617067834</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -15100,34 +15137,34 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="57" t="s">
         <v>347</v>
       </c>
-      <c r="E18" s="57" t="n">
+      <c r="E18" s="59" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="F18" s="58" t="n">
+      <c r="F18" s="60" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G18" s="59" t="n">
+      <c r="G18" s="61" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="H18" s="60" t="n">
+      <c r="H18" s="62" t="n">
         <v>0.0631628727156122</v>
       </c>
-      <c r="I18" s="61" t="s">
+      <c r="I18" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J18" s="55"/>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -15145,13 +15182,13 @@
       <c r="E19" s="11" t="n">
         <v>23.3090909090909</v>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="53" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G19" s="54" t="n">
         <v>-6.3763409090909</v>
       </c>
-      <c r="H19" s="53" t="n">
+      <c r="H19" s="55" t="n">
         <v>-0.273555967238689</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -15159,34 +15196,34 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="57" t="s">
         <v>348</v>
       </c>
-      <c r="E20" s="57" t="n">
+      <c r="E20" s="59" t="n">
         <v>33.7</v>
       </c>
-      <c r="F20" s="58" t="n">
+      <c r="F20" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G20" s="59" t="n">
+      <c r="G20" s="61" t="n">
         <v>0.155499999999996</v>
       </c>
-      <c r="H20" s="60" t="n">
+      <c r="H20" s="62" t="n">
         <v>0.00461424332344203</v>
       </c>
-      <c r="I20" s="61" t="s">
+      <c r="I20" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J20" s="55"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -15204,13 +15241,13 @@
       <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F21" s="53" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G21" s="52" t="n">
+      <c r="G21" s="54" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H21" s="53" t="n">
+      <c r="H21" s="55" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -15233,13 +15270,13 @@
       <c r="E22" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F22" s="51" t="n">
+      <c r="F22" s="53" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G22" s="52" t="n">
+      <c r="G22" s="54" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H22" s="53" t="n">
+      <c r="H22" s="55" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -15262,13 +15299,13 @@
       <c r="E23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F23" s="51" t="n">
+      <c r="F23" s="53" t="n">
         <v>6.011375</v>
       </c>
-      <c r="G23" s="52" t="n">
+      <c r="G23" s="54" t="n">
         <v>-15.988625</v>
       </c>
-      <c r="H23" s="53" t="n">
+      <c r="H23" s="55" t="n">
         <v>-0.726755681818182</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -15276,64 +15313,64 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E24" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F24" s="58" t="n">
+      <c r="F24" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G24" s="59" t="n">
+      <c r="G24" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H24" s="60" t="n">
+      <c r="H24" s="62" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I24" s="61" t="s">
+      <c r="I24" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J24" s="55"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="E25" s="57" t="n">
+      <c r="E25" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F25" s="58" t="n">
+      <c r="F25" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G25" s="59" t="n">
+      <c r="G25" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H25" s="60" t="n">
+      <c r="H25" s="62" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I25" s="61" t="s">
+      <c r="I25" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J25" s="55"/>
+      <c r="J25" s="57"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -15351,13 +15388,13 @@
       <c r="E26" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F26" s="51" t="n">
+      <c r="F26" s="53" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G26" s="52" t="n">
+      <c r="G26" s="54" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H26" s="53" t="n">
+      <c r="H26" s="55" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -15365,34 +15402,34 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="E27" s="57" t="n">
+      <c r="E27" s="59" t="n">
         <v>32.5</v>
       </c>
-      <c r="F27" s="58" t="n">
+      <c r="F27" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G27" s="59" t="n">
+      <c r="G27" s="61" t="n">
         <v>1.3555</v>
       </c>
-      <c r="H27" s="60" t="n">
+      <c r="H27" s="62" t="n">
         <v>0.0417076923076923</v>
       </c>
-      <c r="I27" s="61" t="s">
+      <c r="I27" s="63" t="s">
         <v>346</v>
       </c>
-      <c r="J27" s="55"/>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -15410,13 +15447,13 @@
       <c r="E28" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F28" s="51" t="n">
+      <c r="F28" s="53" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G28" s="52" t="n">
+      <c r="G28" s="54" t="n">
         <v>-11.1445</v>
       </c>
-      <c r="H28" s="53" t="n">
+      <c r="H28" s="55" t="n">
         <v>-0.247655555555556</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -15439,13 +15476,13 @@
       <c r="E29" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="F29" s="54" t="n">
+      <c r="F29" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G29" s="52" t="n">
+      <c r="G29" s="54" t="n">
         <v>-17.73</v>
       </c>
-      <c r="H29" s="53" t="n">
+      <c r="H29" s="55" t="n">
         <v>-0.575649350649351</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -15468,13 +15505,13 @@
       <c r="E30" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="F30" s="54" t="n">
+      <c r="F30" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G30" s="52" t="n">
+      <c r="G30" s="54" t="n">
         <v>-14.93</v>
       </c>
-      <c r="H30" s="53" t="n">
+      <c r="H30" s="55" t="n">
         <v>-0.533214285714286</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -15497,13 +15534,13 @@
       <c r="E31" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F31" s="54" t="n">
+      <c r="F31" s="56" t="n">
         <v>16.04</v>
       </c>
-      <c r="G31" s="52" t="n">
+      <c r="G31" s="54" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H31" s="53" t="n">
+      <c r="H31" s="55" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -15526,13 +15563,13 @@
       <c r="E32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F32" s="54" t="n">
+      <c r="F32" s="56" t="n">
         <v>16.04</v>
       </c>
-      <c r="G32" s="52" t="n">
+      <c r="G32" s="54" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H32" s="53" t="n">
+      <c r="H32" s="55" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -15555,13 +15592,13 @@
       <c r="E33" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F33" s="54" t="n">
+      <c r="F33" s="56" t="n">
         <v>16.04</v>
       </c>
-      <c r="G33" s="52" t="n">
+      <c r="G33" s="54" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H33" s="53" t="n">
+      <c r="H33" s="55" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -15584,13 +15621,13 @@
       <c r="E34" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F34" s="54" t="n">
+      <c r="F34" s="56" t="n">
         <v>16.04</v>
       </c>
-      <c r="G34" s="52" t="n">
+      <c r="G34" s="54" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H34" s="53" t="n">
+      <c r="H34" s="55" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -15613,13 +15650,13 @@
       <c r="E35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F35" s="54" t="n">
+      <c r="F35" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G35" s="52" t="n">
+      <c r="G35" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H35" s="53" t="n">
+      <c r="H35" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -15642,13 +15679,13 @@
       <c r="E36" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F36" s="54" t="n">
+      <c r="F36" s="56" t="n">
         <v>16.04</v>
       </c>
-      <c r="G36" s="52" t="n">
+      <c r="G36" s="54" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H36" s="53" t="n">
+      <c r="H36" s="55" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -15671,13 +15708,13 @@
       <c r="E37" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F37" s="54" t="n">
+      <c r="F37" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G37" s="52" t="n">
+      <c r="G37" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H37" s="53" t="n">
+      <c r="H37" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -15700,13 +15737,13 @@
       <c r="E38" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F38" s="54" t="n">
+      <c r="F38" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G38" s="52" t="n">
+      <c r="G38" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H38" s="53" t="n">
+      <c r="H38" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -15729,13 +15766,13 @@
       <c r="E39" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F39" s="54" t="n">
+      <c r="F39" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G39" s="52" t="n">
+      <c r="G39" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H39" s="53" t="n">
+      <c r="H39" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -15758,13 +15795,13 @@
       <c r="E40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F40" s="54" t="n">
+      <c r="F40" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G40" s="52" t="n">
+      <c r="G40" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H40" s="53" t="n">
+      <c r="H40" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -15787,13 +15824,13 @@
       <c r="E41" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F41" s="54" t="n">
+      <c r="F41" s="56" t="n">
         <v>13.07</v>
       </c>
-      <c r="G41" s="52" t="n">
+      <c r="G41" s="54" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H41" s="53" t="n">
+      <c r="H41" s="55" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -15816,13 +15853,13 @@
       <c r="E42" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="F42" s="54" t="n">
+      <c r="F42" s="56" t="n">
         <v>5.35</v>
       </c>
-      <c r="G42" s="52" t="n">
+      <c r="G42" s="54" t="n">
         <v>-14.7</v>
       </c>
-      <c r="H42" s="53" t="n">
+      <c r="H42" s="55" t="n">
         <v>-0.733167082294264</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -15845,13 +15882,13 @@
       <c r="E43" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F43" s="54" t="n">
+      <c r="F43" s="56" t="n">
         <v>2.67</v>
       </c>
-      <c r="G43" s="52" t="n">
+      <c r="G43" s="54" t="n">
         <v>-6.68454545454545</v>
       </c>
-      <c r="H43" s="53" t="n">
+      <c r="H43" s="55" t="n">
         <v>-0.714577259475219</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -15874,13 +15911,13 @@
       <c r="E44" s="11" t="n">
         <v>23.4090909090909</v>
       </c>
-      <c r="F44" s="54" t="n">
+      <c r="F44" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G44" s="52" t="n">
+      <c r="G44" s="54" t="n">
         <v>-12.7190909090909</v>
       </c>
-      <c r="H44" s="53" t="n">
+      <c r="H44" s="55" t="n">
         <v>-0.543339805825243</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -15903,13 +15940,13 @@
       <c r="E45" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F45" s="54" t="n">
+      <c r="F45" s="56" t="n">
         <v>2.67</v>
       </c>
-      <c r="G45" s="52" t="n">
+      <c r="G45" s="54" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H45" s="53" t="n">
+      <c r="H45" s="55" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -15932,13 +15969,13 @@
       <c r="E46" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="54" t="n">
+      <c r="F46" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="G46" s="52" t="n">
+      <c r="G46" s="54" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H46" s="53" t="n">
+      <c r="H46" s="55" t="n">
         <v>-0.568181818181818</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -15961,13 +15998,13 @@
       <c r="E47" s="11" t="n">
         <v>16.7363636363636</v>
       </c>
-      <c r="F47" s="54" t="n">
+      <c r="F47" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G47" s="52" t="n">
+      <c r="G47" s="54" t="n">
         <v>-6.0463636363636</v>
       </c>
-      <c r="H47" s="53" t="n">
+      <c r="H47" s="55" t="n">
         <v>-0.36127104834329</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -15990,13 +16027,13 @@
       <c r="E48" s="11" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="F48" s="54" t="n">
+      <c r="F48" s="56" t="n">
         <v>5.35</v>
       </c>
-      <c r="G48" s="52" t="n">
+      <c r="G48" s="54" t="n">
         <v>-15.5590909090909</v>
       </c>
-      <c r="H48" s="53" t="n">
+      <c r="H48" s="55" t="n">
         <v>-0.744130434782609</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -16019,13 +16056,13 @@
       <c r="E49" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F49" s="54" t="n">
+      <c r="F49" s="56" t="n">
         <v>5.35</v>
       </c>
-      <c r="G49" s="52" t="n">
+      <c r="G49" s="54" t="n">
         <v>-4.00454545454545</v>
       </c>
-      <c r="H49" s="53" t="n">
+      <c r="H49" s="55" t="n">
         <v>-0.428085519922254</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -16048,13 +16085,13 @@
       <c r="E50" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="F50" s="54" t="n">
+      <c r="F50" s="56" t="n">
         <v>2.67</v>
       </c>
-      <c r="G50" s="52" t="n">
+      <c r="G50" s="54" t="n">
         <v>-7.83</v>
       </c>
-      <c r="H50" s="53" t="n">
+      <c r="H50" s="55" t="n">
         <v>-0.745714285714286</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -16077,13 +16114,13 @@
       <c r="E51" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="F51" s="54" t="n">
+      <c r="F51" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="G51" s="52" t="n">
+      <c r="G51" s="54" t="n">
         <v>-17</v>
       </c>
-      <c r="H51" s="53" t="n">
+      <c r="H51" s="55" t="n">
         <v>-0.641509433962264</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -16106,13 +16143,13 @@
       <c r="E52" s="11" t="n">
         <v>7.81818181818182</v>
       </c>
-      <c r="F52" s="54" t="n">
+      <c r="F52" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="52" t="n">
+      <c r="G52" s="54" t="n">
         <v>-5.81818181818182</v>
       </c>
-      <c r="H52" s="53" t="n">
+      <c r="H52" s="55" t="n">
         <v>-0.744186046511628</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -16135,13 +16172,13 @@
       <c r="E53" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F53" s="54" t="n">
+      <c r="F53" s="56" t="n">
         <v>2.67</v>
       </c>
-      <c r="G53" s="52" t="n">
+      <c r="G53" s="54" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H53" s="53" t="n">
+      <c r="H53" s="55" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -16164,13 +16201,13 @@
       <c r="E54" s="11" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="F54" s="54" t="n">
+      <c r="F54" s="56" t="n">
         <v>4.01</v>
       </c>
-      <c r="G54" s="52" t="n">
+      <c r="G54" s="54" t="n">
         <v>-16.8990909090909</v>
       </c>
-      <c r="H54" s="53" t="n">
+      <c r="H54" s="55" t="n">
         <v>-0.808217391304348</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -16193,13 +16230,13 @@
       <c r="E55" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F55" s="54" t="n">
+      <c r="F55" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G55" s="52" t="n">
+      <c r="G55" s="54" t="n">
         <v>-11.31</v>
       </c>
-      <c r="H55" s="53" t="n">
+      <c r="H55" s="55" t="n">
         <v>-0.514090909090909</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -16222,13 +16259,13 @@
       <c r="E56" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F56" s="54" t="n">
+      <c r="F56" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G56" s="52" t="n">
+      <c r="G56" s="54" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H56" s="53" t="n">
+      <c r="H56" s="55" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -16251,13 +16288,13 @@
       <c r="E57" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F57" s="54" t="n">
+      <c r="F57" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G57" s="52" t="n">
+      <c r="G57" s="54" t="n">
         <v>-11.31</v>
       </c>
-      <c r="H57" s="53" t="n">
+      <c r="H57" s="55" t="n">
         <v>-0.514090909090909</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -16280,13 +16317,13 @@
       <c r="E58" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F58" s="54" t="n">
+      <c r="F58" s="56" t="n">
         <v>2.89</v>
       </c>
-      <c r="G58" s="52" t="n">
+      <c r="G58" s="54" t="n">
         <v>-17.11</v>
       </c>
-      <c r="H58" s="53" t="n">
+      <c r="H58" s="55" t="n">
         <v>-0.8555</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -16309,13 +16346,13 @@
       <c r="E59" s="11" t="n">
         <v>37.6363636363636</v>
       </c>
-      <c r="F59" s="54" t="n">
+      <c r="F59" s="56" t="n">
         <v>1.94</v>
       </c>
-      <c r="G59" s="52" t="n">
+      <c r="G59" s="54" t="n">
         <v>-35.6963636363636</v>
       </c>
-      <c r="H59" s="53" t="n">
+      <c r="H59" s="55" t="n">
         <v>-0.948454106280193</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -16338,13 +16375,13 @@
       <c r="E60" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F60" s="54" t="n">
+      <c r="F60" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G60" s="52" t="n">
+      <c r="G60" s="54" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H60" s="53" t="n">
+      <c r="H60" s="55" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -16367,13 +16404,13 @@
       <c r="E61" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F61" s="54" t="n">
+      <c r="F61" s="56" t="n">
         <v>3.201</v>
       </c>
-      <c r="G61" s="52" t="n">
+      <c r="G61" s="54" t="n">
         <v>-17.2535454545455</v>
       </c>
-      <c r="H61" s="53" t="n">
+      <c r="H61" s="55" t="n">
         <v>-0.843506666666667</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -16396,13 +16433,13 @@
       <c r="E62" s="11" t="n">
         <v>20.55</v>
       </c>
-      <c r="F62" s="54" t="n">
+      <c r="F62" s="56" t="n">
         <v>5.35</v>
       </c>
-      <c r="G62" s="52" t="n">
+      <c r="G62" s="54" t="n">
         <v>-15.2</v>
       </c>
-      <c r="H62" s="53" t="n">
+      <c r="H62" s="55" t="n">
         <v>-0.739659367396594</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -16425,13 +16462,13 @@
       <c r="E63" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F63" s="54" t="n">
+      <c r="F63" s="56" t="n">
         <v>2.67</v>
       </c>
-      <c r="G63" s="52" t="n">
+      <c r="G63" s="54" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H63" s="53" t="n">
+      <c r="H63" s="55" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -16454,13 +16491,13 @@
       <c r="E64" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F64" s="54" t="n">
+      <c r="F64" s="56" t="n">
         <v>10.69</v>
       </c>
-      <c r="G64" s="52" t="n">
+      <c r="G64" s="54" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H64" s="53" t="n">
+      <c r="H64" s="55" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -16468,200 +16505,200 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="62" t="s">
+      <c r="A66" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="B66" s="62"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="62"/>
-      <c r="E66" s="62"/>
-      <c r="F66" s="62"/>
-      <c r="G66" s="62"/>
-      <c r="H66" s="62"/>
-      <c r="I66" s="62"/>
-      <c r="J66" s="62"/>
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="50" t="s">
+      <c r="A67" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="50" t="s">
+      <c r="B67" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="50" t="s">
+      <c r="C67" s="52" t="s">
         <v>351</v>
       </c>
-      <c r="D67" s="50" t="s">
+      <c r="D67" s="52" t="s">
         <v>352</v>
       </c>
-      <c r="E67" s="50" t="s">
+      <c r="E67" s="52" t="s">
         <v>353</v>
       </c>
-      <c r="F67" s="50" t="s">
+      <c r="F67" s="52" t="s">
         <v>354</v>
       </c>
-      <c r="G67" s="50" t="s">
+      <c r="G67" s="52" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="55" t="s">
+      <c r="A68" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="55" t="s">
+      <c r="C68" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="D68" s="57" t="n">
+      <c r="D68" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E68" s="57" t="n">
+      <c r="E68" s="59" t="n">
         <v>16.93275</v>
       </c>
-      <c r="F68" s="59" t="n">
+      <c r="F68" s="61" t="n">
         <v>7.57820454545455</v>
       </c>
-      <c r="G68" s="60" t="n">
+      <c r="G68" s="62" t="n">
         <v>0.447547181967167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="55" t="s">
+      <c r="A69" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="56" t="s">
+      <c r="B69" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="55" t="s">
+      <c r="C69" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="D69" s="57" t="n">
+      <c r="D69" s="59" t="n">
         <v>21.2</v>
       </c>
-      <c r="E69" s="57" t="n">
+      <c r="E69" s="59" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F69" s="59" t="n">
+      <c r="F69" s="61" t="n">
         <v>12.6555</v>
       </c>
-      <c r="G69" s="60" t="n">
+      <c r="G69" s="62" t="n">
         <v>0.373809277665372</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="55" t="s">
+      <c r="A70" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="D70" s="57" t="n">
+      <c r="D70" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E70" s="57" t="n">
+      <c r="E70" s="59" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F70" s="59" t="n">
+      <c r="F70" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G70" s="60" t="n">
+      <c r="G70" s="62" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="55" t="s">
+      <c r="A71" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="55" t="s">
+      <c r="C71" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="D71" s="57" t="n">
+      <c r="D71" s="59" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E71" s="57" t="n">
+      <c r="E71" s="59" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F71" s="59" t="n">
+      <c r="F71" s="61" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G71" s="60" t="n">
+      <c r="G71" s="62" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="55" t="s">
+      <c r="A72" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="55" t="s">
+      <c r="C72" s="57" t="s">
         <v>347</v>
       </c>
-      <c r="D72" s="57" t="n">
+      <c r="D72" s="59" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E72" s="57" t="n">
+      <c r="E72" s="59" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F72" s="59" t="n">
+      <c r="F72" s="61" t="n">
         <v>5.5009545454545</v>
       </c>
-      <c r="G72" s="60" t="n">
+      <c r="G72" s="62" t="n">
         <v>0.162483334922081</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="C73" s="55" t="s">
+      <c r="C73" s="57" t="s">
         <v>347</v>
       </c>
-      <c r="D73" s="57" t="n">
+      <c r="D73" s="59" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E73" s="57" t="n">
+      <c r="E73" s="59" t="n">
         <v>30.1455</v>
       </c>
-      <c r="F73" s="59" t="n">
+      <c r="F73" s="61" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="G73" s="60" t="n">
+      <c r="G73" s="62" t="n">
         <v>0.0594103446768007</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="55" t="s">
+      <c r="A74" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="56" t="s">
+      <c r="B74" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="55" t="s">
+      <c r="C74" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="D74" s="57" t="n">
+      <c r="D74" s="59" t="n">
         <v>32.5</v>
       </c>
-      <c r="E74" s="57" t="n">
+      <c r="E74" s="59" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F74" s="59" t="n">
+      <c r="F74" s="61" t="n">
         <v>1.3555</v>
       </c>
-      <c r="G74" s="60" t="n">
+      <c r="G74" s="62" t="n">
         <v>0.0400378077417258</v>
       </c>
     </row>

--- a/output/RSEA_Comparison_Finished1.xlsx
+++ b/output/RSEA_Comparison_Finished1.xlsx
@@ -1140,16 +1140,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);[RED]&quot;($&quot;#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1258,6 +1257,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1447,7 +1454,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1632,11 +1639,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1648,31 +1659,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1688,23 +1699,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1821,9 +1832,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>401040</xdr:colOff>
+      <xdr:colOff>400680</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>257400</xdr:rowOff>
+      <xdr:rowOff>257040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1837,7 +1848,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17428680" y="22115880"/>
-          <a:ext cx="2188800" cy="2334960"/>
+          <a:ext cx="2188440" cy="2334600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7828,8 +7839,8 @@
       <c r="AA7" s="45" t="n">
         <v>128.75</v>
       </c>
-      <c r="AB7" s="45"/>
-      <c r="AC7" s="45"/>
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="46"/>
       <c r="AD7" s="11" t="n">
         <f aca="false">IF(COUNT(I7,J7,M7,O7,Q7,S7,U7,V7,Y7,AA7,AC7)=0,"N/A",MIN(I7,J7,M7,O7,Q7,S7,U7,V7,Y7,AA7,AC7))</f>
         <v>122.718181818182</v>
@@ -7935,8 +7946,8 @@
       <c r="AA8" s="45" t="n">
         <v>128.75</v>
       </c>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="45"/>
+      <c r="AB8" s="46"/>
+      <c r="AC8" s="46"/>
       <c r="AD8" s="11" t="n">
         <f aca="false">IF(COUNT(I8,J8,M8,O8,Q8,S8,U8,V8,Y8,AA8,AC8)=0,"N/A",MIN(I8,J8,M8,O8,Q8,S8,U8,V8,Y8,AA8,AC8))</f>
         <v>128.75</v>
@@ -8706,23 +8717,23 @@
       <c r="M15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N15" s="46" t="n">
+      <c r="N15" s="47" t="n">
         <v>35.7</v>
       </c>
-      <c r="O15" s="46" t="n">
+      <c r="O15" s="47" t="n">
         <f aca="false">N15/1.1</f>
         <v>32.4545454545455</v>
       </c>
-      <c r="P15" s="46" t="n">
+      <c r="P15" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q15" s="46" t="n">
+      <c r="Q15" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R15" s="46" t="n">
+      <c r="R15" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="S15" s="46" t="n">
+      <c r="S15" s="47" t="n">
         <f aca="false">R15/1.1</f>
         <v>22.7272727272727</v>
       </c>
@@ -8738,10 +8749,10 @@
       <c r="W15" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X15" s="46" t="n">
+      <c r="X15" s="47" t="n">
         <v>35.07</v>
       </c>
-      <c r="Y15" s="46" t="n">
+      <c r="Y15" s="47" t="n">
         <f aca="false">X15/1.1</f>
         <v>31.8818181818182</v>
       </c>
@@ -8815,29 +8826,29 @@
       <c r="K16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L16" s="46" t="n">
+      <c r="L16" s="47" t="n">
         <v>48.29</v>
       </c>
-      <c r="M16" s="46" t="n">
+      <c r="M16" s="47" t="n">
         <v>43.9</v>
       </c>
-      <c r="N16" s="46" t="n">
+      <c r="N16" s="47" t="n">
         <v>39.95</v>
       </c>
-      <c r="O16" s="46" t="n">
+      <c r="O16" s="47" t="n">
         <f aca="false">N16/1.1</f>
         <v>36.3181818181818</v>
       </c>
-      <c r="P16" s="46" t="n">
+      <c r="P16" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q16" s="46" t="n">
+      <c r="Q16" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R16" s="46" t="n">
+      <c r="R16" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="S16" s="46" t="n">
+      <c r="S16" s="47" t="n">
         <f aca="false">R16/1.1</f>
         <v>25</v>
       </c>
@@ -8847,17 +8858,17 @@
       <c r="U16" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V16" s="46" t="n">
+      <c r="V16" s="47" t="n">
         <v>21.9</v>
       </c>
-      <c r="W16" s="46" t="n">
+      <c r="W16" s="47" t="n">
         <f aca="false">V16*1.1</f>
         <v>24.09</v>
       </c>
-      <c r="X16" s="46" t="n">
+      <c r="X16" s="47" t="n">
         <v>42.75</v>
       </c>
-      <c r="Y16" s="46" t="n">
+      <c r="Y16" s="47" t="n">
         <f aca="false">X16/1.1</f>
         <v>38.8636363636364</v>
       </c>
@@ -8931,29 +8942,29 @@
       <c r="K17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L17" s="46" t="n">
+      <c r="L17" s="47" t="n">
         <v>53.63</v>
       </c>
-      <c r="M17" s="46" t="n">
+      <c r="M17" s="47" t="n">
         <v>48.75</v>
       </c>
-      <c r="N17" s="46" t="n">
+      <c r="N17" s="47" t="n">
         <v>35.7</v>
       </c>
-      <c r="O17" s="46" t="n">
+      <c r="O17" s="47" t="n">
         <f aca="false">N17/1.1</f>
         <v>32.4545454545455</v>
       </c>
-      <c r="P17" s="46" t="n">
+      <c r="P17" s="47" t="n">
         <v>11.55</v>
       </c>
-      <c r="Q17" s="46" t="n">
+      <c r="Q17" s="47" t="n">
         <v>10.5</v>
       </c>
-      <c r="R17" s="46" t="n">
+      <c r="R17" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="S17" s="46" t="n">
+      <c r="S17" s="47" t="n">
         <f aca="false">R17/1.1</f>
         <v>22.7272727272727</v>
       </c>
@@ -8969,10 +8980,10 @@
       <c r="W17" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X17" s="46" t="n">
+      <c r="X17" s="47" t="n">
         <v>35.07</v>
       </c>
-      <c r="Y17" s="46" t="n">
+      <c r="Y17" s="47" t="n">
         <f aca="false">X17/1.1</f>
         <v>31.8818181818182</v>
       </c>
@@ -9052,10 +9063,10 @@
       <c r="M18" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N18" s="46" t="n">
+      <c r="N18" s="47" t="n">
         <v>49.5</v>
       </c>
-      <c r="O18" s="46" t="n">
+      <c r="O18" s="47" t="n">
         <f aca="false">N18/1.1</f>
         <v>45</v>
       </c>
@@ -9163,10 +9174,10 @@
       <c r="K19" s="11" t="n">
         <v>99.23</v>
       </c>
-      <c r="L19" s="46" t="n">
+      <c r="L19" s="47" t="n">
         <v>61.59</v>
       </c>
-      <c r="M19" s="46" t="n">
+      <c r="M19" s="47" t="n">
         <v>55.99</v>
       </c>
       <c r="N19" s="11" t="n">
@@ -9416,10 +9427,10 @@
       <c r="Q21" s="11" t="n">
         <v>40.91</v>
       </c>
-      <c r="R21" s="46" t="n">
+      <c r="R21" s="47" t="n">
         <v>37.07</v>
       </c>
-      <c r="S21" s="46" t="n">
+      <c r="S21" s="47" t="n">
         <f aca="false">R21/1.1</f>
         <v>33.7</v>
       </c>
@@ -9745,36 +9756,36 @@
       <c r="K24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L24" s="46" t="n">
+      <c r="L24" s="47" t="n">
         <v>43.15</v>
       </c>
-      <c r="M24" s="46" t="n">
+      <c r="M24" s="47" t="n">
         <v>39.23</v>
       </c>
-      <c r="N24" s="46" t="n">
+      <c r="N24" s="47" t="n">
         <v>35.75</v>
       </c>
-      <c r="O24" s="46" t="n">
+      <c r="O24" s="47" t="n">
         <f aca="false">N24/1.1</f>
         <v>32.5</v>
       </c>
-      <c r="P24" s="46" t="n">
+      <c r="P24" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q24" s="46" t="n">
+      <c r="Q24" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R24" s="46" t="n">
+      <c r="R24" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="S24" s="46" t="n">
+      <c r="S24" s="47" t="n">
         <f aca="false">R24/1.1</f>
         <v>22.7272727272727</v>
       </c>
-      <c r="T24" s="46" t="n">
+      <c r="T24" s="47" t="n">
         <v>33.19</v>
       </c>
-      <c r="U24" s="46" t="n">
+      <c r="U24" s="47" t="n">
         <f aca="false">T24/1.1</f>
         <v>30.1727272727273</v>
       </c>
@@ -9784,10 +9795,10 @@
       <c r="W24" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X24" s="46" t="n">
+      <c r="X24" s="47" t="n">
         <v>35.9</v>
       </c>
-      <c r="Y24" s="46" t="n">
+      <c r="Y24" s="47" t="n">
         <f aca="false">X24/1.1</f>
         <v>32.6363636363636</v>
       </c>
@@ -9860,10 +9871,10 @@
       <c r="K25" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L25" s="46" t="n">
+      <c r="L25" s="47" t="n">
         <v>46.29</v>
       </c>
-      <c r="M25" s="46" t="n">
+      <c r="M25" s="47" t="n">
         <v>42.08</v>
       </c>
       <c r="N25" s="11" t="n">
@@ -10092,10 +10103,10 @@
       <c r="K27" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L27" s="46" t="n">
+      <c r="L27" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M27" s="46" t="n">
+      <c r="M27" s="47" t="n">
         <v>35.98</v>
       </c>
       <c r="N27" s="11" t="n">
@@ -10260,10 +10271,10 @@
       <c r="AA28" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB28" s="46" t="n">
+      <c r="AB28" s="47" t="n">
         <v>90.08</v>
       </c>
-      <c r="AC28" s="46" t="n">
+      <c r="AC28" s="47" t="n">
         <f aca="false">AB28/1.1</f>
         <v>81.8909090909091</v>
       </c>
@@ -10492,10 +10503,10 @@
       <c r="AA30" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB30" s="46" t="n">
+      <c r="AB30" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC30" s="46" t="n">
+      <c r="AC30" s="47" t="n">
         <f aca="false">AB30/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10587,10 +10598,10 @@
         <f aca="false">T31/1.1</f>
         <v>42.8545454545455</v>
       </c>
-      <c r="V31" s="46" t="n">
+      <c r="V31" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="W31" s="46" t="n">
+      <c r="W31" s="47" t="n">
         <f aca="false">V31*1.1</f>
         <v>30.8</v>
       </c>
@@ -10607,8 +10618,8 @@
       <c r="AA31" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB31" s="47"/>
-      <c r="AC31" s="47"/>
+      <c r="AB31" s="48"/>
+      <c r="AC31" s="48"/>
       <c r="AD31" s="11" t="n">
         <f aca="false">IF(COUNT(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31)=0,"N/A",MIN(I31,J31,M31,O31,Q31,S31,U31,V31,Y31,AA31,AC31))</f>
         <v>28</v>
@@ -10717,10 +10728,10 @@
       <c r="AA32" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB32" s="46" t="n">
+      <c r="AB32" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC32" s="46" t="n">
+      <c r="AC32" s="47" t="n">
         <f aca="false">AB32/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10787,10 +10798,10 @@
       <c r="M33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N33" s="46" t="n">
+      <c r="N33" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="O33" s="46" t="n">
+      <c r="O33" s="47" t="n">
         <f aca="false">N33/1.1</f>
         <v>46.3636363636364</v>
       </c>
@@ -10814,10 +10825,10 @@
         <f aca="false">T33/1.1</f>
         <v>53.4909090909091</v>
       </c>
-      <c r="V33" s="46" t="n">
+      <c r="V33" s="47" t="n">
         <v>51.5</v>
       </c>
-      <c r="W33" s="46" t="n">
+      <c r="W33" s="47" t="n">
         <f aca="false">V33*1.1</f>
         <v>56.65</v>
       </c>
@@ -10834,10 +10845,10 @@
       <c r="AA33" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB33" s="46" t="n">
+      <c r="AB33" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC33" s="46" t="n">
+      <c r="AC33" s="47" t="n">
         <f aca="false">AB33/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -10950,10 +10961,10 @@
       <c r="AA34" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB34" s="46" t="n">
+      <c r="AB34" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC34" s="46" t="n">
+      <c r="AC34" s="47" t="n">
         <f aca="false">AB34/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11066,10 +11077,10 @@
       <c r="AA35" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB35" s="46" t="n">
+      <c r="AB35" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC35" s="46" t="n">
+      <c r="AC35" s="47" t="n">
         <f aca="false">AB35/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11183,10 +11194,10 @@
       <c r="AA36" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB36" s="46" t="n">
+      <c r="AB36" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC36" s="46" t="n">
+      <c r="AC36" s="47" t="n">
         <f aca="false">AB36/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11297,10 +11308,10 @@
       <c r="AA37" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB37" s="46" t="n">
+      <c r="AB37" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC37" s="46" t="n">
+      <c r="AC37" s="47" t="n">
         <f aca="false">AB37/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11412,10 +11423,10 @@
       <c r="AA38" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB38" s="46" t="n">
+      <c r="AB38" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC38" s="46" t="n">
+      <c r="AC38" s="47" t="n">
         <f aca="false">AB38/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11528,10 +11539,10 @@
       <c r="AA39" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB39" s="46" t="n">
+      <c r="AB39" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC39" s="46" t="n">
+      <c r="AC39" s="47" t="n">
         <f aca="false">AB39/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11644,10 +11655,10 @@
       <c r="AA40" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB40" s="46" t="n">
+      <c r="AB40" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC40" s="46" t="n">
+      <c r="AC40" s="47" t="n">
         <f aca="false">AB40/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11760,10 +11771,10 @@
       <c r="AA41" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB41" s="46" t="n">
+      <c r="AB41" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC41" s="46" t="n">
+      <c r="AC41" s="47" t="n">
         <f aca="false">AB41/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11876,10 +11887,10 @@
       <c r="AA42" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB42" s="46" t="n">
+      <c r="AB42" s="47" t="n">
         <v>40.83</v>
       </c>
-      <c r="AC42" s="46" t="n">
+      <c r="AC42" s="47" t="n">
         <f aca="false">AB42/1.1</f>
         <v>37.1181818181818</v>
       </c>
@@ -11951,16 +11962,16 @@
       <c r="O43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P43" s="46" t="n">
+      <c r="P43" s="47" t="n">
         <v>22.05</v>
       </c>
-      <c r="Q43" s="46" t="n">
+      <c r="Q43" s="47" t="n">
         <v>20.05</v>
       </c>
-      <c r="R43" s="46" t="n">
+      <c r="R43" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="S43" s="46" t="n">
+      <c r="S43" s="47" t="n">
         <f aca="false">R43/1.1</f>
         <v>25</v>
       </c>
@@ -11976,19 +11987,19 @@
       <c r="W43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X43" s="46" t="n">
+      <c r="X43" s="47" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y43" s="46" t="n">
+      <c r="Y43" s="47" t="n">
         <f aca="false">X43/1.1</f>
         <v>29.0545454545455</v>
       </c>
-      <c r="Z43" s="47"/>
-      <c r="AA43" s="47"/>
-      <c r="AB43" s="46" t="n">
+      <c r="Z43" s="48"/>
+      <c r="AA43" s="48"/>
+      <c r="AB43" s="47" t="n">
         <v>35.9</v>
       </c>
-      <c r="AC43" s="46" t="n">
+      <c r="AC43" s="47" t="n">
         <f aca="false">AB43/1.1</f>
         <v>32.6363636363636</v>
       </c>
@@ -12067,10 +12078,10 @@
       <c r="Q44" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R44" s="46" t="n">
+      <c r="R44" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S44" s="46" t="n">
+      <c r="S44" s="47" t="n">
         <f aca="false">R44/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -12203,10 +12214,10 @@
       <c r="W45" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="X45" s="46" t="n">
+      <c r="X45" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y45" s="46" t="n">
+      <c r="Y45" s="47" t="n">
         <f aca="false">X45/1.1</f>
         <v>41.6</v>
       </c>
@@ -12280,16 +12291,16 @@
       <c r="K46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L46" s="46" t="n">
+      <c r="L46" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M46" s="46" t="n">
+      <c r="M46" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N46" s="46" t="n">
+      <c r="N46" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="O46" s="46" t="n">
+      <c r="O46" s="47" t="n">
         <f aca="false">N46/1.1</f>
         <v>25</v>
       </c>
@@ -12299,10 +12310,10 @@
       <c r="Q46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R46" s="46" t="n">
+      <c r="R46" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S46" s="46" t="n">
+      <c r="S46" s="47" t="n">
         <f aca="false">R46/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -12318,10 +12329,10 @@
       <c r="W46" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X46" s="46" t="n">
+      <c r="X46" s="47" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y46" s="46" t="n">
+      <c r="Y46" s="47" t="n">
         <f aca="false">X46/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -12395,50 +12406,50 @@
       <c r="K47" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L47" s="46" t="n">
+      <c r="L47" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M47" s="46" t="n">
+      <c r="M47" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N47" s="46" t="n">
+      <c r="N47" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="O47" s="46" t="n">
+      <c r="O47" s="47" t="n">
         <f aca="false">N47/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P47" s="46" t="n">
+      <c r="P47" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q47" s="46" t="n">
+      <c r="Q47" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R47" s="46" t="n">
+      <c r="R47" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="S47" s="46" t="n">
+      <c r="S47" s="47" t="n">
         <f aca="false">R47/1.1</f>
         <v>27.2727272727273</v>
       </c>
-      <c r="T47" s="46" t="n">
+      <c r="T47" s="47" t="n">
         <v>28.66</v>
       </c>
-      <c r="U47" s="46" t="n">
+      <c r="U47" s="47" t="n">
         <f aca="false">T47/1.1</f>
         <v>26.0545454545455</v>
       </c>
-      <c r="V47" s="46" t="n">
+      <c r="V47" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="W47" s="46" t="n">
+      <c r="W47" s="47" t="n">
         <f aca="false">V47*1.1</f>
         <v>40.15</v>
       </c>
-      <c r="X47" s="46" t="n">
+      <c r="X47" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y47" s="46" t="n">
+      <c r="Y47" s="47" t="n">
         <f aca="false">X47/1.1</f>
         <v>41.6</v>
       </c>
@@ -12512,43 +12523,43 @@
       <c r="K48" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L48" s="46" t="n">
+      <c r="L48" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M48" s="46" t="n">
+      <c r="M48" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N48" s="46" t="n">
+      <c r="N48" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="O48" s="46" t="n">
+      <c r="O48" s="47" t="n">
         <f aca="false">N48/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P48" s="46" t="n">
+      <c r="P48" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q48" s="46" t="n">
+      <c r="Q48" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R48" s="46" t="n">
+      <c r="R48" s="47" t="n">
         <v>33.5</v>
       </c>
-      <c r="S48" s="46" t="n">
+      <c r="S48" s="47" t="n">
         <f aca="false">R48/1.1</f>
         <v>30.4545454545455</v>
       </c>
-      <c r="T48" s="46" t="n">
+      <c r="T48" s="47" t="n">
         <v>18.41</v>
       </c>
-      <c r="U48" s="46" t="n">
+      <c r="U48" s="47" t="n">
         <f aca="false">T48/1.1</f>
         <v>16.7363636363636</v>
       </c>
-      <c r="V48" s="46" t="n">
+      <c r="V48" s="47" t="n">
         <v>28.5</v>
       </c>
-      <c r="W48" s="46" t="n">
+      <c r="W48" s="47" t="n">
         <f aca="false">V48*1.1</f>
         <v>31.35</v>
       </c>
@@ -12634,17 +12645,17 @@
       <c r="M49" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="N49" s="46" t="n">
+      <c r="N49" s="47" t="n">
         <v>35.4</v>
       </c>
-      <c r="O49" s="46" t="n">
+      <c r="O49" s="47" t="n">
         <f aca="false">N49/1.1</f>
         <v>32.1818181818182</v>
       </c>
-      <c r="P49" s="46" t="n">
+      <c r="P49" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q49" s="46" t="n">
+      <c r="Q49" s="47" t="n">
         <v>22</v>
       </c>
       <c r="R49" s="11" t="n">
@@ -12668,10 +12679,10 @@
       <c r="W49" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X49" s="46" t="n">
+      <c r="X49" s="47" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y49" s="46" t="n">
+      <c r="Y49" s="47" t="n">
         <f aca="false">X49/1.1</f>
         <v>29.0545454545455</v>
       </c>
@@ -12862,43 +12873,43 @@
       <c r="K51" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L51" s="46" t="n">
+      <c r="L51" s="47" t="n">
         <v>34.67</v>
       </c>
-      <c r="M51" s="46" t="n">
+      <c r="M51" s="47" t="n">
         <v>31.52</v>
       </c>
-      <c r="N51" s="46" t="n">
+      <c r="N51" s="47" t="n">
         <v>28.3</v>
       </c>
-      <c r="O51" s="46" t="n">
+      <c r="O51" s="47" t="n">
         <f aca="false">N51/1.1</f>
         <v>25.7272727272727</v>
       </c>
-      <c r="P51" s="46" t="n">
+      <c r="P51" s="47" t="n">
         <v>11.55</v>
       </c>
-      <c r="Q51" s="46" t="n">
+      <c r="Q51" s="47" t="n">
         <v>10.5</v>
       </c>
-      <c r="R51" s="46" t="n">
+      <c r="R51" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S51" s="46" t="n">
+      <c r="S51" s="47" t="n">
         <f aca="false">R51/1.1</f>
         <v>20.4545454545455</v>
       </c>
-      <c r="T51" s="46" t="n">
+      <c r="T51" s="47" t="n">
         <v>33.04</v>
       </c>
-      <c r="U51" s="46" t="n">
+      <c r="U51" s="47" t="n">
         <f aca="false">T51/1.1</f>
         <v>30.0363636363636</v>
       </c>
-      <c r="V51" s="46" t="n">
+      <c r="V51" s="47" t="n">
         <v>19.5</v>
       </c>
-      <c r="W51" s="46" t="n">
+      <c r="W51" s="47" t="n">
         <f aca="false">V51*1.1</f>
         <v>21.45</v>
       </c>
@@ -12978,29 +12989,29 @@
       <c r="K52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L52" s="46" t="n">
+      <c r="L52" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M52" s="46" t="n">
+      <c r="M52" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N52" s="46" t="n">
+      <c r="N52" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="O52" s="46" t="n">
+      <c r="O52" s="47" t="n">
         <f aca="false">N52/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P52" s="46" t="n">
+      <c r="P52" s="47" t="n">
         <v>45.15</v>
       </c>
-      <c r="Q52" s="46" t="n">
+      <c r="Q52" s="47" t="n">
         <v>41.05</v>
       </c>
-      <c r="R52" s="46" t="n">
+      <c r="R52" s="47" t="n">
         <v>33.5</v>
       </c>
-      <c r="S52" s="46" t="n">
+      <c r="S52" s="47" t="n">
         <f aca="false">R52/1.1</f>
         <v>30.4545454545455</v>
       </c>
@@ -13010,17 +13021,17 @@
       <c r="U52" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="V52" s="46" t="n">
+      <c r="V52" s="47" t="n">
         <v>26.5</v>
       </c>
-      <c r="W52" s="46" t="n">
+      <c r="W52" s="47" t="n">
         <f aca="false">V52*1.1</f>
         <v>29.15</v>
       </c>
-      <c r="X52" s="46" t="n">
+      <c r="X52" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y52" s="46" t="n">
+      <c r="Y52" s="47" t="n">
         <f aca="false">X52/1.1</f>
         <v>41.6</v>
       </c>
@@ -13031,8 +13042,8 @@
       <c r="AA52" s="45" t="n">
         <v>70.25</v>
       </c>
-      <c r="AB52" s="45"/>
-      <c r="AC52" s="45"/>
+      <c r="AB52" s="46"/>
+      <c r="AC52" s="46"/>
       <c r="AD52" s="11" t="n">
         <f aca="false">IF(COUNT(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52)=0,"N/A",MIN(I52,J52,M52,O52,Q52,S52,U52,V52,Y52,AA52,AC52))</f>
         <v>26.5</v>
@@ -13200,16 +13211,16 @@
       <c r="K54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L54" s="46" t="n">
+      <c r="L54" s="47" t="n">
         <v>34.67</v>
       </c>
-      <c r="M54" s="46" t="n">
+      <c r="M54" s="47" t="n">
         <v>31.52</v>
       </c>
-      <c r="N54" s="46" t="n">
+      <c r="N54" s="47" t="n">
         <v>28.3</v>
       </c>
-      <c r="O54" s="46" t="n">
+      <c r="O54" s="47" t="n">
         <f aca="false">N54/1.1</f>
         <v>25.7272727272727</v>
       </c>
@@ -13219,10 +13230,10 @@
       <c r="Q54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R54" s="46" t="n">
+      <c r="R54" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S54" s="46" t="n">
+      <c r="S54" s="47" t="n">
         <f aca="false">R54/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -13238,10 +13249,10 @@
       <c r="W54" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X54" s="46" t="n">
+      <c r="X54" s="47" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y54" s="46" t="n">
+      <c r="Y54" s="47" t="n">
         <f aca="false">X54/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -13333,10 +13344,10 @@
       <c r="Q55" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R55" s="46" t="n">
+      <c r="R55" s="47" t="n">
         <v>23</v>
       </c>
-      <c r="S55" s="46" t="n">
+      <c r="S55" s="47" t="n">
         <f aca="false">R55/1.1</f>
         <v>20.9090909090909</v>
       </c>
@@ -13364,8 +13375,8 @@
       <c r="AA55" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="AB55" s="47"/>
-      <c r="AC55" s="47"/>
+      <c r="AB55" s="48"/>
+      <c r="AC55" s="48"/>
       <c r="AD55" s="11" t="n">
         <f aca="false">IF(COUNT(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55)=0,"N/A",MIN(I55,J55,M55,O55,Q55,S55,U55,V55,Y55,AA55,AC55))</f>
         <v>20.9090909090909</v>
@@ -13434,16 +13445,16 @@
       <c r="O56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P56" s="46" t="n">
+      <c r="P56" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q56" s="46" t="n">
+      <c r="Q56" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R56" s="46" t="n">
+      <c r="R56" s="47" t="n">
         <v>33.5</v>
       </c>
-      <c r="S56" s="46" t="n">
+      <c r="S56" s="47" t="n">
         <f aca="false">R56/1.1</f>
         <v>30.4545454545455</v>
       </c>
@@ -13459,10 +13470,10 @@
       <c r="W56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X56" s="46" t="n">
+      <c r="X56" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y56" s="46" t="n">
+      <c r="Y56" s="47" t="n">
         <f aca="false">X56/1.1</f>
         <v>41.6</v>
       </c>
@@ -13472,8 +13483,8 @@
       <c r="AA56" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="AB56" s="47"/>
-      <c r="AC56" s="47"/>
+      <c r="AB56" s="48"/>
+      <c r="AC56" s="48"/>
       <c r="AD56" s="11" t="n">
         <f aca="false">IF(COUNT(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56)=0,"N/A",MIN(I56,J56,M56,O56,Q56,S56,U56,V56,Y56,AA56,AC56))</f>
         <v>22</v>
@@ -13530,10 +13541,10 @@
       <c r="K57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L57" s="46" t="n">
+      <c r="L57" s="47" t="n">
         <v>39.47</v>
       </c>
-      <c r="M57" s="46" t="n">
+      <c r="M57" s="47" t="n">
         <v>35.88</v>
       </c>
       <c r="N57" s="42" t="s">
@@ -13548,10 +13559,10 @@
       <c r="Q57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R57" s="46" t="n">
+      <c r="R57" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="S57" s="46" t="n">
+      <c r="S57" s="47" t="n">
         <f aca="false">R57/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -13567,10 +13578,10 @@
       <c r="W57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X57" s="46" t="n">
+      <c r="X57" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y57" s="46" t="n">
+      <c r="Y57" s="47" t="n">
         <f aca="false">X57/1.1</f>
         <v>41.6</v>
       </c>
@@ -13650,23 +13661,23 @@
       <c r="M58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N58" s="46" t="n">
+      <c r="N58" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="O58" s="46" t="n">
+      <c r="O58" s="47" t="n">
         <f aca="false">N58/1.1</f>
         <v>38.6363636363636</v>
       </c>
-      <c r="P58" s="46" t="n">
+      <c r="P58" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q58" s="46" t="n">
+      <c r="Q58" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R58" s="46" t="n">
+      <c r="R58" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="S58" s="46" t="n">
+      <c r="S58" s="47" t="n">
         <f aca="false">R58/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -13682,10 +13693,10 @@
       <c r="W58" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X58" s="46" t="n">
+      <c r="X58" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y58" s="46" t="n">
+      <c r="Y58" s="47" t="n">
         <f aca="false">X58/1.1</f>
         <v>41.6</v>
       </c>
@@ -13765,10 +13776,10 @@
       <c r="M59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="N59" s="46" t="n">
+      <c r="N59" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="O59" s="46" t="n">
+      <c r="O59" s="47" t="n">
         <f aca="false">N59/1.1</f>
         <v>25</v>
       </c>
@@ -13778,10 +13789,10 @@
       <c r="Q59" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R59" s="46" t="n">
+      <c r="R59" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="S59" s="46" t="n">
+      <c r="S59" s="47" t="n">
         <f aca="false">R59/1.1</f>
         <v>20</v>
       </c>
@@ -13909,10 +13920,10 @@
       <c r="W60" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X60" s="46" t="n">
+      <c r="X60" s="47" t="n">
         <v>41.4</v>
       </c>
-      <c r="Y60" s="46" t="n">
+      <c r="Y60" s="47" t="n">
         <f aca="false">X60/1.1</f>
         <v>37.6363636363636</v>
       </c>
@@ -13986,16 +13997,16 @@
       <c r="K61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L61" s="46" t="n">
+      <c r="L61" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M61" s="46" t="n">
+      <c r="M61" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N61" s="46" t="n">
+      <c r="N61" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="O61" s="46" t="n">
+      <c r="O61" s="47" t="n">
         <f aca="false">N61/1.1</f>
         <v>38.6363636363636</v>
       </c>
@@ -14005,10 +14016,10 @@
       <c r="Q61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="R61" s="46" t="n">
+      <c r="R61" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="S61" s="46" t="n">
+      <c r="S61" s="47" t="n">
         <f aca="false">R61/1.1</f>
         <v>27.2727272727273</v>
       </c>
@@ -14024,10 +14035,10 @@
       <c r="W61" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X61" s="46" t="n">
+      <c r="X61" s="47" t="n">
         <v>45.76</v>
       </c>
-      <c r="Y61" s="46" t="n">
+      <c r="Y61" s="47" t="n">
         <f aca="false">X61/1.1</f>
         <v>41.6</v>
       </c>
@@ -14101,29 +14112,29 @@
       <c r="K62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="46" t="n">
+      <c r="L62" s="47" t="n">
         <v>39.47</v>
       </c>
-      <c r="M62" s="46" t="n">
+      <c r="M62" s="47" t="n">
         <v>35.88</v>
       </c>
-      <c r="N62" s="46" t="n">
+      <c r="N62" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="O62" s="46" t="n">
+      <c r="O62" s="47" t="n">
         <f aca="false">N62/1.1</f>
         <v>25</v>
       </c>
-      <c r="P62" s="46" t="n">
+      <c r="P62" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q62" s="46" t="n">
+      <c r="Q62" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R62" s="46" t="n">
+      <c r="R62" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S62" s="46" t="n">
+      <c r="S62" s="47" t="n">
         <f aca="false">R62/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -14139,10 +14150,10 @@
       <c r="W62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X62" s="46" t="n">
+      <c r="X62" s="47" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y62" s="46" t="n">
+      <c r="Y62" s="47" t="n">
         <f aca="false">X62/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -14216,10 +14227,10 @@
       <c r="K63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L63" s="46" t="n">
+      <c r="L63" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M63" s="46" t="n">
+      <c r="M63" s="47" t="n">
         <v>35.98</v>
       </c>
       <c r="N63" s="42" t="s">
@@ -14228,16 +14239,16 @@
       <c r="O63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="P63" s="46" t="n">
+      <c r="P63" s="47" t="n">
         <v>22.6</v>
       </c>
-      <c r="Q63" s="46" t="n">
+      <c r="Q63" s="47" t="n">
         <v>20.55</v>
       </c>
-      <c r="R63" s="46" t="n">
+      <c r="R63" s="47" t="n">
         <v>23</v>
       </c>
-      <c r="S63" s="46" t="n">
+      <c r="S63" s="47" t="n">
         <f aca="false">R63/1.1</f>
         <v>20.9090909090909</v>
       </c>
@@ -14253,10 +14264,10 @@
       <c r="W63" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X63" s="46" t="n">
+      <c r="X63" s="47" t="n">
         <v>31.96</v>
       </c>
-      <c r="Y63" s="46" t="n">
+      <c r="Y63" s="47" t="n">
         <f aca="false">X63/1.1</f>
         <v>29.0545454545455</v>
       </c>
@@ -14330,29 +14341,29 @@
       <c r="K64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L64" s="46" t="n">
+      <c r="L64" s="47" t="n">
         <v>39.58</v>
       </c>
-      <c r="M64" s="46" t="n">
+      <c r="M64" s="47" t="n">
         <v>35.98</v>
       </c>
-      <c r="N64" s="46" t="n">
+      <c r="N64" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="O64" s="46" t="n">
+      <c r="O64" s="47" t="n">
         <f aca="false">N64/1.1</f>
         <v>25</v>
       </c>
-      <c r="P64" s="46" t="n">
+      <c r="P64" s="47" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q64" s="46" t="n">
+      <c r="Q64" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="R64" s="46" t="n">
+      <c r="R64" s="47" t="n">
         <v>22.5</v>
       </c>
-      <c r="S64" s="46" t="n">
+      <c r="S64" s="47" t="n">
         <f aca="false">R64/1.1</f>
         <v>20.4545454545455</v>
       </c>
@@ -14368,10 +14379,10 @@
       <c r="W64" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="X64" s="46" t="n">
+      <c r="X64" s="47" t="n">
         <v>24.96</v>
       </c>
-      <c r="Y64" s="46" t="n">
+      <c r="Y64" s="47" t="n">
         <f aca="false">X64/1.1</f>
         <v>22.6909090909091</v>
       </c>
@@ -14445,10 +14456,10 @@
       <c r="K65" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="L65" s="46" t="n">
+      <c r="L65" s="47" t="n">
         <v>39.47</v>
       </c>
-      <c r="M65" s="46" t="n">
+      <c r="M65" s="47" t="n">
         <v>35.88</v>
       </c>
       <c r="N65" s="11" t="n">
@@ -14533,7 +14544,7 @@
       </c>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
-      <c r="D68" s="48" t="n">
+      <c r="D68" s="49" t="n">
         <f aca="false">COUNTA(B6:B65)</f>
         <v>60</v>
       </c>
@@ -14544,7 +14555,7 @@
       </c>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
-      <c r="D69" s="48" t="n">
+      <c r="D69" s="49" t="n">
         <f aca="false">COUNTIF(J6:J65,"&gt;0")+COUNTIF(M6:M65,"&gt;0")+COUNTIF(O6:O65,"&gt;0")+COUNTIF(Q6:Q65,"&gt;0")+COUNTIF(S6:S65,"&gt;0")+COUNTIF(U6:U65,"&gt;0")+COUNTIF(V6:V65,"&gt;0")+COUNTIF(Y6:Y65,"&gt;0")+COUNTIF(AA6:AA65,"&gt;0")+COUNTIF(AC6:AC65,"&gt;0")</f>
         <v>407</v>
       </c>
@@ -14555,7 +14566,7 @@
       </c>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
-      <c r="D70" s="48" t="n">
+      <c r="D70" s="49" t="n">
         <f aca="false">COUNTIF(AE6:AE65,"&lt;0")</f>
         <v>53</v>
       </c>
@@ -14566,7 +14577,7 @@
       </c>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
-      <c r="D71" s="48" t="n">
+      <c r="D71" s="49" t="n">
         <f aca="false">COUNTIF(AE6:AE65,"&gt;0")</f>
         <v>7</v>
       </c>
@@ -14577,7 +14588,7 @@
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
-      <c r="D72" s="49" t="n">
+      <c r="D72" s="50" t="n">
         <f aca="false">AVERAGE(AE6:AE65)</f>
         <v>-0.454866678565887</v>
       </c>
@@ -14588,7 +14599,7 @@
       </c>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
-      <c r="D73" s="49" t="n">
+      <c r="D73" s="50" t="n">
         <f aca="false">MEDIAN(AE6:AE65)</f>
         <v>-0.523652597402597</v>
       </c>
@@ -14599,7 +14610,7 @@
       </c>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
-      <c r="D74" s="48" t="n">
+      <c r="D74" s="49" t="n">
         <f aca="false">COUNTIF(AF6:AF65,"&lt;0")</f>
         <v>15</v>
       </c>
@@ -14610,7 +14621,7 @@
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
-      <c r="D75" s="48" t="n">
+      <c r="D75" s="49" t="n">
         <f aca="false">COUNTIF(AF6:AF65,"&gt;0")</f>
         <v>7</v>
       </c>
@@ -14621,7 +14632,7 @@
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
-      <c r="D76" s="49" t="n">
+      <c r="D76" s="50" t="n">
         <f aca="false">AVERAGE(AF6:AF65)</f>
         <v>-0.137849955170021</v>
       </c>
@@ -14632,7 +14643,7 @@
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
-      <c r="D77" s="49" t="n">
+      <c r="D77" s="50" t="n">
         <f aca="false">MEDIAN(AF6:AF65)</f>
         <v>-0.240924975181021</v>
       </c>
@@ -14699,62 +14710,62 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="52" t="s">
         <v>332</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="53" t="s">
         <v>334</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="53" t="s">
         <v>335</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="53" t="s">
         <v>338</v>
       </c>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="53" t="s">
         <v>221</v>
       </c>
     </row>
@@ -14774,13 +14785,13 @@
       <c r="E5" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="54" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G5" s="54" t="n">
+      <c r="G5" s="55" t="n">
         <v>-3.11725</v>
       </c>
-      <c r="H5" s="55" t="n">
+      <c r="H5" s="56" t="n">
         <v>-0.155473815461347</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -14803,13 +14814,13 @@
       <c r="E6" s="11" t="n">
         <v>122.718181818182</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="57" t="n">
         <v>66.83</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="55" t="n">
         <v>-55.888181818182</v>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="56" t="n">
         <v>-0.455418919919995</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -14832,13 +14843,13 @@
       <c r="E7" s="11" t="n">
         <v>128.75</v>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="57" t="n">
         <v>44.55</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="55" t="n">
         <v>-84.2</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="56" t="n">
         <v>-0.653980582524272</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -14861,13 +14872,13 @@
       <c r="E8" s="11" t="n">
         <v>69.245</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="54" t="n">
         <v>45.144</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="55" t="n">
         <v>-24.101</v>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="56" t="n">
         <v>-0.348054011119937</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -14890,13 +14901,13 @@
       <c r="E9" s="11" t="n">
         <v>81.4</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="54" t="n">
         <v>70.538125</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="55" t="n">
         <v>-10.861875</v>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="56" t="n">
         <v>-0.133438267813268</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -14919,13 +14930,13 @@
       <c r="E10" s="11" t="n">
         <v>44.209</v>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="54" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G10" s="54" t="n">
+      <c r="G10" s="55" t="n">
         <v>-10.3535</v>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="56" t="n">
         <v>-0.234194394806487</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -14948,13 +14959,13 @@
       <c r="E11" s="11" t="n">
         <v>70.36</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="54" t="n">
         <v>45.144</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="55" t="n">
         <v>-25.216</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="56" t="n">
         <v>-0.358385446276293</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -14962,34 +14973,34 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="E12" s="59" t="n">
+      <c r="E12" s="60" t="n">
         <v>33.1818181818182</v>
       </c>
-      <c r="F12" s="60" t="n">
+      <c r="F12" s="61" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="62" t="n">
         <v>0.673681818181798</v>
       </c>
-      <c r="H12" s="62" t="n">
+      <c r="H12" s="63" t="n">
         <v>0.0203027397260268</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J12" s="57"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -15007,13 +15018,13 @@
       <c r="E13" s="11" t="n">
         <v>43.09</v>
       </c>
-      <c r="F13" s="53" t="n">
+      <c r="F13" s="54" t="n">
         <v>25.394125</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G13" s="55" t="n">
         <v>-17.695875</v>
       </c>
-      <c r="H13" s="55" t="n">
+      <c r="H13" s="56" t="n">
         <v>-0.410672429798097</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -15036,13 +15047,13 @@
       <c r="E14" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F14" s="53" t="n">
+      <c r="F14" s="54" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="55" t="n">
         <v>-13.538625</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="56" t="n">
         <v>-0.615392045454545</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -15065,13 +15076,13 @@
       <c r="E15" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="F15" s="53" t="n">
+      <c r="F15" s="54" t="n">
         <v>15.81275</v>
       </c>
-      <c r="G15" s="54" t="n">
+      <c r="G15" s="55" t="n">
         <v>-6.08725</v>
       </c>
-      <c r="H15" s="55" t="n">
+      <c r="H15" s="56" t="n">
         <v>-0.277956621004566</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -15094,13 +15105,13 @@
       <c r="E16" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="F16" s="53" t="n">
+      <c r="F16" s="54" t="n">
         <v>8.461375</v>
       </c>
-      <c r="G16" s="54" t="n">
+      <c r="G16" s="55" t="n">
         <v>-2.038625</v>
       </c>
-      <c r="H16" s="55" t="n">
+      <c r="H16" s="56" t="n">
         <v>-0.194154761904762</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -15123,13 +15134,13 @@
       <c r="E17" s="11" t="n">
         <v>37.3909090909091</v>
       </c>
-      <c r="F17" s="53" t="n">
+      <c r="F17" s="54" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G17" s="54" t="n">
+      <c r="G17" s="55" t="n">
         <v>-7.2454090909091</v>
       </c>
-      <c r="H17" s="55" t="n">
+      <c r="H17" s="56" t="n">
         <v>-0.193774617067834</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -15137,34 +15148,34 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="58" t="s">
         <v>347</v>
       </c>
-      <c r="E18" s="59" t="n">
+      <c r="E18" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="F18" s="60" t="n">
+      <c r="F18" s="61" t="n">
         <v>30.1455</v>
       </c>
-      <c r="G18" s="61" t="n">
+      <c r="G18" s="62" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="H18" s="62" t="n">
+      <c r="H18" s="63" t="n">
         <v>0.0631628727156122</v>
       </c>
-      <c r="I18" s="63" t="s">
+      <c r="I18" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J18" s="57"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -15182,13 +15193,13 @@
       <c r="E19" s="11" t="n">
         <v>23.3090909090909</v>
       </c>
-      <c r="F19" s="53" t="n">
+      <c r="F19" s="54" t="n">
         <v>16.93275</v>
       </c>
-      <c r="G19" s="54" t="n">
+      <c r="G19" s="55" t="n">
         <v>-6.3763409090909</v>
       </c>
-      <c r="H19" s="55" t="n">
+      <c r="H19" s="56" t="n">
         <v>-0.273555967238689</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -15196,34 +15207,34 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="58" t="s">
         <v>348</v>
       </c>
-      <c r="E20" s="59" t="n">
+      <c r="E20" s="60" t="n">
         <v>33.7</v>
       </c>
-      <c r="F20" s="60" t="n">
+      <c r="F20" s="61" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G20" s="61" t="n">
+      <c r="G20" s="62" t="n">
         <v>0.155499999999996</v>
       </c>
-      <c r="H20" s="62" t="n">
+      <c r="H20" s="63" t="n">
         <v>0.00461424332344203</v>
       </c>
-      <c r="I20" s="63" t="s">
+      <c r="I20" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J20" s="57"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -15241,13 +15252,13 @@
       <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="53" t="n">
+      <c r="F21" s="54" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G21" s="54" t="n">
+      <c r="G21" s="55" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H21" s="55" t="n">
+      <c r="H21" s="56" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -15270,13 +15281,13 @@
       <c r="E22" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F22" s="53" t="n">
+      <c r="F22" s="54" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G22" s="54" t="n">
+      <c r="G22" s="55" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H22" s="55" t="n">
+      <c r="H22" s="56" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -15299,13 +15310,13 @@
       <c r="E23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F23" s="53" t="n">
+      <c r="F23" s="54" t="n">
         <v>6.011375</v>
       </c>
-      <c r="G23" s="54" t="n">
+      <c r="G23" s="55" t="n">
         <v>-15.988625</v>
       </c>
-      <c r="H23" s="55" t="n">
+      <c r="H23" s="56" t="n">
         <v>-0.726755681818182</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -15313,64 +15324,64 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="E24" s="59" t="n">
+      <c r="E24" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F24" s="60" t="n">
+      <c r="F24" s="61" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G24" s="61" t="n">
+      <c r="G24" s="62" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="63" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I24" s="63" t="s">
+      <c r="I24" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J24" s="57"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="E25" s="59" t="n">
+      <c r="E25" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F25" s="60" t="n">
+      <c r="F25" s="61" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G25" s="61" t="n">
+      <c r="G25" s="62" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="H25" s="62" t="n">
+      <c r="H25" s="63" t="n">
         <v>0.286299805636541</v>
       </c>
-      <c r="I25" s="63" t="s">
+      <c r="I25" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J25" s="57"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -15388,13 +15399,13 @@
       <c r="E26" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="54" t="n">
         <v>12.03275</v>
       </c>
-      <c r="G26" s="54" t="n">
+      <c r="G26" s="55" t="n">
         <v>-9.16725</v>
       </c>
-      <c r="H26" s="55" t="n">
+      <c r="H26" s="56" t="n">
         <v>-0.432417452830189</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -15402,34 +15413,34 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="E27" s="59" t="n">
+      <c r="E27" s="60" t="n">
         <v>32.5</v>
       </c>
-      <c r="F27" s="60" t="n">
+      <c r="F27" s="61" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G27" s="61" t="n">
+      <c r="G27" s="62" t="n">
         <v>1.3555</v>
       </c>
-      <c r="H27" s="62" t="n">
+      <c r="H27" s="63" t="n">
         <v>0.0417076923076923</v>
       </c>
-      <c r="I27" s="63" t="s">
+      <c r="I27" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="J27" s="57"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -15447,13 +15458,13 @@
       <c r="E28" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="54" t="n">
         <v>33.8555</v>
       </c>
-      <c r="G28" s="54" t="n">
+      <c r="G28" s="55" t="n">
         <v>-11.1445</v>
       </c>
-      <c r="H28" s="55" t="n">
+      <c r="H28" s="56" t="n">
         <v>-0.247655555555556</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -15476,13 +15487,13 @@
       <c r="E29" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G29" s="54" t="n">
+      <c r="G29" s="55" t="n">
         <v>-17.73</v>
       </c>
-      <c r="H29" s="55" t="n">
+      <c r="H29" s="56" t="n">
         <v>-0.575649350649351</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -15505,13 +15516,13 @@
       <c r="E30" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="F30" s="56" t="n">
+      <c r="F30" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G30" s="54" t="n">
+      <c r="G30" s="55" t="n">
         <v>-14.93</v>
       </c>
-      <c r="H30" s="55" t="n">
+      <c r="H30" s="56" t="n">
         <v>-0.533214285714286</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -15534,13 +15545,13 @@
       <c r="E31" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F31" s="56" t="n">
+      <c r="F31" s="57" t="n">
         <v>16.04</v>
       </c>
-      <c r="G31" s="54" t="n">
+      <c r="G31" s="55" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H31" s="55" t="n">
+      <c r="H31" s="56" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -15563,13 +15574,13 @@
       <c r="E32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F32" s="56" t="n">
+      <c r="F32" s="57" t="n">
         <v>16.04</v>
       </c>
-      <c r="G32" s="54" t="n">
+      <c r="G32" s="55" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H32" s="55" t="n">
+      <c r="H32" s="56" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -15592,13 +15603,13 @@
       <c r="E33" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="57" t="n">
         <v>16.04</v>
       </c>
-      <c r="G33" s="54" t="n">
+      <c r="G33" s="55" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H33" s="55" t="n">
+      <c r="H33" s="56" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -15621,13 +15632,13 @@
       <c r="E34" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F34" s="56" t="n">
+      <c r="F34" s="57" t="n">
         <v>16.04</v>
       </c>
-      <c r="G34" s="54" t="n">
+      <c r="G34" s="55" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H34" s="55" t="n">
+      <c r="H34" s="56" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -15650,13 +15661,13 @@
       <c r="E35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F35" s="56" t="n">
+      <c r="F35" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G35" s="54" t="n">
+      <c r="G35" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H35" s="55" t="n">
+      <c r="H35" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -15679,13 +15690,13 @@
       <c r="E36" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F36" s="56" t="n">
+      <c r="F36" s="57" t="n">
         <v>16.04</v>
       </c>
-      <c r="G36" s="54" t="n">
+      <c r="G36" s="55" t="n">
         <v>-14.96</v>
       </c>
-      <c r="H36" s="55" t="n">
+      <c r="H36" s="56" t="n">
         <v>-0.48258064516129</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -15708,13 +15719,13 @@
       <c r="E37" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F37" s="56" t="n">
+      <c r="F37" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G37" s="54" t="n">
+      <c r="G37" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H37" s="55" t="n">
+      <c r="H37" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -15737,13 +15748,13 @@
       <c r="E38" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F38" s="56" t="n">
+      <c r="F38" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G38" s="54" t="n">
+      <c r="G38" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H38" s="55" t="n">
+      <c r="H38" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -15766,13 +15777,13 @@
       <c r="E39" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F39" s="56" t="n">
+      <c r="F39" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G39" s="54" t="n">
+      <c r="G39" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H39" s="55" t="n">
+      <c r="H39" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -15795,13 +15806,13 @@
       <c r="E40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F40" s="56" t="n">
+      <c r="F40" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G40" s="54" t="n">
+      <c r="G40" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H40" s="55" t="n">
+      <c r="H40" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -15824,13 +15835,13 @@
       <c r="E41" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="F41" s="56" t="n">
+      <c r="F41" s="57" t="n">
         <v>13.07</v>
       </c>
-      <c r="G41" s="54" t="n">
+      <c r="G41" s="55" t="n">
         <v>-17.93</v>
       </c>
-      <c r="H41" s="55" t="n">
+      <c r="H41" s="56" t="n">
         <v>-0.578387096774194</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -15853,13 +15864,13 @@
       <c r="E42" s="11" t="n">
         <v>20.05</v>
       </c>
-      <c r="F42" s="56" t="n">
+      <c r="F42" s="57" t="n">
         <v>5.35</v>
       </c>
-      <c r="G42" s="54" t="n">
+      <c r="G42" s="55" t="n">
         <v>-14.7</v>
       </c>
-      <c r="H42" s="55" t="n">
+      <c r="H42" s="56" t="n">
         <v>-0.733167082294264</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -15882,13 +15893,13 @@
       <c r="E43" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F43" s="56" t="n">
+      <c r="F43" s="57" t="n">
         <v>2.67</v>
       </c>
-      <c r="G43" s="54" t="n">
+      <c r="G43" s="55" t="n">
         <v>-6.68454545454545</v>
       </c>
-      <c r="H43" s="55" t="n">
+      <c r="H43" s="56" t="n">
         <v>-0.714577259475219</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -15911,13 +15922,13 @@
       <c r="E44" s="11" t="n">
         <v>23.4090909090909</v>
       </c>
-      <c r="F44" s="56" t="n">
+      <c r="F44" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G44" s="54" t="n">
+      <c r="G44" s="55" t="n">
         <v>-12.7190909090909</v>
       </c>
-      <c r="H44" s="55" t="n">
+      <c r="H44" s="56" t="n">
         <v>-0.543339805825243</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -15940,13 +15951,13 @@
       <c r="E45" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F45" s="56" t="n">
+      <c r="F45" s="57" t="n">
         <v>2.67</v>
       </c>
-      <c r="G45" s="54" t="n">
+      <c r="G45" s="55" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H45" s="55" t="n">
+      <c r="H45" s="56" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -15969,13 +15980,13 @@
       <c r="E46" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="56" t="n">
+      <c r="F46" s="57" t="n">
         <v>9.5</v>
       </c>
-      <c r="G46" s="54" t="n">
+      <c r="G46" s="55" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H46" s="55" t="n">
+      <c r="H46" s="56" t="n">
         <v>-0.568181818181818</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -15998,13 +16009,13 @@
       <c r="E47" s="11" t="n">
         <v>16.7363636363636</v>
       </c>
-      <c r="F47" s="56" t="n">
+      <c r="F47" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G47" s="54" t="n">
+      <c r="G47" s="55" t="n">
         <v>-6.0463636363636</v>
       </c>
-      <c r="H47" s="55" t="n">
+      <c r="H47" s="56" t="n">
         <v>-0.36127104834329</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -16027,13 +16038,13 @@
       <c r="E48" s="11" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="F48" s="56" t="n">
+      <c r="F48" s="57" t="n">
         <v>5.35</v>
       </c>
-      <c r="G48" s="54" t="n">
+      <c r="G48" s="55" t="n">
         <v>-15.5590909090909</v>
       </c>
-      <c r="H48" s="55" t="n">
+      <c r="H48" s="56" t="n">
         <v>-0.744130434782609</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -16056,13 +16067,13 @@
       <c r="E49" s="11" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="F49" s="56" t="n">
+      <c r="F49" s="57" t="n">
         <v>5.35</v>
       </c>
-      <c r="G49" s="54" t="n">
+      <c r="G49" s="55" t="n">
         <v>-4.00454545454545</v>
       </c>
-      <c r="H49" s="55" t="n">
+      <c r="H49" s="56" t="n">
         <v>-0.428085519922254</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -16085,13 +16096,13 @@
       <c r="E50" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="F50" s="56" t="n">
+      <c r="F50" s="57" t="n">
         <v>2.67</v>
       </c>
-      <c r="G50" s="54" t="n">
+      <c r="G50" s="55" t="n">
         <v>-7.83</v>
       </c>
-      <c r="H50" s="55" t="n">
+      <c r="H50" s="56" t="n">
         <v>-0.745714285714286</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -16114,13 +16125,13 @@
       <c r="E51" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="F51" s="56" t="n">
+      <c r="F51" s="57" t="n">
         <v>9.5</v>
       </c>
-      <c r="G51" s="54" t="n">
+      <c r="G51" s="55" t="n">
         <v>-17</v>
       </c>
-      <c r="H51" s="55" t="n">
+      <c r="H51" s="56" t="n">
         <v>-0.641509433962264</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -16143,13 +16154,13 @@
       <c r="E52" s="11" t="n">
         <v>7.81818181818182</v>
       </c>
-      <c r="F52" s="56" t="n">
+      <c r="F52" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="54" t="n">
+      <c r="G52" s="55" t="n">
         <v>-5.81818181818182</v>
       </c>
-      <c r="H52" s="55" t="n">
+      <c r="H52" s="56" t="n">
         <v>-0.744186046511628</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -16172,13 +16183,13 @@
       <c r="E53" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F53" s="56" t="n">
+      <c r="F53" s="57" t="n">
         <v>2.67</v>
       </c>
-      <c r="G53" s="54" t="n">
+      <c r="G53" s="55" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H53" s="55" t="n">
+      <c r="H53" s="56" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -16201,13 +16212,13 @@
       <c r="E54" s="11" t="n">
         <v>20.9090909090909</v>
       </c>
-      <c r="F54" s="56" t="n">
+      <c r="F54" s="57" t="n">
         <v>4.01</v>
       </c>
-      <c r="G54" s="54" t="n">
+      <c r="G54" s="55" t="n">
         <v>-16.8990909090909</v>
       </c>
-      <c r="H54" s="55" t="n">
+      <c r="H54" s="56" t="n">
         <v>-0.808217391304348</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -16230,13 +16241,13 @@
       <c r="E55" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F55" s="56" t="n">
+      <c r="F55" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G55" s="54" t="n">
+      <c r="G55" s="55" t="n">
         <v>-11.31</v>
       </c>
-      <c r="H55" s="55" t="n">
+      <c r="H55" s="56" t="n">
         <v>-0.514090909090909</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -16259,13 +16270,13 @@
       <c r="E56" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F56" s="56" t="n">
+      <c r="F56" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G56" s="54" t="n">
+      <c r="G56" s="55" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H56" s="55" t="n">
+      <c r="H56" s="56" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -16288,13 +16299,13 @@
       <c r="E57" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F57" s="56" t="n">
+      <c r="F57" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G57" s="54" t="n">
+      <c r="G57" s="55" t="n">
         <v>-11.31</v>
       </c>
-      <c r="H57" s="55" t="n">
+      <c r="H57" s="56" t="n">
         <v>-0.514090909090909</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -16317,13 +16328,13 @@
       <c r="E58" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F58" s="56" t="n">
+      <c r="F58" s="57" t="n">
         <v>2.89</v>
       </c>
-      <c r="G58" s="54" t="n">
+      <c r="G58" s="55" t="n">
         <v>-17.11</v>
       </c>
-      <c r="H58" s="55" t="n">
+      <c r="H58" s="56" t="n">
         <v>-0.8555</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -16346,13 +16357,13 @@
       <c r="E59" s="11" t="n">
         <v>37.6363636363636</v>
       </c>
-      <c r="F59" s="56" t="n">
+      <c r="F59" s="57" t="n">
         <v>1.94</v>
       </c>
-      <c r="G59" s="54" t="n">
+      <c r="G59" s="55" t="n">
         <v>-35.6963636363636</v>
       </c>
-      <c r="H59" s="55" t="n">
+      <c r="H59" s="56" t="n">
         <v>-0.948454106280193</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -16375,13 +16386,13 @@
       <c r="E60" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F60" s="56" t="n">
+      <c r="F60" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G60" s="54" t="n">
+      <c r="G60" s="55" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H60" s="55" t="n">
+      <c r="H60" s="56" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -16404,13 +16415,13 @@
       <c r="E61" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F61" s="56" t="n">
+      <c r="F61" s="57" t="n">
         <v>3.201</v>
       </c>
-      <c r="G61" s="54" t="n">
+      <c r="G61" s="55" t="n">
         <v>-17.2535454545455</v>
       </c>
-      <c r="H61" s="55" t="n">
+      <c r="H61" s="56" t="n">
         <v>-0.843506666666667</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -16433,13 +16444,13 @@
       <c r="E62" s="11" t="n">
         <v>20.55</v>
       </c>
-      <c r="F62" s="56" t="n">
+      <c r="F62" s="57" t="n">
         <v>5.35</v>
       </c>
-      <c r="G62" s="54" t="n">
+      <c r="G62" s="55" t="n">
         <v>-15.2</v>
       </c>
-      <c r="H62" s="55" t="n">
+      <c r="H62" s="56" t="n">
         <v>-0.739659367396594</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -16462,13 +16473,13 @@
       <c r="E63" s="11" t="n">
         <v>20.4545454545455</v>
       </c>
-      <c r="F63" s="56" t="n">
+      <c r="F63" s="57" t="n">
         <v>2.67</v>
       </c>
-      <c r="G63" s="54" t="n">
+      <c r="G63" s="55" t="n">
         <v>-17.7845454545455</v>
       </c>
-      <c r="H63" s="55" t="n">
+      <c r="H63" s="56" t="n">
         <v>-0.869466666666667</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -16491,13 +16502,13 @@
       <c r="E64" s="11" t="n">
         <v>27.2727272727273</v>
       </c>
-      <c r="F64" s="56" t="n">
+      <c r="F64" s="57" t="n">
         <v>10.69</v>
       </c>
-      <c r="G64" s="54" t="n">
+      <c r="G64" s="55" t="n">
         <v>-16.5827272727273</v>
       </c>
-      <c r="H64" s="55" t="n">
+      <c r="H64" s="56" t="n">
         <v>-0.608033333333334</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -16505,200 +16516,200 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="65" t="s">
         <v>350</v>
       </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="64"/>
-      <c r="G66" s="64"/>
-      <c r="H66" s="64"/>
-      <c r="I66" s="64"/>
-      <c r="J66" s="64"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="65"/>
+      <c r="I66" s="65"/>
+      <c r="J66" s="65"/>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="52" t="s">
+      <c r="A67" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="52" t="s">
+      <c r="B67" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="52" t="s">
+      <c r="C67" s="53" t="s">
         <v>351</v>
       </c>
-      <c r="D67" s="52" t="s">
+      <c r="D67" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="E67" s="52" t="s">
+      <c r="E67" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="F67" s="52" t="s">
+      <c r="F67" s="53" t="s">
         <v>354</v>
       </c>
-      <c r="G67" s="52" t="s">
+      <c r="G67" s="53" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="57" t="s">
+      <c r="A68" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="D68" s="59" t="n">
+      <c r="D68" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E68" s="59" t="n">
+      <c r="E68" s="60" t="n">
         <v>16.93275</v>
       </c>
-      <c r="F68" s="61" t="n">
+      <c r="F68" s="62" t="n">
         <v>7.57820454545455</v>
       </c>
-      <c r="G68" s="62" t="n">
+      <c r="G68" s="63" t="n">
         <v>0.447547181967167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="57" t="s">
+      <c r="A69" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="58" t="s">
+      <c r="B69" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="D69" s="59" t="n">
+      <c r="D69" s="60" t="n">
         <v>21.2</v>
       </c>
-      <c r="E69" s="59" t="n">
+      <c r="E69" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F69" s="61" t="n">
+      <c r="F69" s="62" t="n">
         <v>12.6555</v>
       </c>
-      <c r="G69" s="62" t="n">
+      <c r="G69" s="63" t="n">
         <v>0.373809277665372</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="57" t="s">
+      <c r="A70" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="58" t="s">
+      <c r="B70" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="D70" s="59" t="n">
+      <c r="D70" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E70" s="59" t="n">
+      <c r="E70" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F70" s="61" t="n">
+      <c r="F70" s="62" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G70" s="62" t="n">
+      <c r="G70" s="63" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="57" t="s">
+      <c r="A71" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="58" t="s">
+      <c r="B71" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="D71" s="59" t="n">
+      <c r="D71" s="60" t="n">
         <v>9.35454545454545</v>
       </c>
-      <c r="E71" s="59" t="n">
+      <c r="E71" s="60" t="n">
         <v>12.03275</v>
       </c>
-      <c r="F71" s="61" t="n">
+      <c r="F71" s="62" t="n">
         <v>2.67820454545455</v>
       </c>
-      <c r="G71" s="62" t="n">
+      <c r="G71" s="63" t="n">
         <v>0.222576264399622</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="57" t="s">
+      <c r="A72" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="58" t="s">
+      <c r="B72" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="58" t="s">
         <v>347</v>
       </c>
-      <c r="D72" s="59" t="n">
+      <c r="D72" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E72" s="59" t="n">
+      <c r="E72" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F72" s="61" t="n">
+      <c r="F72" s="62" t="n">
         <v>5.5009545454545</v>
       </c>
-      <c r="G72" s="62" t="n">
+      <c r="G72" s="63" t="n">
         <v>0.162483334922081</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="57" t="s">
+      <c r="A73" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="58" t="s">
+      <c r="B73" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="C73" s="57" t="s">
+      <c r="C73" s="58" t="s">
         <v>347</v>
       </c>
-      <c r="D73" s="59" t="n">
+      <c r="D73" s="60" t="n">
         <v>28.3545454545455</v>
       </c>
-      <c r="E73" s="59" t="n">
+      <c r="E73" s="60" t="n">
         <v>30.1455</v>
       </c>
-      <c r="F73" s="61" t="n">
+      <c r="F73" s="62" t="n">
         <v>1.7909545454545</v>
       </c>
-      <c r="G73" s="62" t="n">
+      <c r="G73" s="63" t="n">
         <v>0.0594103446768007</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="57" t="s">
+      <c r="A74" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="58" t="s">
+      <c r="B74" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="57" t="s">
+      <c r="C74" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="D74" s="59" t="n">
+      <c r="D74" s="60" t="n">
         <v>32.5</v>
       </c>
-      <c r="E74" s="59" t="n">
+      <c r="E74" s="60" t="n">
         <v>33.8555</v>
       </c>
-      <c r="F74" s="61" t="n">
+      <c r="F74" s="62" t="n">
         <v>1.3555</v>
       </c>
-      <c r="G74" s="62" t="n">
+      <c r="G74" s="63" t="n">
         <v>0.0400378077417258</v>
       </c>
     </row>
